--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M172"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -632,58 +632,56 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist II, ML Infrastructure</t>
+          <t>QA Testers Wanted (No experience needed)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Tester Work</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Australia &amp; New Zealand (REMOTE)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>data scientist, ml, anywhere (place)</t>
+          <t>qa, remote (place)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-ml-infrastructure</t>
+          <t>https://www.workingnomads.com/job/go/1860630/</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>a84319c791</t>
+          <t>bf909f7a1f</t>
         </is>
       </c>
     </row>
@@ -699,12 +697,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist II, Infrastructure</t>
+          <t>Data Scientist II, ML Infrastructure</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>data scientist, anywhere (place)</t>
+          <t>data scientist, ml, anywhere (place)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-infrastructure</t>
+          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-ml-infrastructure</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>def323e358</t>
+          <t>a84319c791</t>
         </is>
       </c>
     </row>
@@ -760,52 +760,52 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II, Infrastructure</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>software engineer, golang (tag)</t>
+          <t>data scientist, anywhere (place)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>golang, dev, engineer, digital nomad</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-mirantis-1137387</t>
+          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-infrastructure</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0eb27a0401</t>
+          <t>def323e358</t>
         </is>
       </c>
     </row>
@@ -817,41 +817,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Science Engineer - AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data science, engineer, ai, bangalore (place)</t>
+          <t>software engineer, golang (tag)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>golang, dev, engineer, digital nomad</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880523483?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44AFB881700BC2524FE70C04638A2D65741F5C06</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-mirantis-1137387</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>987c89c61a</t>
+          <t>0eb27a0401</t>
         </is>
       </c>
     </row>
@@ -882,22 +882,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning</t>
+          <t>Data Science Engineer - AI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kotak Neo</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>machine learning, ai, mumbai (place)</t>
+          <t>data science, engineer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880062262?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC74E214D0612FE80831EDD83B8CF67B6032A3E9</t>
+          <t>https://www.adzuna.in/land/ad/5880523483?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44AFB881700BC2524FE70C04638A2D65741F5C06</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>c8b4bb4ba3</t>
+          <t>987c89c61a</t>
         </is>
       </c>
     </row>
@@ -943,37 +943,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>AI &amp; Machine Learning</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Kotak Neo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>software (tag), engineer, ai (tag), ml, worldwide (place)</t>
+          <t>machine learning, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Machine-Learning-Engineer, AI-ML-Engineer, ML-Software-Engineer, ML-Research-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ml-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5880062262?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC74E214D0612FE80831EDD83B8CF67B6032A3E9</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6b92e0e58d</t>
+          <t>c8b4bb4ba3</t>
         </is>
       </c>
     </row>
@@ -1009,47 +1009,47 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data science, india (place), chandigarh (place)</t>
+          <t>software (tag), engineer, ai (tag), ml, worldwide (place)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Machine-Learning-Engineer, AI-ML-Engineer, ML-Software-Engineer, ML-Research-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5879662958?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7C90B2BB52AA81EB60C613281A1D6AF4E5DC8BD8</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ml-engineer</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6557a8e75a</t>
+          <t>6b92e0e58d</t>
         </is>
       </c>
     </row>
@@ -1065,54 +1065,52 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PhD &amp; Academic Expert</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ml (tag), worldwide (place)</t>
+          <t>data science, india (place), chandigarh (place)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Academic-Expert, PhD-Specialist-Consultant, Academic-Consultant, Academic-Subject-Matter-Expert, Academic-Professional, ML-Research-PhD-Expert, PhD-Researcher, Education-Expert, Mid-level, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/phd-academic-expert</t>
+          <t>https://www.adzuna.in/land/ad/5879662958?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7C90B2BB52AA81EB60C613281A1D6AF4E5DC8BD8</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>a8281d77e1</t>
+          <t>6557a8e75a</t>
         </is>
       </c>
     </row>
@@ -1124,23 +1122,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>PhD &amp; Academic Expert</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dura Digital</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1155,27 +1153,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>engineer, backend (tag), python (tag), ai, ml (tag), worldwide (place)</t>
+          <t>ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AI-Engineer, Machine-Learning-Engineer, Backend-Engineer, Data-Engineer, MLOps-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Senior</t>
+          <t>Academic-Expert, PhD-Specialist-Consultant, Academic-Consultant, Academic-Subject-Matter-Expert, Academic-Professional, ML-Research-PhD-Expert, PhD-Researcher, Education-Expert, Mid-level, Senior</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/dura-digital/jobs/ai-engineer</t>
+          <t>https://himalayas.app/companies/micro1/jobs/phd-academic-expert</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>8666ff7b1c</t>
+          <t>a8281d77e1</t>
         </is>
       </c>
     </row>
@@ -1191,17 +1189,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Facial Data Collection Associate</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Dura Digital</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ai, associate (level), worldwide (place)</t>
+          <t>engineer, backend (tag), python (tag), ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AI-Data-Collection-Specialist, Data-Collection-Associate, Facial-Recognition-Data-Collection, AI-Services-Associate, AI-Operations-Associate, AI-Associate, Entry-level</t>
+          <t>AI-Engineer, Machine-Learning-Engineer, Backend-Engineer, Data-Engineer, MLOps-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Senior</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-facial-data-collection-associate</t>
+          <t>https://himalayas.app/companies/dura-digital/jobs/ai-engineer</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>a024718d12</t>
+          <t>8666ff7b1c</t>
         </is>
       </c>
     </row>
@@ -1252,54 +1252,52 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Facial Data Collection Associate</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Omnicom Global Solutions</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>ai, associate (level), worldwide (place)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Data-Collection-Specialist, Data-Collection-Associate, Facial-Recognition-Data-Collection, AI-Services-Associate, AI-Operations-Associate, AI-Associate, Entry-level</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880062427?se=4EjJjS6u8RGGGqTWwpKkng&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E0A2211C95EBCFB9C1236FB6E39F7FBF4A7836A8</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-facial-data-collection-associate</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>c539f926b2</t>
+          <t>a024718d12</t>
         </is>
       </c>
     </row>
@@ -1315,54 +1313,54 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Financial Systems Expert</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Omnicom Global Solutions</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>developer (tag), engineer (tag), worldwide (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Financial-Systems-Specialist, Financial-Systems-Consultant, Financial-Systems-Advisor, Finance-Systems-Specialist, Financial-Systems-Consulting, Finance-Systems-Consultant, Financial-Systems-Developer, Financial-Systems-Integration-Specialist, Financial-Systems-Architect, Financial-Systems-Engineer, Mid-level, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/financial-systems-expert</t>
+          <t>https://www.adzuna.in/land/ad/5880062427?se=4EjJjS6u8RGGGqTWwpKkng&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E0A2211C95EBCFB9C1236FB6E39F7FBF4A7836A8</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>a8090f5869</t>
+          <t>c539f926b2</t>
         </is>
       </c>
     </row>
@@ -1374,56 +1372,58 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>79</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DVP - Data Science AI</t>
+          <t>Financial Systems Expert</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IndiaFirst Life</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data science, ai, mumbai (place)</t>
+          <t>developer (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Financial-Systems-Specialist, Financial-Systems-Consultant, Financial-Systems-Advisor, Finance-Systems-Specialist, Financial-Systems-Consulting, Finance-Systems-Consultant, Financial-Systems-Developer, Financial-Systems-Integration-Specialist, Financial-Systems-Architect, Financial-Systems-Engineer, Mid-level, Senior</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877452336?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C389ADE3462A8F960BCEB9BFB3D8C01182D8F284</t>
+          <t>https://himalayas.app/companies/micro1/jobs/financial-systems-expert</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>d4091e9b06</t>
+          <t>a8090f5869</t>
         </is>
       </c>
     </row>
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DVP - Data Science AI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ryewalk</t>
+          <t>IndiaFirst Life</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data scientist, chennai (place)</t>
+          <t>data science, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877457613?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=858E7DDB9C73029BB012BE9266CDC5516D57BB06</t>
+          <t>https://www.adzuna.in/land/ad/5877452336?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C389ADE3462A8F960BCEB9BFB3D8C01182D8F284</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>5b1e04fbec</t>
+          <t>d4091e9b06</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Ryewalk</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876016078?se=tjzQcmWt8RGk7Nm076a3Fw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=076A6D8BF6D1FAB77910335EA1D3406F73F06FDC</t>
+          <t>https://www.adzuna.in/land/ad/5877457613?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=858E7DDB9C73029BB012BE9266CDC5516D57BB06</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03602a7f75</t>
+          <t>5b1e04fbec</t>
         </is>
       </c>
     </row>
@@ -1561,52 +1561,52 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>QA Tester Entry Level</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ace IT Careers</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>testing (tag), qa, entry level (level), remote (place)</t>
+          <t>data scientist, chennai (place)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>testing, dev, analyst, quality assurance, digital nomad</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-qa-tester-entry-level-ace-it-careers-1136701</t>
+          <t>https://www.adzuna.in/land/ad/5876016078?se=tjzQcmWt8RGk7Nm076a3Fw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=076A6D8BF6D1FAB77910335EA1D3406F73F06FDC</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>066819b5ee</t>
+          <t>03602a7f75</t>
         </is>
       </c>
     </row>
@@ -1622,54 +1622,52 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>QA Tester Entry Level</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sun King</t>
+          <t>Ace IT Careers</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>software (tag), engineer, cloud (tag), api (tag), india (place)</t>
+          <t>testing (tag), qa, entry level (level), remote (place)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Application-Security-Engineer, Security-Engineer, Penetration-Tester, API-Security, Cloud-Security-Engineer, AppSec-Engineer, Application-Security-Engineering, Application-Security-Specialist, Software-Security-Engineer, Mid-level</t>
+          <t>testing, dev, analyst, quality assurance, digital nomad</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/sun-king/jobs/application-security-engineer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-qa-tester-entry-level-ace-it-careers-1136701</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>41b24c0687</t>
+          <t>066819b5ee</t>
         </is>
       </c>
     </row>
@@ -1687,15 +1685,17 @@
       <c r="C21" t="n">
         <v>32</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nuclear Physics Specialist - Fully Remote | Upto $100/hr</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>Sun King</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>engineer (tag), ai (tag), india (place)</t>
+          <t>software (tag), engineer, cloud (tag), api (tag), india (place)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Computational-Physics, Nuclear-Physics, Particle-Physics, AI-Evaluation, Scientific-Computing, Nuclear-Physics-AI-Specialist, Freelance-Physics-Specialist, Reactor-Physics-Engineer, Freelance-Physics-Expert, Physics-Research-Specialist, Physics-Freelancer, Mid-level</t>
+          <t>Application-Security-Engineer, Security-Engineer, Penetration-Tester, API-Security, Cloud-Security-Engineer, AppSec-Engineer, Application-Security-Engineering, Application-Security-Specialist, Software-Security-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/mercor/jobs/nuclear-physics-specialist-fully-remote-upto-100-hr-6652317191</t>
+          <t>https://himalayas.app/companies/sun-king/jobs/application-security-engineer</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>e80acb6174</t>
+          <t>41b24c0687</t>
         </is>
       </c>
     </row>
@@ -1742,58 +1742,56 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>65</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Nuclear Physics Specialist - Fully Remote | Upto $100/hr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dynamics Monk Consulting Services</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>artificial intelligence, india (place), delhi (place)</t>
+          <t>engineer (tag), ai (tag), india (place)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Computational-Physics, Nuclear-Physics, Particle-Physics, AI-Evaluation, Scientific-Computing, Nuclear-Physics-AI-Specialist, Freelance-Physics-Specialist, Reactor-Physics-Engineer, Freelance-Physics-Expert, Physics-Research-Specialist, Physics-Freelancer, Mid-level</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028069?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F290F3C8F39D5ABB349E29F918917B30A38BA853</t>
+          <t>https://himalayas.app/companies/mercor/jobs/nuclear-physics-specialist-fully-remote-upto-100-hr-6652317191</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>9010d87d61</t>
+          <t>e80acb6174</t>
         </is>
       </c>
     </row>
@@ -1809,22 +1807,24 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>54</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vahan.ai</t>
+          <t>Dynamics Monk Consulting Services</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, india (place), delhi (place)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876029045?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1440DAC38EB3556F9000947FA0A0834CFF14AB75</t>
+          <t>https://www.adzuna.in/land/ad/5876028069?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F290F3C8F39D5ABB349E29F918917B30A38BA853</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>56f72b7a03</t>
+          <t>9010d87d61</t>
         </is>
       </c>
     </row>
@@ -1880,12 +1880,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EYEGLOBAL SOLUTIONS PVT. LTD.</t>
+          <t>Vahan.ai</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, chennai (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028703?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9D6C280D30C30F591E884FDA2F691CC4409C3EC6</t>
+          <t>https://www.adzuna.in/land/ad/5876029045?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1440DAC38EB3556F9000947FA0A0834CFF14AB75</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>bafec6742f</t>
+          <t>56f72b7a03</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Appglide Solutions</t>
+          <t>EYEGLOBAL SOLUTIONS PVT. LTD.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1971,12 +1971,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876870603?se=DiEjalis8RGQ-MmLyhoJEg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=987B153BD1BD745987463A7F926C3F0CC163AE60</t>
+          <t>https://www.adzuna.in/land/ad/5876028703?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9D6C280D30C30F591E884FDA2F691CC4409C3EC6</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>d4bbc378a8</t>
+          <t>bafec6742f</t>
         </is>
       </c>
     </row>
@@ -1997,17 +1997,17 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MTS-2 Machine Learning Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Appglide Solutions</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, chennai (place)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877184044?se=ME0PiYGs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=DBDB737DEAF34AD8D344749E581C417C10EC5A31</t>
+          <t>https://www.adzuna.in/land/ad/5876870603?se=DiEjalis8RGQ-MmLyhoJEg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=987B153BD1BD745987463A7F926C3F0CC163AE60</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>37872b8c00</t>
+          <t>d4bbc378a8</t>
         </is>
       </c>
     </row>
@@ -2053,37 +2053,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Account Executive, AI/HPC, Neo / Sovereign Cloud (EMEA)</t>
+          <t>MTS-2 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Everpure</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>cloud, ai, anywhere (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/everpure-account-executive-ai-hpc-neo-sovereign-cloud-emea</t>
+          <t>https://www.adzuna.in/land/ad/5877184044?se=ME0PiYGs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=DBDB737DEAF34AD8D344749E581C417C10EC5A31</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>44fbf0ebf8</t>
+          <t>37872b8c00</t>
         </is>
       </c>
     </row>
@@ -2114,39 +2114,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>49</v>
-      </c>
-      <c r="D28" t="n">
-        <v>3</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Account Executive, AI/HPC, Neo / Sovereign Cloud (EMEA)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Infosys Finacle</t>
+          <t>Everpure</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>cloud, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Sales and Marketing, Full-Time</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2156,12 +2154,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876010793?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8D81876C99F248DACDDC8104E41D7CB59A09112B</t>
+          <t>https://weworkremotely.com/remote-jobs/everpure-account-executive-ai-hpc-neo-sovereign-cloud-emea</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>68b1b69943</t>
+          <t>44fbf0ebf8</t>
         </is>
       </c>
     </row>
@@ -2177,37 +2175,39 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>47</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Frontend Developer - Talent Pool</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Espeo Software</t>
+          <t>Infosys Finacle</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>developer, frontend, software (tag), engineer (tag), react (tag), worldwide (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Frontend-Development, Web-Development, Software-Development, ContractWorks, Freelance-Development, Frontend-Development-Jobs, Tech-Talent-Pool, Front-End-Developer, Technology-Talent-Pool, Engineering-Talent-Pool, Frontend-React-Developer, React-Frontend-Developer, Frontend-Engineer, Developer, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/espeo-software/jobs/frontend-developer-talent-pool</t>
+          <t>https://www.adzuna.in/land/ad/5876010793?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8D81876C99F248DACDDC8104E41D7CB59A09112B</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>409bd93507</t>
+          <t>68b1b69943</t>
         </is>
       </c>
     </row>
@@ -2238,17 +2238,17 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe AEP)</t>
+          <t>Frontend Developer - Talent Pool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TechBiz Global</t>
+          <t>Espeo Software</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data engineer, developer (tag), cloud (tag), worldwide (place)</t>
+          <t>developer, frontend, software (tag), engineer (tag), react (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Data-Engineering, ETL-Development, Cloud-Data-Engineering, Adobe-Experience-Platform, Data-Integration, Adobe-CDP-Engineer, Data-Engineer, Adobe-Experience-Platform-Engineer, Data-Engineer-Jobs, Data-Platform-Engineer, Enterprise-Data-Engineer, Developer, Senior</t>
+          <t>Frontend-Development, Web-Development, Software-Development, ContractWorks, Freelance-Development, Frontend-Development-Jobs, Tech-Talent-Pool, Front-End-Developer, Technology-Talent-Pool, Engineering-Talent-Pool, Frontend-React-Developer, React-Frontend-Developer, Frontend-Engineer, Developer, Senior</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/techbiz-global/jobs/data-engineer-adobe-aep-7933835037</t>
+          <t>https://himalayas.app/companies/espeo-software/jobs/frontend-developer-talent-pool</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3cf5fcdc34</t>
+          <t>409bd93507</t>
         </is>
       </c>
     </row>
@@ -2299,52 +2299,52 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Social Comms</t>
+          <t>Data Engineer (Adobe AEP)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NOPE</t>
+          <t>TechBiz Global</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ai (tag)</t>
+          <t>data engineer, developer (tag), cloud (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>marketing, education, technical, content writing, social media, ai, social</t>
+          <t>Data-Engineering, ETL-Development, Cloud-Data-Engineering, Adobe-Experience-Platform, Data-Integration, Adobe-CDP-Engineer, Data-Engineer, Adobe-Experience-Platform-Engineer, Data-Engineer-Jobs, Data-Platform-Engineer, Enterprise-Data-Engineer, Developer, Senior</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-social-comms-nope-1137314</t>
+          <t>https://himalayas.app/companies/techbiz-global/jobs/data-engineer-adobe-aep-7933835037</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>417f6ff5ea</t>
+          <t>3cf5fcdc34</t>
         </is>
       </c>
     </row>
@@ -2356,56 +2356,56 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Social Comms</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>NOPE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>ai (tag)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>marketing, education, technical, content writing, social media, ai, social</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876024927?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0BB3A9B6F76E859DE51E5C2F0066293EDC5FE6EA</t>
+          <t>https://remoteOK.com/remote-jobs/remote-social-comms-nope-1137314</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0851d46422</t>
+          <t>417f6ff5ea</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Questhiring</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876027895?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=09A0BE7549E8D3105D5BC0AA92FAA0662C7CD065</t>
+          <t>https://www.adzuna.in/land/ad/5876024927?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0BB3A9B6F76E859DE51E5C2F0066293EDC5FE6EA</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>8a025ec1ce</t>
+          <t>0851d46422</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TBO.COM</t>
+          <t>Questhiring</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026044?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FDDB74C699BD4423DAD1E4FB7120816040F747A</t>
+          <t>https://www.adzuna.in/land/ad/5876027895?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=09A0BE7549E8D3105D5BC0AA92FAA0662C7CD065</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>a427b9cd23</t>
+          <t>8a025ec1ce</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ADB SAFEGATE</t>
+          <t>TBO.COM</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, hyderabad (place)</t>
+          <t>artificial intelligence, engineer, india (place)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026294?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9C70BDA29FFF510B21324AF211D635A868DC48AA</t>
+          <t>https://www.adzuna.in/land/ad/5876026044?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FDDB74C699BD4423DAD1E4FB7120816040F747A</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>292ee6d2c1</t>
+          <t>a427b9cd23</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Neural Foundry</t>
+          <t>ADB SAFEGATE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026040?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8CA62DE6EFC7E6B952E843BFE686F26AF0E83028</t>
+          <t>https://www.adzuna.in/land/ad/5876026294?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9C70BDA29FFF510B21324AF211D635A868DC48AA</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>c1e16bca2e</t>
+          <t>292ee6d2c1</t>
         </is>
       </c>
     </row>
@@ -2675,12 +2675,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DotKonnekt</t>
+          <t>Neural Foundry</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, hyderabad (place)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026944?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=51439456D8BA015D122C9B9E72B93BC7715ADC62</t>
+          <t>https://www.adzuna.in/land/ad/5876026040?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8CA62DE6EFC7E6B952E843BFE686F26AF0E83028</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>172ee82bd6</t>
+          <t>c1e16bca2e</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Recro</t>
+          <t>DotKonnekt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876027463?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=40F66C80D240EB217C5AF3C758F1793D002D574F</t>
+          <t>https://www.adzuna.in/land/ad/5876026944?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=51439456D8BA015D122C9B9E72B93BC7715ADC62</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>91af896417</t>
+          <t>172ee82bd6</t>
         </is>
       </c>
     </row>
@@ -2792,17 +2792,17 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer 2</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Frinks AI</t>
+          <t>Recro</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, india (place)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876025062?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=75AA49B421B5A4EB6F3C207636FED47095B332D0</t>
+          <t>https://www.adzuna.in/land/ad/5876027463?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=40F66C80D240EB217C5AF3C758F1793D002D574F</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2d2a6d873d</t>
+          <t>91af896417</t>
         </is>
       </c>
     </row>
@@ -2848,22 +2848,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Specialist</t>
+          <t>Artificial Intelligence Engineer 2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ITC Infotech</t>
+          <t>Frinks AI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>artificial intelligence, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876024946?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=6D480BEF34A3386CBC920920C7CE13B96BCBAD34</t>
+          <t>https://www.adzuna.in/land/ad/5876025062?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=75AA49B421B5A4EB6F3C207636FED47095B332D0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>140496e40b</t>
+          <t>2d2a6d873d</t>
         </is>
       </c>
     </row>
@@ -2914,17 +2914,17 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Artificial Intelligence Specialist</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tech Mahindra</t>
+          <t>ITC Infotech</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>artificial intelligence, bangalore (place)</t>
+          <t>artificial intelligence, india (place)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026586?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=666546215EA3297D7CF61A793A40232CBB0EC67B</t>
+          <t>https://www.adzuna.in/land/ad/5876024946?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=6D480BEF34A3386CBC920920C7CE13B96BCBAD34</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>25604d55ae</t>
+          <t>140496e40b</t>
         </is>
       </c>
     </row>
@@ -2970,22 +2970,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data and AI Scientist</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The Edge Partnership - The Edge in Asia</t>
+          <t>Tech Mahindra</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ai, hyderabad (place)</t>
+          <t>artificial intelligence, bangalore (place)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876025532?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AD1D30D29AD931A0AA847E54CFF303EEB0007BE9</t>
+          <t>https://www.adzuna.in/land/ad/5876026586?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=666546215EA3297D7CF61A793A40232CBB0EC67B</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>bc9357c4ff</t>
+          <t>25604d55ae</t>
         </is>
       </c>
     </row>
@@ -3031,52 +3031,52 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AI Response Evaluator</t>
+          <t>Data and AI Scientist</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>iMerit</t>
+          <t>The Edge Partnership - The Edge in Asia</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>All Other Remote, Contract</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/imerit-ai-response-evaluator</t>
+          <t>https://www.adzuna.in/land/ad/5876025532?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AD1D30D29AD931A0AA847E54CFF303EEB0007BE9</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>d4b5bc7818</t>
+          <t>bc9357c4ff</t>
         </is>
       </c>
     </row>
@@ -3092,37 +3092,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sustainability Full-Stack Developer (100 % remote) (m/f/d)</t>
+          <t>AI Response Evaluator</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EWOR GmbH</t>
+          <t>iMerit</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>fullstack (tag), developer, software (tag), engineer (tag), worldwide (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Fullstack-Development, Web-Development, Sustainability, Software-Engineer, Sustainability-Technology, Remote-Senior-Full-Stack-Developer, Remote-Full-Stack-Developer, Full-Stack-Developer, Senior</t>
+          <t>All Other Remote, Contract</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ewor-gmbh/jobs/sustainability-full-stack-developer-100-remote-m-f-d</t>
+          <t>https://weworkremotely.com/remote-jobs/imerit-ai-response-evaluator</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>7da6fdc2ab</t>
+          <t>d4b5bc7818</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3153,12 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Industrial Tech AgentOps Engineer (100 % remote) (m/f/d)</t>
+          <t>Sustainability Full-Stack Developer (100 % remote) (m/f/d)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>engineer, devops (tag), worldwide (place)</t>
+          <t>fullstack (tag), developer, software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>AgentOps-Engineer, Industrial-Technology, Operations-Engineering, Technical-Product-Management, Start-Up-Operations, Remote-Operations-Engineer, Industrial-IoT-Engineer, Remote-DevOps-Engineer, TechOps-Engineer, Remote-Infrastructure-Monitoring-Engineer, Remote-Distributed-Systems-Engineer-II, Mid-level</t>
+          <t>Fullstack-Development, Web-Development, Sustainability, Software-Engineer, Sustainability-Technology, Remote-Senior-Full-Stack-Developer, Remote-Full-Stack-Developer, Full-Stack-Developer, Senior</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ewor-gmbh/jobs/industrial-tech-agentops-engineer-100-remote-m-f-d</t>
+          <t>https://himalayas.app/companies/ewor-gmbh/jobs/sustainability-full-stack-developer-100-remote-m-f-d</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>cedc8889fb</t>
+          <t>7da6fdc2ab</t>
         </is>
       </c>
     </row>
@@ -3210,56 +3210,56 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AI Response Analyst</t>
+          <t>Industrial Tech AgentOps Engineer (100 % remote) (m/f/d)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>iMerit Technology</t>
+          <t>EWOR GmbH</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>engineer, devops (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>content writing, quality assurance, ai</t>
+          <t>AgentOps-Engineer, Industrial-Technology, Operations-Engineering, Technical-Product-Management, Start-Up-Operations, Remote-Operations-Engineer, Industrial-IoT-Engineer, Remote-DevOps-Engineer, TechOps-Engineer, Remote-Infrastructure-Monitoring-Engineer, Remote-Distributed-Systems-Engineer-II, Mid-level</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-ai-response-analyst-imerit-technology-1137309</t>
+          <t>https://himalayas.app/companies/ewor-gmbh/jobs/industrial-tech-agentops-engineer-100-remote-m-f-d</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>05cb840193</t>
+          <t>cedc8889fb</t>
         </is>
       </c>
     </row>
@@ -3271,58 +3271,56 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>30</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Response Analyst</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>iMerit Technology</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>content writing, quality assurance, ai</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="C47" t="n">
-        <v>57</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Python Backend Engineer (m/f/x)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Makersite</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Worldwide</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>himalayas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>developer (tag), software (tag), engineer, backend, python, api (tag), worldwide (place)</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Python-Backend-Engineering, Backend-Development, Software-Engineer, API-Development, Python-Engineering, Python-Backend-Engineer, Python-Backend-Developer, Senior-Backend-Python-Developer, Senior-Python-Backend-Developer, Backend-Engineer, Product-Backend-Engineer, Backend-Services-Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/makersite/jobs/python-backend-engineer-m-f-x</t>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-response-analyst-imerit-technology-1137309</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>3eb1e889db</t>
+          <t>05cb840193</t>
         </is>
       </c>
     </row>
@@ -3338,19 +3336,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Python Backend Engineer (m/f/x)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>S-PRO</t>
+          <t>Makersite</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3365,12 +3363,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>software (tag), engineer, backend (tag), python, cloud (tag), aws (tag), worldwide (place)</t>
+          <t>developer (tag), software (tag), engineer, backend, python, api (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Python-Engineering, Backend-Development, AWS-Cloud-Development, Serverless-Development, Software-Engineer, Python-Engineer, Python-Software-Engineer, Mid-level</t>
+          <t>Python-Backend-Engineering, Backend-Development, Software-Engineer, API-Development, Python-Engineering, Python-Backend-Engineer, Python-Backend-Developer, Senior-Backend-Python-Developer, Senior-Python-Backend-Developer, Backend-Engineer, Product-Backend-Engineer, Backend-Services-Engineer, Senior</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3380,12 +3378,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/s-pro/jobs/python-engineer</t>
+          <t>https://himalayas.app/companies/makersite/jobs/python-backend-engineer-m-f-x</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>67bda4c374</t>
+          <t>3eb1e889db</t>
         </is>
       </c>
     </row>
@@ -3401,19 +3399,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Daymark Health</t>
+          <t>S-PRO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3428,12 +3426,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), worldwide (place)</t>
+          <t>software (tag), engineer, backend (tag), python, cloud (tag), aws (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Software-Engineer, Healthcare-Technology, Backend-Engineering, Fullstack-Development, Health-Tech, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Developer, Mid-level</t>
+          <t>Python-Engineering, Backend-Development, AWS-Cloud-Development, Serverless-Development, Software-Engineer, Python-Engineer, Python-Software-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3443,12 +3441,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/daymark-health/jobs/software-engineer</t>
+          <t>https://himalayas.app/companies/s-pro/jobs/python-engineer</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>85c899deaf</t>
+          <t>67bda4c374</t>
         </is>
       </c>
     </row>
@@ -3460,56 +3458,58 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>84</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Specialist, Data Science &amp; Artificial Intelligence</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Daymark Health</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>artificial intelligence, data science, india (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>Software-Engineer, Healthcare-Technology, Backend-Engineering, Fullstack-Development, Health-Tech, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5871846075?se=oI2O_Sup8RGogquEo3zAlQ&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=326B6FA659B880A3C0F3E2CA4AB8E0734BF69D7B</t>
+          <t>https://himalayas.app/companies/daymark-health/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>c1e8559189</t>
+          <t>85c899deaf</t>
         </is>
       </c>
     </row>
@@ -3525,39 +3525,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Specialist, Data Science &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>xneelo</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), devops (tag), worldwide (place)</t>
+          <t>artificial intelligence, data science, india (place)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Software-Engineer, Backend-Development, Fullstack-Development, Infrastructure-Engineering, DevOps, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Senior</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3567,12 +3565,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/xneelo-co/jobs/software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5871846075?se=oI2O_Sup8RGogquEo3zAlQ&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=326B6FA659B880A3C0F3E2CA4AB8E0734BF69D7B</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>679e1ed2b3</t>
+          <t>c1e8559189</t>
         </is>
       </c>
     </row>
@@ -3588,39 +3586,39 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AEM Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vonage</t>
+          <t>xneelo</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>developer, devops (tag), anywhere (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), devops (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Software-Engineer, Backend-Development, Fullstack-Development, Infrastructure-Engineering, DevOps, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Senior</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3630,12 +3628,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/vonage-aem-developer</t>
+          <t>https://himalayas.app/companies/xneelo-co/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>9b191a3075</t>
+          <t>679e1ed2b3</t>
         </is>
       </c>
     </row>
@@ -3651,37 +3649,39 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>27</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Video Annotation Expert</t>
+          <t>AEM Developer</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Vonage</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ai (tag), worldwide (place)</t>
+          <t>developer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Video-Annotator, Video-Annotation, Media-Annotation-Specialist, Video-Data-Annotation, Annotation-Specialist, Data-Annotation-Expert, AI-Annotation-Specialist, Content-Annotation-Specialist, Entry-level, Mid-level</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/video-annotation-expert-4408176807</t>
+          <t>https://weworkremotely.com/remote-jobs/vonage-aem-developer</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1b02a267ff</t>
+          <t>9b191a3075</t>
         </is>
       </c>
     </row>
@@ -3708,56 +3708,56 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Subject Matter Expert - Computer Science and Artificial Intelligence</t>
+          <t>Video Annotation Expert</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sultan Chand &amp; Sons Ltd</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>artificial intelligence, noida (place)</t>
+          <t>ai (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Video-Annotator, Video-Annotation, Media-Annotation-Specialist, Video-Data-Annotation, Annotation-Specialist, Data-Annotation-Expert, AI-Annotation-Specialist, Content-Annotation-Specialist, Entry-level, Mid-level</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5869558953?se=ji27_Tqo8RGDXZRVG-VeHA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=41B18BB78E05B29C6C90DA595F6A5EBB3EFE4072</t>
+          <t>https://himalayas.app/companies/micro1/jobs/video-annotation-expert-4408176807</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>91b1f60d0c</t>
+          <t>1b02a267ff</t>
         </is>
       </c>
     </row>
@@ -3773,37 +3773,37 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Software engineer</t>
+          <t>Subject Matter Expert - Computer Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sticker Mule</t>
+          <t>Sultan Chand &amp; Sons Ltd</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>software engineer, typescript (tag), golang (tag), react (tag), global (place)</t>
+          <t>artificial intelligence, noida (place)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Development, react,typescript,golang,graphql,english</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1833624/</t>
+          <t>https://www.adzuna.in/land/ad/5869558953?se=ji27_Tqo8RGDXZRVG-VeHA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=41B18BB78E05B29C6C90DA595F6A5EBB3EFE4072</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>c557da3996</t>
+          <t>91b1f60d0c</t>
         </is>
       </c>
     </row>
@@ -3830,56 +3830,56 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer 3D Developer (remote part/full time)</t>
+          <t>Software engineer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Imnoo AG</t>
+          <t>Sticker Mule</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>machine learning, developer, engineer, ai, ml (tag), worldwide (place)</t>
+          <t>software engineer, typescript (tag), golang (tag), react (tag), global (place)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>AI-Machine-Learning-Engineering, 3D-Development, Computer-Vision, AI-Manufacturing, CAD-Development, Remote-Machine-Learning-Engineer, Remote-Senior-AI-Engineer, Remote-AI-Engineer, AI-ML-Engineer, Lead-AI-ML-Engineer, Machine-Learning-Engineer, Senior</t>
+          <t>Development, react,typescript,golang,graphql,english</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/imnoo-ag/jobs/ai-machine-learning-engineer-3d-developer-remote-part-full-time</t>
+          <t>https://www.workingnomads.com/job/go/1833624/</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>a84b2b9b96</t>
+          <t>c557da3996</t>
         </is>
       </c>
     </row>
@@ -3895,37 +3895,37 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>AI Machine Learning Engineer 3D Developer (remote part/full time)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sustainability Economics.ai</t>
+          <t>Imnoo AG</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>machine learning, intern (level), bangalore (place)</t>
+          <t>machine learning, developer, engineer, ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Machine-Learning-Engineering, 3D-Development, Computer-Vision, AI-Manufacturing, CAD-Development, Remote-Machine-Learning-Engineer, Remote-Senior-AI-Engineer, Remote-AI-Engineer, AI-ML-Engineer, Lead-AI-ML-Engineer, Machine-Learning-Engineer, Senior</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5868794497?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C97284B10F6321E0988BF83E6C1B8DFD30952F6C</t>
+          <t>https://himalayas.app/companies/imnoo-ag/jobs/ai-machine-learning-engineer-3d-developer-remote-part-full-time</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>05411f661c</t>
+          <t>a84b2b9b96</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Machine Learning II</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Sustainability Economics.ai</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>machine learning, qa (tag), bangalore (place)</t>
+          <t>machine learning, intern (level), bangalore (place)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Scientific &amp; QA Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5868154123?se=SoAubXKn8RGZGp_UbifwCA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2A76050FF86A705EC1E71FEE64DFE517445586F0</t>
+          <t>https://www.adzuna.in/land/ad/5868794497?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C97284B10F6321E0988BF83E6C1B8DFD30952F6C</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>520f876dc1</t>
+          <t>05411f661c</t>
         </is>
       </c>
     </row>
@@ -4017,22 +4017,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>Machine Learning II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4042,27 +4042,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>machine learning, qa (tag), bangalore (place)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5852477157?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C196DCD121C33E5FA7A7F99C735E078C53777A1E</t>
+          <t>https://www.adzuna.in/land/ad/5868154123?se=SoAubXKn8RGZGp_UbifwCA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2A76050FF86A705EC1E71FEE64DFE517445586F0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>dab94fe012</t>
+          <t>520f876dc1</t>
         </is>
       </c>
     </row>
@@ -4078,54 +4078,52 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>46</v>
-      </c>
-      <c r="D60" t="n">
-        <v>2</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Data Scientist - Inference, Community Support</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>data scientist, anywhere (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/airbnb-data-scientist-inference-community-support</t>
+          <t>https://www.adzuna.in/land/ad/5852477157?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C196DCD121C33E5FA7A7F99C735E078C53777A1E</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>18eaeb9d4e</t>
+          <t>dab94fe012</t>
         </is>
       </c>
     </row>
@@ -4141,54 +4139,54 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Frontend Engineer Specialist</t>
+          <t>Data Scientist - Inference, Community Support</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>developer (tag), frontend, software (tag), engineer, react (tag), worldwide (place)</t>
+          <t>data scientist, anywhere (place)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Frontend-Engineer, Web-Frontend-Engineer, Front-End-Software-Engineer, Frontend-Web-Software-Engineer, Front-End-Developer, React-Frontend-Engineer, UI-Frontend-Developer, Mid-level</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/frontend-engineer-specialist</t>
+          <t>https://weworkremotely.com/remote-jobs/airbnb-data-scientist-inference-community-support</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>ee1605c3a3</t>
+          <t>18eaeb9d4e</t>
         </is>
       </c>
     </row>
@@ -4200,56 +4198,58 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>44</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Frontend Engineer Specialist</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>developer (tag), frontend, software (tag), engineer, react (tag), worldwide (place)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Frontend-Engineer, Web-Frontend-Engineer, Front-End-Software-Engineer, Frontend-Web-Software-Engineer, Front-End-Developer, React-Frontend-Engineer, UI-Frontend-Developer, Mid-level</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>86</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; NLP Expert</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Synthenova</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>machine learning, nlp, qa (tag), india (place)</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Scientific &amp; QA Jobs</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864426193?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FA0DA9F5539A8E98A42507C72E66BEA28EFB5F71</t>
+          <t>https://himalayas.app/companies/micro1/jobs/frontend-engineer-specialist</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>06a6232301</t>
+          <t>ee1605c3a3</t>
         </is>
       </c>
     </row>
@@ -4265,22 +4265,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning &amp; NLP Expert</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>HT Digital Streams</t>
+          <t>Synthenova</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>data scientist, india (place), delhi (place)</t>
+          <t>machine learning, nlp, qa (tag), india (place)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427594?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1379BD61E95509405A372328EE4CB12520438AC9</t>
+          <t>https://www.adzuna.in/land/ad/5864426193?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FA0DA9F5539A8E98A42507C72E66BEA28EFB5F71</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>e77b0725ce</t>
+          <t>06a6232301</t>
         </is>
       </c>
     </row>
@@ -4326,52 +4326,52 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HeadSpin</t>
+          <t>HT Digital Streams</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), associate (level), worldwide (place)</t>
+          <t>data scientist, india (place), delhi (place)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Engineering, Software-Engineer, Associate-Software-Engineer, Backend-Development, Fullstack-Development, Software-Engineering-Associate, Associate-Software-Developer, Software-Developer-Associate, Associate-Engineer, Associate-Platform-Engineer, Associate-Application-Developer, Associate-Systems-Engineer, Developer, Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/headspin/jobs/associate-software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5864427594?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1379BD61E95509405A372328EE4CB12520438AC9</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>ed41465dce</t>
+          <t>e77b0725ce</t>
         </is>
       </c>
     </row>
@@ -4387,52 +4387,52 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>HeadSpin</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>artificial intelligence, noida (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), associate (level), worldwide (place)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment Jobs</t>
+          <t>Engineering, Software-Engineer, Associate-Software-Engineer, Backend-Development, Fullstack-Development, Software-Engineering-Associate, Associate-Software-Developer, Software-Developer-Associate, Associate-Engineer, Associate-Platform-Engineer, Associate-Application-Developer, Associate-Systems-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864432717?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=616D5B872E024B0E271B6E107D9B24261D8C3B7A</t>
+          <t>https://himalayas.app/companies/headspin/jobs/associate-software-engineer</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>90b00c6445</t>
+          <t>ed41465dce</t>
         </is>
       </c>
     </row>
@@ -4450,22 +4450,20 @@
       <c r="C66" t="n">
         <v>50</v>
       </c>
-      <c r="D66" t="n">
-        <v>3</v>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Machine Learning Specialist</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bandhan Technologies</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4475,27 +4473,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>machine learning, bangalore (place)</t>
+          <t>artificial intelligence, noida (place)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>HR &amp; Recruitment Jobs</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867037827?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=81D91604A259EFB724EEF9EE68D3642F93D7C52A</t>
+          <t>https://www.adzuna.in/land/ad/5864432717?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=616D5B872E024B0E271B6E107D9B24261D8C3B7A</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>55af0af08c</t>
+          <t>90b00c6445</t>
         </is>
       </c>
     </row>
@@ -4511,19 +4509,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Data Science Specialist</t>
+          <t>Machine Learning Specialist</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Polestar Analytics</t>
+          <t>Bandhan Technologies</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4538,7 +4536,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>data science, bangalore (place)</t>
+          <t>machine learning, bangalore (place)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4548,17 +4546,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864434859?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BE53F35ACA83BD29D328C8745F27CF70F132F879</t>
+          <t>https://www.adzuna.in/land/ad/5867037827?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=81D91604A259EFB724EEF9EE68D3642F93D7C52A</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>620816c318</t>
+          <t>55af0af08c</t>
         </is>
       </c>
     </row>
@@ -4576,20 +4574,22 @@
       <c r="C68" t="n">
         <v>49</v>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>Data Science Specialist</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Polestar Analytics</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>data science, bangalore (place)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4609,17 +4609,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867037765?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CCE3B589087C9AE3C6FD3C72DD92F3B9146F772F</t>
+          <t>https://www.adzuna.in/land/ad/5864434859?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BE53F35ACA83BD29D328C8745F27CF70F132F879</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>5ae3a66648</t>
+          <t>620816c318</t>
         </is>
       </c>
     </row>
@@ -4640,17 +4640,17 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Infosys Finacle</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867270149?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=284AB41CD26DD62DA43E2E7866A4F2E72052CFA3</t>
+          <t>https://www.adzuna.in/land/ad/5867037765?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CCE3B589087C9AE3C6FD3C72DD92F3B9146F772F</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>b9e7b78c99</t>
+          <t>5ae3a66648</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Servify</t>
+          <t>Infosys Finacle</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867265604?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=98C25A013410B0B492855DE45F67FF3409A45C24</t>
+          <t>https://www.adzuna.in/land/ad/5867270149?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=284AB41CD26DD62DA43E2E7866A4F2E72052CFA3</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>339ea3cd4c</t>
+          <t>b9e7b78c99</t>
         </is>
       </c>
     </row>
@@ -4757,37 +4757,37 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CEO, AI Finance</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bjak</t>
+          <t>Servify</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/bjak/jobs/ceo-ai-finance-7034716418</t>
+          <t>https://www.adzuna.in/land/ad/5867265604?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=98C25A013410B0B492855DE45F67FF3409A45C24</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>8e23b34067</t>
+          <t>339ea3cd4c</t>
         </is>
       </c>
     </row>
@@ -4818,17 +4818,17 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Accounting Automation Engineer</t>
+          <t>CEO, AI Finance</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spotter Labs</t>
+          <t>Bjak</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>automation, software (tag), engineer, worldwide (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Accounting-Automation-Engineer, Finance-Automation-Engineer, Accounting-Software-Engineer, Accounting-Automation, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3984977259</t>
+          <t>https://himalayas.app/companies/bjak/jobs/ceo-ai-finance-7034716418</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>c570969de5</t>
+          <t>8e23b34067</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Accounting-Automation-Engineer, Accounting, Process-Automation, Financial-Automation, Business-Systems, Finance-Automation-Engineer, Accounting-Software-Engineer, Automation-Engineer, Accounting-Automation, Software-Automation-Engineer, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
+          <t>Accounting-Automation-Engineer, Finance-Automation-Engineer, Accounting-Software-Engineer, Accounting-Automation, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4919,12 +4919,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3943339358</t>
+          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3984977259</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>13edcbb44e</t>
+          <t>c570969de5</t>
         </is>
       </c>
     </row>
@@ -4940,37 +4940,37 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Backend Engineer - Platform - Stacks | Ireland | Remote</t>
+          <t>Accounting Automation Engineer</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grafana Labs</t>
+          <t>Spotter Labs</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>engineer, backend, anywhere (place)</t>
+          <t>automation, software (tag), engineer, worldwide (place)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Accounting-Automation-Engineer, Accounting, Process-Automation, Financial-Automation, Business-Systems, Finance-Automation-Engineer, Accounting-Software-Engineer, Automation-Engineer, Accounting-Automation, Software-Automation-Engineer, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/grafana-labs-backend-engineer-platform-stacks-ireland-remote</t>
+          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3943339358</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>7aae615c8c</t>
+          <t>13edcbb44e</t>
         </is>
       </c>
     </row>
@@ -5001,37 +5001,37 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>STEM Expert</t>
+          <t>Backend Engineer - Platform - Stacks | Ireland | Remote</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ai (tag), worldwide (place)</t>
+          <t>engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>STEM-Expert, STEM-Specialist, STEM-Consultant, STEM-Domain-Expert, STEM-Researcher, STEM-Educator, STEM-AI-Specialist, Japanese-STEM-Specialist, STEM-Advisor, STEM-Instructor, Mid-level</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/stem-expert-40695367</t>
+          <t>https://weworkremotely.com/remote-jobs/grafana-labs-backend-engineer-platform-stacks-ireland-remote</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>9cb40c45fc</t>
+          <t>7aae615c8c</t>
         </is>
       </c>
     </row>
@@ -5062,14 +5062,12 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>21</v>
-      </c>
-      <c r="D76" t="n">
-        <v>3</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Excel Specialist</t>
+          <t>STEM Expert</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5089,12 +5087,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>automation (tag), developer (tag), worldwide (place)</t>
+          <t>ai (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Excel-Specialist, Excel-Expert, Spreadsheet-Specialist, Excel-Automation-Specialist, Excel-Data-Analyst, Microsoft-Excel-Developer, Microsoft-Office-Specialist, Microsoft-Excel-Development, Entry-level, Mid-level</t>
+          <t>STEM-Expert, STEM-Specialist, STEM-Consultant, STEM-Domain-Expert, STEM-Researcher, STEM-Educator, STEM-AI-Specialist, Japanese-STEM-Specialist, STEM-Advisor, STEM-Instructor, Mid-level</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5104,12 +5102,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/excel-specialist-2996931708</t>
+          <t>https://himalayas.app/companies/micro1/jobs/stem-expert-40695367</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>fddf243627</t>
+          <t>9cb40c45fc</t>
         </is>
       </c>
     </row>
@@ -5121,56 +5119,58 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>69</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>Excel Specialist</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ISIR AI</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>data science, qa (tag), intern (level), noida (place)</t>
+          <t>automation (tag), developer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Scientific &amp; QA Jobs</t>
+          <t>Excel-Specialist, Excel-Expert, Spreadsheet-Specialist, Excel-Automation-Specialist, Excel-Data-Analyst, Microsoft-Excel-Developer, Microsoft-Office-Specialist, Microsoft-Excel-Development, Entry-level, Mid-level</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427080?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C509B9B88F855FA7348A37AF1CDF8C3ECC7CA889</t>
+          <t>https://himalayas.app/companies/micro1/jobs/excel-specialist-2996931708</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>84896ab3c6</t>
+          <t>fddf243627</t>
         </is>
       </c>
     </row>
@@ -5186,22 +5186,22 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FRND</t>
+          <t>ISIR AI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>machine learning, intern (level), bangalore (place)</t>
+          <t>data science, qa (tag), intern (level), noida (place)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864424613?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9B60872885E8C7073FE0CC2A962D44A1E48845F7</t>
+          <t>https://www.adzuna.in/land/ad/5864427080?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C509B9B88F855FA7348A37AF1CDF8C3ECC7CA889</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>e00b96a707</t>
+          <t>84896ab3c6</t>
         </is>
       </c>
     </row>
@@ -5247,22 +5247,22 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Intern (Data Science)</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Yubi</t>
+          <t>FRND</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>data science, intern (level), chennai (place)</t>
+          <t>machine learning, intern (level), bangalore (place)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864443163?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4554D5357B8D35F06907356F0816FBF3BD2BBC7E</t>
+          <t>https://www.adzuna.in/land/ad/5864424613?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9B60872885E8C7073FE0CC2A962D44A1E48845F7</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>93516db46a</t>
+          <t>e00b96a707</t>
         </is>
       </c>
     </row>
@@ -5308,37 +5308,37 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AI Inference Engineer QVAC (100% remote Worldwide)</t>
+          <t>Intern (Data Science)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tether Operations Limited</t>
+          <t>Yubi</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>software (tag), engineer, ai, worldwide (place)</t>
+          <t>data science, intern (level), chennai (place)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Software-Engineer, AI-Engineering, Machine-Learning-Engineering, C-Development, Edge-AI, AI-Inference-Engineer, Remote-AI-Engineer, Remote-Machine-Learning-Engineer, Senior-AI-Inference-Engineer, Remote-Senior-AI-Engineer, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/tether-operations-limited/jobs/ai-inference-engineer-qvac-100-remote-worldwide</t>
+          <t>https://www.adzuna.in/land/ad/5864443163?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4554D5357B8D35F06907356F0816FBF3BD2BBC7E</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>f7f40ca44a</t>
+          <t>93516db46a</t>
         </is>
       </c>
     </row>
@@ -5369,37 +5369,37 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Machine Learning Gen AI_Hyderabad,Pune &amp; Bangalore</t>
+          <t>AI Inference Engineer QVAC (100% remote Worldwide)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Tether Operations Limited</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>machine learning, hyderabad (place)</t>
+          <t>software (tag), engineer, ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Software-Engineer, AI-Engineering, Machine-Learning-Engineering, C-Development, Edge-AI, AI-Inference-Engineer, Remote-AI-Engineer, Remote-Machine-Learning-Engineer, Senior-AI-Inference-Engineer, Remote-Senior-AI-Engineer, Senior</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439281?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1F39144C3030195205A212339590BB508623F064</t>
+          <t>https://himalayas.app/companies/tether-operations-limited/jobs/ai-inference-engineer-qvac-100-remote-worldwide</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>55fce19c46</t>
+          <t>f7f40ca44a</t>
         </is>
       </c>
     </row>
@@ -5430,17 +5430,17 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Gen AI_Hyderabad,Pune &amp; Bangalore</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Infosys Consulting</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>data scientist, hyderabad (place)</t>
+          <t>machine learning, hyderabad (place)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864428905?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4E35D1AC081FE279803556ECA4C1E1871550877F</t>
+          <t>https://www.adzuna.in/land/ad/5864439281?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1F39144C3030195205A212339590BB508623F064</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>af7ebeb057</t>
+          <t>55fce19c46</t>
         </is>
       </c>
     </row>
@@ -5493,9 +5493,7 @@
       <c r="C83" t="n">
         <v>49</v>
       </c>
-      <c r="D83" t="n">
-        <v>2</v>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Data Scientist</t>
@@ -5503,12 +5501,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>super.money</t>
+          <t>Infosys Consulting</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5518,7 +5516,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, hyderabad (place)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5533,12 +5531,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864425941?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BF9A171BDEA00E60475790836A0A3589FB8D9EB6</t>
+          <t>https://www.adzuna.in/land/ad/5864428905?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4E35D1AC081FE279803556ECA4C1E1871550877F</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>4f1a679ea3</t>
+          <t>af7ebeb057</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5554,9 @@
       <c r="C84" t="n">
         <v>49</v>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>Data Scientist</t>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lufthansa Technik Services India Pvt Ltd</t>
+          <t>super.money</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864422634?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
+          <t>https://www.adzuna.in/land/ad/5864425941?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BF9A171BDEA00E60475790836A0A3589FB8D9EB6</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>c86fa3dfe3</t>
+          <t>4f1a679ea3</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank</t>
+          <t>Lufthansa Technik Services India Pvt Ltd</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439103?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=73CFB6E1B4115AA2A23A99B0EC8886521BA01450</t>
+          <t>https://www.adzuna.in/land/ad/5864422634?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>08622a68ed</t>
+          <t>c86fa3dfe3</t>
         </is>
       </c>
     </row>
@@ -5681,17 +5681,17 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Navi</t>
+          <t>Kotak Mahindra Bank</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439226?se=jiNNTDmm8RGUNa3mkcr13g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=744BE785510320885EE5287D6F2FE8E098FAED30</t>
+          <t>https://www.adzuna.in/land/ad/5864439103?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=73CFB6E1B4115AA2A23A99B0EC8886521BA01450</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>4e1bb30522</t>
+          <t>08622a68ed</t>
         </is>
       </c>
     </row>
@@ -5742,17 +5742,17 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tricog Health</t>
+          <t>Navi</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5865291446?se=pmQW9lOm8RGs-Y02KTQxmA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=A9D77535171E8EAD7E7898B67A7ADC8ED3D07410</t>
+          <t>https://www.adzuna.in/land/ad/5864439226?se=jiNNTDmm8RGUNa3mkcr13g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=744BE785510320885EE5287D6F2FE8E098FAED30</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>eaec37f6c0</t>
+          <t>4e1bb30522</t>
         </is>
       </c>
     </row>
@@ -5798,54 +5798,52 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>41</v>
-      </c>
-      <c r="D88" t="n">
-        <v>3</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Remote - Automation QA Engineer (Core Team)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Torrero</t>
+          <t>Tricog Health</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>automation, software (tag), engineer, testing (tag), qa, worldwide (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>QA-Engineer, QA-Automation-Engineer, Software-Testing, Quality-Assurance, Manual-Testing, Remote-Test-Automation-Engineer, Remote-QA-Engineer, Remote-Quality-Assurance-Engineer, Remote-UI-Automation-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/torrero/jobs/remote-automation-qa-engineer-core-team</t>
+          <t>https://www.adzuna.in/land/ad/5865291446?se=pmQW9lOm8RGs-Y02KTQxmA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=A9D77535171E8EAD7E7898B67A7ADC8ED3D07410</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>f03380c71d</t>
+          <t>eaec37f6c0</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5859,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>36</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Front-End Developer</t>
+          <t>Remote - Automation QA Engineer (Core Team)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talent Sam</t>
+          <t>Torrero</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>developer, frontend (tag), engineer (tag), react (tag), worldwide (place)</t>
+          <t>automation, software (tag), engineer, testing (tag), qa, worldwide (place)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Frontend-Development, Web-Development, UI-Developer, Frontend-Engineer, Front-End-Developer, Frontend-React-Developer, UI-Frontend-Developer, UX-UI-Front-End-Developer, React-Frontend-Developer, Frontend-Web-Development, Developer, Mid-level</t>
+          <t>QA-Engineer, QA-Automation-Engineer, Software-Testing, Quality-Assurance, Manual-Testing, Remote-Test-Automation-Engineer, Remote-QA-Engineer, Remote-Quality-Assurance-Engineer, Remote-UI-Automation-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/talent-sam/jobs/front-end-developer</t>
+          <t>https://himalayas.app/companies/torrero/jobs/remote-automation-qa-engineer-core-team</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>94d5af612e</t>
+          <t>f03380c71d</t>
         </is>
       </c>
     </row>
@@ -5922,37 +5922,37 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>E-learning Developer</t>
+          <t>Front-End Developer</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>VineGarden Films</t>
+          <t>Talent Sam</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>developer, india (place)</t>
+          <t>developer, frontend (tag), engineer (tag), react (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Teaching Jobs</t>
+          <t>Frontend-Development, Web-Development, UI-Developer, Frontend-Engineer, Front-End-Developer, Frontend-React-Developer, UI-Frontend-Developer, UX-UI-Front-End-Developer, React-Frontend-Developer, Frontend-Web-Development, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864153573?se=SvkgT-Wl8RGUGK7L4gkIgg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FDDF0A4236DF3E6D3081AF93B01799D77599EAD1</t>
+          <t>https://himalayas.app/companies/talent-sam/jobs/front-end-developer</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>248ef46714</t>
+          <t>94d5af612e</t>
         </is>
       </c>
     </row>
@@ -5979,21 +5979,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Data Scientist - Python Deterministic Analytics</t>
+          <t>E-learning Developer</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Capco</t>
+          <t>VineGarden Films</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6008,27 +6008,27 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>data scientist, python, india (place)</t>
+          <t>developer, india (place)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Teaching Jobs</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139747?se=olLfvDql8RGL6NrjcRaTpw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9FA82041CC2CC98F084D6827CF82DA2BE289D998</t>
+          <t>https://www.adzuna.in/land/ad/5864153573?se=SvkgT-Wl8RGUGK7L4gkIgg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FDDF0A4236DF3E6D3081AF93B01799D77599EAD1</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>6f1952e273</t>
+          <t>248ef46714</t>
         </is>
       </c>
     </row>
@@ -6044,22 +6044,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - APAC</t>
+          <t>Data Scientist - Python Deterministic Analytics</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional®</t>
+          <t>Capco</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>data scientist, python, india (place)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6079,17 +6079,17 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5862635702?se=9gaugPCk8RGcfKYe_cIpvA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=53D4DF556D646C5F462C8F3FC782D72E8A35D08B</t>
+          <t>https://www.adzuna.in/land/ad/5837139747?se=olLfvDql8RGL6NrjcRaTpw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9FA82041CC2CC98F084D6827CF82DA2BE289D998</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>d395f3a907</t>
+          <t>6f1952e273</t>
         </is>
       </c>
     </row>
@@ -6105,52 +6105,52 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AI Engineer Data APIs</t>
+          <t>Machine Learning Engineer - APAC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>LexisNexis Legal &amp; Professional®</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>engineer, golang (tag), ai</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>golang, video, engineer</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-ai-engineer-data-apis-benzinga-1137224</t>
+          <t>https://www.adzuna.in/land/ad/5862635702?se=9gaugPCk8RGcfKYe_cIpvA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=53D4DF556D646C5F462C8F3FC782D72E8A35D08B</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>1261a5bcd5</t>
+          <t>d395f3a907</t>
         </is>
       </c>
     </row>
@@ -6166,52 +6166,52 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Agentic Python Engineer</t>
+          <t>AI Engineer Data APIs</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Evaboot</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>WORLDWIDE</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>engineer, python, aws (tag), worldwide (place)</t>
+          <t>engineer, golang (tag), ai</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Development, python,engineer,aws,analytics,seo</t>
+          <t>golang, video, engineer</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1826864/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-engineer-data-apis-benzinga-1137224</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>47ae63b1d0</t>
+          <t>1261a5bcd5</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
@@ -6242,22 +6242,22 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>WORLDWIDE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>engineer, python, anywhere (place)</t>
+          <t>engineer, python, aws (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Development, python,engineer,aws,analytics,seo</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/evaboot-agentic-python-engineer</t>
+          <t>https://www.workingnomads.com/job/go/1826864/</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>d94554bfc7</t>
+          <t>47ae63b1d0</t>
         </is>
       </c>
     </row>
@@ -6284,56 +6284,56 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Agentic Python Engineer</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Evaboot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>engineer, python, anywhere (place)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982687?se=BGNyWVik8RGF59teMJsS7Q&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=64C652991D92D5E3DCA4519D688756F962092321</t>
+          <t>https://weworkremotely.com/remote-jobs/evaboot-agentic-python-engineer</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>dd6de0380a</t>
+          <t>d94554bfc7</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Data Scientist, Knowledge Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982533?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=853C1E923E89428D368371363C6206932A9E653B</t>
+          <t>https://www.adzuna.in/land/ad/5857982687?se=BGNyWVik8RGF59teMJsS7Q&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=64C652991D92D5E3DCA4519D688756F962092321</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>e4df1efe77</t>
+          <t>dd6de0380a</t>
         </is>
       </c>
     </row>
@@ -6415,17 +6415,17 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Data Scientist II, Data Analytics, Hyderabad</t>
+          <t>Data Scientist, Knowledge Management</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>data scientist, hyderabad (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6445,17 +6445,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5860916020?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2CB3A6FFC4393B68C48E0DBE7C464491C08965D1</t>
+          <t>https://www.adzuna.in/land/ad/5857982533?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=853C1E923E89428D368371363C6206932A9E653B</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>ed5cec24b5</t>
+          <t>e4df1efe77</t>
         </is>
       </c>
     </row>
@@ -6471,52 +6471,52 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform - Hyderabad, India</t>
+          <t>Data Scientist II, Data Analytics, Hyderabad</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Speechify</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>software engineer, backend (tag), cloud (tag), api (tag), india (place)</t>
+          <t>data scientist, hyderabad (place)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Platform-Engineering, Backend-Engineering, Software-Engineer, API-Development, Cloud-Infrastructure, Software-Platform-Engineer, Platform-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/speechify/jobs/software-engineer-platform-hyderabad-india</t>
+          <t>https://www.adzuna.in/land/ad/5860916020?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2CB3A6FFC4393B68C48E0DBE7C464491C08965D1</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>d972ee3bee</t>
+          <t>ed5cec24b5</t>
         </is>
       </c>
     </row>
@@ -6532,22 +6532,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>GitHub Contributor</t>
+          <t>Software Engineer, Platform - Hyderabad, India</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Speechify</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, backend (tag), cloud (tag), api (tag), india (place)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
+          <t>Platform-Engineering, Backend-Engineering, Software-Engineer, API-Development, Cloud-Infrastructure, Software-Platform-Engineer, Platform-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6572,12 +6572,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-2145210908</t>
+          <t>https://himalayas.app/companies/speechify/jobs/software-engineer-platform-hyderabad-india</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>9bd86980fc</t>
+          <t>d972ee3bee</t>
         </is>
       </c>
     </row>
@@ -6589,58 +6589,56 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38</v>
-      </c>
-      <c r="D101" t="n">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, PDP Experience</t>
+          <t>GitHub Contributor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>software engineer, backend, anywhere (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/reddit-backend-software-engineer-pdp-experience</t>
+          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-2145210908</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>a954ce85ab</t>
+          <t>9bd86980fc</t>
         </is>
       </c>
     </row>
@@ -6656,37 +6654,39 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>24</v>
-      </c>
-      <c r="D102" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="D102" t="n">
+        <v>3</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Open Source Contributor</t>
+          <t>Backend Software Engineer, PDP Experience</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Open-Source-Software-Developer, Open-Source-Advocate, Open-Source-Engineer, Open-Source-Software-Engineer, Open-Source-Software-Maintainer, Community-Contributor, Entry-level</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/open-source-contributor-4150550716</t>
+          <t>https://weworkremotely.com/remote-jobs/reddit-backend-software-engineer-pdp-experience</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>d8033bd793</t>
+          <t>a954ce85ab</t>
         </is>
       </c>
     </row>
@@ -6713,16 +6713,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Open Source Contributor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6742,27 +6742,27 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>engineer, python (tag), ai, ml (tag), worldwide (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Mid-level</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Open-Source-Software-Developer, Open-Source-Advocate, Open-Source-Engineer, Open-Source-Software-Engineer, Open-Source-Software-Maintainer, Community-Contributor, Entry-level</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-engineer-7982880650</t>
+          <t>https://himalayas.app/companies/micro1/jobs/open-source-contributor-4150550716</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>17936ac69e</t>
+          <t>d8033bd793</t>
         </is>
       </c>
     </row>
@@ -6778,37 +6778,37 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>machine learning, engineer, hyderabad (place)</t>
+          <t>engineer, python (tag), ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Mid-level</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5859662671?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=77410E24CED3D457054E58156829472F42D5B958</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-engineer-7982880650</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>a8bcca74c0</t>
+          <t>17936ac69e</t>
         </is>
       </c>
     </row>
@@ -6844,17 +6844,17 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (T25)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>machine learning, engineer, hyderabad (place)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6874,17 +6874,17 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858538850?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AA8B404BB5F08B6BBBC1A1DAEA80EDAE2331BB01</t>
+          <t>https://www.adzuna.in/land/ad/5859662671?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=77410E24CED3D457054E58156829472F42D5B958</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>e99054d24c</t>
+          <t>a8bcca74c0</t>
         </is>
       </c>
     </row>
@@ -6905,7 +6905,7 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SWE-3 Machine Learning Engineer</t>
+          <t>Machine Learning Engineer (T25)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858537539?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=49BEDAECA8CA01D8F7BFB9CA5D092D8DD046FCF4</t>
+          <t>https://www.adzuna.in/land/ad/5858538850?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AA8B404BB5F08B6BBBC1A1DAEA80EDAE2331BB01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>83e0ebd10e</t>
+          <t>e99054d24c</t>
         </is>
       </c>
     </row>
@@ -6961,22 +6961,22 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>SWE-3 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>engineer, ai, hyderabad (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982475?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=61932F7A965BC6190F96EF3EDD6B34FCA7CA0EFF</t>
+          <t>https://www.adzuna.in/land/ad/5858537539?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=49BEDAECA8CA01D8F7BFB9CA5D092D8DD046FCF4</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>ec1b34ae37</t>
+          <t>83e0ebd10e</t>
         </is>
       </c>
     </row>
@@ -7022,52 +7022,52 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AI Data Annotator - Remote</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Argos Multilingual Inc.</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>All Other Remote, Contract</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/argos-multilingual-inc-ai-data-annotator-remote</t>
+          <t>https://www.adzuna.in/land/ad/5857982475?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=61932F7A965BC6190F96EF3EDD6B34FCA7CA0EFF</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>5c22526a85</t>
+          <t>ec1b34ae37</t>
         </is>
       </c>
     </row>
@@ -7079,56 +7079,56 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Data Scientist - AI &amp; Automation</t>
+          <t>AI Data Annotator - Remote</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Argos Multilingual Inc.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>data scientist, automation, ai, bangalore (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>All Other Remote, Contract</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251125?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C7BA7BE347A1ADA1FC538497AF302C4F3AD6BEDD</t>
+          <t>https://weworkremotely.com/remote-jobs/argos-multilingual-inc-ai-data-annotator-remote</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2e19a4f3f6</t>
+          <t>5c22526a85</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MTS-1 Machine Learning Engineer</t>
+          <t>Data Scientist - AI &amp; Automation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>data scientist, automation, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858537523?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4219F9238C4FE19DFCEAD65DAA98E56A5B89F388</t>
+          <t>https://www.adzuna.in/land/ad/5857251125?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C7BA7BE347A1ADA1FC538497AF302C4F3AD6BEDD</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>c65fcd065c</t>
+          <t>2e19a4f3f6</t>
         </is>
       </c>
     </row>
@@ -7205,22 +7205,22 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>MTS-1 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>data scientist, mumbai (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7240,17 +7240,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5849296977?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FFA2BB725355D26B4B624FA5365F48C2D8B894C</t>
+          <t>https://www.adzuna.in/land/ad/5858537523?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4219F9238C4FE19DFCEAD65DAA98E56A5B89F388</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>200651f002</t>
+          <t>c65fcd065c</t>
         </is>
       </c>
     </row>
@@ -7276,12 +7276,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, mumbai (place)</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7301,17 +7301,17 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251146?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=43EC4FC89638B5AB4C3D5267B80E2B1135A6C706</t>
+          <t>https://www.adzuna.in/land/ad/5849296977?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FFA2BB725355D26B4B624FA5365F48C2D8B894C</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>6a6f7a8419</t>
+          <t>200651f002</t>
         </is>
       </c>
     </row>
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251173?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7E2FD9B14C3A74461E2352F6CFE714131C13E4BC</t>
+          <t>https://www.adzuna.in/land/ad/5857251146?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=43EC4FC89638B5AB4C3D5267B80E2B1135A6C706</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>aa6eef76e8</t>
+          <t>6a6f7a8419</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7393,7 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Data Scientist, Knowledge Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251185?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=74B3EB71D85FA01AB90B707F8DB6AB9F2A17FAFA</t>
+          <t>https://www.adzuna.in/land/ad/5857251173?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7E2FD9B14C3A74461E2352F6CFE714131C13E4BC</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>d1497475d4</t>
+          <t>aa6eef76e8</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Data Scientist with R programming</t>
+          <t>Data Scientist, Knowledge Management</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Capco</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7484,17 +7484,17 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139433?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=221D7BCDBBE6E4012ED68B71EDB34DB2E07507EC</t>
+          <t>https://www.adzuna.in/land/ad/5857251185?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=74B3EB71D85FA01AB90B707F8DB6AB9F2A17FAFA</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>dbec4a04a4</t>
+          <t>d1497475d4</t>
         </is>
       </c>
     </row>
@@ -7510,52 +7510,52 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Data Scientist with R programming</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capco</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Product, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer-1</t>
+          <t>https://www.adzuna.in/land/ad/5837139433?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=221D7BCDBBE6E4012ED68B71EDB34DB2E07507EC</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>e7de7648c1</t>
+          <t>dbec4a04a4</t>
         </is>
       </c>
     </row>
@@ -7611,12 +7611,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer</t>
+          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer-1</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>dada5ade61</t>
+          <t>e7de7648c1</t>
         </is>
       </c>
     </row>
@@ -7632,52 +7632,52 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Education Designer UX UI and AI</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Interaction Design Foundation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>design, content writing, education</t>
+          <t>Product, Full-Time</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-education-designer-ux-ui-and-ai-interaction-design-foundation-1137138</t>
+          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>ca62234445</t>
+          <t>dada5ade61</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Course Writer and Editor UX UI and AI</t>
+          <t>Education Designer UX UI and AI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>design, content writing</t>
+          <t>design, content writing, education</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-course-writer-and-editor-ux-ui-and-ai-interaction-design-foundation-1137136</t>
+          <t>https://remoteOK.com/remote-jobs/remote-education-designer-ux-ui-and-ai-interaction-design-foundation-1137138</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>01210e4343</t>
+          <t>ca62234445</t>
         </is>
       </c>
     </row>
@@ -7750,56 +7750,56 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>App Developer - AI/ML</t>
+          <t>Course Writer and Editor UX UI and AI</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Interaction Design Foundation</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>developer, ai, ml, hyderabad (place)</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>design, content writing</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139469?se=-BSx1eug8RG-Sdz4qyZPjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=16DC1893C3026AA51441662E0B1A61360470917B</t>
+          <t>https://remoteOK.com/remote-jobs/remote-course-writer-and-editor-ux-ui-and-ai-interaction-design-foundation-1137136</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>7a22fe6bd5</t>
+          <t>01210e4343</t>
         </is>
       </c>
     </row>
@@ -7815,17 +7815,17 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>App Developer - AI/ML</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>developer, ai, ml, hyderabad (place)</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7850,17 +7850,17 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857168441?se=TqYc8W2h8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CEB40CB7335D41898800C58388A2B035DF674757</t>
+          <t>https://www.adzuna.in/land/ad/5837139469?se=-BSx1eug8RG-Sdz4qyZPjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=16DC1893C3026AA51441662E0B1A61360470917B</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>84fdce5107</t>
+          <t>7a22fe6bd5</t>
         </is>
       </c>
     </row>
@@ -7876,37 +7876,37 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AI Speech &amp; Audio Specialist – ASR | TTS | Voice AI | Audio Data</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/ai-speech-audio-specialist-asr-tts-voice-ai-audio-data</t>
+          <t>https://www.adzuna.in/land/ad/5857168441?se=TqYc8W2h8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CEB40CB7335D41898800C58388A2B035DF674757</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>bb930fc93f</t>
+          <t>84fdce5107</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Financial Accuracy &amp; Tax Logic Expert (AI Community)</t>
+          <t>AI Speech &amp; Audio Specialist – ASR | TTS | Voice AI | Audio Data</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/financial-accuracy-tax-logic-expert-ai-community-7007868696</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/ai-speech-audio-specialist-asr-tts-voice-ai-audio-data</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>162d6a9ed2</t>
+          <t>bb930fc93f</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Identity Trust &amp; Fraud Intelligence Specialist - Intermediate (AI Community)</t>
+          <t>Financial Accuracy &amp; Tax Logic Expert (AI Community)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -8038,12 +8038,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/identity-trust-fraud-intelligence-specialist-intermediate-ai-community</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/financial-accuracy-tax-logic-expert-ai-community-7007868696</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>637c85a300</t>
+          <t>162d6a9ed2</t>
         </is>
       </c>
     </row>
@@ -8064,32 +8064,32 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Education Designer: UX, UI, and AI</t>
+          <t>Identity Trust &amp; Fraud Intelligence Specialist - Intermediate (AI Community)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>IxDF - Interaction Design Foundation</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Design, Full-Time</t>
+          <t>Entry-level</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-education-designer-ux-ui-and-ai</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/identity-trust-fraud-intelligence-specialist-intermediate-ai-community</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>9fbe655de3</t>
+          <t>637c85a300</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8125,7 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Course Writer and Editor: UX, UI, and AI</t>
+          <t>Education Designer: UX, UI, and AI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-course-writer-and-editor-ux-ui-and-ai</t>
+          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-education-designer-ux-ui-and-ai</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>e8e07f5951</t>
+          <t>9fbe655de3</t>
         </is>
       </c>
     </row>
@@ -8186,32 +8186,32 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AI Consulting Domain Expert</t>
+          <t>Course Writer and Editor: UX, UI, and AI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IxDF - Interaction Design Foundation</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>AI-Domain-Expert, AI-Consultant, AI-Subject-Matter-Expert, Artificial-Intelligence-Consulting, Senior</t>
+          <t>Design, Full-Time</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8221,12 +8221,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-consulting-domain-expert-7128968890</t>
+          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-course-writer-and-editor-ux-ui-and-ai</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>7f1041d829</t>
+          <t>e8e07f5951</t>
         </is>
       </c>
     </row>
@@ -8242,39 +8242,37 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>40</v>
-      </c>
-      <c r="D128" t="n">
-        <v>2</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Software Development Engineer II Full Stack - Business (Remote @ Colombia)</t>
+          <t>AI Consulting Domain Expert</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>full stack, software, engineer, anywhere (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>AI-Domain-Expert, AI-Consultant, AI-Subject-Matter-Expert, Artificial-Intelligence-Consulting, Senior</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8284,12 +8282,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/offerup-software-development-engineer-ii-full-stack-business-remote-colombia</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-consulting-domain-expert-7128968890</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>6fe968b6b9</t>
+          <t>7f1041d829</t>
         </is>
       </c>
     </row>
@@ -8305,37 +8303,39 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>20</v>
-      </c>
-      <c r="D129" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>QA Speech-to-Text Audio Collection Project</t>
+          <t>Software Development Engineer II Full Stack - Business (Remote @ Colombia)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>qa, worldwide (place)</t>
+          <t>full stack, software, engineer, anywhere (place)</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Entry-level</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/qa-speech-to-text-audio-collection-project</t>
+          <t>https://weworkremotely.com/remote-jobs/offerup-software-development-engineer-ii-full-stack-business-remote-colombia</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>a44e738ec6</t>
+          <t>6fe968b6b9</t>
         </is>
       </c>
     </row>
@@ -8362,21 +8362,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AI/RAG engineer</t>
+          <t>QA Speech-to-Text Audio Collection Project</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CoinMarketCap</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8391,27 +8391,27 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>engineer, ai, ml (tag), worldwide (place)</t>
+          <t>qa, worldwide (place)</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>RAG-AI-Engineer, Machine-Learning-Engineering, AI-Engineering, RAG-Development, Vector-Search-Engineer, IA-RAG-Engineer, AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, Mid-level</t>
+          <t>Entry-level</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/coinmarketcap/jobs/ai-rag-engineer</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/qa-speech-to-text-audio-collection-project</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>d199d5cdfc</t>
+          <t>a44e738ec6</t>
         </is>
       </c>
     </row>
@@ -8427,52 +8427,52 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI/RAG engineer</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>CoinMarketCap</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>engineer, ai, mumbai (place)</t>
+          <t>engineer, ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>RAG-AI-Engineer, Machine-Learning-Engineering, AI-Engineering, RAG-Development, Vector-Search-Engineer, IA-RAG-Engineer, AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723676?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F83D2913763A01EA6FBE321571CA8B989BE3F382</t>
+          <t>https://himalayas.app/companies/coinmarketcap/jobs/ai-rag-engineer</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>faa646b456</t>
+          <t>d199d5cdfc</t>
         </is>
       </c>
     </row>
@@ -8493,12 +8493,12 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Data Science-Index Quant Specialist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8513,27 +8513,27 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>data science, mumbai (place)</t>
+          <t>engineer, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Accounting &amp; Finance Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5843137505?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC4079028ED7338B991CD57034DE9EA5AC8D9A0B</t>
+          <t>https://www.adzuna.in/land/ad/5846723676?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F83D2913763A01EA6FBE321571CA8B989BE3F382</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>6ec3848d0b</t>
+          <t>faa646b456</t>
         </is>
       </c>
     </row>
@@ -8554,17 +8554,17 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Science-Index Quant Specialist</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Gurgaon, Haryana</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8574,27 +8574,27 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>data scientist, gurgaon (place)</t>
+          <t>data science, mumbai (place)</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Accounting &amp; Finance Jobs</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5849297019?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E87B9A5E2A9605281144BBEA53533DB7165D1FA0</t>
+          <t>https://www.adzuna.in/land/ad/5843137505?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC4079028ED7338B991CD57034DE9EA5AC8D9A0B</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>e2cd9eda9e</t>
+          <t>6ec3848d0b</t>
         </is>
       </c>
     </row>
@@ -8620,12 +8620,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>Gurgaon, Haryana</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>data scientist, delhi (place)</t>
+          <t>data scientist, gurgaon (place)</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5848650875?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4DF45BC4D3A230C0689E561399F3F0BA2C0FC825</t>
+          <t>https://www.adzuna.in/land/ad/5849297019?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E87B9A5E2A9605281144BBEA53533DB7165D1FA0</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>83a3456095</t>
+          <t>e2cd9eda9e</t>
         </is>
       </c>
     </row>
@@ -8671,52 +8671,52 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>GTM AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Customer.io</t>
+          <t>Danaher</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>New Delhi, Delhi</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>data scientist, delhi (place)</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/customer-io-gtm-ai-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5848650875?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4DF45BC4D3A230C0689E561399F3F0BA2C0FC825</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>19a2ae7abb</t>
+          <t>83a3456095</t>
         </is>
       </c>
     </row>
@@ -8732,17 +8732,17 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Performance Creative Strategist and AI Producer</t>
+          <t>GTM AI Engineer</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Icarus Digital Marketing</t>
+          <t>Customer.io</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/icarus-digital-marketing-performance-creative-strategist-and-ai-producer</t>
+          <t>https://weworkremotely.com/remote-jobs/customer-io-gtm-ai-engineer</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>60c87a59fd</t>
+          <t>19a2ae7abb</t>
         </is>
       </c>
     </row>
@@ -8793,37 +8793,37 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>GTM Coordinator, Cloud Native (Talent Pool)</t>
+          <t>Performance Creative Strategist and AI Producer</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Percona</t>
+          <t>Icarus Digital Marketing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bulgaria, Croatia, Czechia, Greece, Hungary, India, Poland, Portugal, Spain</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>cloud, india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>GTM-Coordinator, Talent-Community-Coordinator, Talent-Operations-Coordinator, Entry-level</t>
+          <t>Sales and Marketing, Full-Time</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/percona/jobs/gtm-coordinator-cloud-native-talent-pool</t>
+          <t>https://weworkremotely.com/remote-jobs/icarus-digital-marketing-performance-creative-strategist-and-ai-producer</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>a97ee1ce9b</t>
+          <t>60c87a59fd</t>
         </is>
       </c>
     </row>
@@ -8854,52 +8854,52 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Offensive Cybersecurity Engineer - Red Team</t>
+          <t>GTM Coordinator, Cloud Native (Talent Pool)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Techno Vista Dynamics</t>
+          <t>Percona</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>APAC,Middle East</t>
+          <t>Bulgaria, Croatia, Czechia, Greece, Hungary, India, Poland, Portugal, Spain</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>engineer, testing (tag), apac (place)</t>
+          <t>cloud, india (place)</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Development, engineer,security,penetration testing</t>
+          <t>GTM-Coordinator, Talent-Community-Coordinator, Talent-Operations-Coordinator, Entry-level</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1781770/</t>
+          <t>https://himalayas.app/companies/percona/jobs/gtm-coordinator-cloud-native-talent-pool</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>0bde4f9b82</t>
+          <t>a97ee1ce9b</t>
         </is>
       </c>
     </row>
@@ -8911,56 +8911,56 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Human-Centered AI Data Scientist, Strategy and Talent</t>
+          <t>Offensive Cybersecurity Engineer - Red Team</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank</t>
+          <t>Techno Vista Dynamics</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>APAC,Middle East</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>data scientist, ai, bangalore (place)</t>
+          <t>engineer, testing (tag), apac (place)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Development, engineer,security,penetration testing</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139276?se=1M6Kj_qf8RGoxpN31Vp7kA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C0F814CBDD0355075DDB000131DE4C8D130504ED</t>
+          <t>https://www.workingnomads.com/job/go/1781770/</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>3130787ee8</t>
+          <t>0bde4f9b82</t>
         </is>
       </c>
     </row>
@@ -8976,52 +8976,52 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Java Software Develper Engineer</t>
+          <t>Human-Centered AI Data Scientist, Strategy and Talent</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>Standard Chartered Bank</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>programmer (tag), developer (tag), software, engineer, backend (tag), java, india (place)</t>
+          <t>data scientist, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Java-Development, Software-Engineer, Entry-Level-Software-Development, Backend-Development, Technical-Support, Java-Software-Engineer, Java-Developer, Java-Developer-Jobs, Java-Application-Developer, Java-Programmer, Developer, Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/csg/jobs/java-software-develper-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5837139276?se=1M6Kj_qf8RGoxpN31Vp7kA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C0F814CBDD0355075DDB000131DE4C8D130504ED</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>7626a2cdd6</t>
+          <t>3130787ee8</t>
         </is>
       </c>
     </row>
@@ -9037,22 +9037,22 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Android Software Engineer</t>
+          <t>Java Software Develper Engineer</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9062,27 +9062,27 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>software engineer, android, kotlin (tag), worldwide (place)</t>
+          <t>programmer (tag), developer (tag), software, engineer, backend (tag), java, india (place)</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Android-Software-Engineer, Mobile-Development, Android-Development, Software-Engineer, Kotlin, Android-Engineer, Android-Software-Engineering, Mobile-Android-Engineer, Android-Systems-Engineer, Android-Engineering, Mobile-Software-Engineer, Senior</t>
+          <t>Java-Development, Software-Engineer, Entry-Level-Software-Development, Backend-Development, Technical-Support, Java-Software-Engineer, Java-Developer, Java-Developer-Jobs, Java-Application-Developer, Java-Programmer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/hudson-manpower/jobs/android-software-engineer</t>
+          <t>https://himalayas.app/companies/csg/jobs/java-software-develper-engineer</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>afb7954487</t>
+          <t>7626a2cdd6</t>
         </is>
       </c>
     </row>
@@ -9098,37 +9098,37 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Application Security Engineer II</t>
+          <t>Android Software Engineer</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>engineer, devops (tag), anywhere (place)</t>
+          <t>software engineer, android, kotlin (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Android-Software-Engineer, Mobile-Development, Android-Development, Software-Engineer, Kotlin, Android-Engineer, Android-Software-Engineering, Mobile-Android-Engineer, Android-Systems-Engineer, Android-Engineering, Mobile-Software-Engineer, Senior</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/abnormal-application-security-engineer-ii</t>
+          <t>https://himalayas.app/companies/hudson-manpower/jobs/android-software-engineer</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>dc9a51cdbc</t>
+          <t>afb7954487</t>
         </is>
       </c>
     </row>
@@ -9155,56 +9155,56 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>DESARROLLADOR FULL STACK</t>
+          <t>Application Security Engineer II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kruger NearShore LLC - Rekluti</t>
+          <t>Abnormal</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>full stack, front end (tag), backend (tag), angular (tag), testing (tag), python (tag), golang (tag), devops (tag), cloud (tag), git (tag)</t>
+          <t>engineer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>full stack, front end, python, dev, testing, web dev, quality assurance, devops, c, cloud, nosql, git, flutter, angular, mobile, golang, backend, digital nomad</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-desarrollador-full-stack-kruger-nearshore-llc-rekluti-1137062</t>
+          <t>https://weworkremotely.com/remote-jobs/abnormal-application-security-engineer-ii</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>911da99485</t>
+          <t>dc9a51cdbc</t>
         </is>
       </c>
     </row>
@@ -9220,52 +9220,52 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AI Transformation Owner, Product &amp; Design</t>
+          <t>DESARROLLADOR FULL STACK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Kruger NearShore LLC - Rekluti</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>full stack, front end (tag), backend (tag), angular (tag), testing (tag), python (tag), golang (tag), devops (tag), cloud (tag), git (tag)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Product, Full-Time</t>
+          <t>full stack, front end, python, dev, testing, web dev, quality assurance, devops, c, cloud, nosql, git, flutter, angular, mobile, golang, backend, digital nomad</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/gitlab-ai-transformation-owner-product-design</t>
+          <t>https://remoteOK.com/remote-jobs/remote-desarrollador-full-stack-kruger-nearshore-llc-rekluti-1137062</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>a0e38d6b98</t>
+          <t>911da99485</t>
         </is>
       </c>
     </row>
@@ -9281,52 +9281,52 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>AI Transformation Owner, Product &amp; Design</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Forrester Research, Inc. (US)</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>developer, software (tag), cloud (tag), india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Salesforce-Developer, CRM-Developer, Salesforce-Administrator, Integration-Developer, Software-Developer, Salesforce-CRM-Developer, Salesforce-Application-Developer, Salesforce-Sales-Cloud-Developer, Salesforce-Development, Salesforce-Solutions-Developer, Salesforce-Platform-Developer, Salesforce-Apex-Developer, Force.Com-Developer, Mid-level</t>
+          <t>Product, Full-Time</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/forrester-research-inc-us/jobs/salesforce-developer-8148624472</t>
+          <t>https://weworkremotely.com/remote-jobs/gitlab-ai-transformation-owner-product-design</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>bbbc562c11</t>
+          <t>a0e38d6b98</t>
         </is>
       </c>
     </row>
@@ -9342,17 +9342,17 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>IT Systems Administrator</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ralliant</t>
+          <t>Forrester Research, Inc. (US)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -9367,27 +9367,27 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>developer (tag), engineer (tag), india (place)</t>
+          <t>developer, software (tag), cloud (tag), india (place)</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Power-Platform-Engineer, Business-intelligence-Engineer, Analytics-Engineer, Microsoft-Fabric-Engineer, Power-BI-Developer, IT-Systems-Administrator, IT-System-Administrator, Systems-Administrator, IT-Systems-Administration, IT-Administrator, Systems-Support-Administrator, Mid-level</t>
+          <t>Salesforce-Developer, CRM-Developer, Salesforce-Administrator, Integration-Developer, Software-Developer, Salesforce-CRM-Developer, Salesforce-Application-Developer, Salesforce-Sales-Cloud-Developer, Salesforce-Development, Salesforce-Solutions-Developer, Salesforce-Platform-Developer, Salesforce-Apex-Developer, Force.Com-Developer, Mid-level</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ralliant/jobs/it-systems-administrator</t>
+          <t>https://himalayas.app/companies/forrester-research-inc-us/jobs/salesforce-developer-8148624472</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>a720a38bd1</t>
+          <t>bbbc562c11</t>
         </is>
       </c>
     </row>
@@ -9399,56 +9399,56 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Talent Pool -FP&amp;A- Data Scientist / Analytics Specialist / Data &amp; AI Specialist</t>
+          <t>IT Systems Administrator</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ralliant</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>data scientist, ai, bangalore (place)</t>
+          <t>developer (tag), engineer (tag), india (place)</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Energy, Oil &amp; Gas Jobs</t>
+          <t>Power-Platform-Engineer, Business-intelligence-Engineer, Analytics-Engineer, Microsoft-Fabric-Engineer, Power-BI-Developer, IT-Systems-Administrator, IT-System-Administrator, Systems-Administrator, IT-Systems-Administration, IT-Administrator, Systems-Support-Administrator, Mid-level</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773115?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=888721B9EAAF876B1F079BC209DECF1099E63440</t>
+          <t>https://himalayas.app/companies/ralliant/jobs/it-systems-administrator</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>5ee47ace79</t>
+          <t>a720a38bd1</t>
         </is>
       </c>
     </row>
@@ -9464,17 +9464,17 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AI and Automation Developer</t>
+          <t>Talent Pool -FP&amp;A- Data Scientist / Analytics Specialist / Data &amp; AI Specialist</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -9489,27 +9489,27 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>automation, developer, ai, bangalore (place)</t>
+          <t>data scientist, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Energy, Oil &amp; Gas Jobs</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5847959817?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44960F01CCAE33F814C0EF4448956DF38E8344F5</t>
+          <t>https://www.adzuna.in/land/ad/5785773115?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=888721B9EAAF876B1F079BC209DECF1099E63440</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>98337240aa</t>
+          <t>5ee47ace79</t>
         </is>
       </c>
     </row>
@@ -9525,52 +9525,52 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>DevOps &amp; Security Engineer - AI-Native Healthcare SaaS</t>
+          <t>AI and Automation Developer</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zenara Health</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>engineer, devops, ai, anywhere (place)</t>
+          <t>automation, developer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/zenara-health-devops-security-engineer-ai-native-healthcare-saas</t>
+          <t>https://www.adzuna.in/land/ad/5847959817?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44960F01CCAE33F814C0EF4448956DF38E8344F5</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>d592e60ddc</t>
+          <t>98337240aa</t>
         </is>
       </c>
     </row>
@@ -9586,37 +9586,37 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps &amp; Security Engineer - AI-Native Healthcare SaaS</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Zenara Health</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>data scientist, mumbai (place)</t>
+          <t>engineer, devops, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723381?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F9660467E3895814968DA45F3A82EF6912496F70</t>
+          <t>https://weworkremotely.com/remote-jobs/zenara-health-devops-security-engineer-ai-native-healthcare-saas</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>c46d670134</t>
+          <t>d592e60ddc</t>
         </is>
       </c>
     </row>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data scientist, mumbai (place)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9682,17 +9682,17 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837138848?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=86962F79F06A105F30676367582529277DE10978</t>
+          <t>https://www.adzuna.in/land/ad/5846723381?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F9660467E3895814968DA45F3A82EF6912496F70</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>39dacd7158</t>
+          <t>c46d670134</t>
         </is>
       </c>
     </row>
@@ -9713,12 +9713,12 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Itvedant Education Pvt. Ltd.</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9743,17 +9743,17 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5833434843?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=95E30E442ED8EDC695067D6ACDD8806A1A4DBE0E</t>
+          <t>https://www.adzuna.in/land/ad/5837138848?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=86962F79F06A105F30676367582529277DE10978</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>660701d5cb</t>
+          <t>39dacd7158</t>
         </is>
       </c>
     </row>
@@ -9774,17 +9774,17 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Itvedant Education Pvt. Ltd.</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>engineer, ai, hyderabad (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9804,17 +9804,17 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139103?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=23D035D0F5CFDFF88D2FBA2CB9721442B70F9874</t>
+          <t>https://www.adzuna.in/land/ad/5833434843?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=95E30E442ED8EDC695067D6ACDD8806A1A4DBE0E</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>c2ca14412d</t>
+          <t>660701d5cb</t>
         </is>
       </c>
     </row>
@@ -9835,17 +9835,17 @@
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>engineer, ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9865,17 +9865,17 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773097?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1AD120B3FB3DFBC7F01669BC535E68EC0F2123A3</t>
+          <t>https://www.adzuna.in/land/ad/5837139103?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=23D035D0F5CFDFF88D2FBA2CB9721442B70F9874</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>1a0dea6270</t>
+          <t>c2ca14412d</t>
         </is>
       </c>
     </row>
@@ -9896,17 +9896,17 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>engineer, ai, bangalore (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723241?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0084818D71681FAC4F572D55AE1C6BC637792931</t>
+          <t>https://www.adzuna.in/land/ad/5785773097?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1AD120B3FB3DFBC7F01669BC535E68EC0F2123A3</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>a2c0a3fc16</t>
+          <t>1a0dea6270</t>
         </is>
       </c>
     </row>
@@ -9957,17 +9957,17 @@
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Part time Data Science Instructor</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9977,27 +9977,27 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>engineer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Part time Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5850983469?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0F708DAB080760E3C6FB3FC40EA3A64A7B0306D9</t>
+          <t>https://www.adzuna.in/land/ad/5846723241?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0084818D71681FAC4F572D55AE1C6BC637792931</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>fa169c0060</t>
+          <t>a2c0a3fc16</t>
         </is>
       </c>
     </row>
@@ -10018,12 +10018,12 @@
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer for AI &amp;DS, BSI</t>
+          <t>Part time Data Science Instructor</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -10038,27 +10038,27 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>engineer, ai, india (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Part time Jobs</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785771743?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F6DC64E0C8FB2D27FC25CBE24085394F367A2687</t>
+          <t>https://www.adzuna.in/land/ad/5850983469?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0F708DAB080760E3C6FB3FC40EA3A64A7B0306D9</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>3fd60b2320</t>
+          <t>fa169c0060</t>
         </is>
       </c>
     </row>
@@ -10079,17 +10079,17 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Agentic AI Engineer for AI &amp;DS, BSI</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>engineer, ai, mumbai (place)</t>
+          <t>engineer, ai, india (place)</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773171?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2185A7049B5506DF1182A45172761BBEF73613FA</t>
+          <t>https://www.adzuna.in/land/ad/5785771743?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F6DC64E0C8FB2D27FC25CBE24085394F367A2687</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>43f406da07</t>
+          <t>3fd60b2320</t>
         </is>
       </c>
     </row>
@@ -10140,17 +10140,17 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Data Scientist - People Analytics</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>engineer, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10170,17 +10170,17 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5821999876?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=08993CE6BE520CA2C34926E81E8CBB0072304E1F</t>
+          <t>https://www.adzuna.in/land/ad/5785773171?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2185A7049B5506DF1182A45172761BBEF73613FA</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>187dc9c03e</t>
+          <t>43f406da07</t>
         </is>
       </c>
     </row>
@@ -10201,17 +10201,17 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>Data Scientist - People Analytics</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Itvedant Education Pvt. Ltd.</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10221,27 +10221,27 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Teaching Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5852476426?se=NskdSSae8RGSb8VpDRDiVA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2B7C55A3F795EE4D2F2D732844EDA9B4CAC3F128</t>
+          <t>https://www.adzuna.in/land/ad/5821999876?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=08993CE6BE520CA2C34926E81E8CBB0072304E1F</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>5c41be551e</t>
+          <t>187dc9c03e</t>
         </is>
       </c>
     </row>
@@ -10257,37 +10257,37 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PHP Developer - Work From Home</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CC Staffing International</t>
+          <t>Itvedant Education Pvt. Ltd.</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>developer, software (tag), engineer (tag), backend (tag), php, india (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>PHP-Developer, Backend-Engineer, Web-Development, Software-Developer, Full-Stack-Developer, Remote-PHP-Developer, PHP-Software-Engineer, Backend-PHP-Developer, Remote-Web-Developer, Developer, Mid-level</t>
+          <t>Teaching Jobs</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10297,12 +10297,12 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/cc-staffing-international/jobs/php-developer-work-from-home</t>
+          <t>https://www.adzuna.in/land/ad/5852476426?se=NskdSSae8RGSb8VpDRDiVA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2B7C55A3F795EE4D2F2D732844EDA9B4CAC3F128</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>14b619fb91</t>
+          <t>5c41be551e</t>
         </is>
       </c>
     </row>
@@ -10318,52 +10318,52 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Kannada</t>
+          <t>PHP Developer - Work From Home</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>RWS</t>
+          <t>CC Staffing International</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>ai, delhi (place)</t>
+          <t>developer, software (tag), engineer (tag), backend (tag), php, india (place)</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>PHP-Developer, Backend-Engineer, Web-Development, Software-Developer, Full-Stack-Developer, Remote-PHP-Developer, PHP-Software-Engineer, Backend-PHP-Developer, Remote-Web-Developer, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772642?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=96F9E6C80B83A39F4F2C05268274FD2EBE13B037</t>
+          <t>https://himalayas.app/companies/cc-staffing-international/jobs/php-developer-work-from-home</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>bb43fd7b08</t>
+          <t>14b619fb91</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Marathi</t>
+          <t>AI Data Specialist - Kannada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772098?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=B26B7FB6A299BC3A2BFD29BF94BF59C981A24A29</t>
+          <t>https://www.adzuna.in/land/ad/5785772642?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=96F9E6C80B83A39F4F2C05268274FD2EBE13B037</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>fe688433d1</t>
+          <t>bb43fd7b08</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10445,7 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Telugu</t>
+          <t>AI Data Specialist - Marathi</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -10480,12 +10480,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785770664?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=D13E17364CDB48C8A2B963F62AC42C33A76C021B</t>
+          <t>https://www.adzuna.in/land/ad/5785772098?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=B26B7FB6A299BC3A2BFD29BF94BF59C981A24A29</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>91c279dfff</t>
+          <t>fe688433d1</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Hindi</t>
+          <t>AI Data Specialist - Telugu</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10536,17 +10536,17 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5795883387?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=38289BC2F5CA723017CE2916CC4536DEA978B9A6</t>
+          <t>https://www.adzuna.in/land/ad/5785770664?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=D13E17364CDB48C8A2B963F62AC42C33A76C021B</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>170ea3eac1</t>
+          <t>91c279dfff</t>
         </is>
       </c>
     </row>
@@ -10567,7 +10567,7 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Tamil</t>
+          <t>AI Data Specialist - Hindi</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10597,17 +10597,17 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772320?se=xp3UHeGd8RGIEJB03vDchg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AB56F1DD143407CEE31E12C4126DC533B06A2AD3</t>
+          <t>https://www.adzuna.in/land/ad/5795883387?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=38289BC2F5CA723017CE2916CC4536DEA978B9A6</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>616fb76ab0</t>
+          <t>170ea3eac1</t>
         </is>
       </c>
     </row>
@@ -10623,52 +10623,52 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Agent Operations Engineer - Fully Remote | Upto $500/task Task based</t>
+          <t>AI Data Specialist - Tamil</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>RWS</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>New Delhi, Delhi</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>engineer, ai (tag), india (place)</t>
+          <t>ai, delhi (place)</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Agent-Engineering, LLMOperations, AI-Engineering, AI-Operations, Machine-Learning-Engineering, AgentOps-Engineer, Agent-Orchestration-Engineer, AI-Agents-Engineer, Operations-Engineer, Remote-AI-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/mercor/jobs/agent-operations-engineer-fully-remote-upto-500-task-task-based</t>
+          <t>https://www.adzuna.in/land/ad/5785772320?se=xp3UHeGd8RGIEJB03vDchg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AB56F1DD143407CEE31E12C4126DC533B06A2AD3</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>be05dc52ff</t>
+          <t>616fb76ab0</t>
         </is>
       </c>
     </row>
@@ -10684,17 +10684,17 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS Authorized Instructor</t>
+          <t>Agent Operations Engineer - Fully Remote | Upto $500/task Task based</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ITC WORLDWIDE</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>cloud (tag), aws, india (place)</t>
+          <t>engineer, ai (tag), india (place)</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>AWS-Training, Cloud-Computing-Instructor, Technical-Trainer, AWS-Authorized-Instructor, Cloud-Education, AWS-Certification-Training, Cloud-Instructor, Cloud-Computing-Trainer, Senior</t>
+          <t>Agent-Engineering, LLMOperations, AI-Engineering, AI-Operations, Machine-Learning-Engineering, AgentOps-Engineer, Agent-Orchestration-Engineer, AI-Agents-Engineer, Operations-Engineer, Remote-AI-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10724,12 +10724,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/itc-worldwide/jobs/aws-authorized-instructor</t>
+          <t>https://himalayas.app/companies/mercor/jobs/agent-operations-engineer-fully-remote-upto-500-task-task-based</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>a42ddc7b02</t>
+          <t>be05dc52ff</t>
         </is>
       </c>
     </row>
@@ -10745,37 +10745,37 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Associate Instructor</t>
+          <t>AWS Authorized Instructor</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>ITC WORLDWIDE</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>devops (tag), associate (level), anywhere (place)</t>
+          <t>cloud (tag), aws, india (place)</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>AWS-Training, Cloud-Computing-Instructor, Technical-Trainer, AWS-Authorized-Instructor, Cloud-Education, AWS-Certification-Training, Cloud-Instructor, Cloud-Computing-Trainer, Senior</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10785,12 +10785,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/beyondtrust-associate-instructor</t>
+          <t>https://himalayas.app/companies/itc-worldwide/jobs/aws-authorized-instructor</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>4c1963b96c</t>
+          <t>a42ddc7b02</t>
         </is>
       </c>
     </row>
@@ -10806,52 +10806,52 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>E-learning Developer</t>
+          <t>Associate Instructor</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Crowe UAE</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>developer, ahmedabad (place)</t>
+          <t>devops (tag), associate (level), anywhere (place)</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5850983902?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F927DE790D9874EE6BA8C142D15CF3A7A97BFA7E</t>
+          <t>https://weworkremotely.com/remote-jobs/beyondtrust-associate-instructor</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>843701dc9e</t>
+          <t>4c1963b96c</t>
         </is>
       </c>
     </row>
@@ -10867,52 +10867,52 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Developer Educator</t>
+          <t>E-learning Developer</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>PlanetScale</t>
+          <t>Crowe UAE</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Ahmedabad, Gujarat</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>developer, anywhere (place)</t>
+          <t>developer, ahmedabad (place)</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/planetscale-developer-educator</t>
+          <t>https://www.adzuna.in/land/ad/5850983902?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F927DE790D9874EE6BA8C142D15CF3A7A97BFA7E</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>c72ab4031d</t>
+          <t>843701dc9e</t>
         </is>
       </c>
     </row>
@@ -10928,50 +10928,111 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
+          <t>Developer Educator</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>PlanetScale</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Anywhere in the World</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>weworkremotely</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>developer, anywhere (place)</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Sales and Marketing, Full-Time</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/planetscale-developer-educator</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>c72ab4031d</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>11</v>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
           <t>Consultant Implementation Engineer</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Harbor</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="H173" t="inlineStr">
         <is>
           <t>remoteok</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I173" t="inlineStr">
         <is>
           <t>engineer, golang (tag), remote (place)</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
+      <c r="J173" t="inlineStr">
         <is>
           <t>consulting, technical, accounting, legal, golang, engineer</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="K173" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-consultant-implementation-engineer-harbor-1136987</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t>f724e65bc8</t>
         </is>
@@ -10979,7 +11040,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A172" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of: new, applied, skipped" prompt="Mark this job applied once you have applied." type="list">
+    <dataValidation sqref="A2:A173" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of: new, applied, skipped" prompt="Mark this job applied once you have applied." type="list">
       <formula1>"new,applied,skipped"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M177"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -506,21 +506,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlys</t>
+          <t>Quest Global Technologies</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -530,32 +532,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>artificial intelligence, intern (level), india (place)</t>
+          <t>fullstack (tag), developer, backend (tag), react (tag), php (tag), india (place)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Laravel-Development, PHP-Development, Backend-Development, Fullstack-Development, Web-Development, Laravel-Developer, Laravel, Mid-Level-Laravel-React-Developer, Laravel-Full-Stack-Development, Laravel-Entwicklung, PHP-Developer, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876870198?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=887C5853FA1B767B096C42327F5C3826C21742CE</t>
+          <t>https://himalayas.app/companies/quest-global-technologies/jobs/laravel-developer-6713783437</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>b169bf4100</t>
+          <t>a772f50cb9</t>
         </is>
       </c>
     </row>
@@ -571,22 +573,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MTS-1 Machine Learning Engineer</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Atlys</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -596,7 +598,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>artificial intelligence, intern (level), india (place)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -611,12 +613,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877184305?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8749753C0B487764A74F37A03D96F548F15161A9</t>
+          <t>https://www.adzuna.in/land/ad/5876870198?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=887C5853FA1B767B096C42327F5C3826C21742CE</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>fab40e54d1</t>
+          <t>b169bf4100</t>
         </is>
       </c>
     </row>
@@ -632,52 +634,52 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MTS-1 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smartcuts</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), frontend (tag), worldwide (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Engineering, Software-Engineer, Frontend-Development, Fullstack-Development, Browser-Extension-Development, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Software-Design-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/smartcuts/jobs/software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5877184305?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8749753C0B487764A74F37A03D96F548F15161A9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1191a23402</t>
+          <t>fab40e54d1</t>
         </is>
       </c>
     </row>
@@ -693,17 +695,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GitHub Contributor</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Smartcuts</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -718,12 +720,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), frontend (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
+          <t>Engineering, Software-Engineer, Frontend-Development, Fullstack-Development, Browser-Extension-Development, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Software-Design-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -733,12 +735,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-106728860</t>
+          <t>https://himalayas.app/companies/smartcuts/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>f02b389972</t>
+          <t>1191a23402</t>
         </is>
       </c>
     </row>
@@ -750,58 +752,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Backend Engineer, IAM</t>
+          <t>GitHub Contributor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>engineer, backend, anywhere (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/reddit-backend-engineer-iam</t>
+          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-106728860</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>790d0d9505</t>
+          <t>f02b389972</t>
         </is>
       </c>
     </row>
@@ -820,16 +820,16 @@
         <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Developer Advocate - Service Management</t>
+          <t>Backend Engineer, IAM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>developer, devops (tag), anywhere (place)</t>
+          <t>engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/datadog-developer-advocate-service-management</t>
+          <t>https://weworkremotely.com/remote-jobs/reddit-backend-engineer-iam</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>4df8de53d8</t>
+          <t>790d0d9505</t>
         </is>
       </c>
     </row>
@@ -880,37 +880,39 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>QA Testers Wanted (No experience needed)</t>
+          <t>Developer Advocate - Service Management</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tester Work</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Australia &amp; New Zealand (REMOTE)</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>qa, remote (place)</t>
+          <t>developer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -920,12 +922,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1860630/</t>
+          <t>https://weworkremotely.com/remote-jobs/datadog-developer-advocate-service-management</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>bf909f7a1f</t>
+          <t>4df8de53d8</t>
         </is>
       </c>
     </row>
@@ -937,58 +939,56 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>74</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist II, ML Infrastructure</t>
+          <t>QA Testers Wanted (No experience needed)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Tester Work</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Australia &amp; New Zealand (REMOTE)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data scientist, ml, anywhere (place)</t>
+          <t>qa, remote (place)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-ml-infrastructure</t>
+          <t>https://www.workingnomads.com/job/go/1860630/</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>a84319c791</t>
+          <t>bf909f7a1f</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,14 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist II, Infrastructure</t>
+          <t>Data Scientist II, ML Infrastructure</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1029,7 +1031,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data scientist, anywhere (place)</t>
+          <t>data scientist, ml, anywhere (place)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1044,12 +1046,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-infrastructure</t>
+          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-ml-infrastructure</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>def323e358</t>
+          <t>a84319c791</t>
         </is>
       </c>
     </row>
@@ -1065,52 +1067,52 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II, Infrastructure</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>software engineer, golang (tag)</t>
+          <t>data scientist, anywhere (place)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>golang, dev, engineer, digital nomad</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-mirantis-1137387</t>
+          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-infrastructure</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0eb27a0401</t>
+          <t>def323e358</t>
         </is>
       </c>
     </row>
@@ -1122,41 +1124,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Science Engineer - AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data science, engineer, ai, bangalore (place)</t>
+          <t>software engineer, golang (tag)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>golang, dev, engineer, digital nomad</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1166,12 +1168,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880523483?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44AFB881700BC2524FE70C04638A2D65741F5C06</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-mirantis-1137387</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>987c89c61a</t>
+          <t>0eb27a0401</t>
         </is>
       </c>
     </row>
@@ -1187,22 +1189,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning</t>
+          <t>Data Science Engineer - AI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kotak Neo</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1212,7 +1214,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>machine learning, ai, mumbai (place)</t>
+          <t>data science, engineer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1227,12 +1229,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880062262?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC74E214D0612FE80831EDD83B8CF67B6032A3E9</t>
+          <t>https://www.adzuna.in/land/ad/5880523483?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44AFB881700BC2524FE70C04638A2D65741F5C06</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>c8b4bb4ba3</t>
+          <t>987c89c61a</t>
         </is>
       </c>
     </row>
@@ -1248,37 +1250,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>AI &amp; Machine Learning</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Kotak Neo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>software (tag), engineer, ai (tag), ml, worldwide (place)</t>
+          <t>machine learning, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Machine-Learning-Engineer, AI-ML-Engineer, ML-Software-Engineer, ML-Research-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1288,12 +1290,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ml-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5880062262?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC74E214D0612FE80831EDD83B8CF67B6032A3E9</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6b92e0e58d</t>
+          <t>c8b4bb4ba3</t>
         </is>
       </c>
     </row>
@@ -1314,47 +1316,47 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data science, india (place), chandigarh (place)</t>
+          <t>software (tag), engineer, ai (tag), ml, worldwide (place)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Machine-Learning-Engineer, AI-ML-Engineer, ML-Software-Engineer, ML-Research-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5879662958?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7C90B2BB52AA81EB60C613281A1D6AF4E5DC8BD8</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ml-engineer</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6557a8e75a</t>
+          <t>6b92e0e58d</t>
         </is>
       </c>
     </row>
@@ -1370,54 +1372,52 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PhD &amp; Academic Expert</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ml (tag), worldwide (place)</t>
+          <t>data science, india (place), chandigarh (place)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Academic-Expert, PhD-Specialist-Consultant, Academic-Consultant, Academic-Subject-Matter-Expert, Academic-Professional, ML-Research-PhD-Expert, PhD-Researcher, Education-Expert, Mid-level, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/phd-academic-expert</t>
+          <t>https://www.adzuna.in/land/ad/5879662958?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7C90B2BB52AA81EB60C613281A1D6AF4E5DC8BD8</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>a8281d77e1</t>
+          <t>6557a8e75a</t>
         </is>
       </c>
     </row>
@@ -1429,23 +1429,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>PhD &amp; Academic Expert</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dura Digital</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1460,27 +1460,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>engineer, backend (tag), python (tag), ai, ml (tag), worldwide (place)</t>
+          <t>ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>AI-Engineer, Machine-Learning-Engineer, Backend-Engineer, Data-Engineer, MLOps-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Senior</t>
+          <t>Academic-Expert, PhD-Specialist-Consultant, Academic-Consultant, Academic-Subject-Matter-Expert, Academic-Professional, ML-Research-PhD-Expert, PhD-Researcher, Education-Expert, Mid-level, Senior</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/dura-digital/jobs/ai-engineer</t>
+          <t>https://himalayas.app/companies/micro1/jobs/phd-academic-expert</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>8666ff7b1c</t>
+          <t>a8281d77e1</t>
         </is>
       </c>
     </row>
@@ -1496,17 +1496,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Facial Data Collection Associate</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Dura Digital</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1521,12 +1523,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ai, associate (level), worldwide (place)</t>
+          <t>engineer, backend (tag), python (tag), ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AI-Data-Collection-Specialist, Data-Collection-Associate, Facial-Recognition-Data-Collection, AI-Services-Associate, AI-Operations-Associate, AI-Associate, Entry-level</t>
+          <t>AI-Engineer, Machine-Learning-Engineer, Backend-Engineer, Data-Engineer, MLOps-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Senior</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1536,12 +1538,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-facial-data-collection-associate</t>
+          <t>https://himalayas.app/companies/dura-digital/jobs/ai-engineer</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>a024718d12</t>
+          <t>8666ff7b1c</t>
         </is>
       </c>
     </row>
@@ -1557,54 +1559,52 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>49</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Facial Data Collection Associate</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Omnicom Global Solutions</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>ai, associate (level), worldwide (place)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Data-Collection-Specialist, Data-Collection-Associate, Facial-Recognition-Data-Collection, AI-Services-Associate, AI-Operations-Associate, AI-Associate, Entry-level</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880062427?se=4EjJjS6u8RGGGqTWwpKkng&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E0A2211C95EBCFB9C1236FB6E39F7FBF4A7836A8</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-facial-data-collection-associate</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>c539f926b2</t>
+          <t>a024718d12</t>
         </is>
       </c>
     </row>
@@ -1620,54 +1620,54 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Financial Systems Expert</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Omnicom Global Solutions</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>developer (tag), engineer (tag), worldwide (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Financial-Systems-Specialist, Financial-Systems-Consultant, Financial-Systems-Advisor, Finance-Systems-Specialist, Financial-Systems-Consulting, Finance-Systems-Consultant, Financial-Systems-Developer, Financial-Systems-Integration-Specialist, Financial-Systems-Architect, Financial-Systems-Engineer, Mid-level, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/financial-systems-expert</t>
+          <t>https://www.adzuna.in/land/ad/5880062427?se=4EjJjS6u8RGGGqTWwpKkng&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E0A2211C95EBCFB9C1236FB6E39F7FBF4A7836A8</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>a8090f5869</t>
+          <t>c539f926b2</t>
         </is>
       </c>
     </row>
@@ -1679,56 +1679,58 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>79</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>DVP - Data Science AI</t>
+          <t>Financial Systems Expert</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IndiaFirst Life</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data science, ai, mumbai (place)</t>
+          <t>developer (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Financial-Systems-Specialist, Financial-Systems-Consultant, Financial-Systems-Advisor, Finance-Systems-Specialist, Financial-Systems-Consulting, Finance-Systems-Consultant, Financial-Systems-Developer, Financial-Systems-Integration-Specialist, Financial-Systems-Architect, Financial-Systems-Engineer, Mid-level, Senior</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877452336?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C389ADE3462A8F960BCEB9BFB3D8C01182D8F284</t>
+          <t>https://himalayas.app/companies/micro1/jobs/financial-systems-expert</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>d4091e9b06</t>
+          <t>a8090f5869</t>
         </is>
       </c>
     </row>
@@ -1744,22 +1746,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DVP - Data Science AI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ryewalk</t>
+          <t>IndiaFirst Life</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1769,7 +1771,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data scientist, chennai (place)</t>
+          <t>data science, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1784,12 +1786,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877457613?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=858E7DDB9C73029BB012BE9266CDC5516D57BB06</t>
+          <t>https://www.adzuna.in/land/ad/5877452336?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C389ADE3462A8F960BCEB9BFB3D8C01182D8F284</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>5b1e04fbec</t>
+          <t>d4091e9b06</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1817,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Ryewalk</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1840,17 +1842,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876016078?se=tjzQcmWt8RGk7Nm076a3Fw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=076A6D8BF6D1FAB77910335EA1D3406F73F06FDC</t>
+          <t>https://www.adzuna.in/land/ad/5877457613?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=858E7DDB9C73029BB012BE9266CDC5516D57BB06</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>03602a7f75</t>
+          <t>5b1e04fbec</t>
         </is>
       </c>
     </row>
@@ -1866,52 +1868,52 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>QA Tester Entry Level</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ace IT Careers</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>testing (tag), qa, entry level (level), remote (place)</t>
+          <t>data scientist, chennai (place)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>testing, dev, analyst, quality assurance, digital nomad</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-qa-tester-entry-level-ace-it-careers-1136701</t>
+          <t>https://www.adzuna.in/land/ad/5876016078?se=tjzQcmWt8RGk7Nm076a3Fw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=076A6D8BF6D1FAB77910335EA1D3406F73F06FDC</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>066819b5ee</t>
+          <t>03602a7f75</t>
         </is>
       </c>
     </row>
@@ -1927,54 +1929,52 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>32</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>QA Tester Entry Level</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sun King</t>
+          <t>Ace IT Careers</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>software (tag), engineer, cloud (tag), api (tag), india (place)</t>
+          <t>testing (tag), qa, entry level (level), remote (place)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Application-Security-Engineer, Security-Engineer, Penetration-Tester, API-Security, Cloud-Security-Engineer, AppSec-Engineer, Application-Security-Engineering, Application-Security-Specialist, Software-Security-Engineer, Mid-level</t>
+          <t>testing, dev, analyst, quality assurance, digital nomad</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/sun-king/jobs/application-security-engineer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-qa-tester-entry-level-ace-it-careers-1136701</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>41b24c0687</t>
+          <t>066819b5ee</t>
         </is>
       </c>
     </row>
@@ -1992,15 +1992,17 @@
       <c r="C26" t="n">
         <v>32</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nuclear Physics Specialist - Fully Remote | Upto $100/hr</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>Sun King</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2015,12 +2017,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>engineer (tag), ai (tag), india (place)</t>
+          <t>software (tag), engineer, cloud (tag), api (tag), india (place)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Computational-Physics, Nuclear-Physics, Particle-Physics, AI-Evaluation, Scientific-Computing, Nuclear-Physics-AI-Specialist, Freelance-Physics-Specialist, Reactor-Physics-Engineer, Freelance-Physics-Expert, Physics-Research-Specialist, Physics-Freelancer, Mid-level</t>
+          <t>Application-Security-Engineer, Security-Engineer, Penetration-Tester, API-Security, Cloud-Security-Engineer, AppSec-Engineer, Application-Security-Engineering, Application-Security-Specialist, Software-Security-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2030,12 +2032,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/mercor/jobs/nuclear-physics-specialist-fully-remote-upto-100-hr-6652317191</t>
+          <t>https://himalayas.app/companies/sun-king/jobs/application-security-engineer</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>e80acb6174</t>
+          <t>41b24c0687</t>
         </is>
       </c>
     </row>
@@ -2047,58 +2049,56 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>65</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Nuclear Physics Specialist - Fully Remote | Upto $100/hr</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dynamics Monk Consulting Services</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>artificial intelligence, india (place), delhi (place)</t>
+          <t>engineer (tag), ai (tag), india (place)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Computational-Physics, Nuclear-Physics, Particle-Physics, AI-Evaluation, Scientific-Computing, Nuclear-Physics-AI-Specialist, Freelance-Physics-Specialist, Reactor-Physics-Engineer, Freelance-Physics-Expert, Physics-Research-Specialist, Physics-Freelancer, Mid-level</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028069?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F290F3C8F39D5ABB349E29F918917B30A38BA853</t>
+          <t>https://himalayas.app/companies/mercor/jobs/nuclear-physics-specialist-fully-remote-upto-100-hr-6652317191</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9010d87d61</t>
+          <t>e80acb6174</t>
         </is>
       </c>
     </row>
@@ -2114,22 +2114,24 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>54</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vahan.ai</t>
+          <t>Dynamics Monk Consulting Services</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2139,7 +2141,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, india (place), delhi (place)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2154,12 +2156,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876029045?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1440DAC38EB3556F9000947FA0A0834CFF14AB75</t>
+          <t>https://www.adzuna.in/land/ad/5876028069?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F290F3C8F39D5ABB349E29F918917B30A38BA853</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>56f72b7a03</t>
+          <t>9010d87d61</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2187,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EYEGLOBAL SOLUTIONS PVT. LTD.</t>
+          <t>Vahan.ai</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2200,7 +2202,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, chennai (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2215,12 +2217,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028703?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9D6C280D30C30F591E884FDA2F691CC4409C3EC6</t>
+          <t>https://www.adzuna.in/land/ad/5876029045?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1440DAC38EB3556F9000947FA0A0834CFF14AB75</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>bafec6742f</t>
+          <t>56f72b7a03</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2248,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Appglide Solutions</t>
+          <t>EYEGLOBAL SOLUTIONS PVT. LTD.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2276,12 +2278,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876870603?se=DiEjalis8RGQ-MmLyhoJEg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=987B153BD1BD745987463A7F926C3F0CC163AE60</t>
+          <t>https://www.adzuna.in/land/ad/5876028703?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9D6C280D30C30F591E884FDA2F691CC4409C3EC6</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>d4bbc378a8</t>
+          <t>bafec6742f</t>
         </is>
       </c>
     </row>
@@ -2302,17 +2304,17 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MTS-2 Machine Learning Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Appglide Solutions</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2322,7 +2324,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, chennai (place)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2337,12 +2339,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877184044?se=ME0PiYGs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=DBDB737DEAF34AD8D344749E581C417C10EC5A31</t>
+          <t>https://www.adzuna.in/land/ad/5876870603?se=DiEjalis8RGQ-MmLyhoJEg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=987B153BD1BD745987463A7F926C3F0CC163AE60</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>37872b8c00</t>
+          <t>d4bbc378a8</t>
         </is>
       </c>
     </row>
@@ -2358,37 +2360,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Account Executive, AI/HPC, Neo / Sovereign Cloud (EMEA)</t>
+          <t>MTS-2 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Everpure</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>cloud, ai, anywhere (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2398,12 +2400,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/everpure-account-executive-ai-hpc-neo-sovereign-cloud-emea</t>
+          <t>https://www.adzuna.in/land/ad/5877184044?se=ME0PiYGs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=DBDB737DEAF34AD8D344749E581C417C10EC5A31</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>44fbf0ebf8</t>
+          <t>37872b8c00</t>
         </is>
       </c>
     </row>
@@ -2419,39 +2421,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>49</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Account Executive, AI/HPC, Neo / Sovereign Cloud (EMEA)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Infosys Finacle</t>
+          <t>Everpure</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>cloud, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Sales and Marketing, Full-Time</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876010793?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8D81876C99F248DACDDC8104E41D7CB59A09112B</t>
+          <t>https://weworkremotely.com/remote-jobs/everpure-account-executive-ai-hpc-neo-sovereign-cloud-emea</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>68b1b69943</t>
+          <t>44fbf0ebf8</t>
         </is>
       </c>
     </row>
@@ -2482,37 +2482,39 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>47</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Frontend Developer - Talent Pool</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Espeo Software</t>
+          <t>Infosys Finacle</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>developer, frontend, software (tag), engineer (tag), react (tag), worldwide (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Frontend-Development, Web-Development, Software-Development, ContractWorks, Freelance-Development, Frontend-Development-Jobs, Tech-Talent-Pool, Front-End-Developer, Technology-Talent-Pool, Engineering-Talent-Pool, Frontend-React-Developer, React-Frontend-Developer, Frontend-Engineer, Developer, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2522,12 +2524,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/espeo-software/jobs/frontend-developer-talent-pool</t>
+          <t>https://www.adzuna.in/land/ad/5876010793?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8D81876C99F248DACDDC8104E41D7CB59A09112B</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>409bd93507</t>
+          <t>68b1b69943</t>
         </is>
       </c>
     </row>
@@ -2543,17 +2545,17 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe AEP)</t>
+          <t>Frontend Developer - Talent Pool</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TechBiz Global</t>
+          <t>Espeo Software</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2568,12 +2570,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data engineer, developer (tag), cloud (tag), worldwide (place)</t>
+          <t>developer, frontend, software (tag), engineer (tag), react (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Data-Engineering, ETL-Development, Cloud-Data-Engineering, Adobe-Experience-Platform, Data-Integration, Adobe-CDP-Engineer, Data-Engineer, Adobe-Experience-Platform-Engineer, Data-Engineer-Jobs, Data-Platform-Engineer, Enterprise-Data-Engineer, Developer, Senior</t>
+          <t>Frontend-Development, Web-Development, Software-Development, ContractWorks, Freelance-Development, Frontend-Development-Jobs, Tech-Talent-Pool, Front-End-Developer, Technology-Talent-Pool, Engineering-Talent-Pool, Frontend-React-Developer, React-Frontend-Developer, Frontend-Engineer, Developer, Senior</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2583,12 +2585,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/techbiz-global/jobs/data-engineer-adobe-aep-7933835037</t>
+          <t>https://himalayas.app/companies/espeo-software/jobs/frontend-developer-talent-pool</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3cf5fcdc34</t>
+          <t>409bd93507</t>
         </is>
       </c>
     </row>
@@ -2604,52 +2606,52 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Social Comms</t>
+          <t>Data Engineer (Adobe AEP)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NOPE</t>
+          <t>TechBiz Global</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ai (tag)</t>
+          <t>data engineer, developer (tag), cloud (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>marketing, education, technical, content writing, social media, ai, social</t>
+          <t>Data-Engineering, ETL-Development, Cloud-Data-Engineering, Adobe-Experience-Platform, Data-Integration, Adobe-CDP-Engineer, Data-Engineer, Adobe-Experience-Platform-Engineer, Data-Engineer-Jobs, Data-Platform-Engineer, Enterprise-Data-Engineer, Developer, Senior</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-social-comms-nope-1137314</t>
+          <t>https://himalayas.app/companies/techbiz-global/jobs/data-engineer-adobe-aep-7933835037</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>417f6ff5ea</t>
+          <t>3cf5fcdc34</t>
         </is>
       </c>
     </row>
@@ -2661,56 +2663,56 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Social Comms</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>NOPE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>ai (tag)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>marketing, education, technical, content writing, social media, ai, social</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876024927?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0BB3A9B6F76E859DE51E5C2F0066293EDC5FE6EA</t>
+          <t>https://remoteOK.com/remote-jobs/remote-social-comms-nope-1137314</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0851d46422</t>
+          <t>417f6ff5ea</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2738,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Questhiring</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2751,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2766,12 +2768,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876027895?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=09A0BE7549E8D3105D5BC0AA92FAA0662C7CD065</t>
+          <t>https://www.adzuna.in/land/ad/5876024927?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0BB3A9B6F76E859DE51E5C2F0066293EDC5FE6EA</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>8a025ec1ce</t>
+          <t>0851d46422</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2799,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TBO.COM</t>
+          <t>Questhiring</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2817,7 +2819,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2827,12 +2829,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026044?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FDDB74C699BD4423DAD1E4FB7120816040F747A</t>
+          <t>https://www.adzuna.in/land/ad/5876027895?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=09A0BE7549E8D3105D5BC0AA92FAA0662C7CD065</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>a427b9cd23</t>
+          <t>8a025ec1ce</t>
         </is>
       </c>
     </row>
@@ -2858,12 +2860,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ADB SAFEGATE</t>
+          <t>TBO.COM</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2873,12 +2875,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, hyderabad (place)</t>
+          <t>artificial intelligence, engineer, india (place)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2888,12 +2890,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026294?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9C70BDA29FFF510B21324AF211D635A868DC48AA</t>
+          <t>https://www.adzuna.in/land/ad/5876026044?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FDDB74C699BD4423DAD1E4FB7120816040F747A</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>292ee6d2c1</t>
+          <t>a427b9cd23</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2921,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Neural Foundry</t>
+          <t>ADB SAFEGATE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2949,12 +2951,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026040?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8CA62DE6EFC7E6B952E843BFE686F26AF0E83028</t>
+          <t>https://www.adzuna.in/land/ad/5876026294?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9C70BDA29FFF510B21324AF211D635A868DC48AA</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>c1e16bca2e</t>
+          <t>292ee6d2c1</t>
         </is>
       </c>
     </row>
@@ -2980,12 +2982,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DotKonnekt</t>
+          <t>Neural Foundry</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2995,7 +2997,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, hyderabad (place)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3010,12 +3012,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026944?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=51439456D8BA015D122C9B9E72B93BC7715ADC62</t>
+          <t>https://www.adzuna.in/land/ad/5876026040?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8CA62DE6EFC7E6B952E843BFE686F26AF0E83028</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>172ee82bd6</t>
+          <t>c1e16bca2e</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3043,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Recro</t>
+          <t>DotKonnekt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3056,7 +3058,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3071,12 +3073,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876027463?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=40F66C80D240EB217C5AF3C758F1793D002D574F</t>
+          <t>https://www.adzuna.in/land/ad/5876026944?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=51439456D8BA015D122C9B9E72B93BC7715ADC62</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>91af896417</t>
+          <t>172ee82bd6</t>
         </is>
       </c>
     </row>
@@ -3097,17 +3099,17 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer 2</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Frinks AI</t>
+          <t>Recro</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3117,7 +3119,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, india (place)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3132,12 +3134,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876025062?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=75AA49B421B5A4EB6F3C207636FED47095B332D0</t>
+          <t>https://www.adzuna.in/land/ad/5876027463?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=40F66C80D240EB217C5AF3C758F1793D002D574F</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2d2a6d873d</t>
+          <t>91af896417</t>
         </is>
       </c>
     </row>
@@ -3153,22 +3155,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Specialist</t>
+          <t>Artificial Intelligence Engineer 2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ITC Infotech</t>
+          <t>Frinks AI</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3178,7 +3180,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>artificial intelligence, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3193,12 +3195,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876024946?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=6D480BEF34A3386CBC920920C7CE13B96BCBAD34</t>
+          <t>https://www.adzuna.in/land/ad/5876025062?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=75AA49B421B5A4EB6F3C207636FED47095B332D0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>140496e40b</t>
+          <t>2d2a6d873d</t>
         </is>
       </c>
     </row>
@@ -3219,17 +3221,17 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Artificial Intelligence Specialist</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tech Mahindra</t>
+          <t>ITC Infotech</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3239,7 +3241,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>artificial intelligence, bangalore (place)</t>
+          <t>artificial intelligence, india (place)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3254,12 +3256,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026586?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=666546215EA3297D7CF61A793A40232CBB0EC67B</t>
+          <t>https://www.adzuna.in/land/ad/5876024946?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=6D480BEF34A3386CBC920920C7CE13B96BCBAD34</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>25604d55ae</t>
+          <t>140496e40b</t>
         </is>
       </c>
     </row>
@@ -3275,22 +3277,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Data and AI Scientist</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>The Edge Partnership - The Edge in Asia</t>
+          <t>Tech Mahindra</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3300,7 +3302,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ai, hyderabad (place)</t>
+          <t>artificial intelligence, bangalore (place)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3315,12 +3317,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876025532?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AD1D30D29AD931A0AA847E54CFF303EEB0007BE9</t>
+          <t>https://www.adzuna.in/land/ad/5876026586?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=666546215EA3297D7CF61A793A40232CBB0EC67B</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>bc9357c4ff</t>
+          <t>25604d55ae</t>
         </is>
       </c>
     </row>
@@ -3336,52 +3338,52 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AI Response Evaluator</t>
+          <t>Data and AI Scientist</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>iMerit</t>
+          <t>The Edge Partnership - The Edge in Asia</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>All Other Remote, Contract</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/imerit-ai-response-evaluator</t>
+          <t>https://www.adzuna.in/land/ad/5876025532?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AD1D30D29AD931A0AA847E54CFF303EEB0007BE9</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>d4b5bc7818</t>
+          <t>bc9357c4ff</t>
         </is>
       </c>
     </row>
@@ -3397,37 +3399,37 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sustainability Full-Stack Developer (100 % remote) (m/f/d)</t>
+          <t>AI Response Evaluator</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>EWOR GmbH</t>
+          <t>iMerit</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>fullstack (tag), developer, software (tag), engineer (tag), worldwide (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Fullstack-Development, Web-Development, Sustainability, Software-Engineer, Sustainability-Technology, Remote-Senior-Full-Stack-Developer, Remote-Full-Stack-Developer, Full-Stack-Developer, Senior</t>
+          <t>All Other Remote, Contract</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3437,12 +3439,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ewor-gmbh/jobs/sustainability-full-stack-developer-100-remote-m-f-d</t>
+          <t>https://weworkremotely.com/remote-jobs/imerit-ai-response-evaluator</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>7da6fdc2ab</t>
+          <t>d4b5bc7818</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3460,12 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Industrial Tech AgentOps Engineer (100 % remote) (m/f/d)</t>
+          <t>Sustainability Full-Stack Developer (100 % remote) (m/f/d)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3483,12 +3485,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>engineer, devops (tag), worldwide (place)</t>
+          <t>fullstack (tag), developer, software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>AgentOps-Engineer, Industrial-Technology, Operations-Engineering, Technical-Product-Management, Start-Up-Operations, Remote-Operations-Engineer, Industrial-IoT-Engineer, Remote-DevOps-Engineer, TechOps-Engineer, Remote-Infrastructure-Monitoring-Engineer, Remote-Distributed-Systems-Engineer-II, Mid-level</t>
+          <t>Fullstack-Development, Web-Development, Sustainability, Software-Engineer, Sustainability-Technology, Remote-Senior-Full-Stack-Developer, Remote-Full-Stack-Developer, Full-Stack-Developer, Senior</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3498,12 +3500,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ewor-gmbh/jobs/industrial-tech-agentops-engineer-100-remote-m-f-d</t>
+          <t>https://himalayas.app/companies/ewor-gmbh/jobs/sustainability-full-stack-developer-100-remote-m-f-d</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>cedc8889fb</t>
+          <t>7da6fdc2ab</t>
         </is>
       </c>
     </row>
@@ -3515,56 +3517,56 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AI Response Analyst</t>
+          <t>Industrial Tech AgentOps Engineer (100 % remote) (m/f/d)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>iMerit Technology</t>
+          <t>EWOR GmbH</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>engineer, devops (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>content writing, quality assurance, ai</t>
+          <t>AgentOps-Engineer, Industrial-Technology, Operations-Engineering, Technical-Product-Management, Start-Up-Operations, Remote-Operations-Engineer, Industrial-IoT-Engineer, Remote-DevOps-Engineer, TechOps-Engineer, Remote-Infrastructure-Monitoring-Engineer, Remote-Distributed-Systems-Engineer-II, Mid-level</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-ai-response-analyst-imerit-technology-1137309</t>
+          <t>https://himalayas.app/companies/ewor-gmbh/jobs/industrial-tech-agentops-engineer-100-remote-m-f-d</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>05cb840193</t>
+          <t>cedc8889fb</t>
         </is>
       </c>
     </row>
@@ -3576,58 +3578,56 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>30</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AI Response Analyst</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>iMerit Technology</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>content writing, quality assurance, ai</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="C52" t="n">
-        <v>57</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Python Backend Engineer (m/f/x)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Makersite</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Worldwide</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>himalayas</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>developer (tag), software (tag), engineer, backend, python, api (tag), worldwide (place)</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Python-Backend-Engineering, Backend-Development, Software-Engineer, API-Development, Python-Engineering, Python-Backend-Engineer, Python-Backend-Developer, Senior-Backend-Python-Developer, Senior-Python-Backend-Developer, Backend-Engineer, Product-Backend-Engineer, Backend-Services-Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/makersite/jobs/python-backend-engineer-m-f-x</t>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-response-analyst-imerit-technology-1137309</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>3eb1e889db</t>
+          <t>05cb840193</t>
         </is>
       </c>
     </row>
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Python Backend Engineer (m/f/x)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>S-PRO</t>
+          <t>Makersite</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3670,12 +3670,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>software (tag), engineer, backend (tag), python, cloud (tag), aws (tag), worldwide (place)</t>
+          <t>developer (tag), software (tag), engineer, backend, python, api (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Python-Engineering, Backend-Development, AWS-Cloud-Development, Serverless-Development, Software-Engineer, Python-Engineer, Python-Software-Engineer, Mid-level</t>
+          <t>Python-Backend-Engineering, Backend-Development, Software-Engineer, API-Development, Python-Engineering, Python-Backend-Engineer, Python-Backend-Developer, Senior-Backend-Python-Developer, Senior-Python-Backend-Developer, Backend-Engineer, Product-Backend-Engineer, Backend-Services-Engineer, Senior</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/s-pro/jobs/python-engineer</t>
+          <t>https://himalayas.app/companies/makersite/jobs/python-backend-engineer-m-f-x</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>67bda4c374</t>
+          <t>3eb1e889db</t>
         </is>
       </c>
     </row>
@@ -3706,19 +3706,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Daymark Health</t>
+          <t>S-PRO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), worldwide (place)</t>
+          <t>software (tag), engineer, backend (tag), python, cloud (tag), aws (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Software-Engineer, Healthcare-Technology, Backend-Engineering, Fullstack-Development, Health-Tech, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Developer, Mid-level</t>
+          <t>Python-Engineering, Backend-Development, AWS-Cloud-Development, Serverless-Development, Software-Engineer, Python-Engineer, Python-Software-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/daymark-health/jobs/software-engineer</t>
+          <t>https://himalayas.app/companies/s-pro/jobs/python-engineer</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>85c899deaf</t>
+          <t>67bda4c374</t>
         </is>
       </c>
     </row>
@@ -3765,56 +3765,58 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>84</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Specialist, Data Science &amp; Artificial Intelligence</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Daymark Health</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>artificial intelligence, data science, india (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>Software-Engineer, Healthcare-Technology, Backend-Engineering, Fullstack-Development, Health-Tech, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5871846075?se=oI2O_Sup8RGogquEo3zAlQ&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=326B6FA659B880A3C0F3E2CA4AB8E0734BF69D7B</t>
+          <t>https://himalayas.app/companies/daymark-health/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>c1e8559189</t>
+          <t>85c899deaf</t>
         </is>
       </c>
     </row>
@@ -3830,39 +3832,37 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>50</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Specialist, Data Science &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>xneelo</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), devops (tag), worldwide (place)</t>
+          <t>artificial intelligence, data science, india (place)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Software-Engineer, Backend-Development, Fullstack-Development, Infrastructure-Engineering, DevOps, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Senior</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/xneelo-co/jobs/software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5871846075?se=oI2O_Sup8RGogquEo3zAlQ&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=326B6FA659B880A3C0F3E2CA4AB8E0734BF69D7B</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>679e1ed2b3</t>
+          <t>c1e8559189</t>
         </is>
       </c>
     </row>
@@ -3893,39 +3893,39 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AEM Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vonage</t>
+          <t>xneelo</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>developer, devops (tag), anywhere (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), devops (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Software-Engineer, Backend-Development, Fullstack-Development, Infrastructure-Engineering, DevOps, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Senior</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/vonage-aem-developer</t>
+          <t>https://himalayas.app/companies/xneelo-co/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>9b191a3075</t>
+          <t>679e1ed2b3</t>
         </is>
       </c>
     </row>
@@ -3956,37 +3956,39 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>27</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Video Annotation Expert</t>
+          <t>AEM Developer</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Vonage</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ai (tag), worldwide (place)</t>
+          <t>developer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Video-Annotator, Video-Annotation, Media-Annotation-Specialist, Video-Data-Annotation, Annotation-Specialist, Data-Annotation-Expert, AI-Annotation-Specialist, Content-Annotation-Specialist, Entry-level, Mid-level</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3996,12 +3998,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/video-annotation-expert-4408176807</t>
+          <t>https://weworkremotely.com/remote-jobs/vonage-aem-developer</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1b02a267ff</t>
+          <t>9b191a3075</t>
         </is>
       </c>
     </row>
@@ -4013,56 +4015,56 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Subject Matter Expert - Computer Science and Artificial Intelligence</t>
+          <t>Video Annotation Expert</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sultan Chand &amp; Sons Ltd</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>artificial intelligence, noida (place)</t>
+          <t>ai (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Video-Annotator, Video-Annotation, Media-Annotation-Specialist, Video-Data-Annotation, Annotation-Specialist, Data-Annotation-Expert, AI-Annotation-Specialist, Content-Annotation-Specialist, Entry-level, Mid-level</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5869558953?se=ji27_Tqo8RGDXZRVG-VeHA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=41B18BB78E05B29C6C90DA595F6A5EBB3EFE4072</t>
+          <t>https://himalayas.app/companies/micro1/jobs/video-annotation-expert-4408176807</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>91b1f60d0c</t>
+          <t>1b02a267ff</t>
         </is>
       </c>
     </row>
@@ -4078,37 +4080,37 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Software engineer</t>
+          <t>Subject Matter Expert - Computer Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sticker Mule</t>
+          <t>Sultan Chand &amp; Sons Ltd</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>software engineer, typescript (tag), golang (tag), react (tag), global (place)</t>
+          <t>artificial intelligence, noida (place)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Development, react,typescript,golang,graphql,english</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4118,12 +4120,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1833624/</t>
+          <t>https://www.adzuna.in/land/ad/5869558953?se=ji27_Tqo8RGDXZRVG-VeHA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=41B18BB78E05B29C6C90DA595F6A5EBB3EFE4072</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>c557da3996</t>
+          <t>91b1f60d0c</t>
         </is>
       </c>
     </row>
@@ -4135,56 +4137,56 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer 3D Developer (remote part/full time)</t>
+          <t>Software engineer</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Imnoo AG</t>
+          <t>Sticker Mule</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>machine learning, developer, engineer, ai, ml (tag), worldwide (place)</t>
+          <t>software engineer, typescript (tag), golang (tag), react (tag), global (place)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>AI-Machine-Learning-Engineering, 3D-Development, Computer-Vision, AI-Manufacturing, CAD-Development, Remote-Machine-Learning-Engineer, Remote-Senior-AI-Engineer, Remote-AI-Engineer, AI-ML-Engineer, Lead-AI-ML-Engineer, Machine-Learning-Engineer, Senior</t>
+          <t>Development, react,typescript,golang,graphql,english</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/imnoo-ag/jobs/ai-machine-learning-engineer-3d-developer-remote-part-full-time</t>
+          <t>https://www.workingnomads.com/job/go/1833624/</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>a84b2b9b96</t>
+          <t>c557da3996</t>
         </is>
       </c>
     </row>
@@ -4200,37 +4202,37 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>AI Machine Learning Engineer 3D Developer (remote part/full time)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sustainability Economics.ai</t>
+          <t>Imnoo AG</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>machine learning, intern (level), bangalore (place)</t>
+          <t>machine learning, developer, engineer, ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Machine-Learning-Engineering, 3D-Development, Computer-Vision, AI-Manufacturing, CAD-Development, Remote-Machine-Learning-Engineer, Remote-Senior-AI-Engineer, Remote-AI-Engineer, AI-ML-Engineer, Lead-AI-ML-Engineer, Machine-Learning-Engineer, Senior</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4240,12 +4242,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5868794497?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C97284B10F6321E0988BF83E6C1B8DFD30952F6C</t>
+          <t>https://himalayas.app/companies/imnoo-ag/jobs/ai-machine-learning-engineer-3d-developer-remote-part-full-time</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>05411f661c</t>
+          <t>a84b2b9b96</t>
         </is>
       </c>
     </row>
@@ -4261,17 +4263,17 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Machine Learning II</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Sustainability Economics.ai</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4286,12 +4288,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>machine learning, qa (tag), bangalore (place)</t>
+          <t>machine learning, intern (level), bangalore (place)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Scientific &amp; QA Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4301,12 +4303,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5868154123?se=SoAubXKn8RGZGp_UbifwCA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2A76050FF86A705EC1E71FEE64DFE517445586F0</t>
+          <t>https://www.adzuna.in/land/ad/5868794497?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C97284B10F6321E0988BF83E6C1B8DFD30952F6C</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>520f876dc1</t>
+          <t>05411f661c</t>
         </is>
       </c>
     </row>
@@ -4322,22 +4324,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>Machine Learning II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4347,27 +4349,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>machine learning, qa (tag), bangalore (place)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5852477157?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C196DCD121C33E5FA7A7F99C735E078C53777A1E</t>
+          <t>https://www.adzuna.in/land/ad/5868154123?se=SoAubXKn8RGZGp_UbifwCA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2A76050FF86A705EC1E71FEE64DFE517445586F0</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>dab94fe012</t>
+          <t>520f876dc1</t>
         </is>
       </c>
     </row>
@@ -4383,54 +4385,52 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>46</v>
-      </c>
-      <c r="D65" t="n">
-        <v>2</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Data Scientist - Inference, Community Support</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>data scientist, anywhere (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/airbnb-data-scientist-inference-community-support</t>
+          <t>https://www.adzuna.in/land/ad/5852477157?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C196DCD121C33E5FA7A7F99C735E078C53777A1E</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>18eaeb9d4e</t>
+          <t>dab94fe012</t>
         </is>
       </c>
     </row>
@@ -4446,54 +4446,54 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Frontend Engineer Specialist</t>
+          <t>Data Scientist - Inference, Community Support</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>developer (tag), frontend, software (tag), engineer, react (tag), worldwide (place)</t>
+          <t>data scientist, anywhere (place)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Frontend-Engineer, Web-Frontend-Engineer, Front-End-Software-Engineer, Frontend-Web-Software-Engineer, Front-End-Developer, React-Frontend-Engineer, UI-Frontend-Developer, Mid-level</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/frontend-engineer-specialist</t>
+          <t>https://weworkremotely.com/remote-jobs/airbnb-data-scientist-inference-community-support</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>ee1605c3a3</t>
+          <t>18eaeb9d4e</t>
         </is>
       </c>
     </row>
@@ -4505,56 +4505,58 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>44</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Frontend Engineer Specialist</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>developer (tag), frontend, software (tag), engineer, react (tag), worldwide (place)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Frontend-Engineer, Web-Frontend-Engineer, Front-End-Software-Engineer, Frontend-Web-Software-Engineer, Front-End-Developer, React-Frontend-Engineer, UI-Frontend-Developer, Mid-level</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="C67" t="n">
-        <v>86</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; NLP Expert</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Synthenova</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>machine learning, nlp, qa (tag), india (place)</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Scientific &amp; QA Jobs</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864426193?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FA0DA9F5539A8E98A42507C72E66BEA28EFB5F71</t>
+          <t>https://himalayas.app/companies/micro1/jobs/frontend-engineer-specialist</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>06a6232301</t>
+          <t>ee1605c3a3</t>
         </is>
       </c>
     </row>
@@ -4570,22 +4572,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning &amp; NLP Expert</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HT Digital Streams</t>
+          <t>Synthenova</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,12 +4597,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>data scientist, india (place), delhi (place)</t>
+          <t>machine learning, nlp, qa (tag), india (place)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4610,12 +4612,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427594?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1379BD61E95509405A372328EE4CB12520438AC9</t>
+          <t>https://www.adzuna.in/land/ad/5864426193?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FA0DA9F5539A8E98A42507C72E66BEA28EFB5F71</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>e77b0725ce</t>
+          <t>06a6232301</t>
         </is>
       </c>
     </row>
@@ -4631,52 +4633,52 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HeadSpin</t>
+          <t>HT Digital Streams</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), associate (level), worldwide (place)</t>
+          <t>data scientist, india (place), delhi (place)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Engineering, Software-Engineer, Associate-Software-Engineer, Backend-Development, Fullstack-Development, Software-Engineering-Associate, Associate-Software-Developer, Software-Developer-Associate, Associate-Engineer, Associate-Platform-Engineer, Associate-Application-Developer, Associate-Systems-Engineer, Developer, Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/headspin/jobs/associate-software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5864427594?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1379BD61E95509405A372328EE4CB12520438AC9</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>ed41465dce</t>
+          <t>e77b0725ce</t>
         </is>
       </c>
     </row>
@@ -4692,52 +4694,52 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>HeadSpin</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>artificial intelligence, noida (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), associate (level), worldwide (place)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment Jobs</t>
+          <t>Engineering, Software-Engineer, Associate-Software-Engineer, Backend-Development, Fullstack-Development, Software-Engineering-Associate, Associate-Software-Developer, Software-Developer-Associate, Associate-Engineer, Associate-Platform-Engineer, Associate-Application-Developer, Associate-Systems-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864432717?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=616D5B872E024B0E271B6E107D9B24261D8C3B7A</t>
+          <t>https://himalayas.app/companies/headspin/jobs/associate-software-engineer</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>90b00c6445</t>
+          <t>ed41465dce</t>
         </is>
       </c>
     </row>
@@ -4755,22 +4757,20 @@
       <c r="C71" t="n">
         <v>50</v>
       </c>
-      <c r="D71" t="n">
-        <v>3</v>
-      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Machine Learning Specialist</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bandhan Technologies</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4780,27 +4780,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>machine learning, bangalore (place)</t>
+          <t>artificial intelligence, noida (place)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>HR &amp; Recruitment Jobs</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867037827?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=81D91604A259EFB724EEF9EE68D3642F93D7C52A</t>
+          <t>https://www.adzuna.in/land/ad/5864432717?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=616D5B872E024B0E271B6E107D9B24261D8C3B7A</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>55af0af08c</t>
+          <t>90b00c6445</t>
         </is>
       </c>
     </row>
@@ -4816,19 +4816,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D72" t="n">
         <v>3</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Data Science Specialist</t>
+          <t>Machine Learning Specialist</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Polestar Analytics</t>
+          <t>Bandhan Technologies</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>data science, bangalore (place)</t>
+          <t>machine learning, bangalore (place)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4853,17 +4853,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864434859?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BE53F35ACA83BD29D328C8745F27CF70F132F879</t>
+          <t>https://www.adzuna.in/land/ad/5867037827?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=81D91604A259EFB724EEF9EE68D3642F93D7C52A</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>620816c318</t>
+          <t>55af0af08c</t>
         </is>
       </c>
     </row>
@@ -4881,20 +4881,22 @@
       <c r="C73" t="n">
         <v>49</v>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>Data Science Specialist</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Polestar Analytics</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4904,7 +4906,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>data science, bangalore (place)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4914,17 +4916,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867037765?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CCE3B589087C9AE3C6FD3C72DD92F3B9146F772F</t>
+          <t>https://www.adzuna.in/land/ad/5864434859?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BE53F35ACA83BD29D328C8745F27CF70F132F879</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>5ae3a66648</t>
+          <t>620816c318</t>
         </is>
       </c>
     </row>
@@ -4945,17 +4947,17 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Infosys Finacle</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4965,12 +4967,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4980,12 +4982,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867270149?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=284AB41CD26DD62DA43E2E7866A4F2E72052CFA3</t>
+          <t>https://www.adzuna.in/land/ad/5867037765?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CCE3B589087C9AE3C6FD3C72DD92F3B9146F772F</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>b9e7b78c99</t>
+          <t>5ae3a66648</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5013,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Servify</t>
+          <t>Infosys Finacle</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5031,7 +5033,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5041,12 +5043,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867265604?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=98C25A013410B0B492855DE45F67FF3409A45C24</t>
+          <t>https://www.adzuna.in/land/ad/5867270149?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=284AB41CD26DD62DA43E2E7866A4F2E72052CFA3</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>339ea3cd4c</t>
+          <t>b9e7b78c99</t>
         </is>
       </c>
     </row>
@@ -5062,37 +5064,37 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CEO, AI Finance</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bjak</t>
+          <t>Servify</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5102,12 +5104,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/bjak/jobs/ceo-ai-finance-7034716418</t>
+          <t>https://www.adzuna.in/land/ad/5867265604?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=98C25A013410B0B492855DE45F67FF3409A45C24</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>8e23b34067</t>
+          <t>339ea3cd4c</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5125,17 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Accounting Automation Engineer</t>
+          <t>CEO, AI Finance</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spotter Labs</t>
+          <t>Bjak</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5148,12 +5150,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>automation, software (tag), engineer, worldwide (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Accounting-Automation-Engineer, Finance-Automation-Engineer, Accounting-Software-Engineer, Accounting-Automation, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5163,12 +5165,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3984977259</t>
+          <t>https://himalayas.app/companies/bjak/jobs/ceo-ai-finance-7034716418</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>c570969de5</t>
+          <t>8e23b34067</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5216,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Accounting-Automation-Engineer, Accounting, Process-Automation, Financial-Automation, Business-Systems, Finance-Automation-Engineer, Accounting-Software-Engineer, Automation-Engineer, Accounting-Automation, Software-Automation-Engineer, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
+          <t>Accounting-Automation-Engineer, Finance-Automation-Engineer, Accounting-Software-Engineer, Accounting-Automation, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5224,12 +5226,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3943339358</t>
+          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3984977259</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>13edcbb44e</t>
+          <t>c570969de5</t>
         </is>
       </c>
     </row>
@@ -5245,37 +5247,37 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Backend Engineer - Platform - Stacks | Ireland | Remote</t>
+          <t>Accounting Automation Engineer</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grafana Labs</t>
+          <t>Spotter Labs</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>engineer, backend, anywhere (place)</t>
+          <t>automation, software (tag), engineer, worldwide (place)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Accounting-Automation-Engineer, Accounting, Process-Automation, Financial-Automation, Business-Systems, Finance-Automation-Engineer, Accounting-Software-Engineer, Automation-Engineer, Accounting-Automation, Software-Automation-Engineer, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5285,12 +5287,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/grafana-labs-backend-engineer-platform-stacks-ireland-remote</t>
+          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3943339358</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>7aae615c8c</t>
+          <t>13edcbb44e</t>
         </is>
       </c>
     </row>
@@ -5306,37 +5308,37 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>STEM Expert</t>
+          <t>Backend Engineer - Platform - Stacks | Ireland | Remote</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ai (tag), worldwide (place)</t>
+          <t>engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>STEM-Expert, STEM-Specialist, STEM-Consultant, STEM-Domain-Expert, STEM-Researcher, STEM-Educator, STEM-AI-Specialist, Japanese-STEM-Specialist, STEM-Advisor, STEM-Instructor, Mid-level</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5346,12 +5348,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/stem-expert-40695367</t>
+          <t>https://weworkremotely.com/remote-jobs/grafana-labs-backend-engineer-platform-stacks-ireland-remote</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>9cb40c45fc</t>
+          <t>7aae615c8c</t>
         </is>
       </c>
     </row>
@@ -5367,14 +5369,12 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>21</v>
-      </c>
-      <c r="D81" t="n">
-        <v>3</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Excel Specialist</t>
+          <t>STEM Expert</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>automation (tag), developer (tag), worldwide (place)</t>
+          <t>ai (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Excel-Specialist, Excel-Expert, Spreadsheet-Specialist, Excel-Automation-Specialist, Excel-Data-Analyst, Microsoft-Excel-Developer, Microsoft-Office-Specialist, Microsoft-Excel-Development, Entry-level, Mid-level</t>
+          <t>STEM-Expert, STEM-Specialist, STEM-Consultant, STEM-Domain-Expert, STEM-Researcher, STEM-Educator, STEM-AI-Specialist, Japanese-STEM-Specialist, STEM-Advisor, STEM-Instructor, Mid-level</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/excel-specialist-2996931708</t>
+          <t>https://himalayas.app/companies/micro1/jobs/stem-expert-40695367</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>fddf243627</t>
+          <t>9cb40c45fc</t>
         </is>
       </c>
     </row>
@@ -5426,56 +5426,58 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>69</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>Excel Specialist</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ISIR AI</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>data science, qa (tag), intern (level), noida (place)</t>
+          <t>automation (tag), developer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Scientific &amp; QA Jobs</t>
+          <t>Excel-Specialist, Excel-Expert, Spreadsheet-Specialist, Excel-Automation-Specialist, Excel-Data-Analyst, Microsoft-Excel-Developer, Microsoft-Office-Specialist, Microsoft-Excel-Development, Entry-level, Mid-level</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427080?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C509B9B88F855FA7348A37AF1CDF8C3ECC7CA889</t>
+          <t>https://himalayas.app/companies/micro1/jobs/excel-specialist-2996931708</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>84896ab3c6</t>
+          <t>fddf243627</t>
         </is>
       </c>
     </row>
@@ -5491,22 +5493,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FRND</t>
+          <t>ISIR AI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5516,12 +5518,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>machine learning, intern (level), bangalore (place)</t>
+          <t>data science, qa (tag), intern (level), noida (place)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5531,12 +5533,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864424613?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9B60872885E8C7073FE0CC2A962D44A1E48845F7</t>
+          <t>https://www.adzuna.in/land/ad/5864427080?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C509B9B88F855FA7348A37AF1CDF8C3ECC7CA889</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>e00b96a707</t>
+          <t>84896ab3c6</t>
         </is>
       </c>
     </row>
@@ -5552,22 +5554,22 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Intern (Data Science)</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Yubi</t>
+          <t>FRND</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5577,7 +5579,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>data science, intern (level), chennai (place)</t>
+          <t>machine learning, intern (level), bangalore (place)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5592,12 +5594,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864443163?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4554D5357B8D35F06907356F0816FBF3BD2BBC7E</t>
+          <t>https://www.adzuna.in/land/ad/5864424613?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9B60872885E8C7073FE0CC2A962D44A1E48845F7</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>93516db46a</t>
+          <t>e00b96a707</t>
         </is>
       </c>
     </row>
@@ -5613,37 +5615,37 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AI Inference Engineer QVAC (100% remote Worldwide)</t>
+          <t>Intern (Data Science)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tether Operations Limited</t>
+          <t>Yubi</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>software (tag), engineer, ai, worldwide (place)</t>
+          <t>data science, intern (level), chennai (place)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Software-Engineer, AI-Engineering, Machine-Learning-Engineering, C-Development, Edge-AI, AI-Inference-Engineer, Remote-AI-Engineer, Remote-Machine-Learning-Engineer, Senior-AI-Inference-Engineer, Remote-Senior-AI-Engineer, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5653,12 +5655,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/tether-operations-limited/jobs/ai-inference-engineer-qvac-100-remote-worldwide</t>
+          <t>https://www.adzuna.in/land/ad/5864443163?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4554D5357B8D35F06907356F0816FBF3BD2BBC7E</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>f7f40ca44a</t>
+          <t>93516db46a</t>
         </is>
       </c>
     </row>
@@ -5674,37 +5676,37 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Machine Learning Gen AI_Hyderabad,Pune &amp; Bangalore</t>
+          <t>AI Inference Engineer QVAC (100% remote Worldwide)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Tether Operations Limited</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>machine learning, hyderabad (place)</t>
+          <t>software (tag), engineer, ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Software-Engineer, AI-Engineering, Machine-Learning-Engineering, C-Development, Edge-AI, AI-Inference-Engineer, Remote-AI-Engineer, Remote-Machine-Learning-Engineer, Senior-AI-Inference-Engineer, Remote-Senior-AI-Engineer, Senior</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5714,12 +5716,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439281?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1F39144C3030195205A212339590BB508623F064</t>
+          <t>https://himalayas.app/companies/tether-operations-limited/jobs/ai-inference-engineer-qvac-100-remote-worldwide</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>55fce19c46</t>
+          <t>f7f40ca44a</t>
         </is>
       </c>
     </row>
@@ -5735,17 +5737,17 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Gen AI_Hyderabad,Pune &amp; Bangalore</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Infosys Consulting</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5760,7 +5762,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>data scientist, hyderabad (place)</t>
+          <t>machine learning, hyderabad (place)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5775,12 +5777,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864428905?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4E35D1AC081FE279803556ECA4C1E1871550877F</t>
+          <t>https://www.adzuna.in/land/ad/5864439281?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1F39144C3030195205A212339590BB508623F064</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>af7ebeb057</t>
+          <t>55fce19c46</t>
         </is>
       </c>
     </row>
@@ -5798,9 +5800,7 @@
       <c r="C88" t="n">
         <v>49</v>
       </c>
-      <c r="D88" t="n">
-        <v>2</v>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Data Scientist</t>
@@ -5808,12 +5808,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>super.money</t>
+          <t>Infosys Consulting</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, hyderabad (place)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864425941?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BF9A171BDEA00E60475790836A0A3589FB8D9EB6</t>
+          <t>https://www.adzuna.in/land/ad/5864428905?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4E35D1AC081FE279803556ECA4C1E1871550877F</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>4f1a679ea3</t>
+          <t>af7ebeb057</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,9 @@
       <c r="C89" t="n">
         <v>49</v>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>Data Scientist</t>
@@ -5869,7 +5871,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lufthansa Technik Services India Pvt Ltd</t>
+          <t>super.money</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5899,12 +5901,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864422634?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
+          <t>https://www.adzuna.in/land/ad/5864425941?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BF9A171BDEA00E60475790836A0A3589FB8D9EB6</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>c86fa3dfe3</t>
+          <t>4f1a679ea3</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5932,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank</t>
+          <t>Lufthansa Technik Services India Pvt Ltd</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5950,7 +5952,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5960,12 +5962,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439103?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=73CFB6E1B4115AA2A23A99B0EC8886521BA01450</t>
+          <t>https://www.adzuna.in/land/ad/5864422634?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>08622a68ed</t>
+          <t>c86fa3dfe3</t>
         </is>
       </c>
     </row>
@@ -5986,17 +5988,17 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Navi</t>
+          <t>Kotak Mahindra Bank</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6006,12 +6008,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6021,12 +6023,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439226?se=jiNNTDmm8RGUNa3mkcr13g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=744BE785510320885EE5287D6F2FE8E098FAED30</t>
+          <t>https://www.adzuna.in/land/ad/5864439103?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=73CFB6E1B4115AA2A23A99B0EC8886521BA01450</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>4e1bb30522</t>
+          <t>08622a68ed</t>
         </is>
       </c>
     </row>
@@ -6047,17 +6049,17 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tricog Health</t>
+          <t>Navi</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6067,7 +6069,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6077,17 +6079,17 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5865291446?se=pmQW9lOm8RGs-Y02KTQxmA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=A9D77535171E8EAD7E7898B67A7ADC8ED3D07410</t>
+          <t>https://www.adzuna.in/land/ad/5864439226?se=jiNNTDmm8RGUNa3mkcr13g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=744BE785510320885EE5287D6F2FE8E098FAED30</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>eaec37f6c0</t>
+          <t>4e1bb30522</t>
         </is>
       </c>
     </row>
@@ -6103,54 +6105,52 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>41</v>
-      </c>
-      <c r="D93" t="n">
-        <v>3</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Remote - Automation QA Engineer (Core Team)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Torrero</t>
+          <t>Tricog Health</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>automation, software (tag), engineer, testing (tag), qa, worldwide (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>QA-Engineer, QA-Automation-Engineer, Software-Testing, Quality-Assurance, Manual-Testing, Remote-Test-Automation-Engineer, Remote-QA-Engineer, Remote-Quality-Assurance-Engineer, Remote-UI-Automation-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/torrero/jobs/remote-automation-qa-engineer-core-team</t>
+          <t>https://www.adzuna.in/land/ad/5865291446?se=pmQW9lOm8RGs-Y02KTQxmA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=A9D77535171E8EAD7E7898B67A7ADC8ED3D07410</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>f03380c71d</t>
+          <t>eaec37f6c0</t>
         </is>
       </c>
     </row>
@@ -6166,17 +6166,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>36</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Front-End Developer</t>
+          <t>Remote - Automation QA Engineer (Core Team)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talent Sam</t>
+          <t>Torrero</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6191,12 +6193,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>developer, frontend (tag), engineer (tag), react (tag), worldwide (place)</t>
+          <t>automation, software (tag), engineer, testing (tag), qa, worldwide (place)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Frontend-Development, Web-Development, UI-Developer, Frontend-Engineer, Front-End-Developer, Frontend-React-Developer, UI-Frontend-Developer, UX-UI-Front-End-Developer, React-Frontend-Developer, Frontend-Web-Development, Developer, Mid-level</t>
+          <t>QA-Engineer, QA-Automation-Engineer, Software-Testing, Quality-Assurance, Manual-Testing, Remote-Test-Automation-Engineer, Remote-QA-Engineer, Remote-Quality-Assurance-Engineer, Remote-UI-Automation-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6206,12 +6208,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/talent-sam/jobs/front-end-developer</t>
+          <t>https://himalayas.app/companies/torrero/jobs/remote-automation-qa-engineer-core-team</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>94d5af612e</t>
+          <t>f03380c71d</t>
         </is>
       </c>
     </row>
@@ -6227,37 +6229,37 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>E-learning Developer</t>
+          <t>Front-End Developer</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>VineGarden Films</t>
+          <t>Talent Sam</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>developer, india (place)</t>
+          <t>developer, frontend (tag), engineer (tag), react (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Teaching Jobs</t>
+          <t>Frontend-Development, Web-Development, UI-Developer, Frontend-Engineer, Front-End-Developer, Frontend-React-Developer, UI-Frontend-Developer, UX-UI-Front-End-Developer, React-Frontend-Developer, Frontend-Web-Development, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6267,12 +6269,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864153573?se=SvkgT-Wl8RGUGK7L4gkIgg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FDDF0A4236DF3E6D3081AF93B01799D77599EAD1</t>
+          <t>https://himalayas.app/companies/talent-sam/jobs/front-end-developer</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>248ef46714</t>
+          <t>94d5af612e</t>
         </is>
       </c>
     </row>
@@ -6284,21 +6286,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Data Scientist - Python Deterministic Analytics</t>
+          <t>E-learning Developer</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Capco</t>
+          <t>VineGarden Films</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6313,27 +6315,27 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>data scientist, python, india (place)</t>
+          <t>developer, india (place)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Teaching Jobs</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139747?se=olLfvDql8RGL6NrjcRaTpw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9FA82041CC2CC98F084D6827CF82DA2BE289D998</t>
+          <t>https://www.adzuna.in/land/ad/5864153573?se=SvkgT-Wl8RGUGK7L4gkIgg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FDDF0A4236DF3E6D3081AF93B01799D77599EAD1</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>6f1952e273</t>
+          <t>248ef46714</t>
         </is>
       </c>
     </row>
@@ -6349,22 +6351,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - APAC</t>
+          <t>Data Scientist - Python Deterministic Analytics</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional®</t>
+          <t>Capco</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6374,7 +6376,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>data scientist, python, india (place)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6384,17 +6386,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5862635702?se=9gaugPCk8RGcfKYe_cIpvA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=53D4DF556D646C5F462C8F3FC782D72E8A35D08B</t>
+          <t>https://www.adzuna.in/land/ad/5837139747?se=olLfvDql8RGL6NrjcRaTpw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9FA82041CC2CC98F084D6827CF82DA2BE289D998</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>d395f3a907</t>
+          <t>6f1952e273</t>
         </is>
       </c>
     </row>
@@ -6410,52 +6412,52 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AI Engineer Data APIs</t>
+          <t>Machine Learning Engineer - APAC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>LexisNexis Legal &amp; Professional®</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>engineer, golang (tag), ai</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>golang, video, engineer</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-ai-engineer-data-apis-benzinga-1137224</t>
+          <t>https://www.adzuna.in/land/ad/5862635702?se=9gaugPCk8RGcfKYe_cIpvA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=53D4DF556D646C5F462C8F3FC782D72E8A35D08B</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>1261a5bcd5</t>
+          <t>d395f3a907</t>
         </is>
       </c>
     </row>
@@ -6471,52 +6473,52 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Agentic Python Engineer</t>
+          <t>AI Engineer Data APIs</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Evaboot</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>WORLDWIDE</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>engineer, python, aws (tag), worldwide (place)</t>
+          <t>engineer, golang (tag), ai</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Development, python,engineer,aws,analytics,seo</t>
+          <t>golang, video, engineer</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1826864/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-engineer-data-apis-benzinga-1137224</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>47ae63b1d0</t>
+          <t>1261a5bcd5</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6534,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
@@ -6547,22 +6549,22 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>WORLDWIDE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>engineer, python, anywhere (place)</t>
+          <t>engineer, python, aws (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Development, python,engineer,aws,analytics,seo</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6572,12 +6574,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/evaboot-agentic-python-engineer</t>
+          <t>https://www.workingnomads.com/job/go/1826864/</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>d94554bfc7</t>
+          <t>47ae63b1d0</t>
         </is>
       </c>
     </row>
@@ -6589,56 +6591,56 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Agentic Python Engineer</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Evaboot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>engineer, python, anywhere (place)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982687?se=BGNyWVik8RGF59teMJsS7Q&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=64C652991D92D5E3DCA4519D688756F962092321</t>
+          <t>https://weworkremotely.com/remote-jobs/evaboot-agentic-python-engineer</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>dd6de0380a</t>
+          <t>d94554bfc7</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6661,7 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Data Scientist, Knowledge Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6694,12 +6696,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982533?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=853C1E923E89428D368371363C6206932A9E653B</t>
+          <t>https://www.adzuna.in/land/ad/5857982687?se=BGNyWVik8RGF59teMJsS7Q&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=64C652991D92D5E3DCA4519D688756F962092321</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>e4df1efe77</t>
+          <t>dd6de0380a</t>
         </is>
       </c>
     </row>
@@ -6720,17 +6722,17 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Data Scientist II, Data Analytics, Hyderabad</t>
+          <t>Data Scientist, Knowledge Management</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6740,7 +6742,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>data scientist, hyderabad (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6750,17 +6752,17 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5860916020?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2CB3A6FFC4393B68C48E0DBE7C464491C08965D1</t>
+          <t>https://www.adzuna.in/land/ad/5857982533?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=853C1E923E89428D368371363C6206932A9E653B</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>ed5cec24b5</t>
+          <t>e4df1efe77</t>
         </is>
       </c>
     </row>
@@ -6776,52 +6778,52 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform - Hyderabad, India</t>
+          <t>Data Scientist II, Data Analytics, Hyderabad</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Speechify</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>software engineer, backend (tag), cloud (tag), api (tag), india (place)</t>
+          <t>data scientist, hyderabad (place)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Platform-Engineering, Backend-Engineering, Software-Engineer, API-Development, Cloud-Infrastructure, Software-Platform-Engineer, Platform-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/speechify/jobs/software-engineer-platform-hyderabad-india</t>
+          <t>https://www.adzuna.in/land/ad/5860916020?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2CB3A6FFC4393B68C48E0DBE7C464491C08965D1</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>d972ee3bee</t>
+          <t>ed5cec24b5</t>
         </is>
       </c>
     </row>
@@ -6837,22 +6839,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>GitHub Contributor</t>
+          <t>Software Engineer, Platform - Hyderabad, India</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Speechify</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6862,12 +6864,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, backend (tag), cloud (tag), api (tag), india (place)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
+          <t>Platform-Engineering, Backend-Engineering, Software-Engineer, API-Development, Cloud-Infrastructure, Software-Platform-Engineer, Platform-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6877,12 +6879,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-2145210908</t>
+          <t>https://himalayas.app/companies/speechify/jobs/software-engineer-platform-hyderabad-india</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>9bd86980fc</t>
+          <t>d972ee3bee</t>
         </is>
       </c>
     </row>
@@ -6894,58 +6896,56 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>38</v>
-      </c>
-      <c r="D106" t="n">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, PDP Experience</t>
+          <t>GitHub Contributor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>software engineer, backend, anywhere (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/reddit-backend-software-engineer-pdp-experience</t>
+          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-2145210908</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>a954ce85ab</t>
+          <t>9bd86980fc</t>
         </is>
       </c>
     </row>
@@ -6961,37 +6961,39 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>24</v>
-      </c>
-      <c r="D107" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="D107" t="n">
+        <v>3</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Open Source Contributor</t>
+          <t>Backend Software Engineer, PDP Experience</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Open-Source-Software-Developer, Open-Source-Advocate, Open-Source-Engineer, Open-Source-Software-Engineer, Open-Source-Software-Maintainer, Community-Contributor, Entry-level</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7001,12 +7003,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/open-source-contributor-4150550716</t>
+          <t>https://weworkremotely.com/remote-jobs/reddit-backend-software-engineer-pdp-experience</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>d8033bd793</t>
+          <t>a954ce85ab</t>
         </is>
       </c>
     </row>
@@ -7018,16 +7020,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Open Source Contributor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -7047,27 +7049,27 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>engineer, python (tag), ai, ml (tag), worldwide (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Mid-level</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Open-Source-Software-Developer, Open-Source-Advocate, Open-Source-Engineer, Open-Source-Software-Engineer, Open-Source-Software-Maintainer, Community-Contributor, Entry-level</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-engineer-7982880650</t>
+          <t>https://himalayas.app/companies/micro1/jobs/open-source-contributor-4150550716</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>17936ac69e</t>
+          <t>d8033bd793</t>
         </is>
       </c>
     </row>
@@ -7083,37 +7085,37 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>machine learning, engineer, hyderabad (place)</t>
+          <t>engineer, python (tag), ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Mid-level</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7123,12 +7125,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5859662671?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=77410E24CED3D457054E58156829472F42D5B958</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-engineer-7982880650</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>a8bcca74c0</t>
+          <t>17936ac69e</t>
         </is>
       </c>
     </row>
@@ -7149,17 +7151,17 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (T25)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7169,7 +7171,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>machine learning, engineer, hyderabad (place)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7179,17 +7181,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858538850?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AA8B404BB5F08B6BBBC1A1DAEA80EDAE2331BB01</t>
+          <t>https://www.adzuna.in/land/ad/5859662671?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=77410E24CED3D457054E58156829472F42D5B958</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>e99054d24c</t>
+          <t>a8bcca74c0</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7212,7 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SWE-3 Machine Learning Engineer</t>
+          <t>Machine Learning Engineer (T25)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7245,12 +7247,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858537539?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=49BEDAECA8CA01D8F7BFB9CA5D092D8DD046FCF4</t>
+          <t>https://www.adzuna.in/land/ad/5858538850?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AA8B404BB5F08B6BBBC1A1DAEA80EDAE2331BB01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>83e0ebd10e</t>
+          <t>e99054d24c</t>
         </is>
       </c>
     </row>
@@ -7266,22 +7268,22 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>SWE-3 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7291,7 +7293,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>engineer, ai, hyderabad (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7306,12 +7308,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982475?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=61932F7A965BC6190F96EF3EDD6B34FCA7CA0EFF</t>
+          <t>https://www.adzuna.in/land/ad/5858537539?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=49BEDAECA8CA01D8F7BFB9CA5D092D8DD046FCF4</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>ec1b34ae37</t>
+          <t>83e0ebd10e</t>
         </is>
       </c>
     </row>
@@ -7327,52 +7329,52 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AI Data Annotator - Remote</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Argos Multilingual Inc.</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>All Other Remote, Contract</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/argos-multilingual-inc-ai-data-annotator-remote</t>
+          <t>https://www.adzuna.in/land/ad/5857982475?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=61932F7A965BC6190F96EF3EDD6B34FCA7CA0EFF</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>5c22526a85</t>
+          <t>ec1b34ae37</t>
         </is>
       </c>
     </row>
@@ -7384,56 +7386,56 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Data Scientist - AI &amp; Automation</t>
+          <t>AI Data Annotator - Remote</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Argos Multilingual Inc.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>data scientist, automation, ai, bangalore (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>All Other Remote, Contract</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251125?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C7BA7BE347A1ADA1FC538497AF302C4F3AD6BEDD</t>
+          <t>https://weworkremotely.com/remote-jobs/argos-multilingual-inc-ai-data-annotator-remote</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2e19a4f3f6</t>
+          <t>5c22526a85</t>
         </is>
       </c>
     </row>
@@ -7449,12 +7451,12 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>MTS-1 Machine Learning Engineer</t>
+          <t>Data Scientist - AI &amp; Automation</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7474,7 +7476,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>data scientist, automation, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7489,12 +7491,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858537523?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4219F9238C4FE19DFCEAD65DAA98E56A5B89F388</t>
+          <t>https://www.adzuna.in/land/ad/5857251125?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C7BA7BE347A1ADA1FC538497AF302C4F3AD6BEDD</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>c65fcd065c</t>
+          <t>2e19a4f3f6</t>
         </is>
       </c>
     </row>
@@ -7510,22 +7512,22 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>MTS-1 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7535,7 +7537,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>data scientist, mumbai (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7545,17 +7547,17 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5849296977?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FFA2BB725355D26B4B624FA5365F48C2D8B894C</t>
+          <t>https://www.adzuna.in/land/ad/5858537523?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4219F9238C4FE19DFCEAD65DAA98E56A5B89F388</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>200651f002</t>
+          <t>c65fcd065c</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7583,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7596,7 +7598,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, mumbai (place)</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7606,17 +7608,17 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251146?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=43EC4FC89638B5AB4C3D5267B80E2B1135A6C706</t>
+          <t>https://www.adzuna.in/land/ad/5849296977?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FFA2BB725355D26B4B624FA5365F48C2D8B894C</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>6a6f7a8419</t>
+          <t>200651f002</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7674,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251173?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7E2FD9B14C3A74461E2352F6CFE714131C13E4BC</t>
+          <t>https://www.adzuna.in/land/ad/5857251146?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=43EC4FC89638B5AB4C3D5267B80E2B1135A6C706</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>aa6eef76e8</t>
+          <t>6a6f7a8419</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7700,7 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Data Scientist, Knowledge Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7733,12 +7735,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251185?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=74B3EB71D85FA01AB90B707F8DB6AB9F2A17FAFA</t>
+          <t>https://www.adzuna.in/land/ad/5857251173?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7E2FD9B14C3A74461E2352F6CFE714131C13E4BC</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>d1497475d4</t>
+          <t>aa6eef76e8</t>
         </is>
       </c>
     </row>
@@ -7759,12 +7761,12 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Data Scientist with R programming</t>
+          <t>Data Scientist, Knowledge Management</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Capco</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7789,17 +7791,17 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139433?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=221D7BCDBBE6E4012ED68B71EDB34DB2E07507EC</t>
+          <t>https://www.adzuna.in/land/ad/5857251185?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=74B3EB71D85FA01AB90B707F8DB6AB9F2A17FAFA</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>dbec4a04a4</t>
+          <t>d1497475d4</t>
         </is>
       </c>
     </row>
@@ -7815,52 +7817,52 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Data Scientist with R programming</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capco</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Product, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer-1</t>
+          <t>https://www.adzuna.in/land/ad/5837139433?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=221D7BCDBBE6E4012ED68B71EDB34DB2E07507EC</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>e7de7648c1</t>
+          <t>dbec4a04a4</t>
         </is>
       </c>
     </row>
@@ -7916,12 +7918,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer</t>
+          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer-1</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>dada5ade61</t>
+          <t>e7de7648c1</t>
         </is>
       </c>
     </row>
@@ -7937,52 +7939,52 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Education Designer UX UI and AI</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Interaction Design Foundation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>design, content writing, education</t>
+          <t>Product, Full-Time</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-education-designer-ux-ui-and-ai-interaction-design-foundation-1137138</t>
+          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>ca62234445</t>
+          <t>dada5ade61</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8005,7 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Course Writer and Editor UX UI and AI</t>
+          <t>Education Designer UX UI and AI</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -8028,7 +8030,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>design, content writing</t>
+          <t>design, content writing, education</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8038,12 +8040,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-course-writer-and-editor-ux-ui-and-ai-interaction-design-foundation-1137136</t>
+          <t>https://remoteOK.com/remote-jobs/remote-education-designer-ux-ui-and-ai-interaction-design-foundation-1137138</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>01210e4343</t>
+          <t>ca62234445</t>
         </is>
       </c>
     </row>
@@ -8055,56 +8057,56 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>App Developer - AI/ML</t>
+          <t>Course Writer and Editor UX UI and AI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Interaction Design Foundation</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>developer, ai, ml, hyderabad (place)</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>design, content writing</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139469?se=-BSx1eug8RG-Sdz4qyZPjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=16DC1893C3026AA51441662E0B1A61360470917B</t>
+          <t>https://remoteOK.com/remote-jobs/remote-course-writer-and-editor-ux-ui-and-ai-interaction-design-foundation-1137136</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>7a22fe6bd5</t>
+          <t>01210e4343</t>
         </is>
       </c>
     </row>
@@ -8120,17 +8122,17 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>App Developer - AI/ML</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8145,7 +8147,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>developer, ai, ml, hyderabad (place)</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8155,17 +8157,17 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857168441?se=TqYc8W2h8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CEB40CB7335D41898800C58388A2B035DF674757</t>
+          <t>https://www.adzuna.in/land/ad/5837139469?se=-BSx1eug8RG-Sdz4qyZPjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=16DC1893C3026AA51441662E0B1A61360470917B</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>84fdce5107</t>
+          <t>7a22fe6bd5</t>
         </is>
       </c>
     </row>
@@ -8181,37 +8183,37 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AI Speech &amp; Audio Specialist – ASR | TTS | Voice AI | Audio Data</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8221,12 +8223,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/ai-speech-audio-specialist-asr-tts-voice-ai-audio-data</t>
+          <t>https://www.adzuna.in/land/ad/5857168441?se=TqYc8W2h8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CEB40CB7335D41898800C58388A2B035DF674757</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>bb930fc93f</t>
+          <t>84fdce5107</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8249,7 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Financial Accuracy &amp; Tax Logic Expert (AI Community)</t>
+          <t>AI Speech &amp; Audio Specialist – ASR | TTS | Voice AI | Audio Data</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8282,12 +8284,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/financial-accuracy-tax-logic-expert-ai-community-7007868696</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/ai-speech-audio-specialist-asr-tts-voice-ai-audio-data</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>162d6a9ed2</t>
+          <t>bb930fc93f</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8310,7 @@
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Identity Trust &amp; Fraud Intelligence Specialist - Intermediate (AI Community)</t>
+          <t>Financial Accuracy &amp; Tax Logic Expert (AI Community)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8343,12 +8345,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/identity-trust-fraud-intelligence-specialist-intermediate-ai-community</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/financial-accuracy-tax-logic-expert-ai-community-7007868696</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>637c85a300</t>
+          <t>162d6a9ed2</t>
         </is>
       </c>
     </row>
@@ -8369,32 +8371,32 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Education Designer: UX, UI, and AI</t>
+          <t>Identity Trust &amp; Fraud Intelligence Specialist - Intermediate (AI Community)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>IxDF - Interaction Design Foundation</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Design, Full-Time</t>
+          <t>Entry-level</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8404,12 +8406,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-education-designer-ux-ui-and-ai</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/identity-trust-fraud-intelligence-specialist-intermediate-ai-community</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>9fbe655de3</t>
+          <t>637c85a300</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8432,7 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Course Writer and Editor: UX, UI, and AI</t>
+          <t>Education Designer: UX, UI, and AI</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8465,12 +8467,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-course-writer-and-editor-ux-ui-and-ai</t>
+          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-education-designer-ux-ui-and-ai</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>e8e07f5951</t>
+          <t>9fbe655de3</t>
         </is>
       </c>
     </row>
@@ -8491,32 +8493,32 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AI Consulting Domain Expert</t>
+          <t>Course Writer and Editor: UX, UI, and AI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IxDF - Interaction Design Foundation</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>AI-Domain-Expert, AI-Consultant, AI-Subject-Matter-Expert, Artificial-Intelligence-Consulting, Senior</t>
+          <t>Design, Full-Time</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8526,12 +8528,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-consulting-domain-expert-7128968890</t>
+          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-course-writer-and-editor-ux-ui-and-ai</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>7f1041d829</t>
+          <t>e8e07f5951</t>
         </is>
       </c>
     </row>
@@ -8547,39 +8549,37 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>40</v>
-      </c>
-      <c r="D133" t="n">
-        <v>2</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Software Development Engineer II Full Stack - Business (Remote @ Colombia)</t>
+          <t>AI Consulting Domain Expert</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>full stack, software, engineer, anywhere (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>AI-Domain-Expert, AI-Consultant, AI-Subject-Matter-Expert, Artificial-Intelligence-Consulting, Senior</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/offerup-software-development-engineer-ii-full-stack-business-remote-colombia</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-consulting-domain-expert-7128968890</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>6fe968b6b9</t>
+          <t>7f1041d829</t>
         </is>
       </c>
     </row>
@@ -8610,37 +8610,39 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>20</v>
-      </c>
-      <c r="D134" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>QA Speech-to-Text Audio Collection Project</t>
+          <t>Software Development Engineer II Full Stack - Business (Remote @ Colombia)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>qa, worldwide (place)</t>
+          <t>full stack, software, engineer, anywhere (place)</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Entry-level</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8650,12 +8652,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/qa-speech-to-text-audio-collection-project</t>
+          <t>https://weworkremotely.com/remote-jobs/offerup-software-development-engineer-ii-full-stack-business-remote-colombia</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>a44e738ec6</t>
+          <t>6fe968b6b9</t>
         </is>
       </c>
     </row>
@@ -8667,21 +8669,21 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AI/RAG engineer</t>
+          <t>QA Speech-to-Text Audio Collection Project</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CoinMarketCap</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8696,27 +8698,27 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>engineer, ai, ml (tag), worldwide (place)</t>
+          <t>qa, worldwide (place)</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>RAG-AI-Engineer, Machine-Learning-Engineering, AI-Engineering, RAG-Development, Vector-Search-Engineer, IA-RAG-Engineer, AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, Mid-level</t>
+          <t>Entry-level</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/coinmarketcap/jobs/ai-rag-engineer</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/qa-speech-to-text-audio-collection-project</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>d199d5cdfc</t>
+          <t>a44e738ec6</t>
         </is>
       </c>
     </row>
@@ -8732,52 +8734,52 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI/RAG engineer</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>CoinMarketCap</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>engineer, ai, mumbai (place)</t>
+          <t>engineer, ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>RAG-AI-Engineer, Machine-Learning-Engineering, AI-Engineering, RAG-Development, Vector-Search-Engineer, IA-RAG-Engineer, AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723676?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F83D2913763A01EA6FBE321571CA8B989BE3F382</t>
+          <t>https://himalayas.app/companies/coinmarketcap/jobs/ai-rag-engineer</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>faa646b456</t>
+          <t>d199d5cdfc</t>
         </is>
       </c>
     </row>
@@ -8798,12 +8800,12 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Data Science-Index Quant Specialist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8818,27 +8820,27 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>data science, mumbai (place)</t>
+          <t>engineer, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Accounting &amp; Finance Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5843137505?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC4079028ED7338B991CD57034DE9EA5AC8D9A0B</t>
+          <t>https://www.adzuna.in/land/ad/5846723676?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F83D2913763A01EA6FBE321571CA8B989BE3F382</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>6ec3848d0b</t>
+          <t>faa646b456</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8861,17 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Science-Index Quant Specialist</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gurgaon, Haryana</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8879,27 +8881,27 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>data scientist, gurgaon (place)</t>
+          <t>data science, mumbai (place)</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Accounting &amp; Finance Jobs</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5849297019?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E87B9A5E2A9605281144BBEA53533DB7165D1FA0</t>
+          <t>https://www.adzuna.in/land/ad/5843137505?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC4079028ED7338B991CD57034DE9EA5AC8D9A0B</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>e2cd9eda9e</t>
+          <t>6ec3848d0b</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8927,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>Gurgaon, Haryana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8940,7 +8942,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>data scientist, delhi (place)</t>
+          <t>data scientist, gurgaon (place)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8955,12 +8957,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5848650875?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4DF45BC4D3A230C0689E561399F3F0BA2C0FC825</t>
+          <t>https://www.adzuna.in/land/ad/5849297019?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E87B9A5E2A9605281144BBEA53533DB7165D1FA0</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>83a3456095</t>
+          <t>e2cd9eda9e</t>
         </is>
       </c>
     </row>
@@ -8976,52 +8978,52 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>GTM AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Customer.io</t>
+          <t>Danaher</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>New Delhi, Delhi</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>data scientist, delhi (place)</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/customer-io-gtm-ai-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5848650875?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4DF45BC4D3A230C0689E561399F3F0BA2C0FC825</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>19a2ae7abb</t>
+          <t>83a3456095</t>
         </is>
       </c>
     </row>
@@ -9037,17 +9039,17 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Performance Creative Strategist and AI Producer</t>
+          <t>GTM AI Engineer</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Icarus Digital Marketing</t>
+          <t>Customer.io</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -9062,7 +9064,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9077,12 +9079,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/icarus-digital-marketing-performance-creative-strategist-and-ai-producer</t>
+          <t>https://weworkremotely.com/remote-jobs/customer-io-gtm-ai-engineer</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>60c87a59fd</t>
+          <t>19a2ae7abb</t>
         </is>
       </c>
     </row>
@@ -9098,37 +9100,37 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>GTM Coordinator, Cloud Native (Talent Pool)</t>
+          <t>Performance Creative Strategist and AI Producer</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Percona</t>
+          <t>Icarus Digital Marketing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bulgaria, Croatia, Czechia, Greece, Hungary, India, Poland, Portugal, Spain</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>cloud, india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>GTM-Coordinator, Talent-Community-Coordinator, Talent-Operations-Coordinator, Entry-level</t>
+          <t>Sales and Marketing, Full-Time</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9138,12 +9140,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/percona/jobs/gtm-coordinator-cloud-native-talent-pool</t>
+          <t>https://weworkremotely.com/remote-jobs/icarus-digital-marketing-performance-creative-strategist-and-ai-producer</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>a97ee1ce9b</t>
+          <t>60c87a59fd</t>
         </is>
       </c>
     </row>
@@ -9159,52 +9161,52 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Offensive Cybersecurity Engineer - Red Team</t>
+          <t>GTM Coordinator, Cloud Native (Talent Pool)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Techno Vista Dynamics</t>
+          <t>Percona</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>APAC,Middle East</t>
+          <t>Bulgaria, Croatia, Czechia, Greece, Hungary, India, Poland, Portugal, Spain</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>engineer, testing (tag), apac (place)</t>
+          <t>cloud, india (place)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Development, engineer,security,penetration testing</t>
+          <t>GTM-Coordinator, Talent-Community-Coordinator, Talent-Operations-Coordinator, Entry-level</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1781770/</t>
+          <t>https://himalayas.app/companies/percona/jobs/gtm-coordinator-cloud-native-talent-pool</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>0bde4f9b82</t>
+          <t>a97ee1ce9b</t>
         </is>
       </c>
     </row>
@@ -9216,56 +9218,56 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Human-Centered AI Data Scientist, Strategy and Talent</t>
+          <t>Offensive Cybersecurity Engineer - Red Team</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank</t>
+          <t>Techno Vista Dynamics</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>APAC,Middle East</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>data scientist, ai, bangalore (place)</t>
+          <t>engineer, testing (tag), apac (place)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Development, engineer,security,penetration testing</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139276?se=1M6Kj_qf8RGoxpN31Vp7kA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C0F814CBDD0355075DDB000131DE4C8D130504ED</t>
+          <t>https://www.workingnomads.com/job/go/1781770/</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>3130787ee8</t>
+          <t>0bde4f9b82</t>
         </is>
       </c>
     </row>
@@ -9281,52 +9283,52 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Java Software Develper Engineer</t>
+          <t>Human-Centered AI Data Scientist, Strategy and Talent</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>Standard Chartered Bank</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>programmer (tag), developer (tag), software, engineer, backend (tag), java, india (place)</t>
+          <t>data scientist, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Java-Development, Software-Engineer, Entry-Level-Software-Development, Backend-Development, Technical-Support, Java-Software-Engineer, Java-Developer, Java-Developer-Jobs, Java-Application-Developer, Java-Programmer, Developer, Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/csg/jobs/java-software-develper-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5837139276?se=1M6Kj_qf8RGoxpN31Vp7kA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C0F814CBDD0355075DDB000131DE4C8D130504ED</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>7626a2cdd6</t>
+          <t>3130787ee8</t>
         </is>
       </c>
     </row>
@@ -9342,22 +9344,22 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Android Software Engineer</t>
+          <t>Java Software Develper Engineer</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9367,27 +9369,27 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>software engineer, android, kotlin (tag), worldwide (place)</t>
+          <t>programmer (tag), developer (tag), software, engineer, backend (tag), java, india (place)</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Android-Software-Engineer, Mobile-Development, Android-Development, Software-Engineer, Kotlin, Android-Engineer, Android-Software-Engineering, Mobile-Android-Engineer, Android-Systems-Engineer, Android-Engineering, Mobile-Software-Engineer, Senior</t>
+          <t>Java-Development, Software-Engineer, Entry-Level-Software-Development, Backend-Development, Technical-Support, Java-Software-Engineer, Java-Developer, Java-Developer-Jobs, Java-Application-Developer, Java-Programmer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/hudson-manpower/jobs/android-software-engineer</t>
+          <t>https://himalayas.app/companies/csg/jobs/java-software-develper-engineer</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>afb7954487</t>
+          <t>7626a2cdd6</t>
         </is>
       </c>
     </row>
@@ -9403,37 +9405,37 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Application Security Engineer II</t>
+          <t>Android Software Engineer</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>engineer, devops (tag), anywhere (place)</t>
+          <t>software engineer, android, kotlin (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Android-Software-Engineer, Mobile-Development, Android-Development, Software-Engineer, Kotlin, Android-Engineer, Android-Software-Engineering, Mobile-Android-Engineer, Android-Systems-Engineer, Android-Engineering, Mobile-Software-Engineer, Senior</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9443,12 +9445,12 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/abnormal-application-security-engineer-ii</t>
+          <t>https://himalayas.app/companies/hudson-manpower/jobs/android-software-engineer</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>dc9a51cdbc</t>
+          <t>afb7954487</t>
         </is>
       </c>
     </row>
@@ -9460,56 +9462,56 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>DESARROLLADOR FULL STACK</t>
+          <t>Application Security Engineer II</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kruger NearShore LLC - Rekluti</t>
+          <t>Abnormal</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>full stack, front end (tag), backend (tag), angular (tag), testing (tag), python (tag), golang (tag), devops (tag), cloud (tag), git (tag)</t>
+          <t>engineer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>full stack, front end, python, dev, testing, web dev, quality assurance, devops, c, cloud, nosql, git, flutter, angular, mobile, golang, backend, digital nomad</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-desarrollador-full-stack-kruger-nearshore-llc-rekluti-1137062</t>
+          <t>https://weworkremotely.com/remote-jobs/abnormal-application-security-engineer-ii</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>911da99485</t>
+          <t>dc9a51cdbc</t>
         </is>
       </c>
     </row>
@@ -9525,52 +9527,52 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AI Transformation Owner, Product &amp; Design</t>
+          <t>DESARROLLADOR FULL STACK</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Kruger NearShore LLC - Rekluti</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>full stack, front end (tag), backend (tag), angular (tag), testing (tag), python (tag), golang (tag), devops (tag), cloud (tag), git (tag)</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Product, Full-Time</t>
+          <t>full stack, front end, python, dev, testing, web dev, quality assurance, devops, c, cloud, nosql, git, flutter, angular, mobile, golang, backend, digital nomad</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/gitlab-ai-transformation-owner-product-design</t>
+          <t>https://remoteOK.com/remote-jobs/remote-desarrollador-full-stack-kruger-nearshore-llc-rekluti-1137062</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>a0e38d6b98</t>
+          <t>911da99485</t>
         </is>
       </c>
     </row>
@@ -9586,52 +9588,52 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>AI Transformation Owner, Product &amp; Design</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Forrester Research, Inc. (US)</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>developer, software (tag), cloud (tag), india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Salesforce-Developer, CRM-Developer, Salesforce-Administrator, Integration-Developer, Software-Developer, Salesforce-CRM-Developer, Salesforce-Application-Developer, Salesforce-Sales-Cloud-Developer, Salesforce-Development, Salesforce-Solutions-Developer, Salesforce-Platform-Developer, Salesforce-Apex-Developer, Force.Com-Developer, Mid-level</t>
+          <t>Product, Full-Time</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/forrester-research-inc-us/jobs/salesforce-developer-8148624472</t>
+          <t>https://weworkremotely.com/remote-jobs/gitlab-ai-transformation-owner-product-design</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>bbbc562c11</t>
+          <t>a0e38d6b98</t>
         </is>
       </c>
     </row>
@@ -9647,17 +9649,17 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>IT Systems Administrator</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ralliant</t>
+          <t>Forrester Research, Inc. (US)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9672,27 +9674,27 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>developer (tag), engineer (tag), india (place)</t>
+          <t>developer, software (tag), cloud (tag), india (place)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Power-Platform-Engineer, Business-intelligence-Engineer, Analytics-Engineer, Microsoft-Fabric-Engineer, Power-BI-Developer, IT-Systems-Administrator, IT-System-Administrator, Systems-Administrator, IT-Systems-Administration, IT-Administrator, Systems-Support-Administrator, Mid-level</t>
+          <t>Salesforce-Developer, CRM-Developer, Salesforce-Administrator, Integration-Developer, Software-Developer, Salesforce-CRM-Developer, Salesforce-Application-Developer, Salesforce-Sales-Cloud-Developer, Salesforce-Development, Salesforce-Solutions-Developer, Salesforce-Platform-Developer, Salesforce-Apex-Developer, Force.Com-Developer, Mid-level</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ralliant/jobs/it-systems-administrator</t>
+          <t>https://himalayas.app/companies/forrester-research-inc-us/jobs/salesforce-developer-8148624472</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>a720a38bd1</t>
+          <t>bbbc562c11</t>
         </is>
       </c>
     </row>
@@ -9704,56 +9706,56 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Talent Pool -FP&amp;A- Data Scientist / Analytics Specialist / Data &amp; AI Specialist</t>
+          <t>IT Systems Administrator</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ralliant</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>data scientist, ai, bangalore (place)</t>
+          <t>developer (tag), engineer (tag), india (place)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Energy, Oil &amp; Gas Jobs</t>
+          <t>Power-Platform-Engineer, Business-intelligence-Engineer, Analytics-Engineer, Microsoft-Fabric-Engineer, Power-BI-Developer, IT-Systems-Administrator, IT-System-Administrator, Systems-Administrator, IT-Systems-Administration, IT-Administrator, Systems-Support-Administrator, Mid-level</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773115?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=888721B9EAAF876B1F079BC209DECF1099E63440</t>
+          <t>https://himalayas.app/companies/ralliant/jobs/it-systems-administrator</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>5ee47ace79</t>
+          <t>a720a38bd1</t>
         </is>
       </c>
     </row>
@@ -9769,17 +9771,17 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AI and Automation Developer</t>
+          <t>Talent Pool -FP&amp;A- Data Scientist / Analytics Specialist / Data &amp; AI Specialist</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9794,27 +9796,27 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>automation, developer, ai, bangalore (place)</t>
+          <t>data scientist, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Energy, Oil &amp; Gas Jobs</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5847959817?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44960F01CCAE33F814C0EF4448956DF38E8344F5</t>
+          <t>https://www.adzuna.in/land/ad/5785773115?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=888721B9EAAF876B1F079BC209DECF1099E63440</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>98337240aa</t>
+          <t>5ee47ace79</t>
         </is>
       </c>
     </row>
@@ -9830,52 +9832,52 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>DevOps &amp; Security Engineer - AI-Native Healthcare SaaS</t>
+          <t>AI and Automation Developer</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Zenara Health</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>engineer, devops, ai, anywhere (place)</t>
+          <t>automation, developer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/zenara-health-devops-security-engineer-ai-native-healthcare-saas</t>
+          <t>https://www.adzuna.in/land/ad/5847959817?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44960F01CCAE33F814C0EF4448956DF38E8344F5</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>d592e60ddc</t>
+          <t>98337240aa</t>
         </is>
       </c>
     </row>
@@ -9891,37 +9893,37 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps &amp; Security Engineer - AI-Native Healthcare SaaS</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Zenara Health</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>data scientist, mumbai (place)</t>
+          <t>engineer, devops, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9931,12 +9933,12 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723381?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F9660467E3895814968DA45F3A82EF6912496F70</t>
+          <t>https://weworkremotely.com/remote-jobs/zenara-health-devops-security-engineer-ai-native-healthcare-saas</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>c46d670134</t>
+          <t>d592e60ddc</t>
         </is>
       </c>
     </row>
@@ -9962,12 +9964,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9977,7 +9979,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data scientist, mumbai (place)</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9987,17 +9989,17 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837138848?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=86962F79F06A105F30676367582529277DE10978</t>
+          <t>https://www.adzuna.in/land/ad/5846723381?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F9660467E3895814968DA45F3A82EF6912496F70</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>39dacd7158</t>
+          <t>c46d670134</t>
         </is>
       </c>
     </row>
@@ -10018,12 +10020,12 @@
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Itvedant Education Pvt. Ltd.</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -10038,7 +10040,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10048,17 +10050,17 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5833434843?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=95E30E442ED8EDC695067D6ACDD8806A1A4DBE0E</t>
+          <t>https://www.adzuna.in/land/ad/5837138848?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=86962F79F06A105F30676367582529277DE10978</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>660701d5cb</t>
+          <t>39dacd7158</t>
         </is>
       </c>
     </row>
@@ -10079,17 +10081,17 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Itvedant Education Pvt. Ltd.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10099,7 +10101,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>engineer, ai, hyderabad (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10109,17 +10111,17 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139103?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=23D035D0F5CFDFF88D2FBA2CB9721442B70F9874</t>
+          <t>https://www.adzuna.in/land/ad/5833434843?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=95E30E442ED8EDC695067D6ACDD8806A1A4DBE0E</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>c2ca14412d</t>
+          <t>660701d5cb</t>
         </is>
       </c>
     </row>
@@ -10140,17 +10142,17 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10160,7 +10162,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>engineer, ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10170,17 +10172,17 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773097?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1AD120B3FB3DFBC7F01669BC535E68EC0F2123A3</t>
+          <t>https://www.adzuna.in/land/ad/5837139103?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=23D035D0F5CFDFF88D2FBA2CB9721442B70F9874</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>1a0dea6270</t>
+          <t>c2ca14412d</t>
         </is>
       </c>
     </row>
@@ -10201,17 +10203,17 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10221,7 +10223,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>engineer, ai, bangalore (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10231,17 +10233,17 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723241?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0084818D71681FAC4F572D55AE1C6BC637792931</t>
+          <t>https://www.adzuna.in/land/ad/5785773097?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1AD120B3FB3DFBC7F01669BC535E68EC0F2123A3</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>a2c0a3fc16</t>
+          <t>1a0dea6270</t>
         </is>
       </c>
     </row>
@@ -10262,17 +10264,17 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Part time Data Science Instructor</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10282,27 +10284,27 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>engineer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Part time Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5850983469?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0F708DAB080760E3C6FB3FC40EA3A64A7B0306D9</t>
+          <t>https://www.adzuna.in/land/ad/5846723241?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0084818D71681FAC4F572D55AE1C6BC637792931</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>fa169c0060</t>
+          <t>a2c0a3fc16</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10325,12 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer for AI &amp;DS, BSI</t>
+          <t>Part time Data Science Instructor</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -10343,27 +10345,27 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>engineer, ai, india (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Part time Jobs</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785771743?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F6DC64E0C8FB2D27FC25CBE24085394F367A2687</t>
+          <t>https://www.adzuna.in/land/ad/5850983469?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0F708DAB080760E3C6FB3FC40EA3A64A7B0306D9</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>3fd60b2320</t>
+          <t>fa169c0060</t>
         </is>
       </c>
     </row>
@@ -10384,17 +10386,17 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Agentic AI Engineer for AI &amp;DS, BSI</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10404,7 +10406,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>engineer, ai, mumbai (place)</t>
+          <t>engineer, ai, india (place)</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10419,12 +10421,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773171?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2185A7049B5506DF1182A45172761BBEF73613FA</t>
+          <t>https://www.adzuna.in/land/ad/5785771743?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F6DC64E0C8FB2D27FC25CBE24085394F367A2687</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>43f406da07</t>
+          <t>3fd60b2320</t>
         </is>
       </c>
     </row>
@@ -10445,17 +10447,17 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Data Scientist - People Analytics</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10465,7 +10467,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>engineer, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10475,17 +10477,17 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5821999876?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=08993CE6BE520CA2C34926E81E8CBB0072304E1F</t>
+          <t>https://www.adzuna.in/land/ad/5785773171?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2185A7049B5506DF1182A45172761BBEF73613FA</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>187dc9c03e</t>
+          <t>43f406da07</t>
         </is>
       </c>
     </row>
@@ -10506,17 +10508,17 @@
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>Data Scientist - People Analytics</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Itvedant Education Pvt. Ltd.</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10526,27 +10528,27 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Teaching Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5852476426?se=NskdSSae8RGSb8VpDRDiVA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2B7C55A3F795EE4D2F2D732844EDA9B4CAC3F128</t>
+          <t>https://www.adzuna.in/land/ad/5821999876?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=08993CE6BE520CA2C34926E81E8CBB0072304E1F</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>5c41be551e</t>
+          <t>187dc9c03e</t>
         </is>
       </c>
     </row>
@@ -10562,37 +10564,37 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PHP Developer - Work From Home</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CC Staffing International</t>
+          <t>Itvedant Education Pvt. Ltd.</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>developer, software (tag), engineer (tag), backend (tag), php, india (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>PHP-Developer, Backend-Engineer, Web-Development, Software-Developer, Full-Stack-Developer, Remote-PHP-Developer, PHP-Software-Engineer, Backend-PHP-Developer, Remote-Web-Developer, Developer, Mid-level</t>
+          <t>Teaching Jobs</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -10602,12 +10604,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/cc-staffing-international/jobs/php-developer-work-from-home</t>
+          <t>https://www.adzuna.in/land/ad/5852476426?se=NskdSSae8RGSb8VpDRDiVA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2B7C55A3F795EE4D2F2D732844EDA9B4CAC3F128</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>14b619fb91</t>
+          <t>5c41be551e</t>
         </is>
       </c>
     </row>
@@ -10623,52 +10625,52 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Kannada</t>
+          <t>PHP Developer - Work From Home</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>RWS</t>
+          <t>CC Staffing International</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>ai, delhi (place)</t>
+          <t>developer, software (tag), engineer (tag), backend (tag), php, india (place)</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>PHP-Developer, Backend-Engineer, Web-Development, Software-Developer, Full-Stack-Developer, Remote-PHP-Developer, PHP-Software-Engineer, Backend-PHP-Developer, Remote-Web-Developer, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772642?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=96F9E6C80B83A39F4F2C05268274FD2EBE13B037</t>
+          <t>https://himalayas.app/companies/cc-staffing-international/jobs/php-developer-work-from-home</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>bb43fd7b08</t>
+          <t>14b619fb91</t>
         </is>
       </c>
     </row>
@@ -10689,7 +10691,7 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Marathi</t>
+          <t>AI Data Specialist - Kannada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10724,12 +10726,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772098?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=B26B7FB6A299BC3A2BFD29BF94BF59C981A24A29</t>
+          <t>https://www.adzuna.in/land/ad/5785772642?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=96F9E6C80B83A39F4F2C05268274FD2EBE13B037</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>fe688433d1</t>
+          <t>bb43fd7b08</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10752,7 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Telugu</t>
+          <t>AI Data Specialist - Marathi</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -10785,12 +10787,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785770664?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=D13E17364CDB48C8A2B963F62AC42C33A76C021B</t>
+          <t>https://www.adzuna.in/land/ad/5785772098?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=B26B7FB6A299BC3A2BFD29BF94BF59C981A24A29</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>91c279dfff</t>
+          <t>fe688433d1</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10813,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Hindi</t>
+          <t>AI Data Specialist - Telugu</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10841,17 +10843,17 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5795883387?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=38289BC2F5CA723017CE2916CC4536DEA978B9A6</t>
+          <t>https://www.adzuna.in/land/ad/5785770664?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=D13E17364CDB48C8A2B963F62AC42C33A76C021B</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>170ea3eac1</t>
+          <t>91c279dfff</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10874,7 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Tamil</t>
+          <t>AI Data Specialist - Hindi</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -10902,17 +10904,17 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772320?se=xp3UHeGd8RGIEJB03vDchg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AB56F1DD143407CEE31E12C4126DC533B06A2AD3</t>
+          <t>https://www.adzuna.in/land/ad/5795883387?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=38289BC2F5CA723017CE2916CC4536DEA978B9A6</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>616fb76ab0</t>
+          <t>170ea3eac1</t>
         </is>
       </c>
     </row>
@@ -10928,52 +10930,52 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Agent Operations Engineer - Fully Remote | Upto $500/task Task based</t>
+          <t>AI Data Specialist - Tamil</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>RWS</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>New Delhi, Delhi</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>engineer, ai (tag), india (place)</t>
+          <t>ai, delhi (place)</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Agent-Engineering, LLMOperations, AI-Engineering, AI-Operations, Machine-Learning-Engineering, AgentOps-Engineer, Agent-Orchestration-Engineer, AI-Agents-Engineer, Operations-Engineer, Remote-AI-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/mercor/jobs/agent-operations-engineer-fully-remote-upto-500-task-task-based</t>
+          <t>https://www.adzuna.in/land/ad/5785772320?se=xp3UHeGd8RGIEJB03vDchg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AB56F1DD143407CEE31E12C4126DC533B06A2AD3</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>be05dc52ff</t>
+          <t>616fb76ab0</t>
         </is>
       </c>
     </row>
@@ -10989,17 +10991,17 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS Authorized Instructor</t>
+          <t>Agent Operations Engineer - Fully Remote | Upto $500/task Task based</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ITC WORLDWIDE</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -11014,12 +11016,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>cloud (tag), aws, india (place)</t>
+          <t>engineer, ai (tag), india (place)</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>AWS-Training, Cloud-Computing-Instructor, Technical-Trainer, AWS-Authorized-Instructor, Cloud-Education, AWS-Certification-Training, Cloud-Instructor, Cloud-Computing-Trainer, Senior</t>
+          <t>Agent-Engineering, LLMOperations, AI-Engineering, AI-Operations, Machine-Learning-Engineering, AgentOps-Engineer, Agent-Orchestration-Engineer, AI-Agents-Engineer, Operations-Engineer, Remote-AI-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -11029,12 +11031,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/itc-worldwide/jobs/aws-authorized-instructor</t>
+          <t>https://himalayas.app/companies/mercor/jobs/agent-operations-engineer-fully-remote-upto-500-task-task-based</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>a42ddc7b02</t>
+          <t>be05dc52ff</t>
         </is>
       </c>
     </row>
@@ -11050,37 +11052,37 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Associate Instructor</t>
+          <t>AWS Authorized Instructor</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>ITC WORLDWIDE</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>devops (tag), associate (level), anywhere (place)</t>
+          <t>cloud (tag), aws, india (place)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>AWS-Training, Cloud-Computing-Instructor, Technical-Trainer, AWS-Authorized-Instructor, Cloud-Education, AWS-Certification-Training, Cloud-Instructor, Cloud-Computing-Trainer, Senior</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -11090,12 +11092,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/beyondtrust-associate-instructor</t>
+          <t>https://himalayas.app/companies/itc-worldwide/jobs/aws-authorized-instructor</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>4c1963b96c</t>
+          <t>a42ddc7b02</t>
         </is>
       </c>
     </row>
@@ -11111,52 +11113,52 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>E-learning Developer</t>
+          <t>Associate Instructor</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Crowe UAE</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>developer, ahmedabad (place)</t>
+          <t>devops (tag), associate (level), anywhere (place)</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5850983902?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F927DE790D9874EE6BA8C142D15CF3A7A97BFA7E</t>
+          <t>https://weworkremotely.com/remote-jobs/beyondtrust-associate-instructor</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>843701dc9e</t>
+          <t>4c1963b96c</t>
         </is>
       </c>
     </row>
@@ -11172,52 +11174,52 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Developer Educator</t>
+          <t>E-learning Developer</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>PlanetScale</t>
+          <t>Crowe UAE</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Ahmedabad, Gujarat</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>developer, anywhere (place)</t>
+          <t>developer, ahmedabad (place)</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/planetscale-developer-educator</t>
+          <t>https://www.adzuna.in/land/ad/5850983902?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F927DE790D9874EE6BA8C142D15CF3A7A97BFA7E</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>c72ab4031d</t>
+          <t>843701dc9e</t>
         </is>
       </c>
     </row>
@@ -11233,50 +11235,111 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
+          <t>Developer Educator</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>PlanetScale</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Anywhere in the World</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>weworkremotely</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>developer, anywhere (place)</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Sales and Marketing, Full-Time</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/planetscale-developer-educator</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>c72ab4031d</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>11</v>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
           <t>Consultant Implementation Engineer</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>Harbor</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="G178" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="H178" t="inlineStr">
         <is>
           <t>remoteok</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="I178" t="inlineStr">
         <is>
           <t>engineer, golang (tag), remote (place)</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
+      <c r="J178" t="inlineStr">
         <is>
           <t>consulting, technical, accounting, legal, golang, engineer</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="K178" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-consultant-implementation-engineer-harbor-1136987</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t>f724e65bc8</t>
         </is>
@@ -11284,7 +11347,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A177" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of: new, applied, skipped" prompt="Mark this job applied once you have applied." type="list">
+    <dataValidation sqref="A2:A178" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of: new, applied, skipped" prompt="Mark this job applied once you have applied." type="list">
       <formula1>"new,applied,skipped"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M178"/>
+  <dimension ref="A1:M179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -569,56 +569,56 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Anthropic Fellows Program, AI Safety &amp; Security</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlys</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>artificial intelligence, intern (level), india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>All Other Remote, Full-Time</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876870198?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=887C5853FA1B767B096C42327F5C3826C21742CE</t>
+          <t>https://weworkremotely.com/remote-jobs/anthropic-anthropic-fellows-program-ai-safety-security</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>b169bf4100</t>
+          <t>bf649aa9a3</t>
         </is>
       </c>
     </row>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MTS-1 Machine Learning Engineer</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Atlys</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>artificial intelligence, intern (level), india (place)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877184305?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8749753C0B487764A74F37A03D96F548F15161A9</t>
+          <t>https://www.adzuna.in/land/ad/5876870198?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=887C5853FA1B767B096C42327F5C3826C21742CE</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>fab40e54d1</t>
+          <t>b169bf4100</t>
         </is>
       </c>
     </row>
@@ -695,52 +695,52 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MTS-1 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smartcuts</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), frontend (tag), worldwide (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Engineering, Software-Engineer, Frontend-Development, Fullstack-Development, Browser-Extension-Development, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Software-Design-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/smartcuts/jobs/software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5877184305?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8749753C0B487764A74F37A03D96F548F15161A9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1191a23402</t>
+          <t>fab40e54d1</t>
         </is>
       </c>
     </row>
@@ -756,17 +756,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GitHub Contributor</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Smartcuts</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), frontend (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
+          <t>Engineering, Software-Engineer, Frontend-Development, Fullstack-Development, Browser-Extension-Development, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Software-Design-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-106728860</t>
+          <t>https://himalayas.app/companies/smartcuts/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>f02b389972</t>
+          <t>1191a23402</t>
         </is>
       </c>
     </row>
@@ -813,58 +813,56 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Backend Engineer, IAM</t>
+          <t>GitHub Contributor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>engineer, backend, anywhere (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/reddit-backend-engineer-iam</t>
+          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-106728860</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>790d0d9505</t>
+          <t>f02b389972</t>
         </is>
       </c>
     </row>
@@ -883,16 +881,16 @@
         <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Developer Advocate - Service Management</t>
+          <t>Backend Engineer, IAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -907,12 +905,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>developer, devops (tag), anywhere (place)</t>
+          <t>engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -922,12 +920,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/datadog-developer-advocate-service-management</t>
+          <t>https://weworkremotely.com/remote-jobs/reddit-backend-engineer-iam</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4df8de53d8</t>
+          <t>790d0d9505</t>
         </is>
       </c>
     </row>
@@ -943,37 +941,39 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>QA Testers Wanted (No experience needed)</t>
+          <t>Developer Advocate - Service Management</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tester Work</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Australia &amp; New Zealand (REMOTE)</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>qa, remote (place)</t>
+          <t>developer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1860630/</t>
+          <t>https://weworkremotely.com/remote-jobs/datadog-developer-advocate-service-management</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>bf909f7a1f</t>
+          <t>4df8de53d8</t>
         </is>
       </c>
     </row>
@@ -1000,58 +1000,56 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>74</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist II, ML Infrastructure</t>
+          <t>QA Testers Wanted (No experience needed)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Tester Work</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Australia &amp; New Zealand (REMOTE)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data scientist, ml, anywhere (place)</t>
+          <t>qa, remote (place)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-ml-infrastructure</t>
+          <t>https://www.workingnomads.com/job/go/1860630/</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>a84319c791</t>
+          <t>bf909f7a1f</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1065,14 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist II, Infrastructure</t>
+          <t>Data Scientist II, ML Infrastructure</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data scientist, anywhere (place)</t>
+          <t>data scientist, ml, anywhere (place)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-infrastructure</t>
+          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-ml-infrastructure</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>def323e358</t>
+          <t>a84319c791</t>
         </is>
       </c>
     </row>
@@ -1128,52 +1128,52 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II, Infrastructure</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>software engineer, golang (tag)</t>
+          <t>data scientist, anywhere (place)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>golang, dev, engineer, digital nomad</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-mirantis-1137387</t>
+          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-infrastructure</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0eb27a0401</t>
+          <t>def323e358</t>
         </is>
       </c>
     </row>
@@ -1185,41 +1185,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Science Engineer - AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data science, engineer, ai, bangalore (place)</t>
+          <t>software engineer, golang (tag)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>golang, dev, engineer, digital nomad</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880523483?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44AFB881700BC2524FE70C04638A2D65741F5C06</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-mirantis-1137387</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>987c89c61a</t>
+          <t>0eb27a0401</t>
         </is>
       </c>
     </row>
@@ -1250,22 +1250,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning</t>
+          <t>Data Science Engineer - AI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kotak Neo</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>machine learning, ai, mumbai (place)</t>
+          <t>data science, engineer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880062262?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC74E214D0612FE80831EDD83B8CF67B6032A3E9</t>
+          <t>https://www.adzuna.in/land/ad/5880523483?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44AFB881700BC2524FE70C04638A2D65741F5C06</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>c8b4bb4ba3</t>
+          <t>987c89c61a</t>
         </is>
       </c>
     </row>
@@ -1311,37 +1311,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>AI &amp; Machine Learning</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Kotak Neo</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>software (tag), engineer, ai (tag), ml, worldwide (place)</t>
+          <t>machine learning, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Machine-Learning-Engineer, AI-ML-Engineer, ML-Software-Engineer, ML-Research-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ml-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5880062262?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC74E214D0612FE80831EDD83B8CF67B6032A3E9</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6b92e0e58d</t>
+          <t>c8b4bb4ba3</t>
         </is>
       </c>
     </row>
@@ -1377,47 +1377,47 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data science, india (place), chandigarh (place)</t>
+          <t>software (tag), engineer, ai (tag), ml, worldwide (place)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Machine-Learning-Engineer, AI-ML-Engineer, ML-Software-Engineer, ML-Research-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5879662958?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7C90B2BB52AA81EB60C613281A1D6AF4E5DC8BD8</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ml-engineer</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6557a8e75a</t>
+          <t>6b92e0e58d</t>
         </is>
       </c>
     </row>
@@ -1433,54 +1433,52 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PhD &amp; Academic Expert</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ml (tag), worldwide (place)</t>
+          <t>data science, india (place), chandigarh (place)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Academic-Expert, PhD-Specialist-Consultant, Academic-Consultant, Academic-Subject-Matter-Expert, Academic-Professional, ML-Research-PhD-Expert, PhD-Researcher, Education-Expert, Mid-level, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/phd-academic-expert</t>
+          <t>https://www.adzuna.in/land/ad/5879662958?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7C90B2BB52AA81EB60C613281A1D6AF4E5DC8BD8</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>a8281d77e1</t>
+          <t>6557a8e75a</t>
         </is>
       </c>
     </row>
@@ -1492,23 +1490,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>PhD &amp; Academic Expert</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dura Digital</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1523,27 +1521,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>engineer, backend (tag), python (tag), ai, ml (tag), worldwide (place)</t>
+          <t>ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AI-Engineer, Machine-Learning-Engineer, Backend-Engineer, Data-Engineer, MLOps-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Senior</t>
+          <t>Academic-Expert, PhD-Specialist-Consultant, Academic-Consultant, Academic-Subject-Matter-Expert, Academic-Professional, ML-Research-PhD-Expert, PhD-Researcher, Education-Expert, Mid-level, Senior</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/dura-digital/jobs/ai-engineer</t>
+          <t>https://himalayas.app/companies/micro1/jobs/phd-academic-expert</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>8666ff7b1c</t>
+          <t>a8281d77e1</t>
         </is>
       </c>
     </row>
@@ -1559,17 +1557,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>50</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Facial Data Collection Associate</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Dura Digital</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ai, associate (level), worldwide (place)</t>
+          <t>engineer, backend (tag), python (tag), ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>AI-Data-Collection-Specialist, Data-Collection-Associate, Facial-Recognition-Data-Collection, AI-Services-Associate, AI-Operations-Associate, AI-Associate, Entry-level</t>
+          <t>AI-Engineer, Machine-Learning-Engineer, Backend-Engineer, Data-Engineer, MLOps-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Senior</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-facial-data-collection-associate</t>
+          <t>https://himalayas.app/companies/dura-digital/jobs/ai-engineer</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>a024718d12</t>
+          <t>8666ff7b1c</t>
         </is>
       </c>
     </row>
@@ -1620,54 +1620,52 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>49</v>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Facial Data Collection Associate</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Omnicom Global Solutions</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>ai, associate (level), worldwide (place)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Data-Collection-Specialist, Data-Collection-Associate, Facial-Recognition-Data-Collection, AI-Services-Associate, AI-Operations-Associate, AI-Associate, Entry-level</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880062427?se=4EjJjS6u8RGGGqTWwpKkng&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E0A2211C95EBCFB9C1236FB6E39F7FBF4A7836A8</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-facial-data-collection-associate</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>c539f926b2</t>
+          <t>a024718d12</t>
         </is>
       </c>
     </row>
@@ -1683,54 +1681,54 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Financial Systems Expert</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Omnicom Global Solutions</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>developer (tag), engineer (tag), worldwide (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Financial-Systems-Specialist, Financial-Systems-Consultant, Financial-Systems-Advisor, Finance-Systems-Specialist, Financial-Systems-Consulting, Finance-Systems-Consultant, Financial-Systems-Developer, Financial-Systems-Integration-Specialist, Financial-Systems-Architect, Financial-Systems-Engineer, Mid-level, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/financial-systems-expert</t>
+          <t>https://www.adzuna.in/land/ad/5880062427?se=4EjJjS6u8RGGGqTWwpKkng&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E0A2211C95EBCFB9C1236FB6E39F7FBF4A7836A8</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>a8090f5869</t>
+          <t>c539f926b2</t>
         </is>
       </c>
     </row>
@@ -1742,56 +1740,58 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>79</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DVP - Data Science AI</t>
+          <t>Financial Systems Expert</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IndiaFirst Life</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>data science, ai, mumbai (place)</t>
+          <t>developer (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Financial-Systems-Specialist, Financial-Systems-Consultant, Financial-Systems-Advisor, Finance-Systems-Specialist, Financial-Systems-Consulting, Finance-Systems-Consultant, Financial-Systems-Developer, Financial-Systems-Integration-Specialist, Financial-Systems-Architect, Financial-Systems-Engineer, Mid-level, Senior</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877452336?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C389ADE3462A8F960BCEB9BFB3D8C01182D8F284</t>
+          <t>https://himalayas.app/companies/micro1/jobs/financial-systems-expert</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>d4091e9b06</t>
+          <t>a8090f5869</t>
         </is>
       </c>
     </row>
@@ -1807,22 +1807,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DVP - Data Science AI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ryewalk</t>
+          <t>IndiaFirst Life</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data scientist, chennai (place)</t>
+          <t>data science, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877457613?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=858E7DDB9C73029BB012BE9266CDC5516D57BB06</t>
+          <t>https://www.adzuna.in/land/ad/5877452336?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C389ADE3462A8F960BCEB9BFB3D8C01182D8F284</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5b1e04fbec</t>
+          <t>d4091e9b06</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Ryewalk</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876016078?se=tjzQcmWt8RGk7Nm076a3Fw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=076A6D8BF6D1FAB77910335EA1D3406F73F06FDC</t>
+          <t>https://www.adzuna.in/land/ad/5877457613?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=858E7DDB9C73029BB012BE9266CDC5516D57BB06</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03602a7f75</t>
+          <t>5b1e04fbec</t>
         </is>
       </c>
     </row>
@@ -1929,52 +1929,52 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>QA Tester Entry Level</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ace IT Careers</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>testing (tag), qa, entry level (level), remote (place)</t>
+          <t>data scientist, chennai (place)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>testing, dev, analyst, quality assurance, digital nomad</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-qa-tester-entry-level-ace-it-careers-1136701</t>
+          <t>https://www.adzuna.in/land/ad/5876016078?se=tjzQcmWt8RGk7Nm076a3Fw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=076A6D8BF6D1FAB77910335EA1D3406F73F06FDC</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>066819b5ee</t>
+          <t>03602a7f75</t>
         </is>
       </c>
     </row>
@@ -1990,54 +1990,52 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>32</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>QA Tester Entry Level</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sun King</t>
+          <t>Ace IT Careers</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>software (tag), engineer, cloud (tag), api (tag), india (place)</t>
+          <t>testing (tag), qa, entry level (level), remote (place)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Application-Security-Engineer, Security-Engineer, Penetration-Tester, API-Security, Cloud-Security-Engineer, AppSec-Engineer, Application-Security-Engineering, Application-Security-Specialist, Software-Security-Engineer, Mid-level</t>
+          <t>testing, dev, analyst, quality assurance, digital nomad</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/sun-king/jobs/application-security-engineer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-qa-tester-entry-level-ace-it-careers-1136701</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>41b24c0687</t>
+          <t>066819b5ee</t>
         </is>
       </c>
     </row>
@@ -2055,15 +2053,17 @@
       <c r="C27" t="n">
         <v>32</v>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nuclear Physics Specialist - Fully Remote | Upto $100/hr</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>Sun King</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>engineer (tag), ai (tag), india (place)</t>
+          <t>software (tag), engineer, cloud (tag), api (tag), india (place)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Computational-Physics, Nuclear-Physics, Particle-Physics, AI-Evaluation, Scientific-Computing, Nuclear-Physics-AI-Specialist, Freelance-Physics-Specialist, Reactor-Physics-Engineer, Freelance-Physics-Expert, Physics-Research-Specialist, Physics-Freelancer, Mid-level</t>
+          <t>Application-Security-Engineer, Security-Engineer, Penetration-Tester, API-Security, Cloud-Security-Engineer, AppSec-Engineer, Application-Security-Engineering, Application-Security-Specialist, Software-Security-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/mercor/jobs/nuclear-physics-specialist-fully-remote-upto-100-hr-6652317191</t>
+          <t>https://himalayas.app/companies/sun-king/jobs/application-security-engineer</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>e80acb6174</t>
+          <t>41b24c0687</t>
         </is>
       </c>
     </row>
@@ -2110,58 +2110,56 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>65</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Nuclear Physics Specialist - Fully Remote | Upto $100/hr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dynamics Monk Consulting Services</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>artificial intelligence, india (place), delhi (place)</t>
+          <t>engineer (tag), ai (tag), india (place)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Computational-Physics, Nuclear-Physics, Particle-Physics, AI-Evaluation, Scientific-Computing, Nuclear-Physics-AI-Specialist, Freelance-Physics-Specialist, Reactor-Physics-Engineer, Freelance-Physics-Expert, Physics-Research-Specialist, Physics-Freelancer, Mid-level</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028069?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F290F3C8F39D5ABB349E29F918917B30A38BA853</t>
+          <t>https://himalayas.app/companies/mercor/jobs/nuclear-physics-specialist-fully-remote-upto-100-hr-6652317191</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9010d87d61</t>
+          <t>e80acb6174</t>
         </is>
       </c>
     </row>
@@ -2177,22 +2175,24 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>54</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vahan.ai</t>
+          <t>Dynamics Monk Consulting Services</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, india (place), delhi (place)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876029045?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1440DAC38EB3556F9000947FA0A0834CFF14AB75</t>
+          <t>https://www.adzuna.in/land/ad/5876028069?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F290F3C8F39D5ABB349E29F918917B30A38BA853</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>56f72b7a03</t>
+          <t>9010d87d61</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2248,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EYEGLOBAL SOLUTIONS PVT. LTD.</t>
+          <t>Vahan.ai</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, chennai (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028703?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9D6C280D30C30F591E884FDA2F691CC4409C3EC6</t>
+          <t>https://www.adzuna.in/land/ad/5876029045?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1440DAC38EB3556F9000947FA0A0834CFF14AB75</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>bafec6742f</t>
+          <t>56f72b7a03</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Appglide Solutions</t>
+          <t>EYEGLOBAL SOLUTIONS PVT. LTD.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876870603?se=DiEjalis8RGQ-MmLyhoJEg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=987B153BD1BD745987463A7F926C3F0CC163AE60</t>
+          <t>https://www.adzuna.in/land/ad/5876028703?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9D6C280D30C30F591E884FDA2F691CC4409C3EC6</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>d4bbc378a8</t>
+          <t>bafec6742f</t>
         </is>
       </c>
     </row>
@@ -2365,17 +2365,17 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MTS-2 Machine Learning Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Appglide Solutions</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, chennai (place)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877184044?se=ME0PiYGs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=DBDB737DEAF34AD8D344749E581C417C10EC5A31</t>
+          <t>https://www.adzuna.in/land/ad/5876870603?se=DiEjalis8RGQ-MmLyhoJEg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=987B153BD1BD745987463A7F926C3F0CC163AE60</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>37872b8c00</t>
+          <t>d4bbc378a8</t>
         </is>
       </c>
     </row>
@@ -2421,37 +2421,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Account Executive, AI/HPC, Neo / Sovereign Cloud (EMEA)</t>
+          <t>MTS-2 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Everpure</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>cloud, ai, anywhere (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/everpure-account-executive-ai-hpc-neo-sovereign-cloud-emea</t>
+          <t>https://www.adzuna.in/land/ad/5877184044?se=ME0PiYGs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=DBDB737DEAF34AD8D344749E581C417C10EC5A31</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>44fbf0ebf8</t>
+          <t>37872b8c00</t>
         </is>
       </c>
     </row>
@@ -2482,39 +2482,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>49</v>
-      </c>
-      <c r="D34" t="n">
-        <v>3</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Account Executive, AI/HPC, Neo / Sovereign Cloud (EMEA)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Infosys Finacle</t>
+          <t>Everpure</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>cloud, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Sales and Marketing, Full-Time</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2524,12 +2522,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876010793?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8D81876C99F248DACDDC8104E41D7CB59A09112B</t>
+          <t>https://weworkremotely.com/remote-jobs/everpure-account-executive-ai-hpc-neo-sovereign-cloud-emea</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>68b1b69943</t>
+          <t>44fbf0ebf8</t>
         </is>
       </c>
     </row>
@@ -2545,37 +2543,39 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>47</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Frontend Developer - Talent Pool</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Espeo Software</t>
+          <t>Infosys Finacle</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>developer, frontend, software (tag), engineer (tag), react (tag), worldwide (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Frontend-Development, Web-Development, Software-Development, ContractWorks, Freelance-Development, Frontend-Development-Jobs, Tech-Talent-Pool, Front-End-Developer, Technology-Talent-Pool, Engineering-Talent-Pool, Frontend-React-Developer, React-Frontend-Developer, Frontend-Engineer, Developer, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/espeo-software/jobs/frontend-developer-talent-pool</t>
+          <t>https://www.adzuna.in/land/ad/5876010793?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8D81876C99F248DACDDC8104E41D7CB59A09112B</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>409bd93507</t>
+          <t>68b1b69943</t>
         </is>
       </c>
     </row>
@@ -2606,17 +2606,17 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe AEP)</t>
+          <t>Frontend Developer - Talent Pool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TechBiz Global</t>
+          <t>Espeo Software</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>data engineer, developer (tag), cloud (tag), worldwide (place)</t>
+          <t>developer, frontend, software (tag), engineer (tag), react (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Data-Engineering, ETL-Development, Cloud-Data-Engineering, Adobe-Experience-Platform, Data-Integration, Adobe-CDP-Engineer, Data-Engineer, Adobe-Experience-Platform-Engineer, Data-Engineer-Jobs, Data-Platform-Engineer, Enterprise-Data-Engineer, Developer, Senior</t>
+          <t>Frontend-Development, Web-Development, Software-Development, ContractWorks, Freelance-Development, Frontend-Development-Jobs, Tech-Talent-Pool, Front-End-Developer, Technology-Talent-Pool, Engineering-Talent-Pool, Frontend-React-Developer, React-Frontend-Developer, Frontend-Engineer, Developer, Senior</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/techbiz-global/jobs/data-engineer-adobe-aep-7933835037</t>
+          <t>https://himalayas.app/companies/espeo-software/jobs/frontend-developer-talent-pool</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>3cf5fcdc34</t>
+          <t>409bd93507</t>
         </is>
       </c>
     </row>
@@ -2667,52 +2667,52 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Social Comms</t>
+          <t>Data Engineer (Adobe AEP)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NOPE</t>
+          <t>TechBiz Global</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ai (tag)</t>
+          <t>data engineer, developer (tag), cloud (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>marketing, education, technical, content writing, social media, ai, social</t>
+          <t>Data-Engineering, ETL-Development, Cloud-Data-Engineering, Adobe-Experience-Platform, Data-Integration, Adobe-CDP-Engineer, Data-Engineer, Adobe-Experience-Platform-Engineer, Data-Engineer-Jobs, Data-Platform-Engineer, Enterprise-Data-Engineer, Developer, Senior</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-social-comms-nope-1137314</t>
+          <t>https://himalayas.app/companies/techbiz-global/jobs/data-engineer-adobe-aep-7933835037</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>417f6ff5ea</t>
+          <t>3cf5fcdc34</t>
         </is>
       </c>
     </row>
@@ -2724,56 +2724,56 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Social Comms</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>NOPE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>ai (tag)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>marketing, education, technical, content writing, social media, ai, social</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876024927?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0BB3A9B6F76E859DE51E5C2F0066293EDC5FE6EA</t>
+          <t>https://remoteOK.com/remote-jobs/remote-social-comms-nope-1137314</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0851d46422</t>
+          <t>417f6ff5ea</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Questhiring</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876027895?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=09A0BE7549E8D3105D5BC0AA92FAA0662C7CD065</t>
+          <t>https://www.adzuna.in/land/ad/5876024927?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0BB3A9B6F76E859DE51E5C2F0066293EDC5FE6EA</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>8a025ec1ce</t>
+          <t>0851d46422</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TBO.COM</t>
+          <t>Questhiring</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026044?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FDDB74C699BD4423DAD1E4FB7120816040F747A</t>
+          <t>https://www.adzuna.in/land/ad/5876027895?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=09A0BE7549E8D3105D5BC0AA92FAA0662C7CD065</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>a427b9cd23</t>
+          <t>8a025ec1ce</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ADB SAFEGATE</t>
+          <t>TBO.COM</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, hyderabad (place)</t>
+          <t>artificial intelligence, engineer, india (place)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026294?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9C70BDA29FFF510B21324AF211D635A868DC48AA</t>
+          <t>https://www.adzuna.in/land/ad/5876026044?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FDDB74C699BD4423DAD1E4FB7120816040F747A</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>292ee6d2c1</t>
+          <t>a427b9cd23</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neural Foundry</t>
+          <t>ADB SAFEGATE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026040?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8CA62DE6EFC7E6B952E843BFE686F26AF0E83028</t>
+          <t>https://www.adzuna.in/land/ad/5876026294?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9C70BDA29FFF510B21324AF211D635A868DC48AA</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>c1e16bca2e</t>
+          <t>292ee6d2c1</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DotKonnekt</t>
+          <t>Neural Foundry</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, hyderabad (place)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026944?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=51439456D8BA015D122C9B9E72B93BC7715ADC62</t>
+          <t>https://www.adzuna.in/land/ad/5876026040?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8CA62DE6EFC7E6B952E843BFE686F26AF0E83028</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>172ee82bd6</t>
+          <t>c1e16bca2e</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Recro</t>
+          <t>DotKonnekt</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876027463?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=40F66C80D240EB217C5AF3C758F1793D002D574F</t>
+          <t>https://www.adzuna.in/land/ad/5876026944?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=51439456D8BA015D122C9B9E72B93BC7715ADC62</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>91af896417</t>
+          <t>172ee82bd6</t>
         </is>
       </c>
     </row>
@@ -3160,17 +3160,17 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer 2</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Frinks AI</t>
+          <t>Recro</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, india (place)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876025062?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=75AA49B421B5A4EB6F3C207636FED47095B332D0</t>
+          <t>https://www.adzuna.in/land/ad/5876027463?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=40F66C80D240EB217C5AF3C758F1793D002D574F</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2d2a6d873d</t>
+          <t>91af896417</t>
         </is>
       </c>
     </row>
@@ -3216,22 +3216,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Specialist</t>
+          <t>Artificial Intelligence Engineer 2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ITC Infotech</t>
+          <t>Frinks AI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>artificial intelligence, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876024946?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=6D480BEF34A3386CBC920920C7CE13B96BCBAD34</t>
+          <t>https://www.adzuna.in/land/ad/5876025062?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=75AA49B421B5A4EB6F3C207636FED47095B332D0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>140496e40b</t>
+          <t>2d2a6d873d</t>
         </is>
       </c>
     </row>
@@ -3282,17 +3282,17 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Artificial Intelligence Specialist</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tech Mahindra</t>
+          <t>ITC Infotech</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>artificial intelligence, bangalore (place)</t>
+          <t>artificial intelligence, india (place)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026586?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=666546215EA3297D7CF61A793A40232CBB0EC67B</t>
+          <t>https://www.adzuna.in/land/ad/5876024946?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=6D480BEF34A3386CBC920920C7CE13B96BCBAD34</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>25604d55ae</t>
+          <t>140496e40b</t>
         </is>
       </c>
     </row>
@@ -3338,22 +3338,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Data and AI Scientist</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>The Edge Partnership - The Edge in Asia</t>
+          <t>Tech Mahindra</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ai, hyderabad (place)</t>
+          <t>artificial intelligence, bangalore (place)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876025532?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AD1D30D29AD931A0AA847E54CFF303EEB0007BE9</t>
+          <t>https://www.adzuna.in/land/ad/5876026586?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=666546215EA3297D7CF61A793A40232CBB0EC67B</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>bc9357c4ff</t>
+          <t>25604d55ae</t>
         </is>
       </c>
     </row>
@@ -3399,52 +3399,52 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AI Response Evaluator</t>
+          <t>Data and AI Scientist</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>iMerit</t>
+          <t>The Edge Partnership - The Edge in Asia</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>All Other Remote, Contract</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/imerit-ai-response-evaluator</t>
+          <t>https://www.adzuna.in/land/ad/5876025532?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AD1D30D29AD931A0AA847E54CFF303EEB0007BE9</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>d4b5bc7818</t>
+          <t>bc9357c4ff</t>
         </is>
       </c>
     </row>
@@ -3460,37 +3460,37 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sustainability Full-Stack Developer (100 % remote) (m/f/d)</t>
+          <t>AI Response Evaluator</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>EWOR GmbH</t>
+          <t>iMerit</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>fullstack (tag), developer, software (tag), engineer (tag), worldwide (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Fullstack-Development, Web-Development, Sustainability, Software-Engineer, Sustainability-Technology, Remote-Senior-Full-Stack-Developer, Remote-Full-Stack-Developer, Full-Stack-Developer, Senior</t>
+          <t>All Other Remote, Contract</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ewor-gmbh/jobs/sustainability-full-stack-developer-100-remote-m-f-d</t>
+          <t>https://weworkremotely.com/remote-jobs/imerit-ai-response-evaluator</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>7da6fdc2ab</t>
+          <t>d4b5bc7818</t>
         </is>
       </c>
     </row>
@@ -3521,12 +3521,12 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Industrial Tech AgentOps Engineer (100 % remote) (m/f/d)</t>
+          <t>Sustainability Full-Stack Developer (100 % remote) (m/f/d)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>engineer, devops (tag), worldwide (place)</t>
+          <t>fullstack (tag), developer, software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>AgentOps-Engineer, Industrial-Technology, Operations-Engineering, Technical-Product-Management, Start-Up-Operations, Remote-Operations-Engineer, Industrial-IoT-Engineer, Remote-DevOps-Engineer, TechOps-Engineer, Remote-Infrastructure-Monitoring-Engineer, Remote-Distributed-Systems-Engineer-II, Mid-level</t>
+          <t>Fullstack-Development, Web-Development, Sustainability, Software-Engineer, Sustainability-Technology, Remote-Senior-Full-Stack-Developer, Remote-Full-Stack-Developer, Full-Stack-Developer, Senior</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ewor-gmbh/jobs/industrial-tech-agentops-engineer-100-remote-m-f-d</t>
+          <t>https://himalayas.app/companies/ewor-gmbh/jobs/sustainability-full-stack-developer-100-remote-m-f-d</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>cedc8889fb</t>
+          <t>7da6fdc2ab</t>
         </is>
       </c>
     </row>
@@ -3578,56 +3578,56 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AI Response Analyst</t>
+          <t>Industrial Tech AgentOps Engineer (100 % remote) (m/f/d)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>iMerit Technology</t>
+          <t>EWOR GmbH</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>engineer, devops (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>content writing, quality assurance, ai</t>
+          <t>AgentOps-Engineer, Industrial-Technology, Operations-Engineering, Technical-Product-Management, Start-Up-Operations, Remote-Operations-Engineer, Industrial-IoT-Engineer, Remote-DevOps-Engineer, TechOps-Engineer, Remote-Infrastructure-Monitoring-Engineer, Remote-Distributed-Systems-Engineer-II, Mid-level</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-ai-response-analyst-imerit-technology-1137309</t>
+          <t>https://himalayas.app/companies/ewor-gmbh/jobs/industrial-tech-agentops-engineer-100-remote-m-f-d</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>05cb840193</t>
+          <t>cedc8889fb</t>
         </is>
       </c>
     </row>
@@ -3639,58 +3639,56 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>30</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Response Analyst</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>iMerit Technology</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>content writing, quality assurance, ai</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>57</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Python Backend Engineer (m/f/x)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Makersite</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Worldwide</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>himalayas</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>developer (tag), software (tag), engineer, backend, python, api (tag), worldwide (place)</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Python-Backend-Engineering, Backend-Development, Software-Engineer, API-Development, Python-Engineering, Python-Backend-Engineer, Python-Backend-Developer, Senior-Backend-Python-Developer, Senior-Python-Backend-Developer, Backend-Engineer, Product-Backend-Engineer, Backend-Services-Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/makersite/jobs/python-backend-engineer-m-f-x</t>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-response-analyst-imerit-technology-1137309</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>3eb1e889db</t>
+          <t>05cb840193</t>
         </is>
       </c>
     </row>
@@ -3706,19 +3704,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Python Backend Engineer (m/f/x)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>S-PRO</t>
+          <t>Makersite</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3733,12 +3731,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>software (tag), engineer, backend (tag), python, cloud (tag), aws (tag), worldwide (place)</t>
+          <t>developer (tag), software (tag), engineer, backend, python, api (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Python-Engineering, Backend-Development, AWS-Cloud-Development, Serverless-Development, Software-Engineer, Python-Engineer, Python-Software-Engineer, Mid-level</t>
+          <t>Python-Backend-Engineering, Backend-Development, Software-Engineer, API-Development, Python-Engineering, Python-Backend-Engineer, Python-Backend-Developer, Senior-Backend-Python-Developer, Senior-Python-Backend-Developer, Backend-Engineer, Product-Backend-Engineer, Backend-Services-Engineer, Senior</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3748,12 +3746,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/s-pro/jobs/python-engineer</t>
+          <t>https://himalayas.app/companies/makersite/jobs/python-backend-engineer-m-f-x</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>67bda4c374</t>
+          <t>3eb1e889db</t>
         </is>
       </c>
     </row>
@@ -3769,19 +3767,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Daymark Health</t>
+          <t>S-PRO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3796,12 +3794,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), worldwide (place)</t>
+          <t>software (tag), engineer, backend (tag), python, cloud (tag), aws (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Software-Engineer, Healthcare-Technology, Backend-Engineering, Fullstack-Development, Health-Tech, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Developer, Mid-level</t>
+          <t>Python-Engineering, Backend-Development, AWS-Cloud-Development, Serverless-Development, Software-Engineer, Python-Engineer, Python-Software-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3811,12 +3809,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/daymark-health/jobs/software-engineer</t>
+          <t>https://himalayas.app/companies/s-pro/jobs/python-engineer</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>85c899deaf</t>
+          <t>67bda4c374</t>
         </is>
       </c>
     </row>
@@ -3828,56 +3826,58 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>84</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Specialist, Data Science &amp; Artificial Intelligence</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Daymark Health</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>artificial intelligence, data science, india (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>Software-Engineer, Healthcare-Technology, Backend-Engineering, Fullstack-Development, Health-Tech, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5871846075?se=oI2O_Sup8RGogquEo3zAlQ&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=326B6FA659B880A3C0F3E2CA4AB8E0734BF69D7B</t>
+          <t>https://himalayas.app/companies/daymark-health/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>c1e8559189</t>
+          <t>85c899deaf</t>
         </is>
       </c>
     </row>
@@ -3893,39 +3893,37 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>50</v>
-      </c>
-      <c r="D57" t="n">
-        <v>2</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Specialist, Data Science &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>xneelo</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), devops (tag), worldwide (place)</t>
+          <t>artificial intelligence, data science, india (place)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Software-Engineer, Backend-Development, Fullstack-Development, Infrastructure-Engineering, DevOps, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Senior</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3935,12 +3933,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/xneelo-co/jobs/software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5871846075?se=oI2O_Sup8RGogquEo3zAlQ&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=326B6FA659B880A3C0F3E2CA4AB8E0734BF69D7B</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>679e1ed2b3</t>
+          <t>c1e8559189</t>
         </is>
       </c>
     </row>
@@ -3956,39 +3954,39 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AEM Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vonage</t>
+          <t>xneelo</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>developer, devops (tag), anywhere (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), devops (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Software-Engineer, Backend-Development, Fullstack-Development, Infrastructure-Engineering, DevOps, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Senior</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3998,12 +3996,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/vonage-aem-developer</t>
+          <t>https://himalayas.app/companies/xneelo-co/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>9b191a3075</t>
+          <t>679e1ed2b3</t>
         </is>
       </c>
     </row>
@@ -4019,37 +4017,39 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>27</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Video Annotation Expert</t>
+          <t>AEM Developer</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Vonage</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ai (tag), worldwide (place)</t>
+          <t>developer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Video-Annotator, Video-Annotation, Media-Annotation-Specialist, Video-Data-Annotation, Annotation-Specialist, Data-Annotation-Expert, AI-Annotation-Specialist, Content-Annotation-Specialist, Entry-level, Mid-level</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/video-annotation-expert-4408176807</t>
+          <t>https://weworkremotely.com/remote-jobs/vonage-aem-developer</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1b02a267ff</t>
+          <t>9b191a3075</t>
         </is>
       </c>
     </row>
@@ -4076,56 +4076,56 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Subject Matter Expert - Computer Science and Artificial Intelligence</t>
+          <t>Video Annotation Expert</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sultan Chand &amp; Sons Ltd</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>artificial intelligence, noida (place)</t>
+          <t>ai (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Video-Annotator, Video-Annotation, Media-Annotation-Specialist, Video-Data-Annotation, Annotation-Specialist, Data-Annotation-Expert, AI-Annotation-Specialist, Content-Annotation-Specialist, Entry-level, Mid-level</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5869558953?se=ji27_Tqo8RGDXZRVG-VeHA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=41B18BB78E05B29C6C90DA595F6A5EBB3EFE4072</t>
+          <t>https://himalayas.app/companies/micro1/jobs/video-annotation-expert-4408176807</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>91b1f60d0c</t>
+          <t>1b02a267ff</t>
         </is>
       </c>
     </row>
@@ -4141,37 +4141,37 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Software engineer</t>
+          <t>Subject Matter Expert - Computer Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sticker Mule</t>
+          <t>Sultan Chand &amp; Sons Ltd</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>software engineer, typescript (tag), golang (tag), react (tag), global (place)</t>
+          <t>artificial intelligence, noida (place)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Development, react,typescript,golang,graphql,english</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1833624/</t>
+          <t>https://www.adzuna.in/land/ad/5869558953?se=ji27_Tqo8RGDXZRVG-VeHA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=41B18BB78E05B29C6C90DA595F6A5EBB3EFE4072</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>c557da3996</t>
+          <t>91b1f60d0c</t>
         </is>
       </c>
     </row>
@@ -4198,56 +4198,56 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer 3D Developer (remote part/full time)</t>
+          <t>Software engineer</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Imnoo AG</t>
+          <t>Sticker Mule</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>machine learning, developer, engineer, ai, ml (tag), worldwide (place)</t>
+          <t>software engineer, typescript (tag), golang (tag), react (tag), global (place)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>AI-Machine-Learning-Engineering, 3D-Development, Computer-Vision, AI-Manufacturing, CAD-Development, Remote-Machine-Learning-Engineer, Remote-Senior-AI-Engineer, Remote-AI-Engineer, AI-ML-Engineer, Lead-AI-ML-Engineer, Machine-Learning-Engineer, Senior</t>
+          <t>Development, react,typescript,golang,graphql,english</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/imnoo-ag/jobs/ai-machine-learning-engineer-3d-developer-remote-part-full-time</t>
+          <t>https://www.workingnomads.com/job/go/1833624/</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>a84b2b9b96</t>
+          <t>c557da3996</t>
         </is>
       </c>
     </row>
@@ -4263,37 +4263,37 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>AI Machine Learning Engineer 3D Developer (remote part/full time)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sustainability Economics.ai</t>
+          <t>Imnoo AG</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>machine learning, intern (level), bangalore (place)</t>
+          <t>machine learning, developer, engineer, ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Machine-Learning-Engineering, 3D-Development, Computer-Vision, AI-Manufacturing, CAD-Development, Remote-Machine-Learning-Engineer, Remote-Senior-AI-Engineer, Remote-AI-Engineer, AI-ML-Engineer, Lead-AI-ML-Engineer, Machine-Learning-Engineer, Senior</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5868794497?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C97284B10F6321E0988BF83E6C1B8DFD30952F6C</t>
+          <t>https://himalayas.app/companies/imnoo-ag/jobs/ai-machine-learning-engineer-3d-developer-remote-part-full-time</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>05411f661c</t>
+          <t>a84b2b9b96</t>
         </is>
       </c>
     </row>
@@ -4324,17 +4324,17 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Machine Learning II</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Sustainability Economics.ai</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>machine learning, qa (tag), bangalore (place)</t>
+          <t>machine learning, intern (level), bangalore (place)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Scientific &amp; QA Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5868154123?se=SoAubXKn8RGZGp_UbifwCA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2A76050FF86A705EC1E71FEE64DFE517445586F0</t>
+          <t>https://www.adzuna.in/land/ad/5868794497?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C97284B10F6321E0988BF83E6C1B8DFD30952F6C</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>520f876dc1</t>
+          <t>05411f661c</t>
         </is>
       </c>
     </row>
@@ -4385,22 +4385,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>Machine Learning II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4410,27 +4410,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>machine learning, qa (tag), bangalore (place)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5852477157?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C196DCD121C33E5FA7A7F99C735E078C53777A1E</t>
+          <t>https://www.adzuna.in/land/ad/5868154123?se=SoAubXKn8RGZGp_UbifwCA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2A76050FF86A705EC1E71FEE64DFE517445586F0</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>dab94fe012</t>
+          <t>520f876dc1</t>
         </is>
       </c>
     </row>
@@ -4446,54 +4446,52 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>46</v>
-      </c>
-      <c r="D66" t="n">
-        <v>2</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Data Scientist - Inference, Community Support</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>data scientist, anywhere (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/airbnb-data-scientist-inference-community-support</t>
+          <t>https://www.adzuna.in/land/ad/5852477157?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C196DCD121C33E5FA7A7F99C735E078C53777A1E</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>18eaeb9d4e</t>
+          <t>dab94fe012</t>
         </is>
       </c>
     </row>
@@ -4509,54 +4507,54 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Frontend Engineer Specialist</t>
+          <t>Data Scientist - Inference, Community Support</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>developer (tag), frontend, software (tag), engineer, react (tag), worldwide (place)</t>
+          <t>data scientist, anywhere (place)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Frontend-Engineer, Web-Frontend-Engineer, Front-End-Software-Engineer, Frontend-Web-Software-Engineer, Front-End-Developer, React-Frontend-Engineer, UI-Frontend-Developer, Mid-level</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/frontend-engineer-specialist</t>
+          <t>https://weworkremotely.com/remote-jobs/airbnb-data-scientist-inference-community-support</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>ee1605c3a3</t>
+          <t>18eaeb9d4e</t>
         </is>
       </c>
     </row>
@@ -4568,56 +4566,58 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>44</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Frontend Engineer Specialist</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>developer (tag), frontend, software (tag), engineer, react (tag), worldwide (place)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Frontend-Engineer, Web-Frontend-Engineer, Front-End-Software-Engineer, Frontend-Web-Software-Engineer, Front-End-Developer, React-Frontend-Engineer, UI-Frontend-Developer, Mid-level</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>86</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; NLP Expert</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Synthenova</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>machine learning, nlp, qa (tag), india (place)</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Scientific &amp; QA Jobs</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864426193?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FA0DA9F5539A8E98A42507C72E66BEA28EFB5F71</t>
+          <t>https://himalayas.app/companies/micro1/jobs/frontend-engineer-specialist</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>06a6232301</t>
+          <t>ee1605c3a3</t>
         </is>
       </c>
     </row>
@@ -4633,22 +4633,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning &amp; NLP Expert</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>HT Digital Streams</t>
+          <t>Synthenova</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>data scientist, india (place), delhi (place)</t>
+          <t>machine learning, nlp, qa (tag), india (place)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427594?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1379BD61E95509405A372328EE4CB12520438AC9</t>
+          <t>https://www.adzuna.in/land/ad/5864426193?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FA0DA9F5539A8E98A42507C72E66BEA28EFB5F71</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>e77b0725ce</t>
+          <t>06a6232301</t>
         </is>
       </c>
     </row>
@@ -4694,52 +4694,52 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>HeadSpin</t>
+          <t>HT Digital Streams</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), associate (level), worldwide (place)</t>
+          <t>data scientist, india (place), delhi (place)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Engineering, Software-Engineer, Associate-Software-Engineer, Backend-Development, Fullstack-Development, Software-Engineering-Associate, Associate-Software-Developer, Software-Developer-Associate, Associate-Engineer, Associate-Platform-Engineer, Associate-Application-Developer, Associate-Systems-Engineer, Developer, Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/headspin/jobs/associate-software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5864427594?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1379BD61E95509405A372328EE4CB12520438AC9</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>ed41465dce</t>
+          <t>e77b0725ce</t>
         </is>
       </c>
     </row>
@@ -4755,52 +4755,52 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>HeadSpin</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>artificial intelligence, noida (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), associate (level), worldwide (place)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment Jobs</t>
+          <t>Engineering, Software-Engineer, Associate-Software-Engineer, Backend-Development, Fullstack-Development, Software-Engineering-Associate, Associate-Software-Developer, Software-Developer-Associate, Associate-Engineer, Associate-Platform-Engineer, Associate-Application-Developer, Associate-Systems-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864432717?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=616D5B872E024B0E271B6E107D9B24261D8C3B7A</t>
+          <t>https://himalayas.app/companies/headspin/jobs/associate-software-engineer</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>90b00c6445</t>
+          <t>ed41465dce</t>
         </is>
       </c>
     </row>
@@ -4818,22 +4818,20 @@
       <c r="C72" t="n">
         <v>50</v>
       </c>
-      <c r="D72" t="n">
-        <v>3</v>
-      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Machine Learning Specialist</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bandhan Technologies</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4843,27 +4841,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>machine learning, bangalore (place)</t>
+          <t>artificial intelligence, noida (place)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>HR &amp; Recruitment Jobs</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867037827?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=81D91604A259EFB724EEF9EE68D3642F93D7C52A</t>
+          <t>https://www.adzuna.in/land/ad/5864432717?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=616D5B872E024B0E271B6E107D9B24261D8C3B7A</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>55af0af08c</t>
+          <t>90b00c6445</t>
         </is>
       </c>
     </row>
@@ -4879,19 +4877,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D73" t="n">
         <v>3</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Data Science Specialist</t>
+          <t>Machine Learning Specialist</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Polestar Analytics</t>
+          <t>Bandhan Technologies</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4906,7 +4904,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>data science, bangalore (place)</t>
+          <t>machine learning, bangalore (place)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4916,17 +4914,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864434859?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BE53F35ACA83BD29D328C8745F27CF70F132F879</t>
+          <t>https://www.adzuna.in/land/ad/5867037827?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=81D91604A259EFB724EEF9EE68D3642F93D7C52A</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>620816c318</t>
+          <t>55af0af08c</t>
         </is>
       </c>
     </row>
@@ -4944,20 +4942,22 @@
       <c r="C74" t="n">
         <v>49</v>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="n">
+        <v>3</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>Data Science Specialist</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Polestar Analytics</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>data science, bangalore (place)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867037765?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CCE3B589087C9AE3C6FD3C72DD92F3B9146F772F</t>
+          <t>https://www.adzuna.in/land/ad/5864434859?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BE53F35ACA83BD29D328C8745F27CF70F132F879</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>5ae3a66648</t>
+          <t>620816c318</t>
         </is>
       </c>
     </row>
@@ -5008,17 +5008,17 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Infosys Finacle</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867270149?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=284AB41CD26DD62DA43E2E7866A4F2E72052CFA3</t>
+          <t>https://www.adzuna.in/land/ad/5867037765?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CCE3B589087C9AE3C6FD3C72DD92F3B9146F772F</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>b9e7b78c99</t>
+          <t>5ae3a66648</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Servify</t>
+          <t>Infosys Finacle</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867265604?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=98C25A013410B0B492855DE45F67FF3409A45C24</t>
+          <t>https://www.adzuna.in/land/ad/5867270149?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=284AB41CD26DD62DA43E2E7866A4F2E72052CFA3</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>339ea3cd4c</t>
+          <t>b9e7b78c99</t>
         </is>
       </c>
     </row>
@@ -5125,37 +5125,37 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CEO, AI Finance</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bjak</t>
+          <t>Servify</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/bjak/jobs/ceo-ai-finance-7034716418</t>
+          <t>https://www.adzuna.in/land/ad/5867265604?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=98C25A013410B0B492855DE45F67FF3409A45C24</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>8e23b34067</t>
+          <t>339ea3cd4c</t>
         </is>
       </c>
     </row>
@@ -5186,17 +5186,17 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Accounting Automation Engineer</t>
+          <t>CEO, AI Finance</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spotter Labs</t>
+          <t>Bjak</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>automation, software (tag), engineer, worldwide (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Accounting-Automation-Engineer, Finance-Automation-Engineer, Accounting-Software-Engineer, Accounting-Automation, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3984977259</t>
+          <t>https://himalayas.app/companies/bjak/jobs/ceo-ai-finance-7034716418</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>c570969de5</t>
+          <t>8e23b34067</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Accounting-Automation-Engineer, Accounting, Process-Automation, Financial-Automation, Business-Systems, Finance-Automation-Engineer, Accounting-Software-Engineer, Automation-Engineer, Accounting-Automation, Software-Automation-Engineer, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
+          <t>Accounting-Automation-Engineer, Finance-Automation-Engineer, Accounting-Software-Engineer, Accounting-Automation, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3943339358</t>
+          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3984977259</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>13edcbb44e</t>
+          <t>c570969de5</t>
         </is>
       </c>
     </row>
@@ -5308,37 +5308,37 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Backend Engineer - Platform - Stacks | Ireland | Remote</t>
+          <t>Accounting Automation Engineer</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grafana Labs</t>
+          <t>Spotter Labs</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>engineer, backend, anywhere (place)</t>
+          <t>automation, software (tag), engineer, worldwide (place)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Accounting-Automation-Engineer, Accounting, Process-Automation, Financial-Automation, Business-Systems, Finance-Automation-Engineer, Accounting-Software-Engineer, Automation-Engineer, Accounting-Automation, Software-Automation-Engineer, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/grafana-labs-backend-engineer-platform-stacks-ireland-remote</t>
+          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3943339358</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>7aae615c8c</t>
+          <t>13edcbb44e</t>
         </is>
       </c>
     </row>
@@ -5369,37 +5369,37 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>STEM Expert</t>
+          <t>Backend Engineer - Platform - Stacks | Ireland | Remote</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ai (tag), worldwide (place)</t>
+          <t>engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>STEM-Expert, STEM-Specialist, STEM-Consultant, STEM-Domain-Expert, STEM-Researcher, STEM-Educator, STEM-AI-Specialist, Japanese-STEM-Specialist, STEM-Advisor, STEM-Instructor, Mid-level</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/stem-expert-40695367</t>
+          <t>https://weworkremotely.com/remote-jobs/grafana-labs-backend-engineer-platform-stacks-ireland-remote</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>9cb40c45fc</t>
+          <t>7aae615c8c</t>
         </is>
       </c>
     </row>
@@ -5430,14 +5430,12 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>21</v>
-      </c>
-      <c r="D82" t="n">
-        <v>3</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Excel Specialist</t>
+          <t>STEM Expert</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5457,12 +5455,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>automation (tag), developer (tag), worldwide (place)</t>
+          <t>ai (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Excel-Specialist, Excel-Expert, Spreadsheet-Specialist, Excel-Automation-Specialist, Excel-Data-Analyst, Microsoft-Excel-Developer, Microsoft-Office-Specialist, Microsoft-Excel-Development, Entry-level, Mid-level</t>
+          <t>STEM-Expert, STEM-Specialist, STEM-Consultant, STEM-Domain-Expert, STEM-Researcher, STEM-Educator, STEM-AI-Specialist, Japanese-STEM-Specialist, STEM-Advisor, STEM-Instructor, Mid-level</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5472,12 +5470,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/excel-specialist-2996931708</t>
+          <t>https://himalayas.app/companies/micro1/jobs/stem-expert-40695367</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>fddf243627</t>
+          <t>9cb40c45fc</t>
         </is>
       </c>
     </row>
@@ -5489,56 +5487,58 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>69</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>Excel Specialist</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ISIR AI</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>data science, qa (tag), intern (level), noida (place)</t>
+          <t>automation (tag), developer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Scientific &amp; QA Jobs</t>
+          <t>Excel-Specialist, Excel-Expert, Spreadsheet-Specialist, Excel-Automation-Specialist, Excel-Data-Analyst, Microsoft-Excel-Developer, Microsoft-Office-Specialist, Microsoft-Excel-Development, Entry-level, Mid-level</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427080?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C509B9B88F855FA7348A37AF1CDF8C3ECC7CA889</t>
+          <t>https://himalayas.app/companies/micro1/jobs/excel-specialist-2996931708</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>84896ab3c6</t>
+          <t>fddf243627</t>
         </is>
       </c>
     </row>
@@ -5554,22 +5554,22 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FRND</t>
+          <t>ISIR AI</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>machine learning, intern (level), bangalore (place)</t>
+          <t>data science, qa (tag), intern (level), noida (place)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864424613?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9B60872885E8C7073FE0CC2A962D44A1E48845F7</t>
+          <t>https://www.adzuna.in/land/ad/5864427080?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C509B9B88F855FA7348A37AF1CDF8C3ECC7CA889</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>e00b96a707</t>
+          <t>84896ab3c6</t>
         </is>
       </c>
     </row>
@@ -5615,22 +5615,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Intern (Data Science)</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Yubi</t>
+          <t>FRND</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>data science, intern (level), chennai (place)</t>
+          <t>machine learning, intern (level), bangalore (place)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864443163?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4554D5357B8D35F06907356F0816FBF3BD2BBC7E</t>
+          <t>https://www.adzuna.in/land/ad/5864424613?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9B60872885E8C7073FE0CC2A962D44A1E48845F7</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>93516db46a</t>
+          <t>e00b96a707</t>
         </is>
       </c>
     </row>
@@ -5676,37 +5676,37 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AI Inference Engineer QVAC (100% remote Worldwide)</t>
+          <t>Intern (Data Science)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tether Operations Limited</t>
+          <t>Yubi</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>software (tag), engineer, ai, worldwide (place)</t>
+          <t>data science, intern (level), chennai (place)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Software-Engineer, AI-Engineering, Machine-Learning-Engineering, C-Development, Edge-AI, AI-Inference-Engineer, Remote-AI-Engineer, Remote-Machine-Learning-Engineer, Senior-AI-Inference-Engineer, Remote-Senior-AI-Engineer, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/tether-operations-limited/jobs/ai-inference-engineer-qvac-100-remote-worldwide</t>
+          <t>https://www.adzuna.in/land/ad/5864443163?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4554D5357B8D35F06907356F0816FBF3BD2BBC7E</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>f7f40ca44a</t>
+          <t>93516db46a</t>
         </is>
       </c>
     </row>
@@ -5737,37 +5737,37 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Machine Learning Gen AI_Hyderabad,Pune &amp; Bangalore</t>
+          <t>AI Inference Engineer QVAC (100% remote Worldwide)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Tether Operations Limited</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>machine learning, hyderabad (place)</t>
+          <t>software (tag), engineer, ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Software-Engineer, AI-Engineering, Machine-Learning-Engineering, C-Development, Edge-AI, AI-Inference-Engineer, Remote-AI-Engineer, Remote-Machine-Learning-Engineer, Senior-AI-Inference-Engineer, Remote-Senior-AI-Engineer, Senior</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439281?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1F39144C3030195205A212339590BB508623F064</t>
+          <t>https://himalayas.app/companies/tether-operations-limited/jobs/ai-inference-engineer-qvac-100-remote-worldwide</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>55fce19c46</t>
+          <t>f7f40ca44a</t>
         </is>
       </c>
     </row>
@@ -5798,17 +5798,17 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Gen AI_Hyderabad,Pune &amp; Bangalore</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Infosys Consulting</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>data scientist, hyderabad (place)</t>
+          <t>machine learning, hyderabad (place)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864428905?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4E35D1AC081FE279803556ECA4C1E1871550877F</t>
+          <t>https://www.adzuna.in/land/ad/5864439281?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1F39144C3030195205A212339590BB508623F064</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>af7ebeb057</t>
+          <t>55fce19c46</t>
         </is>
       </c>
     </row>
@@ -5861,9 +5861,7 @@
       <c r="C89" t="n">
         <v>49</v>
       </c>
-      <c r="D89" t="n">
-        <v>2</v>
-      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Data Scientist</t>
@@ -5871,12 +5869,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>super.money</t>
+          <t>Infosys Consulting</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5886,7 +5884,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, hyderabad (place)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5901,12 +5899,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864425941?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BF9A171BDEA00E60475790836A0A3589FB8D9EB6</t>
+          <t>https://www.adzuna.in/land/ad/5864428905?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4E35D1AC081FE279803556ECA4C1E1871550877F</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>4f1a679ea3</t>
+          <t>af7ebeb057</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5922,9 @@
       <c r="C90" t="n">
         <v>49</v>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>2</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>Data Scientist</t>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lufthansa Technik Services India Pvt Ltd</t>
+          <t>super.money</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864422634?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
+          <t>https://www.adzuna.in/land/ad/5864425941?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BF9A171BDEA00E60475790836A0A3589FB8D9EB6</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>c86fa3dfe3</t>
+          <t>4f1a679ea3</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank</t>
+          <t>Lufthansa Technik Services India Pvt Ltd</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439103?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=73CFB6E1B4115AA2A23A99B0EC8886521BA01450</t>
+          <t>https://www.adzuna.in/land/ad/5864422634?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>08622a68ed</t>
+          <t>c86fa3dfe3</t>
         </is>
       </c>
     </row>
@@ -6049,17 +6049,17 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Navi</t>
+          <t>Kotak Mahindra Bank</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439226?se=jiNNTDmm8RGUNa3mkcr13g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=744BE785510320885EE5287D6F2FE8E098FAED30</t>
+          <t>https://www.adzuna.in/land/ad/5864439103?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=73CFB6E1B4115AA2A23A99B0EC8886521BA01450</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>4e1bb30522</t>
+          <t>08622a68ed</t>
         </is>
       </c>
     </row>
@@ -6110,17 +6110,17 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tricog Health</t>
+          <t>Navi</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5865291446?se=pmQW9lOm8RGs-Y02KTQxmA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=A9D77535171E8EAD7E7898B67A7ADC8ED3D07410</t>
+          <t>https://www.adzuna.in/land/ad/5864439226?se=jiNNTDmm8RGUNa3mkcr13g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=744BE785510320885EE5287D6F2FE8E098FAED30</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>eaec37f6c0</t>
+          <t>4e1bb30522</t>
         </is>
       </c>
     </row>
@@ -6166,54 +6166,52 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>41</v>
-      </c>
-      <c r="D94" t="n">
-        <v>3</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Remote - Automation QA Engineer (Core Team)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Torrero</t>
+          <t>Tricog Health</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>automation, software (tag), engineer, testing (tag), qa, worldwide (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>QA-Engineer, QA-Automation-Engineer, Software-Testing, Quality-Assurance, Manual-Testing, Remote-Test-Automation-Engineer, Remote-QA-Engineer, Remote-Quality-Assurance-Engineer, Remote-UI-Automation-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/torrero/jobs/remote-automation-qa-engineer-core-team</t>
+          <t>https://www.adzuna.in/land/ad/5865291446?se=pmQW9lOm8RGs-Y02KTQxmA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=A9D77535171E8EAD7E7898B67A7ADC8ED3D07410</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>f03380c71d</t>
+          <t>eaec37f6c0</t>
         </is>
       </c>
     </row>
@@ -6229,17 +6227,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>36</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Front-End Developer</t>
+          <t>Remote - Automation QA Engineer (Core Team)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talent Sam</t>
+          <t>Torrero</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>developer, frontend (tag), engineer (tag), react (tag), worldwide (place)</t>
+          <t>automation, software (tag), engineer, testing (tag), qa, worldwide (place)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Frontend-Development, Web-Development, UI-Developer, Frontend-Engineer, Front-End-Developer, Frontend-React-Developer, UI-Frontend-Developer, UX-UI-Front-End-Developer, React-Frontend-Developer, Frontend-Web-Development, Developer, Mid-level</t>
+          <t>QA-Engineer, QA-Automation-Engineer, Software-Testing, Quality-Assurance, Manual-Testing, Remote-Test-Automation-Engineer, Remote-QA-Engineer, Remote-Quality-Assurance-Engineer, Remote-UI-Automation-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/talent-sam/jobs/front-end-developer</t>
+          <t>https://himalayas.app/companies/torrero/jobs/remote-automation-qa-engineer-core-team</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>94d5af612e</t>
+          <t>f03380c71d</t>
         </is>
       </c>
     </row>
@@ -6290,37 +6290,37 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>E-learning Developer</t>
+          <t>Front-End Developer</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>VineGarden Films</t>
+          <t>Talent Sam</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>developer, india (place)</t>
+          <t>developer, frontend (tag), engineer (tag), react (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Teaching Jobs</t>
+          <t>Frontend-Development, Web-Development, UI-Developer, Frontend-Engineer, Front-End-Developer, Frontend-React-Developer, UI-Frontend-Developer, UX-UI-Front-End-Developer, React-Frontend-Developer, Frontend-Web-Development, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864153573?se=SvkgT-Wl8RGUGK7L4gkIgg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FDDF0A4236DF3E6D3081AF93B01799D77599EAD1</t>
+          <t>https://himalayas.app/companies/talent-sam/jobs/front-end-developer</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>248ef46714</t>
+          <t>94d5af612e</t>
         </is>
       </c>
     </row>
@@ -6347,21 +6347,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Data Scientist - Python Deterministic Analytics</t>
+          <t>E-learning Developer</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Capco</t>
+          <t>VineGarden Films</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6376,27 +6376,27 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>data scientist, python, india (place)</t>
+          <t>developer, india (place)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Teaching Jobs</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139747?se=olLfvDql8RGL6NrjcRaTpw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9FA82041CC2CC98F084D6827CF82DA2BE289D998</t>
+          <t>https://www.adzuna.in/land/ad/5864153573?se=SvkgT-Wl8RGUGK7L4gkIgg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FDDF0A4236DF3E6D3081AF93B01799D77599EAD1</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>6f1952e273</t>
+          <t>248ef46714</t>
         </is>
       </c>
     </row>
@@ -6412,22 +6412,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - APAC</t>
+          <t>Data Scientist - Python Deterministic Analytics</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional®</t>
+          <t>Capco</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>data scientist, python, india (place)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6447,17 +6447,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5862635702?se=9gaugPCk8RGcfKYe_cIpvA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=53D4DF556D646C5F462C8F3FC782D72E8A35D08B</t>
+          <t>https://www.adzuna.in/land/ad/5837139747?se=olLfvDql8RGL6NrjcRaTpw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9FA82041CC2CC98F084D6827CF82DA2BE289D998</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>d395f3a907</t>
+          <t>6f1952e273</t>
         </is>
       </c>
     </row>
@@ -6473,52 +6473,52 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AI Engineer Data APIs</t>
+          <t>Machine Learning Engineer - APAC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>LexisNexis Legal &amp; Professional®</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>engineer, golang (tag), ai</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>golang, video, engineer</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-ai-engineer-data-apis-benzinga-1137224</t>
+          <t>https://www.adzuna.in/land/ad/5862635702?se=9gaugPCk8RGcfKYe_cIpvA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=53D4DF556D646C5F462C8F3FC782D72E8A35D08B</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>1261a5bcd5</t>
+          <t>d395f3a907</t>
         </is>
       </c>
     </row>
@@ -6534,52 +6534,52 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Agentic Python Engineer</t>
+          <t>AI Engineer Data APIs</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Evaboot</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>WORLDWIDE</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>engineer, python, aws (tag), worldwide (place)</t>
+          <t>engineer, golang (tag), ai</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Development, python,engineer,aws,analytics,seo</t>
+          <t>golang, video, engineer</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1826864/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-engineer-data-apis-benzinga-1137224</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>47ae63b1d0</t>
+          <t>1261a5bcd5</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
@@ -6610,22 +6610,22 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>WORLDWIDE</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>engineer, python, anywhere (place)</t>
+          <t>engineer, python, aws (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Development, python,engineer,aws,analytics,seo</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/evaboot-agentic-python-engineer</t>
+          <t>https://www.workingnomads.com/job/go/1826864/</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>d94554bfc7</t>
+          <t>47ae63b1d0</t>
         </is>
       </c>
     </row>
@@ -6652,56 +6652,56 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Agentic Python Engineer</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Evaboot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>engineer, python, anywhere (place)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982687?se=BGNyWVik8RGF59teMJsS7Q&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=64C652991D92D5E3DCA4519D688756F962092321</t>
+          <t>https://weworkremotely.com/remote-jobs/evaboot-agentic-python-engineer</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>dd6de0380a</t>
+          <t>d94554bfc7</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Data Scientist, Knowledge Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982533?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=853C1E923E89428D368371363C6206932A9E653B</t>
+          <t>https://www.adzuna.in/land/ad/5857982687?se=BGNyWVik8RGF59teMJsS7Q&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=64C652991D92D5E3DCA4519D688756F962092321</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>e4df1efe77</t>
+          <t>dd6de0380a</t>
         </is>
       </c>
     </row>
@@ -6783,17 +6783,17 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Data Scientist II, Data Analytics, Hyderabad</t>
+          <t>Data Scientist, Knowledge Management</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>data scientist, hyderabad (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6813,17 +6813,17 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5860916020?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2CB3A6FFC4393B68C48E0DBE7C464491C08965D1</t>
+          <t>https://www.adzuna.in/land/ad/5857982533?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=853C1E923E89428D368371363C6206932A9E653B</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>ed5cec24b5</t>
+          <t>e4df1efe77</t>
         </is>
       </c>
     </row>
@@ -6839,52 +6839,52 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform - Hyderabad, India</t>
+          <t>Data Scientist II, Data Analytics, Hyderabad</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Speechify</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>software engineer, backend (tag), cloud (tag), api (tag), india (place)</t>
+          <t>data scientist, hyderabad (place)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Platform-Engineering, Backend-Engineering, Software-Engineer, API-Development, Cloud-Infrastructure, Software-Platform-Engineer, Platform-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/speechify/jobs/software-engineer-platform-hyderabad-india</t>
+          <t>https://www.adzuna.in/land/ad/5860916020?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2CB3A6FFC4393B68C48E0DBE7C464491C08965D1</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>d972ee3bee</t>
+          <t>ed5cec24b5</t>
         </is>
       </c>
     </row>
@@ -6900,22 +6900,22 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>GitHub Contributor</t>
+          <t>Software Engineer, Platform - Hyderabad, India</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Speechify</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, backend (tag), cloud (tag), api (tag), india (place)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
+          <t>Platform-Engineering, Backend-Engineering, Software-Engineer, API-Development, Cloud-Infrastructure, Software-Platform-Engineer, Platform-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-2145210908</t>
+          <t>https://himalayas.app/companies/speechify/jobs/software-engineer-platform-hyderabad-india</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>9bd86980fc</t>
+          <t>d972ee3bee</t>
         </is>
       </c>
     </row>
@@ -6957,58 +6957,56 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>38</v>
-      </c>
-      <c r="D107" t="n">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, PDP Experience</t>
+          <t>GitHub Contributor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>software engineer, backend, anywhere (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/reddit-backend-software-engineer-pdp-experience</t>
+          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-2145210908</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>a954ce85ab</t>
+          <t>9bd86980fc</t>
         </is>
       </c>
     </row>
@@ -7024,37 +7022,39 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>24</v>
-      </c>
-      <c r="D108" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Open Source Contributor</t>
+          <t>Backend Software Engineer, PDP Experience</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Open-Source-Software-Developer, Open-Source-Advocate, Open-Source-Engineer, Open-Source-Software-Engineer, Open-Source-Software-Maintainer, Community-Contributor, Entry-level</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7064,12 +7064,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/open-source-contributor-4150550716</t>
+          <t>https://weworkremotely.com/remote-jobs/reddit-backend-software-engineer-pdp-experience</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>d8033bd793</t>
+          <t>a954ce85ab</t>
         </is>
       </c>
     </row>
@@ -7081,16 +7081,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Open Source Contributor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7110,27 +7110,27 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>engineer, python (tag), ai, ml (tag), worldwide (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Mid-level</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Open-Source-Software-Developer, Open-Source-Advocate, Open-Source-Engineer, Open-Source-Software-Engineer, Open-Source-Software-Maintainer, Community-Contributor, Entry-level</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-engineer-7982880650</t>
+          <t>https://himalayas.app/companies/micro1/jobs/open-source-contributor-4150550716</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>17936ac69e</t>
+          <t>d8033bd793</t>
         </is>
       </c>
     </row>
@@ -7146,37 +7146,37 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>machine learning, engineer, hyderabad (place)</t>
+          <t>engineer, python (tag), ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Mid-level</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5859662671?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=77410E24CED3D457054E58156829472F42D5B958</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-engineer-7982880650</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>a8bcca74c0</t>
+          <t>17936ac69e</t>
         </is>
       </c>
     </row>
@@ -7212,17 +7212,17 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (T25)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>machine learning, engineer, hyderabad (place)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7242,17 +7242,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858538850?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AA8B404BB5F08B6BBBC1A1DAEA80EDAE2331BB01</t>
+          <t>https://www.adzuna.in/land/ad/5859662671?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=77410E24CED3D457054E58156829472F42D5B958</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>e99054d24c</t>
+          <t>a8bcca74c0</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SWE-3 Machine Learning Engineer</t>
+          <t>Machine Learning Engineer (T25)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858537539?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=49BEDAECA8CA01D8F7BFB9CA5D092D8DD046FCF4</t>
+          <t>https://www.adzuna.in/land/ad/5858538850?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AA8B404BB5F08B6BBBC1A1DAEA80EDAE2331BB01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>83e0ebd10e</t>
+          <t>e99054d24c</t>
         </is>
       </c>
     </row>
@@ -7329,22 +7329,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>SWE-3 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>engineer, ai, hyderabad (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982475?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=61932F7A965BC6190F96EF3EDD6B34FCA7CA0EFF</t>
+          <t>https://www.adzuna.in/land/ad/5858537539?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=49BEDAECA8CA01D8F7BFB9CA5D092D8DD046FCF4</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>ec1b34ae37</t>
+          <t>83e0ebd10e</t>
         </is>
       </c>
     </row>
@@ -7390,52 +7390,52 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AI Data Annotator - Remote</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Argos Multilingual Inc.</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>All Other Remote, Contract</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/argos-multilingual-inc-ai-data-annotator-remote</t>
+          <t>https://www.adzuna.in/land/ad/5857982475?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=61932F7A965BC6190F96EF3EDD6B34FCA7CA0EFF</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>5c22526a85</t>
+          <t>ec1b34ae37</t>
         </is>
       </c>
     </row>
@@ -7447,56 +7447,56 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Data Scientist - AI &amp; Automation</t>
+          <t>AI Data Annotator - Remote</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Argos Multilingual Inc.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>data scientist, automation, ai, bangalore (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>All Other Remote, Contract</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251125?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C7BA7BE347A1ADA1FC538497AF302C4F3AD6BEDD</t>
+          <t>https://weworkremotely.com/remote-jobs/argos-multilingual-inc-ai-data-annotator-remote</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2e19a4f3f6</t>
+          <t>5c22526a85</t>
         </is>
       </c>
     </row>
@@ -7512,12 +7512,12 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MTS-1 Machine Learning Engineer</t>
+          <t>Data Scientist - AI &amp; Automation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>data scientist, automation, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858537523?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4219F9238C4FE19DFCEAD65DAA98E56A5B89F388</t>
+          <t>https://www.adzuna.in/land/ad/5857251125?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C7BA7BE347A1ADA1FC538497AF302C4F3AD6BEDD</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>c65fcd065c</t>
+          <t>2e19a4f3f6</t>
         </is>
       </c>
     </row>
@@ -7573,22 +7573,22 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>MTS-1 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>data scientist, mumbai (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7608,17 +7608,17 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5849296977?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FFA2BB725355D26B4B624FA5365F48C2D8B894C</t>
+          <t>https://www.adzuna.in/land/ad/5858537523?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4219F9238C4FE19DFCEAD65DAA98E56A5B89F388</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>200651f002</t>
+          <t>c65fcd065c</t>
         </is>
       </c>
     </row>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, mumbai (place)</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251146?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=43EC4FC89638B5AB4C3D5267B80E2B1135A6C706</t>
+          <t>https://www.adzuna.in/land/ad/5849296977?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FFA2BB725355D26B4B624FA5365F48C2D8B894C</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>6a6f7a8419</t>
+          <t>200651f002</t>
         </is>
       </c>
     </row>
@@ -7735,12 +7735,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251173?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7E2FD9B14C3A74461E2352F6CFE714131C13E4BC</t>
+          <t>https://www.adzuna.in/land/ad/5857251146?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=43EC4FC89638B5AB4C3D5267B80E2B1135A6C706</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>aa6eef76e8</t>
+          <t>6a6f7a8419</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Data Scientist, Knowledge Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251185?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=74B3EB71D85FA01AB90B707F8DB6AB9F2A17FAFA</t>
+          <t>https://www.adzuna.in/land/ad/5857251173?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7E2FD9B14C3A74461E2352F6CFE714131C13E4BC</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>d1497475d4</t>
+          <t>aa6eef76e8</t>
         </is>
       </c>
     </row>
@@ -7822,12 +7822,12 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Data Scientist with R programming</t>
+          <t>Data Scientist, Knowledge Management</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Capco</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7852,17 +7852,17 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139433?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=221D7BCDBBE6E4012ED68B71EDB34DB2E07507EC</t>
+          <t>https://www.adzuna.in/land/ad/5857251185?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=74B3EB71D85FA01AB90B707F8DB6AB9F2A17FAFA</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>dbec4a04a4</t>
+          <t>d1497475d4</t>
         </is>
       </c>
     </row>
@@ -7878,52 +7878,52 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Data Scientist with R programming</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capco</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Product, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer-1</t>
+          <t>https://www.adzuna.in/land/ad/5837139433?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=221D7BCDBBE6E4012ED68B71EDB34DB2E07507EC</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>e7de7648c1</t>
+          <t>dbec4a04a4</t>
         </is>
       </c>
     </row>
@@ -7979,12 +7979,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer</t>
+          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer-1</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>dada5ade61</t>
+          <t>e7de7648c1</t>
         </is>
       </c>
     </row>
@@ -8000,52 +8000,52 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Education Designer UX UI and AI</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Interaction Design Foundation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>design, content writing, education</t>
+          <t>Product, Full-Time</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-education-designer-ux-ui-and-ai-interaction-design-foundation-1137138</t>
+          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>ca62234445</t>
+          <t>dada5ade61</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Course Writer and Editor UX UI and AI</t>
+          <t>Education Designer UX UI and AI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>design, content writing</t>
+          <t>design, content writing, education</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-course-writer-and-editor-ux-ui-and-ai-interaction-design-foundation-1137136</t>
+          <t>https://remoteOK.com/remote-jobs/remote-education-designer-ux-ui-and-ai-interaction-design-foundation-1137138</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>01210e4343</t>
+          <t>ca62234445</t>
         </is>
       </c>
     </row>
@@ -8118,56 +8118,56 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>App Developer - AI/ML</t>
+          <t>Course Writer and Editor UX UI and AI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Interaction Design Foundation</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>developer, ai, ml, hyderabad (place)</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>design, content writing</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139469?se=-BSx1eug8RG-Sdz4qyZPjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=16DC1893C3026AA51441662E0B1A61360470917B</t>
+          <t>https://remoteOK.com/remote-jobs/remote-course-writer-and-editor-ux-ui-and-ai-interaction-design-foundation-1137136</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>7a22fe6bd5</t>
+          <t>01210e4343</t>
         </is>
       </c>
     </row>
@@ -8183,17 +8183,17 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>App Developer - AI/ML</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>developer, ai, ml, hyderabad (place)</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857168441?se=TqYc8W2h8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CEB40CB7335D41898800C58388A2B035DF674757</t>
+          <t>https://www.adzuna.in/land/ad/5837139469?se=-BSx1eug8RG-Sdz4qyZPjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=16DC1893C3026AA51441662E0B1A61360470917B</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>84fdce5107</t>
+          <t>7a22fe6bd5</t>
         </is>
       </c>
     </row>
@@ -8244,37 +8244,37 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AI Speech &amp; Audio Specialist – ASR | TTS | Voice AI | Audio Data</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/ai-speech-audio-specialist-asr-tts-voice-ai-audio-data</t>
+          <t>https://www.adzuna.in/land/ad/5857168441?se=TqYc8W2h8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CEB40CB7335D41898800C58388A2B035DF674757</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>bb930fc93f</t>
+          <t>84fdce5107</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Financial Accuracy &amp; Tax Logic Expert (AI Community)</t>
+          <t>AI Speech &amp; Audio Specialist – ASR | TTS | Voice AI | Audio Data</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/financial-accuracy-tax-logic-expert-ai-community-7007868696</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/ai-speech-audio-specialist-asr-tts-voice-ai-audio-data</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>162d6a9ed2</t>
+          <t>bb930fc93f</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Identity Trust &amp; Fraud Intelligence Specialist - Intermediate (AI Community)</t>
+          <t>Financial Accuracy &amp; Tax Logic Expert (AI Community)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/identity-trust-fraud-intelligence-specialist-intermediate-ai-community</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/financial-accuracy-tax-logic-expert-ai-community-7007868696</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>637c85a300</t>
+          <t>162d6a9ed2</t>
         </is>
       </c>
     </row>
@@ -8432,32 +8432,32 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Education Designer: UX, UI, and AI</t>
+          <t>Identity Trust &amp; Fraud Intelligence Specialist - Intermediate (AI Community)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>IxDF - Interaction Design Foundation</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Design, Full-Time</t>
+          <t>Entry-level</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-education-designer-ux-ui-and-ai</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/identity-trust-fraud-intelligence-specialist-intermediate-ai-community</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>9fbe655de3</t>
+          <t>637c85a300</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Course Writer and Editor: UX, UI, and AI</t>
+          <t>Education Designer: UX, UI, and AI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-course-writer-and-editor-ux-ui-and-ai</t>
+          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-education-designer-ux-ui-and-ai</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>e8e07f5951</t>
+          <t>9fbe655de3</t>
         </is>
       </c>
     </row>
@@ -8554,32 +8554,32 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AI Consulting Domain Expert</t>
+          <t>Course Writer and Editor: UX, UI, and AI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IxDF - Interaction Design Foundation</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>AI-Domain-Expert, AI-Consultant, AI-Subject-Matter-Expert, Artificial-Intelligence-Consulting, Senior</t>
+          <t>Design, Full-Time</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-consulting-domain-expert-7128968890</t>
+          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-course-writer-and-editor-ux-ui-and-ai</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>7f1041d829</t>
+          <t>e8e07f5951</t>
         </is>
       </c>
     </row>
@@ -8610,39 +8610,37 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>40</v>
-      </c>
-      <c r="D134" t="n">
-        <v>2</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Software Development Engineer II Full Stack - Business (Remote @ Colombia)</t>
+          <t>AI Consulting Domain Expert</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>full stack, software, engineer, anywhere (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>AI-Domain-Expert, AI-Consultant, AI-Subject-Matter-Expert, Artificial-Intelligence-Consulting, Senior</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8652,12 +8650,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/offerup-software-development-engineer-ii-full-stack-business-remote-colombia</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-consulting-domain-expert-7128968890</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>6fe968b6b9</t>
+          <t>7f1041d829</t>
         </is>
       </c>
     </row>
@@ -8673,37 +8671,39 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>20</v>
-      </c>
-      <c r="D135" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>QA Speech-to-Text Audio Collection Project</t>
+          <t>Software Development Engineer II Full Stack - Business (Remote @ Colombia)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>qa, worldwide (place)</t>
+          <t>full stack, software, engineer, anywhere (place)</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Entry-level</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/qa-speech-to-text-audio-collection-project</t>
+          <t>https://weworkremotely.com/remote-jobs/offerup-software-development-engineer-ii-full-stack-business-remote-colombia</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>a44e738ec6</t>
+          <t>6fe968b6b9</t>
         </is>
       </c>
     </row>
@@ -8730,21 +8730,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AI/RAG engineer</t>
+          <t>QA Speech-to-Text Audio Collection Project</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CoinMarketCap</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8759,27 +8759,27 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>engineer, ai, ml (tag), worldwide (place)</t>
+          <t>qa, worldwide (place)</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>RAG-AI-Engineer, Machine-Learning-Engineering, AI-Engineering, RAG-Development, Vector-Search-Engineer, IA-RAG-Engineer, AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, Mid-level</t>
+          <t>Entry-level</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/coinmarketcap/jobs/ai-rag-engineer</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/qa-speech-to-text-audio-collection-project</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>d199d5cdfc</t>
+          <t>a44e738ec6</t>
         </is>
       </c>
     </row>
@@ -8795,52 +8795,52 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI/RAG engineer</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>CoinMarketCap</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>engineer, ai, mumbai (place)</t>
+          <t>engineer, ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>RAG-AI-Engineer, Machine-Learning-Engineering, AI-Engineering, RAG-Development, Vector-Search-Engineer, IA-RAG-Engineer, AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723676?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F83D2913763A01EA6FBE321571CA8B989BE3F382</t>
+          <t>https://himalayas.app/companies/coinmarketcap/jobs/ai-rag-engineer</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>faa646b456</t>
+          <t>d199d5cdfc</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Data Science-Index Quant Specialist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8881,27 +8881,27 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>data science, mumbai (place)</t>
+          <t>engineer, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Accounting &amp; Finance Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5843137505?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC4079028ED7338B991CD57034DE9EA5AC8D9A0B</t>
+          <t>https://www.adzuna.in/land/ad/5846723676?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F83D2913763A01EA6FBE321571CA8B989BE3F382</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>6ec3848d0b</t>
+          <t>faa646b456</t>
         </is>
       </c>
     </row>
@@ -8922,17 +8922,17 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Science-Index Quant Specialist</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Gurgaon, Haryana</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8942,27 +8942,27 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>data scientist, gurgaon (place)</t>
+          <t>data science, mumbai (place)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Accounting &amp; Finance Jobs</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5849297019?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E87B9A5E2A9605281144BBEA53533DB7165D1FA0</t>
+          <t>https://www.adzuna.in/land/ad/5843137505?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC4079028ED7338B991CD57034DE9EA5AC8D9A0B</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>e2cd9eda9e</t>
+          <t>6ec3848d0b</t>
         </is>
       </c>
     </row>
@@ -8988,12 +8988,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>Gurgaon, Haryana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>data scientist, delhi (place)</t>
+          <t>data scientist, gurgaon (place)</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5848650875?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4DF45BC4D3A230C0689E561399F3F0BA2C0FC825</t>
+          <t>https://www.adzuna.in/land/ad/5849297019?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E87B9A5E2A9605281144BBEA53533DB7165D1FA0</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>83a3456095</t>
+          <t>e2cd9eda9e</t>
         </is>
       </c>
     </row>
@@ -9039,52 +9039,52 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>GTM AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Customer.io</t>
+          <t>Danaher</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>New Delhi, Delhi</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>data scientist, delhi (place)</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/customer-io-gtm-ai-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5848650875?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4DF45BC4D3A230C0689E561399F3F0BA2C0FC825</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>19a2ae7abb</t>
+          <t>83a3456095</t>
         </is>
       </c>
     </row>
@@ -9100,17 +9100,17 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Performance Creative Strategist and AI Producer</t>
+          <t>GTM AI Engineer</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Icarus Digital Marketing</t>
+          <t>Customer.io</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/icarus-digital-marketing-performance-creative-strategist-and-ai-producer</t>
+          <t>https://weworkremotely.com/remote-jobs/customer-io-gtm-ai-engineer</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>60c87a59fd</t>
+          <t>19a2ae7abb</t>
         </is>
       </c>
     </row>
@@ -9161,37 +9161,37 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>GTM Coordinator, Cloud Native (Talent Pool)</t>
+          <t>Performance Creative Strategist and AI Producer</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Percona</t>
+          <t>Icarus Digital Marketing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bulgaria, Croatia, Czechia, Greece, Hungary, India, Poland, Portugal, Spain</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>cloud, india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>GTM-Coordinator, Talent-Community-Coordinator, Talent-Operations-Coordinator, Entry-level</t>
+          <t>Sales and Marketing, Full-Time</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/percona/jobs/gtm-coordinator-cloud-native-talent-pool</t>
+          <t>https://weworkremotely.com/remote-jobs/icarus-digital-marketing-performance-creative-strategist-and-ai-producer</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>a97ee1ce9b</t>
+          <t>60c87a59fd</t>
         </is>
       </c>
     </row>
@@ -9222,52 +9222,52 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Offensive Cybersecurity Engineer - Red Team</t>
+          <t>GTM Coordinator, Cloud Native (Talent Pool)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Techno Vista Dynamics</t>
+          <t>Percona</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>APAC,Middle East</t>
+          <t>Bulgaria, Croatia, Czechia, Greece, Hungary, India, Poland, Portugal, Spain</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>engineer, testing (tag), apac (place)</t>
+          <t>cloud, india (place)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Development, engineer,security,penetration testing</t>
+          <t>GTM-Coordinator, Talent-Community-Coordinator, Talent-Operations-Coordinator, Entry-level</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1781770/</t>
+          <t>https://himalayas.app/companies/percona/jobs/gtm-coordinator-cloud-native-talent-pool</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>0bde4f9b82</t>
+          <t>a97ee1ce9b</t>
         </is>
       </c>
     </row>
@@ -9279,56 +9279,56 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Human-Centered AI Data Scientist, Strategy and Talent</t>
+          <t>Offensive Cybersecurity Engineer - Red Team</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank</t>
+          <t>Techno Vista Dynamics</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>APAC,Middle East</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>data scientist, ai, bangalore (place)</t>
+          <t>engineer, testing (tag), apac (place)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Development, engineer,security,penetration testing</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139276?se=1M6Kj_qf8RGoxpN31Vp7kA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C0F814CBDD0355075DDB000131DE4C8D130504ED</t>
+          <t>https://www.workingnomads.com/job/go/1781770/</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>3130787ee8</t>
+          <t>0bde4f9b82</t>
         </is>
       </c>
     </row>
@@ -9344,52 +9344,52 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Java Software Develper Engineer</t>
+          <t>Human-Centered AI Data Scientist, Strategy and Talent</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>Standard Chartered Bank</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>programmer (tag), developer (tag), software, engineer, backend (tag), java, india (place)</t>
+          <t>data scientist, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Java-Development, Software-Engineer, Entry-Level-Software-Development, Backend-Development, Technical-Support, Java-Software-Engineer, Java-Developer, Java-Developer-Jobs, Java-Application-Developer, Java-Programmer, Developer, Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/csg/jobs/java-software-develper-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5837139276?se=1M6Kj_qf8RGoxpN31Vp7kA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C0F814CBDD0355075DDB000131DE4C8D130504ED</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>7626a2cdd6</t>
+          <t>3130787ee8</t>
         </is>
       </c>
     </row>
@@ -9405,22 +9405,22 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Android Software Engineer</t>
+          <t>Java Software Develper Engineer</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9430,27 +9430,27 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>software engineer, android, kotlin (tag), worldwide (place)</t>
+          <t>programmer (tag), developer (tag), software, engineer, backend (tag), java, india (place)</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Android-Software-Engineer, Mobile-Development, Android-Development, Software-Engineer, Kotlin, Android-Engineer, Android-Software-Engineering, Mobile-Android-Engineer, Android-Systems-Engineer, Android-Engineering, Mobile-Software-Engineer, Senior</t>
+          <t>Java-Development, Software-Engineer, Entry-Level-Software-Development, Backend-Development, Technical-Support, Java-Software-Engineer, Java-Developer, Java-Developer-Jobs, Java-Application-Developer, Java-Programmer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/hudson-manpower/jobs/android-software-engineer</t>
+          <t>https://himalayas.app/companies/csg/jobs/java-software-develper-engineer</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>afb7954487</t>
+          <t>7626a2cdd6</t>
         </is>
       </c>
     </row>
@@ -9466,37 +9466,37 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Application Security Engineer II</t>
+          <t>Android Software Engineer</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>engineer, devops (tag), anywhere (place)</t>
+          <t>software engineer, android, kotlin (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Android-Software-Engineer, Mobile-Development, Android-Development, Software-Engineer, Kotlin, Android-Engineer, Android-Software-Engineering, Mobile-Android-Engineer, Android-Systems-Engineer, Android-Engineering, Mobile-Software-Engineer, Senior</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/abnormal-application-security-engineer-ii</t>
+          <t>https://himalayas.app/companies/hudson-manpower/jobs/android-software-engineer</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>dc9a51cdbc</t>
+          <t>afb7954487</t>
         </is>
       </c>
     </row>
@@ -9523,56 +9523,56 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>DESARROLLADOR FULL STACK</t>
+          <t>Application Security Engineer II</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kruger NearShore LLC - Rekluti</t>
+          <t>Abnormal</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>full stack, front end (tag), backend (tag), angular (tag), testing (tag), python (tag), golang (tag), devops (tag), cloud (tag), git (tag)</t>
+          <t>engineer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>full stack, front end, python, dev, testing, web dev, quality assurance, devops, c, cloud, nosql, git, flutter, angular, mobile, golang, backend, digital nomad</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-desarrollador-full-stack-kruger-nearshore-llc-rekluti-1137062</t>
+          <t>https://weworkremotely.com/remote-jobs/abnormal-application-security-engineer-ii</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>911da99485</t>
+          <t>dc9a51cdbc</t>
         </is>
       </c>
     </row>
@@ -9588,52 +9588,52 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AI Transformation Owner, Product &amp; Design</t>
+          <t>DESARROLLADOR FULL STACK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Kruger NearShore LLC - Rekluti</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>full stack, front end (tag), backend (tag), angular (tag), testing (tag), python (tag), golang (tag), devops (tag), cloud (tag), git (tag)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Product, Full-Time</t>
+          <t>full stack, front end, python, dev, testing, web dev, quality assurance, devops, c, cloud, nosql, git, flutter, angular, mobile, golang, backend, digital nomad</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/gitlab-ai-transformation-owner-product-design</t>
+          <t>https://remoteOK.com/remote-jobs/remote-desarrollador-full-stack-kruger-nearshore-llc-rekluti-1137062</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>a0e38d6b98</t>
+          <t>911da99485</t>
         </is>
       </c>
     </row>
@@ -9649,52 +9649,52 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>AI Transformation Owner, Product &amp; Design</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Forrester Research, Inc. (US)</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>developer, software (tag), cloud (tag), india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Salesforce-Developer, CRM-Developer, Salesforce-Administrator, Integration-Developer, Software-Developer, Salesforce-CRM-Developer, Salesforce-Application-Developer, Salesforce-Sales-Cloud-Developer, Salesforce-Development, Salesforce-Solutions-Developer, Salesforce-Platform-Developer, Salesforce-Apex-Developer, Force.Com-Developer, Mid-level</t>
+          <t>Product, Full-Time</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/forrester-research-inc-us/jobs/salesforce-developer-8148624472</t>
+          <t>https://weworkremotely.com/remote-jobs/gitlab-ai-transformation-owner-product-design</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>bbbc562c11</t>
+          <t>a0e38d6b98</t>
         </is>
       </c>
     </row>
@@ -9710,17 +9710,17 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>IT Systems Administrator</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ralliant</t>
+          <t>Forrester Research, Inc. (US)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9735,27 +9735,27 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>developer (tag), engineer (tag), india (place)</t>
+          <t>developer, software (tag), cloud (tag), india (place)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Power-Platform-Engineer, Business-intelligence-Engineer, Analytics-Engineer, Microsoft-Fabric-Engineer, Power-BI-Developer, IT-Systems-Administrator, IT-System-Administrator, Systems-Administrator, IT-Systems-Administration, IT-Administrator, Systems-Support-Administrator, Mid-level</t>
+          <t>Salesforce-Developer, CRM-Developer, Salesforce-Administrator, Integration-Developer, Software-Developer, Salesforce-CRM-Developer, Salesforce-Application-Developer, Salesforce-Sales-Cloud-Developer, Salesforce-Development, Salesforce-Solutions-Developer, Salesforce-Platform-Developer, Salesforce-Apex-Developer, Force.Com-Developer, Mid-level</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ralliant/jobs/it-systems-administrator</t>
+          <t>https://himalayas.app/companies/forrester-research-inc-us/jobs/salesforce-developer-8148624472</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>a720a38bd1</t>
+          <t>bbbc562c11</t>
         </is>
       </c>
     </row>
@@ -9767,56 +9767,56 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Talent Pool -FP&amp;A- Data Scientist / Analytics Specialist / Data &amp; AI Specialist</t>
+          <t>IT Systems Administrator</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ralliant</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>data scientist, ai, bangalore (place)</t>
+          <t>developer (tag), engineer (tag), india (place)</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Energy, Oil &amp; Gas Jobs</t>
+          <t>Power-Platform-Engineer, Business-intelligence-Engineer, Analytics-Engineer, Microsoft-Fabric-Engineer, Power-BI-Developer, IT-Systems-Administrator, IT-System-Administrator, Systems-Administrator, IT-Systems-Administration, IT-Administrator, Systems-Support-Administrator, Mid-level</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773115?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=888721B9EAAF876B1F079BC209DECF1099E63440</t>
+          <t>https://himalayas.app/companies/ralliant/jobs/it-systems-administrator</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>5ee47ace79</t>
+          <t>a720a38bd1</t>
         </is>
       </c>
     </row>
@@ -9832,17 +9832,17 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AI and Automation Developer</t>
+          <t>Talent Pool -FP&amp;A- Data Scientist / Analytics Specialist / Data &amp; AI Specialist</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9857,27 +9857,27 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>automation, developer, ai, bangalore (place)</t>
+          <t>data scientist, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Energy, Oil &amp; Gas Jobs</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5847959817?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44960F01CCAE33F814C0EF4448956DF38E8344F5</t>
+          <t>https://www.adzuna.in/land/ad/5785773115?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=888721B9EAAF876B1F079BC209DECF1099E63440</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>98337240aa</t>
+          <t>5ee47ace79</t>
         </is>
       </c>
     </row>
@@ -9893,52 +9893,52 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>DevOps &amp; Security Engineer - AI-Native Healthcare SaaS</t>
+          <t>AI and Automation Developer</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Zenara Health</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>engineer, devops, ai, anywhere (place)</t>
+          <t>automation, developer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/zenara-health-devops-security-engineer-ai-native-healthcare-saas</t>
+          <t>https://www.adzuna.in/land/ad/5847959817?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44960F01CCAE33F814C0EF4448956DF38E8344F5</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>d592e60ddc</t>
+          <t>98337240aa</t>
         </is>
       </c>
     </row>
@@ -9954,37 +9954,37 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps &amp; Security Engineer - AI-Native Healthcare SaaS</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Zenara Health</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>data scientist, mumbai (place)</t>
+          <t>engineer, devops, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723381?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F9660467E3895814968DA45F3A82EF6912496F70</t>
+          <t>https://weworkremotely.com/remote-jobs/zenara-health-devops-security-engineer-ai-native-healthcare-saas</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>c46d670134</t>
+          <t>d592e60ddc</t>
         </is>
       </c>
     </row>
@@ -10025,12 +10025,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data scientist, mumbai (place)</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10050,17 +10050,17 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837138848?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=86962F79F06A105F30676367582529277DE10978</t>
+          <t>https://www.adzuna.in/land/ad/5846723381?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F9660467E3895814968DA45F3A82EF6912496F70</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>39dacd7158</t>
+          <t>c46d670134</t>
         </is>
       </c>
     </row>
@@ -10081,12 +10081,12 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Itvedant Education Pvt. Ltd.</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10111,17 +10111,17 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5833434843?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=95E30E442ED8EDC695067D6ACDD8806A1A4DBE0E</t>
+          <t>https://www.adzuna.in/land/ad/5837138848?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=86962F79F06A105F30676367582529277DE10978</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>660701d5cb</t>
+          <t>39dacd7158</t>
         </is>
       </c>
     </row>
@@ -10142,17 +10142,17 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Itvedant Education Pvt. Ltd.</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>engineer, ai, hyderabad (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10172,17 +10172,17 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139103?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=23D035D0F5CFDFF88D2FBA2CB9721442B70F9874</t>
+          <t>https://www.adzuna.in/land/ad/5833434843?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=95E30E442ED8EDC695067D6ACDD8806A1A4DBE0E</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>c2ca14412d</t>
+          <t>660701d5cb</t>
         </is>
       </c>
     </row>
@@ -10203,17 +10203,17 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>engineer, ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10233,17 +10233,17 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773097?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1AD120B3FB3DFBC7F01669BC535E68EC0F2123A3</t>
+          <t>https://www.adzuna.in/land/ad/5837139103?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=23D035D0F5CFDFF88D2FBA2CB9721442B70F9874</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>1a0dea6270</t>
+          <t>c2ca14412d</t>
         </is>
       </c>
     </row>
@@ -10264,17 +10264,17 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>engineer, ai, bangalore (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10294,17 +10294,17 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723241?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0084818D71681FAC4F572D55AE1C6BC637792931</t>
+          <t>https://www.adzuna.in/land/ad/5785773097?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1AD120B3FB3DFBC7F01669BC535E68EC0F2123A3</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>a2c0a3fc16</t>
+          <t>1a0dea6270</t>
         </is>
       </c>
     </row>
@@ -10325,17 +10325,17 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Part time Data Science Instructor</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10345,27 +10345,27 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>engineer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Part time Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5850983469?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0F708DAB080760E3C6FB3FC40EA3A64A7B0306D9</t>
+          <t>https://www.adzuna.in/land/ad/5846723241?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0084818D71681FAC4F572D55AE1C6BC637792931</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>fa169c0060</t>
+          <t>a2c0a3fc16</t>
         </is>
       </c>
     </row>
@@ -10386,12 +10386,12 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer for AI &amp;DS, BSI</t>
+          <t>Part time Data Science Instructor</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -10406,27 +10406,27 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>engineer, ai, india (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Part time Jobs</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785771743?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F6DC64E0C8FB2D27FC25CBE24085394F367A2687</t>
+          <t>https://www.adzuna.in/land/ad/5850983469?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0F708DAB080760E3C6FB3FC40EA3A64A7B0306D9</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>3fd60b2320</t>
+          <t>fa169c0060</t>
         </is>
       </c>
     </row>
@@ -10447,17 +10447,17 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Agentic AI Engineer for AI &amp;DS, BSI</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>engineer, ai, mumbai (place)</t>
+          <t>engineer, ai, india (place)</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773171?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2185A7049B5506DF1182A45172761BBEF73613FA</t>
+          <t>https://www.adzuna.in/land/ad/5785771743?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F6DC64E0C8FB2D27FC25CBE24085394F367A2687</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>43f406da07</t>
+          <t>3fd60b2320</t>
         </is>
       </c>
     </row>
@@ -10508,17 +10508,17 @@
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Data Scientist - People Analytics</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>engineer, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10538,17 +10538,17 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5821999876?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=08993CE6BE520CA2C34926E81E8CBB0072304E1F</t>
+          <t>https://www.adzuna.in/land/ad/5785773171?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2185A7049B5506DF1182A45172761BBEF73613FA</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>187dc9c03e</t>
+          <t>43f406da07</t>
         </is>
       </c>
     </row>
@@ -10569,17 +10569,17 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>Data Scientist - People Analytics</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Itvedant Education Pvt. Ltd.</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10589,27 +10589,27 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Teaching Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5852476426?se=NskdSSae8RGSb8VpDRDiVA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2B7C55A3F795EE4D2F2D732844EDA9B4CAC3F128</t>
+          <t>https://www.adzuna.in/land/ad/5821999876?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=08993CE6BE520CA2C34926E81E8CBB0072304E1F</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>5c41be551e</t>
+          <t>187dc9c03e</t>
         </is>
       </c>
     </row>
@@ -10625,37 +10625,37 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PHP Developer - Work From Home</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>CC Staffing International</t>
+          <t>Itvedant Education Pvt. Ltd.</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>developer, software (tag), engineer (tag), backend (tag), php, india (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>PHP-Developer, Backend-Engineer, Web-Development, Software-Developer, Full-Stack-Developer, Remote-PHP-Developer, PHP-Software-Engineer, Backend-PHP-Developer, Remote-Web-Developer, Developer, Mid-level</t>
+          <t>Teaching Jobs</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/cc-staffing-international/jobs/php-developer-work-from-home</t>
+          <t>https://www.adzuna.in/land/ad/5852476426?se=NskdSSae8RGSb8VpDRDiVA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2B7C55A3F795EE4D2F2D732844EDA9B4CAC3F128</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>14b619fb91</t>
+          <t>5c41be551e</t>
         </is>
       </c>
     </row>
@@ -10686,52 +10686,52 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Kannada</t>
+          <t>PHP Developer - Work From Home</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>RWS</t>
+          <t>CC Staffing International</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>ai, delhi (place)</t>
+          <t>developer, software (tag), engineer (tag), backend (tag), php, india (place)</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>PHP-Developer, Backend-Engineer, Web-Development, Software-Developer, Full-Stack-Developer, Remote-PHP-Developer, PHP-Software-Engineer, Backend-PHP-Developer, Remote-Web-Developer, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772642?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=96F9E6C80B83A39F4F2C05268274FD2EBE13B037</t>
+          <t>https://himalayas.app/companies/cc-staffing-international/jobs/php-developer-work-from-home</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>bb43fd7b08</t>
+          <t>14b619fb91</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Marathi</t>
+          <t>AI Data Specialist - Kannada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772098?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=B26B7FB6A299BC3A2BFD29BF94BF59C981A24A29</t>
+          <t>https://www.adzuna.in/land/ad/5785772642?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=96F9E6C80B83A39F4F2C05268274FD2EBE13B037</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>fe688433d1</t>
+          <t>bb43fd7b08</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10813,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Telugu</t>
+          <t>AI Data Specialist - Marathi</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785770664?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=D13E17364CDB48C8A2B963F62AC42C33A76C021B</t>
+          <t>https://www.adzuna.in/land/ad/5785772098?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=B26B7FB6A299BC3A2BFD29BF94BF59C981A24A29</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>91c279dfff</t>
+          <t>fe688433d1</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Hindi</t>
+          <t>AI Data Specialist - Telugu</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -10904,17 +10904,17 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5795883387?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=38289BC2F5CA723017CE2916CC4536DEA978B9A6</t>
+          <t>https://www.adzuna.in/land/ad/5785770664?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=D13E17364CDB48C8A2B963F62AC42C33A76C021B</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>170ea3eac1</t>
+          <t>91c279dfff</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10935,7 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Tamil</t>
+          <t>AI Data Specialist - Hindi</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10965,17 +10965,17 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772320?se=xp3UHeGd8RGIEJB03vDchg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AB56F1DD143407CEE31E12C4126DC533B06A2AD3</t>
+          <t>https://www.adzuna.in/land/ad/5795883387?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=38289BC2F5CA723017CE2916CC4536DEA978B9A6</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>616fb76ab0</t>
+          <t>170ea3eac1</t>
         </is>
       </c>
     </row>
@@ -10991,52 +10991,52 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Agent Operations Engineer - Fully Remote | Upto $500/task Task based</t>
+          <t>AI Data Specialist - Tamil</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>RWS</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>New Delhi, Delhi</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>engineer, ai (tag), india (place)</t>
+          <t>ai, delhi (place)</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Agent-Engineering, LLMOperations, AI-Engineering, AI-Operations, Machine-Learning-Engineering, AgentOps-Engineer, Agent-Orchestration-Engineer, AI-Agents-Engineer, Operations-Engineer, Remote-AI-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/mercor/jobs/agent-operations-engineer-fully-remote-upto-500-task-task-based</t>
+          <t>https://www.adzuna.in/land/ad/5785772320?se=xp3UHeGd8RGIEJB03vDchg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AB56F1DD143407CEE31E12C4126DC533B06A2AD3</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>be05dc52ff</t>
+          <t>616fb76ab0</t>
         </is>
       </c>
     </row>
@@ -11052,17 +11052,17 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS Authorized Instructor</t>
+          <t>Agent Operations Engineer - Fully Remote | Upto $500/task Task based</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>ITC WORLDWIDE</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>cloud (tag), aws, india (place)</t>
+          <t>engineer, ai (tag), india (place)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>AWS-Training, Cloud-Computing-Instructor, Technical-Trainer, AWS-Authorized-Instructor, Cloud-Education, AWS-Certification-Training, Cloud-Instructor, Cloud-Computing-Trainer, Senior</t>
+          <t>Agent-Engineering, LLMOperations, AI-Engineering, AI-Operations, Machine-Learning-Engineering, AgentOps-Engineer, Agent-Orchestration-Engineer, AI-Agents-Engineer, Operations-Engineer, Remote-AI-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/itc-worldwide/jobs/aws-authorized-instructor</t>
+          <t>https://himalayas.app/companies/mercor/jobs/agent-operations-engineer-fully-remote-upto-500-task-task-based</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>a42ddc7b02</t>
+          <t>be05dc52ff</t>
         </is>
       </c>
     </row>
@@ -11113,37 +11113,37 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Associate Instructor</t>
+          <t>AWS Authorized Instructor</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>ITC WORLDWIDE</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>devops (tag), associate (level), anywhere (place)</t>
+          <t>cloud (tag), aws, india (place)</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>AWS-Training, Cloud-Computing-Instructor, Technical-Trainer, AWS-Authorized-Instructor, Cloud-Education, AWS-Certification-Training, Cloud-Instructor, Cloud-Computing-Trainer, Senior</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/beyondtrust-associate-instructor</t>
+          <t>https://himalayas.app/companies/itc-worldwide/jobs/aws-authorized-instructor</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>4c1963b96c</t>
+          <t>a42ddc7b02</t>
         </is>
       </c>
     </row>
@@ -11174,52 +11174,52 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>E-learning Developer</t>
+          <t>Associate Instructor</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Crowe UAE</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>developer, ahmedabad (place)</t>
+          <t>devops (tag), associate (level), anywhere (place)</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5850983902?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F927DE790D9874EE6BA8C142D15CF3A7A97BFA7E</t>
+          <t>https://weworkremotely.com/remote-jobs/beyondtrust-associate-instructor</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>843701dc9e</t>
+          <t>4c1963b96c</t>
         </is>
       </c>
     </row>
@@ -11235,52 +11235,52 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Developer Educator</t>
+          <t>E-learning Developer</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>PlanetScale</t>
+          <t>Crowe UAE</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Ahmedabad, Gujarat</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>developer, anywhere (place)</t>
+          <t>developer, ahmedabad (place)</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/planetscale-developer-educator</t>
+          <t>https://www.adzuna.in/land/ad/5850983902?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F927DE790D9874EE6BA8C142D15CF3A7A97BFA7E</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>c72ab4031d</t>
+          <t>843701dc9e</t>
         </is>
       </c>
     </row>
@@ -11296,50 +11296,111 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
+          <t>Developer Educator</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>PlanetScale</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Anywhere in the World</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>weworkremotely</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>developer, anywhere (place)</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Sales and Marketing, Full-Time</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/planetscale-developer-educator</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>c72ab4031d</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>11</v>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
           <t>Consultant Implementation Engineer</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>Harbor</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G179" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="H179" t="inlineStr">
         <is>
           <t>remoteok</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="I179" t="inlineStr">
         <is>
           <t>engineer, golang (tag), remote (place)</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
+      <c r="J179" t="inlineStr">
         <is>
           <t>consulting, technical, accounting, legal, golang, engineer</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="K179" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-consultant-implementation-engineer-harbor-1136987</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t>f724e65bc8</t>
         </is>
@@ -11347,7 +11408,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A178" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of: new, applied, skipped" prompt="Mark this job applied once you have applied." type="list">
+    <dataValidation sqref="A2:A179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of: new, applied, skipped" prompt="Mark this job applied once you have applied." type="list">
       <formula1>"new,applied,skipped"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M179"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -573,17 +573,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anthropic Fellows Program, AI Safety &amp; Security</t>
+          <t>AI agent engineer</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Sticker Mule</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>All Other Remote, Full-Time</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/anthropic-anthropic-fellows-program-ai-safety-security</t>
+          <t>https://weworkremotely.com/remote-jobs/sticker-mule-ai-agent-engineer</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bf649aa9a3</t>
+          <t>e0b3cdfcc1</t>
         </is>
       </c>
     </row>
@@ -630,56 +630,56 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Anthropic Fellows Program, AI Safety &amp; Security</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atlys</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>artificial intelligence, intern (level), india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>All Other Remote, Full-Time</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876870198?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=887C5853FA1B767B096C42327F5C3826C21742CE</t>
+          <t>https://weworkremotely.com/remote-jobs/anthropic-anthropic-fellows-program-ai-safety-security</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>b169bf4100</t>
+          <t>bf649aa9a3</t>
         </is>
       </c>
     </row>
@@ -695,22 +695,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MTS-1 Machine Learning Engineer</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Atlys</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>artificial intelligence, intern (level), india (place)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877184305?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8749753C0B487764A74F37A03D96F548F15161A9</t>
+          <t>https://www.adzuna.in/land/ad/5876870198?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=887C5853FA1B767B096C42327F5C3826C21742CE</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>fab40e54d1</t>
+          <t>b169bf4100</t>
         </is>
       </c>
     </row>
@@ -756,52 +756,52 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MTS-1 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smartcuts</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), frontend (tag), worldwide (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Engineering, Software-Engineer, Frontend-Development, Fullstack-Development, Browser-Extension-Development, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Software-Design-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/smartcuts/jobs/software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5877184305?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8749753C0B487764A74F37A03D96F548F15161A9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1191a23402</t>
+          <t>fab40e54d1</t>
         </is>
       </c>
     </row>
@@ -817,17 +817,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GitHub Contributor</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Smartcuts</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), frontend (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
+          <t>Engineering, Software-Engineer, Frontend-Development, Fullstack-Development, Browser-Extension-Development, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Software-Design-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-106728860</t>
+          <t>https://himalayas.app/companies/smartcuts/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>f02b389972</t>
+          <t>1191a23402</t>
         </is>
       </c>
     </row>
@@ -874,58 +874,56 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Backend Engineer, IAM</t>
+          <t>GitHub Contributor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>engineer, backend, anywhere (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/reddit-backend-engineer-iam</t>
+          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-106728860</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>790d0d9505</t>
+          <t>f02b389972</t>
         </is>
       </c>
     </row>
@@ -944,16 +942,16 @@
         <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Developer Advocate - Service Management</t>
+          <t>Backend Engineer, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -968,12 +966,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>developer, devops (tag), anywhere (place)</t>
+          <t>engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -983,12 +981,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/datadog-developer-advocate-service-management</t>
+          <t>https://weworkremotely.com/remote-jobs/reddit-backend-engineer-iam</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>4df8de53d8</t>
+          <t>790d0d9505</t>
         </is>
       </c>
     </row>
@@ -1004,37 +1002,39 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>QA Testers Wanted (No experience needed)</t>
+          <t>Developer Advocate - Service Management</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tester Work</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Australia &amp; New Zealand (REMOTE)</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>qa, remote (place)</t>
+          <t>developer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1860630/</t>
+          <t>https://weworkremotely.com/remote-jobs/datadog-developer-advocate-service-management</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>bf909f7a1f</t>
+          <t>4df8de53d8</t>
         </is>
       </c>
     </row>
@@ -1061,58 +1061,56 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist II, ML Infrastructure</t>
+          <t>QA Testers Wanted (No experience needed)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Tester Work</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Australia &amp; New Zealand (REMOTE)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data scientist, ml, anywhere (place)</t>
+          <t>qa, remote (place)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-ml-infrastructure</t>
+          <t>https://www.workingnomads.com/job/go/1860630/</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>a84319c791</t>
+          <t>bf909f7a1f</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1126,14 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist II, Infrastructure</t>
+          <t>Data Scientist II, ML Infrastructure</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data scientist, anywhere (place)</t>
+          <t>data scientist, ml, anywhere (place)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-infrastructure</t>
+          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-ml-infrastructure</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>def323e358</t>
+          <t>a84319c791</t>
         </is>
       </c>
     </row>
@@ -1189,52 +1189,52 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II, Infrastructure</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>software engineer, golang (tag)</t>
+          <t>data scientist, anywhere (place)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>golang, dev, engineer, digital nomad</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-mirantis-1137387</t>
+          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-infrastructure</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0eb27a0401</t>
+          <t>def323e358</t>
         </is>
       </c>
     </row>
@@ -1246,41 +1246,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Science Engineer - AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data science, engineer, ai, bangalore (place)</t>
+          <t>software engineer, golang (tag)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>golang, dev, engineer, digital nomad</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880523483?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44AFB881700BC2524FE70C04638A2D65741F5C06</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-mirantis-1137387</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>987c89c61a</t>
+          <t>0eb27a0401</t>
         </is>
       </c>
     </row>
@@ -1311,22 +1311,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning</t>
+          <t>Data Science Engineer - AI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kotak Neo</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>machine learning, ai, mumbai (place)</t>
+          <t>data science, engineer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880062262?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC74E214D0612FE80831EDD83B8CF67B6032A3E9</t>
+          <t>https://www.adzuna.in/land/ad/5880523483?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44AFB881700BC2524FE70C04638A2D65741F5C06</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>c8b4bb4ba3</t>
+          <t>987c89c61a</t>
         </is>
       </c>
     </row>
@@ -1372,37 +1372,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>AI &amp; Machine Learning</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Kotak Neo</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>software (tag), engineer, ai (tag), ml, worldwide (place)</t>
+          <t>machine learning, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Machine-Learning-Engineer, AI-ML-Engineer, ML-Software-Engineer, ML-Research-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ml-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5880062262?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC74E214D0612FE80831EDD83B8CF67B6032A3E9</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6b92e0e58d</t>
+          <t>c8b4bb4ba3</t>
         </is>
       </c>
     </row>
@@ -1438,47 +1438,47 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data science, india (place), chandigarh (place)</t>
+          <t>software (tag), engineer, ai (tag), ml, worldwide (place)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Machine-Learning-Engineer, AI-ML-Engineer, ML-Software-Engineer, ML-Research-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5879662958?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7C90B2BB52AA81EB60C613281A1D6AF4E5DC8BD8</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ml-engineer</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6557a8e75a</t>
+          <t>6b92e0e58d</t>
         </is>
       </c>
     </row>
@@ -1494,54 +1494,52 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PhD &amp; Academic Expert</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ml (tag), worldwide (place)</t>
+          <t>data science, india (place), chandigarh (place)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Academic-Expert, PhD-Specialist-Consultant, Academic-Consultant, Academic-Subject-Matter-Expert, Academic-Professional, ML-Research-PhD-Expert, PhD-Researcher, Education-Expert, Mid-level, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/phd-academic-expert</t>
+          <t>https://www.adzuna.in/land/ad/5879662958?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7C90B2BB52AA81EB60C613281A1D6AF4E5DC8BD8</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>a8281d77e1</t>
+          <t>6557a8e75a</t>
         </is>
       </c>
     </row>
@@ -1553,23 +1551,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>PhD &amp; Academic Expert</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dura Digital</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1584,27 +1582,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>engineer, backend (tag), python (tag), ai, ml (tag), worldwide (place)</t>
+          <t>ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>AI-Engineer, Machine-Learning-Engineer, Backend-Engineer, Data-Engineer, MLOps-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Senior</t>
+          <t>Academic-Expert, PhD-Specialist-Consultant, Academic-Consultant, Academic-Subject-Matter-Expert, Academic-Professional, ML-Research-PhD-Expert, PhD-Researcher, Education-Expert, Mid-level, Senior</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/dura-digital/jobs/ai-engineer</t>
+          <t>https://himalayas.app/companies/micro1/jobs/phd-academic-expert</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>8666ff7b1c</t>
+          <t>a8281d77e1</t>
         </is>
       </c>
     </row>
@@ -1620,17 +1618,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Facial Data Collection Associate</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Dura Digital</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ai, associate (level), worldwide (place)</t>
+          <t>engineer, backend (tag), python (tag), ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>AI-Data-Collection-Specialist, Data-Collection-Associate, Facial-Recognition-Data-Collection, AI-Services-Associate, AI-Operations-Associate, AI-Associate, Entry-level</t>
+          <t>AI-Engineer, Machine-Learning-Engineer, Backend-Engineer, Data-Engineer, MLOps-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Senior</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-facial-data-collection-associate</t>
+          <t>https://himalayas.app/companies/dura-digital/jobs/ai-engineer</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>a024718d12</t>
+          <t>8666ff7b1c</t>
         </is>
       </c>
     </row>
@@ -1681,54 +1681,52 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>49</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Facial Data Collection Associate</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Omnicom Global Solutions</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>ai, associate (level), worldwide (place)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Data-Collection-Specialist, Data-Collection-Associate, Facial-Recognition-Data-Collection, AI-Services-Associate, AI-Operations-Associate, AI-Associate, Entry-level</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880062427?se=4EjJjS6u8RGGGqTWwpKkng&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E0A2211C95EBCFB9C1236FB6E39F7FBF4A7836A8</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-facial-data-collection-associate</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>c539f926b2</t>
+          <t>a024718d12</t>
         </is>
       </c>
     </row>
@@ -1744,54 +1742,54 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Financial Systems Expert</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Omnicom Global Solutions</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>developer (tag), engineer (tag), worldwide (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Financial-Systems-Specialist, Financial-Systems-Consultant, Financial-Systems-Advisor, Finance-Systems-Specialist, Financial-Systems-Consulting, Finance-Systems-Consultant, Financial-Systems-Developer, Financial-Systems-Integration-Specialist, Financial-Systems-Architect, Financial-Systems-Engineer, Mid-level, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/financial-systems-expert</t>
+          <t>https://www.adzuna.in/land/ad/5880062427?se=4EjJjS6u8RGGGqTWwpKkng&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E0A2211C95EBCFB9C1236FB6E39F7FBF4A7836A8</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>a8090f5869</t>
+          <t>c539f926b2</t>
         </is>
       </c>
     </row>
@@ -1803,56 +1801,58 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>79</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DVP - Data Science AI</t>
+          <t>Financial Systems Expert</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IndiaFirst Life</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>data science, ai, mumbai (place)</t>
+          <t>developer (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Financial-Systems-Specialist, Financial-Systems-Consultant, Financial-Systems-Advisor, Finance-Systems-Specialist, Financial-Systems-Consulting, Finance-Systems-Consultant, Financial-Systems-Developer, Financial-Systems-Integration-Specialist, Financial-Systems-Architect, Financial-Systems-Engineer, Mid-level, Senior</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877452336?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C389ADE3462A8F960BCEB9BFB3D8C01182D8F284</t>
+          <t>https://himalayas.app/companies/micro1/jobs/financial-systems-expert</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>d4091e9b06</t>
+          <t>a8090f5869</t>
         </is>
       </c>
     </row>
@@ -1868,22 +1868,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DVP - Data Science AI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ryewalk</t>
+          <t>IndiaFirst Life</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data scientist, chennai (place)</t>
+          <t>data science, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877457613?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=858E7DDB9C73029BB012BE9266CDC5516D57BB06</t>
+          <t>https://www.adzuna.in/land/ad/5877452336?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C389ADE3462A8F960BCEB9BFB3D8C01182D8F284</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5b1e04fbec</t>
+          <t>d4091e9b06</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Ryewalk</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876016078?se=tjzQcmWt8RGk7Nm076a3Fw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=076A6D8BF6D1FAB77910335EA1D3406F73F06FDC</t>
+          <t>https://www.adzuna.in/land/ad/5877457613?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=858E7DDB9C73029BB012BE9266CDC5516D57BB06</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03602a7f75</t>
+          <t>5b1e04fbec</t>
         </is>
       </c>
     </row>
@@ -1990,52 +1990,52 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>QA Tester Entry Level</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ace IT Careers</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>testing (tag), qa, entry level (level), remote (place)</t>
+          <t>data scientist, chennai (place)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>testing, dev, analyst, quality assurance, digital nomad</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-qa-tester-entry-level-ace-it-careers-1136701</t>
+          <t>https://www.adzuna.in/land/ad/5876016078?se=tjzQcmWt8RGk7Nm076a3Fw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=076A6D8BF6D1FAB77910335EA1D3406F73F06FDC</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>066819b5ee</t>
+          <t>03602a7f75</t>
         </is>
       </c>
     </row>
@@ -2051,54 +2051,52 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>32</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>QA Tester Entry Level</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sun King</t>
+          <t>Ace IT Careers</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>software (tag), engineer, cloud (tag), api (tag), india (place)</t>
+          <t>testing (tag), qa, entry level (level), remote (place)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Application-Security-Engineer, Security-Engineer, Penetration-Tester, API-Security, Cloud-Security-Engineer, AppSec-Engineer, Application-Security-Engineering, Application-Security-Specialist, Software-Security-Engineer, Mid-level</t>
+          <t>testing, dev, analyst, quality assurance, digital nomad</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/sun-king/jobs/application-security-engineer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-qa-tester-entry-level-ace-it-careers-1136701</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>41b24c0687</t>
+          <t>066819b5ee</t>
         </is>
       </c>
     </row>
@@ -2116,15 +2114,17 @@
       <c r="C28" t="n">
         <v>32</v>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nuclear Physics Specialist - Fully Remote | Upto $100/hr</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>Sun King</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>engineer (tag), ai (tag), india (place)</t>
+          <t>software (tag), engineer, cloud (tag), api (tag), india (place)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Computational-Physics, Nuclear-Physics, Particle-Physics, AI-Evaluation, Scientific-Computing, Nuclear-Physics-AI-Specialist, Freelance-Physics-Specialist, Reactor-Physics-Engineer, Freelance-Physics-Expert, Physics-Research-Specialist, Physics-Freelancer, Mid-level</t>
+          <t>Application-Security-Engineer, Security-Engineer, Penetration-Tester, API-Security, Cloud-Security-Engineer, AppSec-Engineer, Application-Security-Engineering, Application-Security-Specialist, Software-Security-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/mercor/jobs/nuclear-physics-specialist-fully-remote-upto-100-hr-6652317191</t>
+          <t>https://himalayas.app/companies/sun-king/jobs/application-security-engineer</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>e80acb6174</t>
+          <t>41b24c0687</t>
         </is>
       </c>
     </row>
@@ -2171,58 +2171,56 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>65</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Nuclear Physics Specialist - Fully Remote | Upto $100/hr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dynamics Monk Consulting Services</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>artificial intelligence, india (place), delhi (place)</t>
+          <t>engineer (tag), ai (tag), india (place)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Computational-Physics, Nuclear-Physics, Particle-Physics, AI-Evaluation, Scientific-Computing, Nuclear-Physics-AI-Specialist, Freelance-Physics-Specialist, Reactor-Physics-Engineer, Freelance-Physics-Expert, Physics-Research-Specialist, Physics-Freelancer, Mid-level</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028069?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F290F3C8F39D5ABB349E29F918917B30A38BA853</t>
+          <t>https://himalayas.app/companies/mercor/jobs/nuclear-physics-specialist-fully-remote-upto-100-hr-6652317191</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9010d87d61</t>
+          <t>e80acb6174</t>
         </is>
       </c>
     </row>
@@ -2238,22 +2236,24 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>54</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vahan.ai</t>
+          <t>Dynamics Monk Consulting Services</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, india (place), delhi (place)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876029045?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1440DAC38EB3556F9000947FA0A0834CFF14AB75</t>
+          <t>https://www.adzuna.in/land/ad/5876028069?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F290F3C8F39D5ABB349E29F918917B30A38BA853</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>56f72b7a03</t>
+          <t>9010d87d61</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>EYEGLOBAL SOLUTIONS PVT. LTD.</t>
+          <t>Vahan.ai</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, chennai (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028703?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9D6C280D30C30F591E884FDA2F691CC4409C3EC6</t>
+          <t>https://www.adzuna.in/land/ad/5876029045?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1440DAC38EB3556F9000947FA0A0834CFF14AB75</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>bafec6742f</t>
+          <t>56f72b7a03</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Appglide Solutions</t>
+          <t>EYEGLOBAL SOLUTIONS PVT. LTD.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876870603?se=DiEjalis8RGQ-MmLyhoJEg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=987B153BD1BD745987463A7F926C3F0CC163AE60</t>
+          <t>https://www.adzuna.in/land/ad/5876028703?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9D6C280D30C30F591E884FDA2F691CC4409C3EC6</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>d4bbc378a8</t>
+          <t>bafec6742f</t>
         </is>
       </c>
     </row>
@@ -2426,17 +2426,17 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MTS-2 Machine Learning Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Appglide Solutions</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, chennai (place)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877184044?se=ME0PiYGs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=DBDB737DEAF34AD8D344749E581C417C10EC5A31</t>
+          <t>https://www.adzuna.in/land/ad/5876870603?se=DiEjalis8RGQ-MmLyhoJEg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=987B153BD1BD745987463A7F926C3F0CC163AE60</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>37872b8c00</t>
+          <t>d4bbc378a8</t>
         </is>
       </c>
     </row>
@@ -2482,37 +2482,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Account Executive, AI/HPC, Neo / Sovereign Cloud (EMEA)</t>
+          <t>MTS-2 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Everpure</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>cloud, ai, anywhere (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/everpure-account-executive-ai-hpc-neo-sovereign-cloud-emea</t>
+          <t>https://www.adzuna.in/land/ad/5877184044?se=ME0PiYGs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=DBDB737DEAF34AD8D344749E581C417C10EC5A31</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>44fbf0ebf8</t>
+          <t>37872b8c00</t>
         </is>
       </c>
     </row>
@@ -2543,39 +2543,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>49</v>
-      </c>
-      <c r="D35" t="n">
-        <v>3</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Account Executive, AI/HPC, Neo / Sovereign Cloud (EMEA)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Infosys Finacle</t>
+          <t>Everpure</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>cloud, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Sales and Marketing, Full-Time</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2585,12 +2583,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876010793?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8D81876C99F248DACDDC8104E41D7CB59A09112B</t>
+          <t>https://weworkremotely.com/remote-jobs/everpure-account-executive-ai-hpc-neo-sovereign-cloud-emea</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>68b1b69943</t>
+          <t>44fbf0ebf8</t>
         </is>
       </c>
     </row>
@@ -2606,37 +2604,39 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>47</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Frontend Developer - Talent Pool</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Espeo Software</t>
+          <t>Infosys Finacle</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>developer, frontend, software (tag), engineer (tag), react (tag), worldwide (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Frontend-Development, Web-Development, Software-Development, ContractWorks, Freelance-Development, Frontend-Development-Jobs, Tech-Talent-Pool, Front-End-Developer, Technology-Talent-Pool, Engineering-Talent-Pool, Frontend-React-Developer, React-Frontend-Developer, Frontend-Engineer, Developer, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/espeo-software/jobs/frontend-developer-talent-pool</t>
+          <t>https://www.adzuna.in/land/ad/5876010793?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8D81876C99F248DACDDC8104E41D7CB59A09112B</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>409bd93507</t>
+          <t>68b1b69943</t>
         </is>
       </c>
     </row>
@@ -2667,17 +2667,17 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe AEP)</t>
+          <t>Frontend Developer - Talent Pool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TechBiz Global</t>
+          <t>Espeo Software</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>data engineer, developer (tag), cloud (tag), worldwide (place)</t>
+          <t>developer, frontend, software (tag), engineer (tag), react (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Data-Engineering, ETL-Development, Cloud-Data-Engineering, Adobe-Experience-Platform, Data-Integration, Adobe-CDP-Engineer, Data-Engineer, Adobe-Experience-Platform-Engineer, Data-Engineer-Jobs, Data-Platform-Engineer, Enterprise-Data-Engineer, Developer, Senior</t>
+          <t>Frontend-Development, Web-Development, Software-Development, ContractWorks, Freelance-Development, Frontend-Development-Jobs, Tech-Talent-Pool, Front-End-Developer, Technology-Talent-Pool, Engineering-Talent-Pool, Frontend-React-Developer, React-Frontend-Developer, Frontend-Engineer, Developer, Senior</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/techbiz-global/jobs/data-engineer-adobe-aep-7933835037</t>
+          <t>https://himalayas.app/companies/espeo-software/jobs/frontend-developer-talent-pool</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3cf5fcdc34</t>
+          <t>409bd93507</t>
         </is>
       </c>
     </row>
@@ -2728,52 +2728,52 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Social Comms</t>
+          <t>Data Engineer (Adobe AEP)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NOPE</t>
+          <t>TechBiz Global</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ai (tag)</t>
+          <t>data engineer, developer (tag), cloud (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>marketing, education, technical, content writing, social media, ai, social</t>
+          <t>Data-Engineering, ETL-Development, Cloud-Data-Engineering, Adobe-Experience-Platform, Data-Integration, Adobe-CDP-Engineer, Data-Engineer, Adobe-Experience-Platform-Engineer, Data-Engineer-Jobs, Data-Platform-Engineer, Enterprise-Data-Engineer, Developer, Senior</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-social-comms-nope-1137314</t>
+          <t>https://himalayas.app/companies/techbiz-global/jobs/data-engineer-adobe-aep-7933835037</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>417f6ff5ea</t>
+          <t>3cf5fcdc34</t>
         </is>
       </c>
     </row>
@@ -2785,56 +2785,56 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Social Comms</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>NOPE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>ai (tag)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>marketing, education, technical, content writing, social media, ai, social</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876024927?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0BB3A9B6F76E859DE51E5C2F0066293EDC5FE6EA</t>
+          <t>https://remoteOK.com/remote-jobs/remote-social-comms-nope-1137314</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0851d46422</t>
+          <t>417f6ff5ea</t>
         </is>
       </c>
     </row>
@@ -2860,12 +2860,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Questhiring</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876027895?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=09A0BE7549E8D3105D5BC0AA92FAA0662C7CD065</t>
+          <t>https://www.adzuna.in/land/ad/5876024927?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0BB3A9B6F76E859DE51E5C2F0066293EDC5FE6EA</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>8a025ec1ce</t>
+          <t>0851d46422</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TBO.COM</t>
+          <t>Questhiring</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026044?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FDDB74C699BD4423DAD1E4FB7120816040F747A</t>
+          <t>https://www.adzuna.in/land/ad/5876027895?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=09A0BE7549E8D3105D5BC0AA92FAA0662C7CD065</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>a427b9cd23</t>
+          <t>8a025ec1ce</t>
         </is>
       </c>
     </row>
@@ -2982,12 +2982,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ADB SAFEGATE</t>
+          <t>TBO.COM</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2997,12 +2997,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, hyderabad (place)</t>
+          <t>artificial intelligence, engineer, india (place)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026294?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9C70BDA29FFF510B21324AF211D635A868DC48AA</t>
+          <t>https://www.adzuna.in/land/ad/5876026044?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FDDB74C699BD4423DAD1E4FB7120816040F747A</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>292ee6d2c1</t>
+          <t>a427b9cd23</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neural Foundry</t>
+          <t>ADB SAFEGATE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026040?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8CA62DE6EFC7E6B952E843BFE686F26AF0E83028</t>
+          <t>https://www.adzuna.in/land/ad/5876026294?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9C70BDA29FFF510B21324AF211D635A868DC48AA</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>c1e16bca2e</t>
+          <t>292ee6d2c1</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DotKonnekt</t>
+          <t>Neural Foundry</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, hyderabad (place)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026944?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=51439456D8BA015D122C9B9E72B93BC7715ADC62</t>
+          <t>https://www.adzuna.in/land/ad/5876026040?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8CA62DE6EFC7E6B952E843BFE686F26AF0E83028</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>172ee82bd6</t>
+          <t>c1e16bca2e</t>
         </is>
       </c>
     </row>
@@ -3165,12 +3165,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Recro</t>
+          <t>DotKonnekt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876027463?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=40F66C80D240EB217C5AF3C758F1793D002D574F</t>
+          <t>https://www.adzuna.in/land/ad/5876026944?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=51439456D8BA015D122C9B9E72B93BC7715ADC62</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>91af896417</t>
+          <t>172ee82bd6</t>
         </is>
       </c>
     </row>
@@ -3221,17 +3221,17 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer 2</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Frinks AI</t>
+          <t>Recro</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, india (place)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876025062?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=75AA49B421B5A4EB6F3C207636FED47095B332D0</t>
+          <t>https://www.adzuna.in/land/ad/5876027463?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=40F66C80D240EB217C5AF3C758F1793D002D574F</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2d2a6d873d</t>
+          <t>91af896417</t>
         </is>
       </c>
     </row>
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Specialist</t>
+          <t>Artificial Intelligence Engineer 2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ITC Infotech</t>
+          <t>Frinks AI</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>artificial intelligence, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876024946?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=6D480BEF34A3386CBC920920C7CE13B96BCBAD34</t>
+          <t>https://www.adzuna.in/land/ad/5876025062?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=75AA49B421B5A4EB6F3C207636FED47095B332D0</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>140496e40b</t>
+          <t>2d2a6d873d</t>
         </is>
       </c>
     </row>
@@ -3343,17 +3343,17 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Artificial Intelligence Specialist</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tech Mahindra</t>
+          <t>ITC Infotech</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>artificial intelligence, bangalore (place)</t>
+          <t>artificial intelligence, india (place)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026586?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=666546215EA3297D7CF61A793A40232CBB0EC67B</t>
+          <t>https://www.adzuna.in/land/ad/5876024946?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=6D480BEF34A3386CBC920920C7CE13B96BCBAD34</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>25604d55ae</t>
+          <t>140496e40b</t>
         </is>
       </c>
     </row>
@@ -3399,22 +3399,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Data and AI Scientist</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>The Edge Partnership - The Edge in Asia</t>
+          <t>Tech Mahindra</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ai, hyderabad (place)</t>
+          <t>artificial intelligence, bangalore (place)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876025532?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AD1D30D29AD931A0AA847E54CFF303EEB0007BE9</t>
+          <t>https://www.adzuna.in/land/ad/5876026586?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=666546215EA3297D7CF61A793A40232CBB0EC67B</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>bc9357c4ff</t>
+          <t>25604d55ae</t>
         </is>
       </c>
     </row>
@@ -3460,52 +3460,52 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AI Response Evaluator</t>
+          <t>Data and AI Scientist</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>iMerit</t>
+          <t>The Edge Partnership - The Edge in Asia</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>All Other Remote, Contract</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/imerit-ai-response-evaluator</t>
+          <t>https://www.adzuna.in/land/ad/5876025532?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AD1D30D29AD931A0AA847E54CFF303EEB0007BE9</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>d4b5bc7818</t>
+          <t>bc9357c4ff</t>
         </is>
       </c>
     </row>
@@ -3521,37 +3521,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sustainability Full-Stack Developer (100 % remote) (m/f/d)</t>
+          <t>AI Response Evaluator</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>EWOR GmbH</t>
+          <t>iMerit</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>fullstack (tag), developer, software (tag), engineer (tag), worldwide (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Fullstack-Development, Web-Development, Sustainability, Software-Engineer, Sustainability-Technology, Remote-Senior-Full-Stack-Developer, Remote-Full-Stack-Developer, Full-Stack-Developer, Senior</t>
+          <t>All Other Remote, Contract</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ewor-gmbh/jobs/sustainability-full-stack-developer-100-remote-m-f-d</t>
+          <t>https://weworkremotely.com/remote-jobs/imerit-ai-response-evaluator</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>7da6fdc2ab</t>
+          <t>d4b5bc7818</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Industrial Tech AgentOps Engineer (100 % remote) (m/f/d)</t>
+          <t>Sustainability Full-Stack Developer (100 % remote) (m/f/d)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>engineer, devops (tag), worldwide (place)</t>
+          <t>fullstack (tag), developer, software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>AgentOps-Engineer, Industrial-Technology, Operations-Engineering, Technical-Product-Management, Start-Up-Operations, Remote-Operations-Engineer, Industrial-IoT-Engineer, Remote-DevOps-Engineer, TechOps-Engineer, Remote-Infrastructure-Monitoring-Engineer, Remote-Distributed-Systems-Engineer-II, Mid-level</t>
+          <t>Fullstack-Development, Web-Development, Sustainability, Software-Engineer, Sustainability-Technology, Remote-Senior-Full-Stack-Developer, Remote-Full-Stack-Developer, Full-Stack-Developer, Senior</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ewor-gmbh/jobs/industrial-tech-agentops-engineer-100-remote-m-f-d</t>
+          <t>https://himalayas.app/companies/ewor-gmbh/jobs/sustainability-full-stack-developer-100-remote-m-f-d</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>cedc8889fb</t>
+          <t>7da6fdc2ab</t>
         </is>
       </c>
     </row>
@@ -3639,56 +3639,56 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AI Response Analyst</t>
+          <t>Industrial Tech AgentOps Engineer (100 % remote) (m/f/d)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>iMerit Technology</t>
+          <t>EWOR GmbH</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>engineer, devops (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>content writing, quality assurance, ai</t>
+          <t>AgentOps-Engineer, Industrial-Technology, Operations-Engineering, Technical-Product-Management, Start-Up-Operations, Remote-Operations-Engineer, Industrial-IoT-Engineer, Remote-DevOps-Engineer, TechOps-Engineer, Remote-Infrastructure-Monitoring-Engineer, Remote-Distributed-Systems-Engineer-II, Mid-level</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-ai-response-analyst-imerit-technology-1137309</t>
+          <t>https://himalayas.app/companies/ewor-gmbh/jobs/industrial-tech-agentops-engineer-100-remote-m-f-d</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>05cb840193</t>
+          <t>cedc8889fb</t>
         </is>
       </c>
     </row>
@@ -3700,58 +3700,56 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>30</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Response Analyst</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>iMerit Technology</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>content writing, quality assurance, ai</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>57</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Python Backend Engineer (m/f/x)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Makersite</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Worldwide</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>himalayas</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>developer (tag), software (tag), engineer, backend, python, api (tag), worldwide (place)</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Python-Backend-Engineering, Backend-Development, Software-Engineer, API-Development, Python-Engineering, Python-Backend-Engineer, Python-Backend-Developer, Senior-Backend-Python-Developer, Senior-Python-Backend-Developer, Backend-Engineer, Product-Backend-Engineer, Backend-Services-Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/makersite/jobs/python-backend-engineer-m-f-x</t>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-response-analyst-imerit-technology-1137309</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>3eb1e889db</t>
+          <t>05cb840193</t>
         </is>
       </c>
     </row>
@@ -3767,19 +3765,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Python Backend Engineer (m/f/x)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>S-PRO</t>
+          <t>Makersite</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3794,12 +3792,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>software (tag), engineer, backend (tag), python, cloud (tag), aws (tag), worldwide (place)</t>
+          <t>developer (tag), software (tag), engineer, backend, python, api (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Python-Engineering, Backend-Development, AWS-Cloud-Development, Serverless-Development, Software-Engineer, Python-Engineer, Python-Software-Engineer, Mid-level</t>
+          <t>Python-Backend-Engineering, Backend-Development, Software-Engineer, API-Development, Python-Engineering, Python-Backend-Engineer, Python-Backend-Developer, Senior-Backend-Python-Developer, Senior-Python-Backend-Developer, Backend-Engineer, Product-Backend-Engineer, Backend-Services-Engineer, Senior</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3809,12 +3807,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/s-pro/jobs/python-engineer</t>
+          <t>https://himalayas.app/companies/makersite/jobs/python-backend-engineer-m-f-x</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>67bda4c374</t>
+          <t>3eb1e889db</t>
         </is>
       </c>
     </row>
@@ -3830,19 +3828,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Daymark Health</t>
+          <t>S-PRO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3857,12 +3855,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), worldwide (place)</t>
+          <t>software (tag), engineer, backend (tag), python, cloud (tag), aws (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Software-Engineer, Healthcare-Technology, Backend-Engineering, Fullstack-Development, Health-Tech, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Developer, Mid-level</t>
+          <t>Python-Engineering, Backend-Development, AWS-Cloud-Development, Serverless-Development, Software-Engineer, Python-Engineer, Python-Software-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3872,12 +3870,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/daymark-health/jobs/software-engineer</t>
+          <t>https://himalayas.app/companies/s-pro/jobs/python-engineer</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>85c899deaf</t>
+          <t>67bda4c374</t>
         </is>
       </c>
     </row>
@@ -3889,56 +3887,58 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>84</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Specialist, Data Science &amp; Artificial Intelligence</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Daymark Health</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>artificial intelligence, data science, india (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>Software-Engineer, Healthcare-Technology, Backend-Engineering, Fullstack-Development, Health-Tech, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5871846075?se=oI2O_Sup8RGogquEo3zAlQ&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=326B6FA659B880A3C0F3E2CA4AB8E0734BF69D7B</t>
+          <t>https://himalayas.app/companies/daymark-health/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>c1e8559189</t>
+          <t>85c899deaf</t>
         </is>
       </c>
     </row>
@@ -3954,39 +3954,37 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>50</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Specialist, Data Science &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>xneelo</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), devops (tag), worldwide (place)</t>
+          <t>artificial intelligence, data science, india (place)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Software-Engineer, Backend-Development, Fullstack-Development, Infrastructure-Engineering, DevOps, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Senior</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3996,12 +3994,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/xneelo-co/jobs/software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5871846075?se=oI2O_Sup8RGogquEo3zAlQ&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=326B6FA659B880A3C0F3E2CA4AB8E0734BF69D7B</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>679e1ed2b3</t>
+          <t>c1e8559189</t>
         </is>
       </c>
     </row>
@@ -4017,39 +4015,39 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AEM Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vonage</t>
+          <t>xneelo</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>developer, devops (tag), anywhere (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), devops (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Software-Engineer, Backend-Development, Fullstack-Development, Infrastructure-Engineering, DevOps, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Senior</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4059,12 +4057,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/vonage-aem-developer</t>
+          <t>https://himalayas.app/companies/xneelo-co/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>9b191a3075</t>
+          <t>679e1ed2b3</t>
         </is>
       </c>
     </row>
@@ -4080,37 +4078,39 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>27</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Video Annotation Expert</t>
+          <t>AEM Developer</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Vonage</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ai (tag), worldwide (place)</t>
+          <t>developer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Video-Annotator, Video-Annotation, Media-Annotation-Specialist, Video-Data-Annotation, Annotation-Specialist, Data-Annotation-Expert, AI-Annotation-Specialist, Content-Annotation-Specialist, Entry-level, Mid-level</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/video-annotation-expert-4408176807</t>
+          <t>https://weworkremotely.com/remote-jobs/vonage-aem-developer</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1b02a267ff</t>
+          <t>9b191a3075</t>
         </is>
       </c>
     </row>
@@ -4137,56 +4137,56 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Subject Matter Expert - Computer Science and Artificial Intelligence</t>
+          <t>Video Annotation Expert</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sultan Chand &amp; Sons Ltd</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>artificial intelligence, noida (place)</t>
+          <t>ai (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Video-Annotator, Video-Annotation, Media-Annotation-Specialist, Video-Data-Annotation, Annotation-Specialist, Data-Annotation-Expert, AI-Annotation-Specialist, Content-Annotation-Specialist, Entry-level, Mid-level</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5869558953?se=ji27_Tqo8RGDXZRVG-VeHA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=41B18BB78E05B29C6C90DA595F6A5EBB3EFE4072</t>
+          <t>https://himalayas.app/companies/micro1/jobs/video-annotation-expert-4408176807</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>91b1f60d0c</t>
+          <t>1b02a267ff</t>
         </is>
       </c>
     </row>
@@ -4202,37 +4202,37 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Software engineer</t>
+          <t>Subject Matter Expert - Computer Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sticker Mule</t>
+          <t>Sultan Chand &amp; Sons Ltd</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>software engineer, typescript (tag), golang (tag), react (tag), global (place)</t>
+          <t>artificial intelligence, noida (place)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Development, react,typescript,golang,graphql,english</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1833624/</t>
+          <t>https://www.adzuna.in/land/ad/5869558953?se=ji27_Tqo8RGDXZRVG-VeHA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=41B18BB78E05B29C6C90DA595F6A5EBB3EFE4072</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>c557da3996</t>
+          <t>91b1f60d0c</t>
         </is>
       </c>
     </row>
@@ -4259,56 +4259,56 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer 3D Developer (remote part/full time)</t>
+          <t>Software engineer</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Imnoo AG</t>
+          <t>Sticker Mule</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>machine learning, developer, engineer, ai, ml (tag), worldwide (place)</t>
+          <t>software engineer, typescript (tag), golang (tag), react (tag), global (place)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>AI-Machine-Learning-Engineering, 3D-Development, Computer-Vision, AI-Manufacturing, CAD-Development, Remote-Machine-Learning-Engineer, Remote-Senior-AI-Engineer, Remote-AI-Engineer, AI-ML-Engineer, Lead-AI-ML-Engineer, Machine-Learning-Engineer, Senior</t>
+          <t>Development, react,typescript,golang,graphql,english</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/imnoo-ag/jobs/ai-machine-learning-engineer-3d-developer-remote-part-full-time</t>
+          <t>https://www.workingnomads.com/job/go/1833624/</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>a84b2b9b96</t>
+          <t>c557da3996</t>
         </is>
       </c>
     </row>
@@ -4324,37 +4324,37 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>AI Machine Learning Engineer 3D Developer (remote part/full time)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sustainability Economics.ai</t>
+          <t>Imnoo AG</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>machine learning, intern (level), bangalore (place)</t>
+          <t>machine learning, developer, engineer, ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Machine-Learning-Engineering, 3D-Development, Computer-Vision, AI-Manufacturing, CAD-Development, Remote-Machine-Learning-Engineer, Remote-Senior-AI-Engineer, Remote-AI-Engineer, AI-ML-Engineer, Lead-AI-ML-Engineer, Machine-Learning-Engineer, Senior</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5868794497?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C97284B10F6321E0988BF83E6C1B8DFD30952F6C</t>
+          <t>https://himalayas.app/companies/imnoo-ag/jobs/ai-machine-learning-engineer-3d-developer-remote-part-full-time</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>05411f661c</t>
+          <t>a84b2b9b96</t>
         </is>
       </c>
     </row>
@@ -4385,17 +4385,17 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Machine Learning II</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Sustainability Economics.ai</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>machine learning, qa (tag), bangalore (place)</t>
+          <t>machine learning, intern (level), bangalore (place)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Scientific &amp; QA Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5868154123?se=SoAubXKn8RGZGp_UbifwCA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2A76050FF86A705EC1E71FEE64DFE517445586F0</t>
+          <t>https://www.adzuna.in/land/ad/5868794497?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C97284B10F6321E0988BF83E6C1B8DFD30952F6C</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>520f876dc1</t>
+          <t>05411f661c</t>
         </is>
       </c>
     </row>
@@ -4446,22 +4446,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>Machine Learning II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4471,27 +4471,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>machine learning, qa (tag), bangalore (place)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5852477157?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C196DCD121C33E5FA7A7F99C735E078C53777A1E</t>
+          <t>https://www.adzuna.in/land/ad/5868154123?se=SoAubXKn8RGZGp_UbifwCA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2A76050FF86A705EC1E71FEE64DFE517445586F0</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>dab94fe012</t>
+          <t>520f876dc1</t>
         </is>
       </c>
     </row>
@@ -4507,54 +4507,52 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>46</v>
-      </c>
-      <c r="D67" t="n">
-        <v>2</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Data Scientist - Inference, Community Support</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>data scientist, anywhere (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/airbnb-data-scientist-inference-community-support</t>
+          <t>https://www.adzuna.in/land/ad/5852477157?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C196DCD121C33E5FA7A7F99C735E078C53777A1E</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>18eaeb9d4e</t>
+          <t>dab94fe012</t>
         </is>
       </c>
     </row>
@@ -4570,54 +4568,54 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Frontend Engineer Specialist</t>
+          <t>Data Scientist - Inference, Community Support</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>developer (tag), frontend, software (tag), engineer, react (tag), worldwide (place)</t>
+          <t>data scientist, anywhere (place)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Frontend-Engineer, Web-Frontend-Engineer, Front-End-Software-Engineer, Frontend-Web-Software-Engineer, Front-End-Developer, React-Frontend-Engineer, UI-Frontend-Developer, Mid-level</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/frontend-engineer-specialist</t>
+          <t>https://weworkremotely.com/remote-jobs/airbnb-data-scientist-inference-community-support</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>ee1605c3a3</t>
+          <t>18eaeb9d4e</t>
         </is>
       </c>
     </row>
@@ -4629,56 +4627,58 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>44</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Frontend Engineer Specialist</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>developer (tag), frontend, software (tag), engineer, react (tag), worldwide (place)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Frontend-Engineer, Web-Frontend-Engineer, Front-End-Software-Engineer, Frontend-Web-Software-Engineer, Front-End-Developer, React-Frontend-Engineer, UI-Frontend-Developer, Mid-level</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>86</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; NLP Expert</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Synthenova</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>machine learning, nlp, qa (tag), india (place)</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Scientific &amp; QA Jobs</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864426193?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FA0DA9F5539A8E98A42507C72E66BEA28EFB5F71</t>
+          <t>https://himalayas.app/companies/micro1/jobs/frontend-engineer-specialist</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>06a6232301</t>
+          <t>ee1605c3a3</t>
         </is>
       </c>
     </row>
@@ -4694,22 +4694,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning &amp; NLP Expert</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>HT Digital Streams</t>
+          <t>Synthenova</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>data scientist, india (place), delhi (place)</t>
+          <t>machine learning, nlp, qa (tag), india (place)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427594?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1379BD61E95509405A372328EE4CB12520438AC9</t>
+          <t>https://www.adzuna.in/land/ad/5864426193?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FA0DA9F5539A8E98A42507C72E66BEA28EFB5F71</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>e77b0725ce</t>
+          <t>06a6232301</t>
         </is>
       </c>
     </row>
@@ -4755,52 +4755,52 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>HeadSpin</t>
+          <t>HT Digital Streams</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), associate (level), worldwide (place)</t>
+          <t>data scientist, india (place), delhi (place)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Engineering, Software-Engineer, Associate-Software-Engineer, Backend-Development, Fullstack-Development, Software-Engineering-Associate, Associate-Software-Developer, Software-Developer-Associate, Associate-Engineer, Associate-Platform-Engineer, Associate-Application-Developer, Associate-Systems-Engineer, Developer, Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/headspin/jobs/associate-software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5864427594?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1379BD61E95509405A372328EE4CB12520438AC9</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>ed41465dce</t>
+          <t>e77b0725ce</t>
         </is>
       </c>
     </row>
@@ -4816,52 +4816,52 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>HeadSpin</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>artificial intelligence, noida (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), associate (level), worldwide (place)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment Jobs</t>
+          <t>Engineering, Software-Engineer, Associate-Software-Engineer, Backend-Development, Fullstack-Development, Software-Engineering-Associate, Associate-Software-Developer, Software-Developer-Associate, Associate-Engineer, Associate-Platform-Engineer, Associate-Application-Developer, Associate-Systems-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864432717?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=616D5B872E024B0E271B6E107D9B24261D8C3B7A</t>
+          <t>https://himalayas.app/companies/headspin/jobs/associate-software-engineer</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>90b00c6445</t>
+          <t>ed41465dce</t>
         </is>
       </c>
     </row>
@@ -4879,22 +4879,20 @@
       <c r="C73" t="n">
         <v>50</v>
       </c>
-      <c r="D73" t="n">
-        <v>3</v>
-      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Machine Learning Specialist</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bandhan Technologies</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4904,27 +4902,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>machine learning, bangalore (place)</t>
+          <t>artificial intelligence, noida (place)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>HR &amp; Recruitment Jobs</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867037827?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=81D91604A259EFB724EEF9EE68D3642F93D7C52A</t>
+          <t>https://www.adzuna.in/land/ad/5864432717?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=616D5B872E024B0E271B6E107D9B24261D8C3B7A</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>55af0af08c</t>
+          <t>90b00c6445</t>
         </is>
       </c>
     </row>
@@ -4940,19 +4938,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D74" t="n">
         <v>3</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Data Science Specialist</t>
+          <t>Machine Learning Specialist</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Polestar Analytics</t>
+          <t>Bandhan Technologies</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4967,7 +4965,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>data science, bangalore (place)</t>
+          <t>machine learning, bangalore (place)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4977,17 +4975,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864434859?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BE53F35ACA83BD29D328C8745F27CF70F132F879</t>
+          <t>https://www.adzuna.in/land/ad/5867037827?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=81D91604A259EFB724EEF9EE68D3642F93D7C52A</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>620816c318</t>
+          <t>55af0af08c</t>
         </is>
       </c>
     </row>
@@ -5005,20 +5003,22 @@
       <c r="C75" t="n">
         <v>49</v>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>Data Science Specialist</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Polestar Analytics</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>data science, bangalore (place)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5038,17 +5038,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867037765?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CCE3B589087C9AE3C6FD3C72DD92F3B9146F772F</t>
+          <t>https://www.adzuna.in/land/ad/5864434859?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BE53F35ACA83BD29D328C8745F27CF70F132F879</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>5ae3a66648</t>
+          <t>620816c318</t>
         </is>
       </c>
     </row>
@@ -5069,17 +5069,17 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Infosys Finacle</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867270149?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=284AB41CD26DD62DA43E2E7866A4F2E72052CFA3</t>
+          <t>https://www.adzuna.in/land/ad/5867037765?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CCE3B589087C9AE3C6FD3C72DD92F3B9146F772F</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>b9e7b78c99</t>
+          <t>5ae3a66648</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Servify</t>
+          <t>Infosys Finacle</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867265604?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=98C25A013410B0B492855DE45F67FF3409A45C24</t>
+          <t>https://www.adzuna.in/land/ad/5867270149?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=284AB41CD26DD62DA43E2E7866A4F2E72052CFA3</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>339ea3cd4c</t>
+          <t>b9e7b78c99</t>
         </is>
       </c>
     </row>
@@ -5186,37 +5186,37 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CEO, AI Finance</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bjak</t>
+          <t>Servify</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/bjak/jobs/ceo-ai-finance-7034716418</t>
+          <t>https://www.adzuna.in/land/ad/5867265604?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=98C25A013410B0B492855DE45F67FF3409A45C24</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>8e23b34067</t>
+          <t>339ea3cd4c</t>
         </is>
       </c>
     </row>
@@ -5247,17 +5247,17 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Accounting Automation Engineer</t>
+          <t>CEO, AI Finance</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spotter Labs</t>
+          <t>Bjak</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>automation, software (tag), engineer, worldwide (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Accounting-Automation-Engineer, Finance-Automation-Engineer, Accounting-Software-Engineer, Accounting-Automation, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3984977259</t>
+          <t>https://himalayas.app/companies/bjak/jobs/ceo-ai-finance-7034716418</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>c570969de5</t>
+          <t>8e23b34067</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Accounting-Automation-Engineer, Accounting, Process-Automation, Financial-Automation, Business-Systems, Finance-Automation-Engineer, Accounting-Software-Engineer, Automation-Engineer, Accounting-Automation, Software-Automation-Engineer, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
+          <t>Accounting-Automation-Engineer, Finance-Automation-Engineer, Accounting-Software-Engineer, Accounting-Automation, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3943339358</t>
+          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3984977259</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>13edcbb44e</t>
+          <t>c570969de5</t>
         </is>
       </c>
     </row>
@@ -5369,37 +5369,37 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Backend Engineer - Platform - Stacks | Ireland | Remote</t>
+          <t>Accounting Automation Engineer</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grafana Labs</t>
+          <t>Spotter Labs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>engineer, backend, anywhere (place)</t>
+          <t>automation, software (tag), engineer, worldwide (place)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Accounting-Automation-Engineer, Accounting, Process-Automation, Financial-Automation, Business-Systems, Finance-Automation-Engineer, Accounting-Software-Engineer, Automation-Engineer, Accounting-Automation, Software-Automation-Engineer, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/grafana-labs-backend-engineer-platform-stacks-ireland-remote</t>
+          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3943339358</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>7aae615c8c</t>
+          <t>13edcbb44e</t>
         </is>
       </c>
     </row>
@@ -5430,37 +5430,37 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>STEM Expert</t>
+          <t>Backend Engineer - Platform - Stacks | Ireland | Remote</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ai (tag), worldwide (place)</t>
+          <t>engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>STEM-Expert, STEM-Specialist, STEM-Consultant, STEM-Domain-Expert, STEM-Researcher, STEM-Educator, STEM-AI-Specialist, Japanese-STEM-Specialist, STEM-Advisor, STEM-Instructor, Mid-level</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/stem-expert-40695367</t>
+          <t>https://weworkremotely.com/remote-jobs/grafana-labs-backend-engineer-platform-stacks-ireland-remote</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>9cb40c45fc</t>
+          <t>7aae615c8c</t>
         </is>
       </c>
     </row>
@@ -5491,14 +5491,12 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>21</v>
-      </c>
-      <c r="D83" t="n">
-        <v>3</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Excel Specialist</t>
+          <t>STEM Expert</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5518,12 +5516,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>automation (tag), developer (tag), worldwide (place)</t>
+          <t>ai (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Excel-Specialist, Excel-Expert, Spreadsheet-Specialist, Excel-Automation-Specialist, Excel-Data-Analyst, Microsoft-Excel-Developer, Microsoft-Office-Specialist, Microsoft-Excel-Development, Entry-level, Mid-level</t>
+          <t>STEM-Expert, STEM-Specialist, STEM-Consultant, STEM-Domain-Expert, STEM-Researcher, STEM-Educator, STEM-AI-Specialist, Japanese-STEM-Specialist, STEM-Advisor, STEM-Instructor, Mid-level</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5533,12 +5531,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/excel-specialist-2996931708</t>
+          <t>https://himalayas.app/companies/micro1/jobs/stem-expert-40695367</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>fddf243627</t>
+          <t>9cb40c45fc</t>
         </is>
       </c>
     </row>
@@ -5550,56 +5548,58 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>69</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>Excel Specialist</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ISIR AI</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>data science, qa (tag), intern (level), noida (place)</t>
+          <t>automation (tag), developer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Scientific &amp; QA Jobs</t>
+          <t>Excel-Specialist, Excel-Expert, Spreadsheet-Specialist, Excel-Automation-Specialist, Excel-Data-Analyst, Microsoft-Excel-Developer, Microsoft-Office-Specialist, Microsoft-Excel-Development, Entry-level, Mid-level</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427080?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C509B9B88F855FA7348A37AF1CDF8C3ECC7CA889</t>
+          <t>https://himalayas.app/companies/micro1/jobs/excel-specialist-2996931708</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>84896ab3c6</t>
+          <t>fddf243627</t>
         </is>
       </c>
     </row>
@@ -5615,22 +5615,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FRND</t>
+          <t>ISIR AI</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>machine learning, intern (level), bangalore (place)</t>
+          <t>data science, qa (tag), intern (level), noida (place)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864424613?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9B60872885E8C7073FE0CC2A962D44A1E48845F7</t>
+          <t>https://www.adzuna.in/land/ad/5864427080?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C509B9B88F855FA7348A37AF1CDF8C3ECC7CA889</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>e00b96a707</t>
+          <t>84896ab3c6</t>
         </is>
       </c>
     </row>
@@ -5676,22 +5676,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Intern (Data Science)</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Yubi</t>
+          <t>FRND</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>data science, intern (level), chennai (place)</t>
+          <t>machine learning, intern (level), bangalore (place)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864443163?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4554D5357B8D35F06907356F0816FBF3BD2BBC7E</t>
+          <t>https://www.adzuna.in/land/ad/5864424613?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9B60872885E8C7073FE0CC2A962D44A1E48845F7</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>93516db46a</t>
+          <t>e00b96a707</t>
         </is>
       </c>
     </row>
@@ -5737,37 +5737,37 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AI Inference Engineer QVAC (100% remote Worldwide)</t>
+          <t>Intern (Data Science)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tether Operations Limited</t>
+          <t>Yubi</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>software (tag), engineer, ai, worldwide (place)</t>
+          <t>data science, intern (level), chennai (place)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Software-Engineer, AI-Engineering, Machine-Learning-Engineering, C-Development, Edge-AI, AI-Inference-Engineer, Remote-AI-Engineer, Remote-Machine-Learning-Engineer, Senior-AI-Inference-Engineer, Remote-Senior-AI-Engineer, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/tether-operations-limited/jobs/ai-inference-engineer-qvac-100-remote-worldwide</t>
+          <t>https://www.adzuna.in/land/ad/5864443163?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4554D5357B8D35F06907356F0816FBF3BD2BBC7E</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>f7f40ca44a</t>
+          <t>93516db46a</t>
         </is>
       </c>
     </row>
@@ -5798,37 +5798,37 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Machine Learning Gen AI_Hyderabad,Pune &amp; Bangalore</t>
+          <t>AI Inference Engineer QVAC (100% remote Worldwide)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Tether Operations Limited</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>machine learning, hyderabad (place)</t>
+          <t>software (tag), engineer, ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Software-Engineer, AI-Engineering, Machine-Learning-Engineering, C-Development, Edge-AI, AI-Inference-Engineer, Remote-AI-Engineer, Remote-Machine-Learning-Engineer, Senior-AI-Inference-Engineer, Remote-Senior-AI-Engineer, Senior</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439281?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1F39144C3030195205A212339590BB508623F064</t>
+          <t>https://himalayas.app/companies/tether-operations-limited/jobs/ai-inference-engineer-qvac-100-remote-worldwide</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>55fce19c46</t>
+          <t>f7f40ca44a</t>
         </is>
       </c>
     </row>
@@ -5859,17 +5859,17 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Gen AI_Hyderabad,Pune &amp; Bangalore</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Infosys Consulting</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>data scientist, hyderabad (place)</t>
+          <t>machine learning, hyderabad (place)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864428905?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4E35D1AC081FE279803556ECA4C1E1871550877F</t>
+          <t>https://www.adzuna.in/land/ad/5864439281?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1F39144C3030195205A212339590BB508623F064</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>af7ebeb057</t>
+          <t>55fce19c46</t>
         </is>
       </c>
     </row>
@@ -5922,9 +5922,7 @@
       <c r="C90" t="n">
         <v>49</v>
       </c>
-      <c r="D90" t="n">
-        <v>2</v>
-      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Data Scientist</t>
@@ -5932,12 +5930,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>super.money</t>
+          <t>Infosys Consulting</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5947,7 +5945,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, hyderabad (place)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5962,12 +5960,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864425941?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BF9A171BDEA00E60475790836A0A3589FB8D9EB6</t>
+          <t>https://www.adzuna.in/land/ad/5864428905?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4E35D1AC081FE279803556ECA4C1E1871550877F</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>4f1a679ea3</t>
+          <t>af7ebeb057</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5983,9 @@
       <c r="C91" t="n">
         <v>49</v>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>2</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>Data Scientist</t>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lufthansa Technik Services India Pvt Ltd</t>
+          <t>super.money</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864422634?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
+          <t>https://www.adzuna.in/land/ad/5864425941?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BF9A171BDEA00E60475790836A0A3589FB8D9EB6</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>c86fa3dfe3</t>
+          <t>4f1a679ea3</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank</t>
+          <t>Lufthansa Technik Services India Pvt Ltd</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439103?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=73CFB6E1B4115AA2A23A99B0EC8886521BA01450</t>
+          <t>https://www.adzuna.in/land/ad/5864422634?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>08622a68ed</t>
+          <t>c86fa3dfe3</t>
         </is>
       </c>
     </row>
@@ -6110,17 +6110,17 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Navi</t>
+          <t>Kotak Mahindra Bank</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439226?se=jiNNTDmm8RGUNa3mkcr13g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=744BE785510320885EE5287D6F2FE8E098FAED30</t>
+          <t>https://www.adzuna.in/land/ad/5864439103?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=73CFB6E1B4115AA2A23A99B0EC8886521BA01450</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>4e1bb30522</t>
+          <t>08622a68ed</t>
         </is>
       </c>
     </row>
@@ -6171,17 +6171,17 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tricog Health</t>
+          <t>Navi</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6201,17 +6201,17 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5865291446?se=pmQW9lOm8RGs-Y02KTQxmA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=A9D77535171E8EAD7E7898B67A7ADC8ED3D07410</t>
+          <t>https://www.adzuna.in/land/ad/5864439226?se=jiNNTDmm8RGUNa3mkcr13g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=744BE785510320885EE5287D6F2FE8E098FAED30</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>eaec37f6c0</t>
+          <t>4e1bb30522</t>
         </is>
       </c>
     </row>
@@ -6227,54 +6227,52 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>41</v>
-      </c>
-      <c r="D95" t="n">
-        <v>3</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Remote - Automation QA Engineer (Core Team)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Torrero</t>
+          <t>Tricog Health</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>automation, software (tag), engineer, testing (tag), qa, worldwide (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>QA-Engineer, QA-Automation-Engineer, Software-Testing, Quality-Assurance, Manual-Testing, Remote-Test-Automation-Engineer, Remote-QA-Engineer, Remote-Quality-Assurance-Engineer, Remote-UI-Automation-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/torrero/jobs/remote-automation-qa-engineer-core-team</t>
+          <t>https://www.adzuna.in/land/ad/5865291446?se=pmQW9lOm8RGs-Y02KTQxmA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=A9D77535171E8EAD7E7898B67A7ADC8ED3D07410</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>f03380c71d</t>
+          <t>eaec37f6c0</t>
         </is>
       </c>
     </row>
@@ -6290,17 +6288,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="D96" t="n">
+        <v>3</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Front-End Developer</t>
+          <t>Remote - Automation QA Engineer (Core Team)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talent Sam</t>
+          <t>Torrero</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>developer, frontend (tag), engineer (tag), react (tag), worldwide (place)</t>
+          <t>automation, software (tag), engineer, testing (tag), qa, worldwide (place)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Frontend-Development, Web-Development, UI-Developer, Frontend-Engineer, Front-End-Developer, Frontend-React-Developer, UI-Frontend-Developer, UX-UI-Front-End-Developer, React-Frontend-Developer, Frontend-Web-Development, Developer, Mid-level</t>
+          <t>QA-Engineer, QA-Automation-Engineer, Software-Testing, Quality-Assurance, Manual-Testing, Remote-Test-Automation-Engineer, Remote-QA-Engineer, Remote-Quality-Assurance-Engineer, Remote-UI-Automation-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/talent-sam/jobs/front-end-developer</t>
+          <t>https://himalayas.app/companies/torrero/jobs/remote-automation-qa-engineer-core-team</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>94d5af612e</t>
+          <t>f03380c71d</t>
         </is>
       </c>
     </row>
@@ -6351,37 +6351,37 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>E-learning Developer</t>
+          <t>Front-End Developer</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>VineGarden Films</t>
+          <t>Talent Sam</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>developer, india (place)</t>
+          <t>developer, frontend (tag), engineer (tag), react (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Teaching Jobs</t>
+          <t>Frontend-Development, Web-Development, UI-Developer, Frontend-Engineer, Front-End-Developer, Frontend-React-Developer, UI-Frontend-Developer, UX-UI-Front-End-Developer, React-Frontend-Developer, Frontend-Web-Development, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864153573?se=SvkgT-Wl8RGUGK7L4gkIgg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FDDF0A4236DF3E6D3081AF93B01799D77599EAD1</t>
+          <t>https://himalayas.app/companies/talent-sam/jobs/front-end-developer</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>248ef46714</t>
+          <t>94d5af612e</t>
         </is>
       </c>
     </row>
@@ -6408,21 +6408,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Data Scientist - Python Deterministic Analytics</t>
+          <t>E-learning Developer</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Capco</t>
+          <t>VineGarden Films</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6437,27 +6437,27 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>data scientist, python, india (place)</t>
+          <t>developer, india (place)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Teaching Jobs</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139747?se=olLfvDql8RGL6NrjcRaTpw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9FA82041CC2CC98F084D6827CF82DA2BE289D998</t>
+          <t>https://www.adzuna.in/land/ad/5864153573?se=SvkgT-Wl8RGUGK7L4gkIgg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FDDF0A4236DF3E6D3081AF93B01799D77599EAD1</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>6f1952e273</t>
+          <t>248ef46714</t>
         </is>
       </c>
     </row>
@@ -6473,22 +6473,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - APAC</t>
+          <t>Data Scientist - Python Deterministic Analytics</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional®</t>
+          <t>Capco</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>data scientist, python, india (place)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6508,17 +6508,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5862635702?se=9gaugPCk8RGcfKYe_cIpvA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=53D4DF556D646C5F462C8F3FC782D72E8A35D08B</t>
+          <t>https://www.adzuna.in/land/ad/5837139747?se=olLfvDql8RGL6NrjcRaTpw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9FA82041CC2CC98F084D6827CF82DA2BE289D998</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>d395f3a907</t>
+          <t>6f1952e273</t>
         </is>
       </c>
     </row>
@@ -6534,52 +6534,52 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AI Engineer Data APIs</t>
+          <t>Machine Learning Engineer - APAC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>LexisNexis Legal &amp; Professional®</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>engineer, golang (tag), ai</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>golang, video, engineer</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-ai-engineer-data-apis-benzinga-1137224</t>
+          <t>https://www.adzuna.in/land/ad/5862635702?se=9gaugPCk8RGcfKYe_cIpvA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=53D4DF556D646C5F462C8F3FC782D72E8A35D08B</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>1261a5bcd5</t>
+          <t>d395f3a907</t>
         </is>
       </c>
     </row>
@@ -6595,52 +6595,52 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Agentic Python Engineer</t>
+          <t>AI Engineer Data APIs</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Evaboot</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>WORLDWIDE</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>engineer, python, aws (tag), worldwide (place)</t>
+          <t>engineer, golang (tag), ai</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Development, python,engineer,aws,analytics,seo</t>
+          <t>golang, video, engineer</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1826864/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-engineer-data-apis-benzinga-1137224</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>47ae63b1d0</t>
+          <t>1261a5bcd5</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
@@ -6671,22 +6671,22 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>WORLDWIDE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>engineer, python, anywhere (place)</t>
+          <t>engineer, python, aws (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Development, python,engineer,aws,analytics,seo</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/evaboot-agentic-python-engineer</t>
+          <t>https://www.workingnomads.com/job/go/1826864/</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>d94554bfc7</t>
+          <t>47ae63b1d0</t>
         </is>
       </c>
     </row>
@@ -6713,56 +6713,56 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Agentic Python Engineer</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Evaboot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>engineer, python, anywhere (place)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982687?se=BGNyWVik8RGF59teMJsS7Q&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=64C652991D92D5E3DCA4519D688756F962092321</t>
+          <t>https://weworkremotely.com/remote-jobs/evaboot-agentic-python-engineer</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>dd6de0380a</t>
+          <t>d94554bfc7</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Data Scientist, Knowledge Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982533?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=853C1E923E89428D368371363C6206932A9E653B</t>
+          <t>https://www.adzuna.in/land/ad/5857982687?se=BGNyWVik8RGF59teMJsS7Q&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=64C652991D92D5E3DCA4519D688756F962092321</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>e4df1efe77</t>
+          <t>dd6de0380a</t>
         </is>
       </c>
     </row>
@@ -6844,17 +6844,17 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Data Scientist II, Data Analytics, Hyderabad</t>
+          <t>Data Scientist, Knowledge Management</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>data scientist, hyderabad (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6874,17 +6874,17 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5860916020?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2CB3A6FFC4393B68C48E0DBE7C464491C08965D1</t>
+          <t>https://www.adzuna.in/land/ad/5857982533?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=853C1E923E89428D368371363C6206932A9E653B</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>ed5cec24b5</t>
+          <t>e4df1efe77</t>
         </is>
       </c>
     </row>
@@ -6900,52 +6900,52 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform - Hyderabad, India</t>
+          <t>Data Scientist II, Data Analytics, Hyderabad</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Speechify</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>software engineer, backend (tag), cloud (tag), api (tag), india (place)</t>
+          <t>data scientist, hyderabad (place)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Platform-Engineering, Backend-Engineering, Software-Engineer, API-Development, Cloud-Infrastructure, Software-Platform-Engineer, Platform-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/speechify/jobs/software-engineer-platform-hyderabad-india</t>
+          <t>https://www.adzuna.in/land/ad/5860916020?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2CB3A6FFC4393B68C48E0DBE7C464491C08965D1</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>d972ee3bee</t>
+          <t>ed5cec24b5</t>
         </is>
       </c>
     </row>
@@ -6961,22 +6961,22 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>GitHub Contributor</t>
+          <t>Software Engineer, Platform - Hyderabad, India</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Speechify</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6986,12 +6986,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, backend (tag), cloud (tag), api (tag), india (place)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
+          <t>Platform-Engineering, Backend-Engineering, Software-Engineer, API-Development, Cloud-Infrastructure, Software-Platform-Engineer, Platform-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-2145210908</t>
+          <t>https://himalayas.app/companies/speechify/jobs/software-engineer-platform-hyderabad-india</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>9bd86980fc</t>
+          <t>d972ee3bee</t>
         </is>
       </c>
     </row>
@@ -7018,58 +7018,56 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>38</v>
-      </c>
-      <c r="D108" t="n">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, PDP Experience</t>
+          <t>GitHub Contributor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>software engineer, backend, anywhere (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/reddit-backend-software-engineer-pdp-experience</t>
+          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-2145210908</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>a954ce85ab</t>
+          <t>9bd86980fc</t>
         </is>
       </c>
     </row>
@@ -7085,37 +7083,39 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>24</v>
-      </c>
-      <c r="D109" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Open Source Contributor</t>
+          <t>Backend Software Engineer, PDP Experience</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Open-Source-Software-Developer, Open-Source-Advocate, Open-Source-Engineer, Open-Source-Software-Engineer, Open-Source-Software-Maintainer, Community-Contributor, Entry-level</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/open-source-contributor-4150550716</t>
+          <t>https://weworkremotely.com/remote-jobs/reddit-backend-software-engineer-pdp-experience</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>d8033bd793</t>
+          <t>a954ce85ab</t>
         </is>
       </c>
     </row>
@@ -7142,16 +7142,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Open Source Contributor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7171,27 +7171,27 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>engineer, python (tag), ai, ml (tag), worldwide (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Mid-level</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Open-Source-Software-Developer, Open-Source-Advocate, Open-Source-Engineer, Open-Source-Software-Engineer, Open-Source-Software-Maintainer, Community-Contributor, Entry-level</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-engineer-7982880650</t>
+          <t>https://himalayas.app/companies/micro1/jobs/open-source-contributor-4150550716</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>17936ac69e</t>
+          <t>d8033bd793</t>
         </is>
       </c>
     </row>
@@ -7207,37 +7207,37 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>machine learning, engineer, hyderabad (place)</t>
+          <t>engineer, python (tag), ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Mid-level</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5859662671?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=77410E24CED3D457054E58156829472F42D5B958</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-engineer-7982880650</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>a8bcca74c0</t>
+          <t>17936ac69e</t>
         </is>
       </c>
     </row>
@@ -7273,17 +7273,17 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (T25)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>machine learning, engineer, hyderabad (place)</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7303,17 +7303,17 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858538850?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AA8B404BB5F08B6BBBC1A1DAEA80EDAE2331BB01</t>
+          <t>https://www.adzuna.in/land/ad/5859662671?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=77410E24CED3D457054E58156829472F42D5B958</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>e99054d24c</t>
+          <t>a8bcca74c0</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SWE-3 Machine Learning Engineer</t>
+          <t>Machine Learning Engineer (T25)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858537539?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=49BEDAECA8CA01D8F7BFB9CA5D092D8DD046FCF4</t>
+          <t>https://www.adzuna.in/land/ad/5858538850?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AA8B404BB5F08B6BBBC1A1DAEA80EDAE2331BB01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>83e0ebd10e</t>
+          <t>e99054d24c</t>
         </is>
       </c>
     </row>
@@ -7390,22 +7390,22 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>SWE-3 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>engineer, ai, hyderabad (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7430,12 +7430,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982475?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=61932F7A965BC6190F96EF3EDD6B34FCA7CA0EFF</t>
+          <t>https://www.adzuna.in/land/ad/5858537539?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=49BEDAECA8CA01D8F7BFB9CA5D092D8DD046FCF4</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>ec1b34ae37</t>
+          <t>83e0ebd10e</t>
         </is>
       </c>
     </row>
@@ -7451,52 +7451,52 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AI Data Annotator - Remote</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Argos Multilingual Inc.</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>All Other Remote, Contract</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/argos-multilingual-inc-ai-data-annotator-remote</t>
+          <t>https://www.adzuna.in/land/ad/5857982475?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=61932F7A965BC6190F96EF3EDD6B34FCA7CA0EFF</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>5c22526a85</t>
+          <t>ec1b34ae37</t>
         </is>
       </c>
     </row>
@@ -7508,56 +7508,56 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Data Scientist - AI &amp; Automation</t>
+          <t>AI Data Annotator - Remote</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Argos Multilingual Inc.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>data scientist, automation, ai, bangalore (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>All Other Remote, Contract</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251125?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C7BA7BE347A1ADA1FC538497AF302C4F3AD6BEDD</t>
+          <t>https://weworkremotely.com/remote-jobs/argos-multilingual-inc-ai-data-annotator-remote</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2e19a4f3f6</t>
+          <t>5c22526a85</t>
         </is>
       </c>
     </row>
@@ -7573,12 +7573,12 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>MTS-1 Machine Learning Engineer</t>
+          <t>Data Scientist - AI &amp; Automation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>data scientist, automation, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858537523?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4219F9238C4FE19DFCEAD65DAA98E56A5B89F388</t>
+          <t>https://www.adzuna.in/land/ad/5857251125?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C7BA7BE347A1ADA1FC538497AF302C4F3AD6BEDD</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>c65fcd065c</t>
+          <t>2e19a4f3f6</t>
         </is>
       </c>
     </row>
@@ -7634,22 +7634,22 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>MTS-1 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>data scientist, mumbai (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5849296977?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FFA2BB725355D26B4B624FA5365F48C2D8B894C</t>
+          <t>https://www.adzuna.in/land/ad/5858537523?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4219F9238C4FE19DFCEAD65DAA98E56A5B89F388</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>200651f002</t>
+          <t>c65fcd065c</t>
         </is>
       </c>
     </row>
@@ -7705,12 +7705,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, mumbai (place)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7730,17 +7730,17 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251146?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=43EC4FC89638B5AB4C3D5267B80E2B1135A6C706</t>
+          <t>https://www.adzuna.in/land/ad/5849296977?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FFA2BB725355D26B4B624FA5365F48C2D8B894C</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>6a6f7a8419</t>
+          <t>200651f002</t>
         </is>
       </c>
     </row>
@@ -7796,12 +7796,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251173?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7E2FD9B14C3A74461E2352F6CFE714131C13E4BC</t>
+          <t>https://www.adzuna.in/land/ad/5857251146?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=43EC4FC89638B5AB4C3D5267B80E2B1135A6C706</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>aa6eef76e8</t>
+          <t>6a6f7a8419</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Data Scientist, Knowledge Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251185?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=74B3EB71D85FA01AB90B707F8DB6AB9F2A17FAFA</t>
+          <t>https://www.adzuna.in/land/ad/5857251173?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7E2FD9B14C3A74461E2352F6CFE714131C13E4BC</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>d1497475d4</t>
+          <t>aa6eef76e8</t>
         </is>
       </c>
     </row>
@@ -7883,12 +7883,12 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Data Scientist with R programming</t>
+          <t>Data Scientist, Knowledge Management</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Capco</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7913,17 +7913,17 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139433?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=221D7BCDBBE6E4012ED68B71EDB34DB2E07507EC</t>
+          <t>https://www.adzuna.in/land/ad/5857251185?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=74B3EB71D85FA01AB90B707F8DB6AB9F2A17FAFA</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>dbec4a04a4</t>
+          <t>d1497475d4</t>
         </is>
       </c>
     </row>
@@ -7939,52 +7939,52 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Data Scientist with R programming</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capco</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Product, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer-1</t>
+          <t>https://www.adzuna.in/land/ad/5837139433?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=221D7BCDBBE6E4012ED68B71EDB34DB2E07507EC</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>e7de7648c1</t>
+          <t>dbec4a04a4</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer</t>
+          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer-1</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>dada5ade61</t>
+          <t>e7de7648c1</t>
         </is>
       </c>
     </row>
@@ -8061,52 +8061,52 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Education Designer UX UI and AI</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Interaction Design Foundation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>design, content writing, education</t>
+          <t>Product, Full-Time</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-education-designer-ux-ui-and-ai-interaction-design-foundation-1137138</t>
+          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>ca62234445</t>
+          <t>dada5ade61</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Course Writer and Editor UX UI and AI</t>
+          <t>Education Designer UX UI and AI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>design, content writing</t>
+          <t>design, content writing, education</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-course-writer-and-editor-ux-ui-and-ai-interaction-design-foundation-1137136</t>
+          <t>https://remoteOK.com/remote-jobs/remote-education-designer-ux-ui-and-ai-interaction-design-foundation-1137138</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>01210e4343</t>
+          <t>ca62234445</t>
         </is>
       </c>
     </row>
@@ -8179,56 +8179,56 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>App Developer - AI/ML</t>
+          <t>Course Writer and Editor UX UI and AI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Interaction Design Foundation</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>developer, ai, ml, hyderabad (place)</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>design, content writing</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139469?se=-BSx1eug8RG-Sdz4qyZPjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=16DC1893C3026AA51441662E0B1A61360470917B</t>
+          <t>https://remoteOK.com/remote-jobs/remote-course-writer-and-editor-ux-ui-and-ai-interaction-design-foundation-1137136</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>7a22fe6bd5</t>
+          <t>01210e4343</t>
         </is>
       </c>
     </row>
@@ -8244,17 +8244,17 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>App Developer - AI/ML</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>developer, ai, ml, hyderabad (place)</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8279,17 +8279,17 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857168441?se=TqYc8W2h8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CEB40CB7335D41898800C58388A2B035DF674757</t>
+          <t>https://www.adzuna.in/land/ad/5837139469?se=-BSx1eug8RG-Sdz4qyZPjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=16DC1893C3026AA51441662E0B1A61360470917B</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>84fdce5107</t>
+          <t>7a22fe6bd5</t>
         </is>
       </c>
     </row>
@@ -8305,37 +8305,37 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AI Speech &amp; Audio Specialist – ASR | TTS | Voice AI | Audio Data</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/ai-speech-audio-specialist-asr-tts-voice-ai-audio-data</t>
+          <t>https://www.adzuna.in/land/ad/5857168441?se=TqYc8W2h8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CEB40CB7335D41898800C58388A2B035DF674757</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>bb930fc93f</t>
+          <t>84fdce5107</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Financial Accuracy &amp; Tax Logic Expert (AI Community)</t>
+          <t>AI Speech &amp; Audio Specialist – ASR | TTS | Voice AI | Audio Data</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/financial-accuracy-tax-logic-expert-ai-community-7007868696</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/ai-speech-audio-specialist-asr-tts-voice-ai-audio-data</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>162d6a9ed2</t>
+          <t>bb930fc93f</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Identity Trust &amp; Fraud Intelligence Specialist - Intermediate (AI Community)</t>
+          <t>Financial Accuracy &amp; Tax Logic Expert (AI Community)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/identity-trust-fraud-intelligence-specialist-intermediate-ai-community</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/financial-accuracy-tax-logic-expert-ai-community-7007868696</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>637c85a300</t>
+          <t>162d6a9ed2</t>
         </is>
       </c>
     </row>
@@ -8493,32 +8493,32 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Education Designer: UX, UI, and AI</t>
+          <t>Identity Trust &amp; Fraud Intelligence Specialist - Intermediate (AI Community)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>IxDF - Interaction Design Foundation</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Design, Full-Time</t>
+          <t>Entry-level</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-education-designer-ux-ui-and-ai</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/identity-trust-fraud-intelligence-specialist-intermediate-ai-community</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>9fbe655de3</t>
+          <t>637c85a300</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Course Writer and Editor: UX, UI, and AI</t>
+          <t>Education Designer: UX, UI, and AI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-course-writer-and-editor-ux-ui-and-ai</t>
+          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-education-designer-ux-ui-and-ai</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>e8e07f5951</t>
+          <t>9fbe655de3</t>
         </is>
       </c>
     </row>
@@ -8615,32 +8615,32 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AI Consulting Domain Expert</t>
+          <t>Course Writer and Editor: UX, UI, and AI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IxDF - Interaction Design Foundation</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>AI-Domain-Expert, AI-Consultant, AI-Subject-Matter-Expert, Artificial-Intelligence-Consulting, Senior</t>
+          <t>Design, Full-Time</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-consulting-domain-expert-7128968890</t>
+          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-course-writer-and-editor-ux-ui-and-ai</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>7f1041d829</t>
+          <t>e8e07f5951</t>
         </is>
       </c>
     </row>
@@ -8671,39 +8671,37 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>40</v>
-      </c>
-      <c r="D135" t="n">
-        <v>2</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Software Development Engineer II Full Stack - Business (Remote @ Colombia)</t>
+          <t>AI Consulting Domain Expert</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>full stack, software, engineer, anywhere (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>AI-Domain-Expert, AI-Consultant, AI-Subject-Matter-Expert, Artificial-Intelligence-Consulting, Senior</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8713,12 +8711,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/offerup-software-development-engineer-ii-full-stack-business-remote-colombia</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-consulting-domain-expert-7128968890</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>6fe968b6b9</t>
+          <t>7f1041d829</t>
         </is>
       </c>
     </row>
@@ -8734,37 +8732,39 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>20</v>
-      </c>
-      <c r="D136" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>QA Speech-to-Text Audio Collection Project</t>
+          <t>Software Development Engineer II Full Stack - Business (Remote @ Colombia)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>qa, worldwide (place)</t>
+          <t>full stack, software, engineer, anywhere (place)</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Entry-level</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/qa-speech-to-text-audio-collection-project</t>
+          <t>https://weworkremotely.com/remote-jobs/offerup-software-development-engineer-ii-full-stack-business-remote-colombia</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>a44e738ec6</t>
+          <t>6fe968b6b9</t>
         </is>
       </c>
     </row>
@@ -8791,21 +8791,21 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AI/RAG engineer</t>
+          <t>QA Speech-to-Text Audio Collection Project</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CoinMarketCap</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8820,27 +8820,27 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>engineer, ai, ml (tag), worldwide (place)</t>
+          <t>qa, worldwide (place)</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>RAG-AI-Engineer, Machine-Learning-Engineering, AI-Engineering, RAG-Development, Vector-Search-Engineer, IA-RAG-Engineer, AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, Mid-level</t>
+          <t>Entry-level</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/coinmarketcap/jobs/ai-rag-engineer</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/qa-speech-to-text-audio-collection-project</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>d199d5cdfc</t>
+          <t>a44e738ec6</t>
         </is>
       </c>
     </row>
@@ -8856,52 +8856,52 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI/RAG engineer</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>CoinMarketCap</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>engineer, ai, mumbai (place)</t>
+          <t>engineer, ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>RAG-AI-Engineer, Machine-Learning-Engineering, AI-Engineering, RAG-Development, Vector-Search-Engineer, IA-RAG-Engineer, AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723676?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F83D2913763A01EA6FBE321571CA8B989BE3F382</t>
+          <t>https://himalayas.app/companies/coinmarketcap/jobs/ai-rag-engineer</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>faa646b456</t>
+          <t>d199d5cdfc</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Data Science-Index Quant Specialist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8942,27 +8942,27 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>data science, mumbai (place)</t>
+          <t>engineer, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Accounting &amp; Finance Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5843137505?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC4079028ED7338B991CD57034DE9EA5AC8D9A0B</t>
+          <t>https://www.adzuna.in/land/ad/5846723676?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F83D2913763A01EA6FBE321571CA8B989BE3F382</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>6ec3848d0b</t>
+          <t>faa646b456</t>
         </is>
       </c>
     </row>
@@ -8983,17 +8983,17 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Science-Index Quant Specialist</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Gurgaon, Haryana</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9003,27 +9003,27 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>data scientist, gurgaon (place)</t>
+          <t>data science, mumbai (place)</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Accounting &amp; Finance Jobs</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5849297019?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E87B9A5E2A9605281144BBEA53533DB7165D1FA0</t>
+          <t>https://www.adzuna.in/land/ad/5843137505?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC4079028ED7338B991CD57034DE9EA5AC8D9A0B</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>e2cd9eda9e</t>
+          <t>6ec3848d0b</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>Gurgaon, Haryana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>data scientist, delhi (place)</t>
+          <t>data scientist, gurgaon (place)</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5848650875?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4DF45BC4D3A230C0689E561399F3F0BA2C0FC825</t>
+          <t>https://www.adzuna.in/land/ad/5849297019?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E87B9A5E2A9605281144BBEA53533DB7165D1FA0</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>83a3456095</t>
+          <t>e2cd9eda9e</t>
         </is>
       </c>
     </row>
@@ -9100,52 +9100,52 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>GTM AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Customer.io</t>
+          <t>Danaher</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>New Delhi, Delhi</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>data scientist, delhi (place)</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/customer-io-gtm-ai-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5848650875?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4DF45BC4D3A230C0689E561399F3F0BA2C0FC825</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>19a2ae7abb</t>
+          <t>83a3456095</t>
         </is>
       </c>
     </row>
@@ -9161,17 +9161,17 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Performance Creative Strategist and AI Producer</t>
+          <t>GTM AI Engineer</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Icarus Digital Marketing</t>
+          <t>Customer.io</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/icarus-digital-marketing-performance-creative-strategist-and-ai-producer</t>
+          <t>https://weworkremotely.com/remote-jobs/customer-io-gtm-ai-engineer</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>60c87a59fd</t>
+          <t>19a2ae7abb</t>
         </is>
       </c>
     </row>
@@ -9222,37 +9222,37 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>GTM Coordinator, Cloud Native (Talent Pool)</t>
+          <t>Performance Creative Strategist and AI Producer</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Percona</t>
+          <t>Icarus Digital Marketing</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bulgaria, Croatia, Czechia, Greece, Hungary, India, Poland, Portugal, Spain</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>cloud, india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>GTM-Coordinator, Talent-Community-Coordinator, Talent-Operations-Coordinator, Entry-level</t>
+          <t>Sales and Marketing, Full-Time</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/percona/jobs/gtm-coordinator-cloud-native-talent-pool</t>
+          <t>https://weworkremotely.com/remote-jobs/icarus-digital-marketing-performance-creative-strategist-and-ai-producer</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>a97ee1ce9b</t>
+          <t>60c87a59fd</t>
         </is>
       </c>
     </row>
@@ -9283,52 +9283,52 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Offensive Cybersecurity Engineer - Red Team</t>
+          <t>GTM Coordinator, Cloud Native (Talent Pool)</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Techno Vista Dynamics</t>
+          <t>Percona</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>APAC,Middle East</t>
+          <t>Bulgaria, Croatia, Czechia, Greece, Hungary, India, Poland, Portugal, Spain</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>engineer, testing (tag), apac (place)</t>
+          <t>cloud, india (place)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Development, engineer,security,penetration testing</t>
+          <t>GTM-Coordinator, Talent-Community-Coordinator, Talent-Operations-Coordinator, Entry-level</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1781770/</t>
+          <t>https://himalayas.app/companies/percona/jobs/gtm-coordinator-cloud-native-talent-pool</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>0bde4f9b82</t>
+          <t>a97ee1ce9b</t>
         </is>
       </c>
     </row>
@@ -9340,56 +9340,56 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Human-Centered AI Data Scientist, Strategy and Talent</t>
+          <t>Offensive Cybersecurity Engineer - Red Team</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank</t>
+          <t>Techno Vista Dynamics</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>APAC,Middle East</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>data scientist, ai, bangalore (place)</t>
+          <t>engineer, testing (tag), apac (place)</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Development, engineer,security,penetration testing</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139276?se=1M6Kj_qf8RGoxpN31Vp7kA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C0F814CBDD0355075DDB000131DE4C8D130504ED</t>
+          <t>https://www.workingnomads.com/job/go/1781770/</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>3130787ee8</t>
+          <t>0bde4f9b82</t>
         </is>
       </c>
     </row>
@@ -9405,52 +9405,52 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Java Software Develper Engineer</t>
+          <t>Human-Centered AI Data Scientist, Strategy and Talent</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>Standard Chartered Bank</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>programmer (tag), developer (tag), software, engineer, backend (tag), java, india (place)</t>
+          <t>data scientist, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Java-Development, Software-Engineer, Entry-Level-Software-Development, Backend-Development, Technical-Support, Java-Software-Engineer, Java-Developer, Java-Developer-Jobs, Java-Application-Developer, Java-Programmer, Developer, Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/csg/jobs/java-software-develper-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5837139276?se=1M6Kj_qf8RGoxpN31Vp7kA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C0F814CBDD0355075DDB000131DE4C8D130504ED</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>7626a2cdd6</t>
+          <t>3130787ee8</t>
         </is>
       </c>
     </row>
@@ -9466,22 +9466,22 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Android Software Engineer</t>
+          <t>Java Software Develper Engineer</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9491,27 +9491,27 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>software engineer, android, kotlin (tag), worldwide (place)</t>
+          <t>programmer (tag), developer (tag), software, engineer, backend (tag), java, india (place)</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Android-Software-Engineer, Mobile-Development, Android-Development, Software-Engineer, Kotlin, Android-Engineer, Android-Software-Engineering, Mobile-Android-Engineer, Android-Systems-Engineer, Android-Engineering, Mobile-Software-Engineer, Senior</t>
+          <t>Java-Development, Software-Engineer, Entry-Level-Software-Development, Backend-Development, Technical-Support, Java-Software-Engineer, Java-Developer, Java-Developer-Jobs, Java-Application-Developer, Java-Programmer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/hudson-manpower/jobs/android-software-engineer</t>
+          <t>https://himalayas.app/companies/csg/jobs/java-software-develper-engineer</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>afb7954487</t>
+          <t>7626a2cdd6</t>
         </is>
       </c>
     </row>
@@ -9527,37 +9527,37 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Application Security Engineer II</t>
+          <t>Android Software Engineer</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>engineer, devops (tag), anywhere (place)</t>
+          <t>software engineer, android, kotlin (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Android-Software-Engineer, Mobile-Development, Android-Development, Software-Engineer, Kotlin, Android-Engineer, Android-Software-Engineering, Mobile-Android-Engineer, Android-Systems-Engineer, Android-Engineering, Mobile-Software-Engineer, Senior</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/abnormal-application-security-engineer-ii</t>
+          <t>https://himalayas.app/companies/hudson-manpower/jobs/android-software-engineer</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>dc9a51cdbc</t>
+          <t>afb7954487</t>
         </is>
       </c>
     </row>
@@ -9584,56 +9584,56 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>DESARROLLADOR FULL STACK</t>
+          <t>Application Security Engineer II</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kruger NearShore LLC - Rekluti</t>
+          <t>Abnormal</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>full stack, front end (tag), backend (tag), angular (tag), testing (tag), python (tag), golang (tag), devops (tag), cloud (tag), git (tag)</t>
+          <t>engineer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>full stack, front end, python, dev, testing, web dev, quality assurance, devops, c, cloud, nosql, git, flutter, angular, mobile, golang, backend, digital nomad</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-desarrollador-full-stack-kruger-nearshore-llc-rekluti-1137062</t>
+          <t>https://weworkremotely.com/remote-jobs/abnormal-application-security-engineer-ii</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>911da99485</t>
+          <t>dc9a51cdbc</t>
         </is>
       </c>
     </row>
@@ -9649,52 +9649,52 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AI Transformation Owner, Product &amp; Design</t>
+          <t>DESARROLLADOR FULL STACK</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Kruger NearShore LLC - Rekluti</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>full stack, front end (tag), backend (tag), angular (tag), testing (tag), python (tag), golang (tag), devops (tag), cloud (tag), git (tag)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Product, Full-Time</t>
+          <t>full stack, front end, python, dev, testing, web dev, quality assurance, devops, c, cloud, nosql, git, flutter, angular, mobile, golang, backend, digital nomad</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/gitlab-ai-transformation-owner-product-design</t>
+          <t>https://remoteOK.com/remote-jobs/remote-desarrollador-full-stack-kruger-nearshore-llc-rekluti-1137062</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>a0e38d6b98</t>
+          <t>911da99485</t>
         </is>
       </c>
     </row>
@@ -9710,52 +9710,52 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>AI Transformation Owner, Product &amp; Design</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Forrester Research, Inc. (US)</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>developer, software (tag), cloud (tag), india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Salesforce-Developer, CRM-Developer, Salesforce-Administrator, Integration-Developer, Software-Developer, Salesforce-CRM-Developer, Salesforce-Application-Developer, Salesforce-Sales-Cloud-Developer, Salesforce-Development, Salesforce-Solutions-Developer, Salesforce-Platform-Developer, Salesforce-Apex-Developer, Force.Com-Developer, Mid-level</t>
+          <t>Product, Full-Time</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/forrester-research-inc-us/jobs/salesforce-developer-8148624472</t>
+          <t>https://weworkremotely.com/remote-jobs/gitlab-ai-transformation-owner-product-design</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>bbbc562c11</t>
+          <t>a0e38d6b98</t>
         </is>
       </c>
     </row>
@@ -9771,17 +9771,17 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>IT Systems Administrator</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ralliant</t>
+          <t>Forrester Research, Inc. (US)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9796,27 +9796,27 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>developer (tag), engineer (tag), india (place)</t>
+          <t>developer, software (tag), cloud (tag), india (place)</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Power-Platform-Engineer, Business-intelligence-Engineer, Analytics-Engineer, Microsoft-Fabric-Engineer, Power-BI-Developer, IT-Systems-Administrator, IT-System-Administrator, Systems-Administrator, IT-Systems-Administration, IT-Administrator, Systems-Support-Administrator, Mid-level</t>
+          <t>Salesforce-Developer, CRM-Developer, Salesforce-Administrator, Integration-Developer, Software-Developer, Salesforce-CRM-Developer, Salesforce-Application-Developer, Salesforce-Sales-Cloud-Developer, Salesforce-Development, Salesforce-Solutions-Developer, Salesforce-Platform-Developer, Salesforce-Apex-Developer, Force.Com-Developer, Mid-level</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ralliant/jobs/it-systems-administrator</t>
+          <t>https://himalayas.app/companies/forrester-research-inc-us/jobs/salesforce-developer-8148624472</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>a720a38bd1</t>
+          <t>bbbc562c11</t>
         </is>
       </c>
     </row>
@@ -9828,56 +9828,56 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Talent Pool -FP&amp;A- Data Scientist / Analytics Specialist / Data &amp; AI Specialist</t>
+          <t>IT Systems Administrator</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ralliant</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>data scientist, ai, bangalore (place)</t>
+          <t>developer (tag), engineer (tag), india (place)</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Energy, Oil &amp; Gas Jobs</t>
+          <t>Power-Platform-Engineer, Business-intelligence-Engineer, Analytics-Engineer, Microsoft-Fabric-Engineer, Power-BI-Developer, IT-Systems-Administrator, IT-System-Administrator, Systems-Administrator, IT-Systems-Administration, IT-Administrator, Systems-Support-Administrator, Mid-level</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773115?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=888721B9EAAF876B1F079BC209DECF1099E63440</t>
+          <t>https://himalayas.app/companies/ralliant/jobs/it-systems-administrator</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>5ee47ace79</t>
+          <t>a720a38bd1</t>
         </is>
       </c>
     </row>
@@ -9893,17 +9893,17 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AI and Automation Developer</t>
+          <t>Talent Pool -FP&amp;A- Data Scientist / Analytics Specialist / Data &amp; AI Specialist</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9918,27 +9918,27 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>automation, developer, ai, bangalore (place)</t>
+          <t>data scientist, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Energy, Oil &amp; Gas Jobs</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5847959817?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44960F01CCAE33F814C0EF4448956DF38E8344F5</t>
+          <t>https://www.adzuna.in/land/ad/5785773115?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=888721B9EAAF876B1F079BC209DECF1099E63440</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>98337240aa</t>
+          <t>5ee47ace79</t>
         </is>
       </c>
     </row>
@@ -9954,52 +9954,52 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>DevOps &amp; Security Engineer - AI-Native Healthcare SaaS</t>
+          <t>AI and Automation Developer</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Zenara Health</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>engineer, devops, ai, anywhere (place)</t>
+          <t>automation, developer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/zenara-health-devops-security-engineer-ai-native-healthcare-saas</t>
+          <t>https://www.adzuna.in/land/ad/5847959817?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44960F01CCAE33F814C0EF4448956DF38E8344F5</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>d592e60ddc</t>
+          <t>98337240aa</t>
         </is>
       </c>
     </row>
@@ -10015,37 +10015,37 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps &amp; Security Engineer - AI-Native Healthcare SaaS</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Zenara Health</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>data scientist, mumbai (place)</t>
+          <t>engineer, devops, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723381?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F9660467E3895814968DA45F3A82EF6912496F70</t>
+          <t>https://weworkremotely.com/remote-jobs/zenara-health-devops-security-engineer-ai-native-healthcare-saas</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>c46d670134</t>
+          <t>d592e60ddc</t>
         </is>
       </c>
     </row>
@@ -10086,12 +10086,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data scientist, mumbai (place)</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10111,17 +10111,17 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837138848?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=86962F79F06A105F30676367582529277DE10978</t>
+          <t>https://www.adzuna.in/land/ad/5846723381?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F9660467E3895814968DA45F3A82EF6912496F70</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>39dacd7158</t>
+          <t>c46d670134</t>
         </is>
       </c>
     </row>
@@ -10142,12 +10142,12 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Itvedant Education Pvt. Ltd.</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10172,17 +10172,17 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5833434843?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=95E30E442ED8EDC695067D6ACDD8806A1A4DBE0E</t>
+          <t>https://www.adzuna.in/land/ad/5837138848?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=86962F79F06A105F30676367582529277DE10978</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>660701d5cb</t>
+          <t>39dacd7158</t>
         </is>
       </c>
     </row>
@@ -10203,17 +10203,17 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Itvedant Education Pvt. Ltd.</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>engineer, ai, hyderabad (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10233,17 +10233,17 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139103?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=23D035D0F5CFDFF88D2FBA2CB9721442B70F9874</t>
+          <t>https://www.adzuna.in/land/ad/5833434843?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=95E30E442ED8EDC695067D6ACDD8806A1A4DBE0E</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>c2ca14412d</t>
+          <t>660701d5cb</t>
         </is>
       </c>
     </row>
@@ -10264,17 +10264,17 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>engineer, ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10294,17 +10294,17 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773097?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1AD120B3FB3DFBC7F01669BC535E68EC0F2123A3</t>
+          <t>https://www.adzuna.in/land/ad/5837139103?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=23D035D0F5CFDFF88D2FBA2CB9721442B70F9874</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>1a0dea6270</t>
+          <t>c2ca14412d</t>
         </is>
       </c>
     </row>
@@ -10325,17 +10325,17 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>engineer, ai, bangalore (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10355,17 +10355,17 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723241?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0084818D71681FAC4F572D55AE1C6BC637792931</t>
+          <t>https://www.adzuna.in/land/ad/5785773097?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1AD120B3FB3DFBC7F01669BC535E68EC0F2123A3</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>a2c0a3fc16</t>
+          <t>1a0dea6270</t>
         </is>
       </c>
     </row>
@@ -10386,17 +10386,17 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Part time Data Science Instructor</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10406,27 +10406,27 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>engineer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Part time Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5850983469?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0F708DAB080760E3C6FB3FC40EA3A64A7B0306D9</t>
+          <t>https://www.adzuna.in/land/ad/5846723241?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0084818D71681FAC4F572D55AE1C6BC637792931</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>fa169c0060</t>
+          <t>a2c0a3fc16</t>
         </is>
       </c>
     </row>
@@ -10447,12 +10447,12 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer for AI &amp;DS, BSI</t>
+          <t>Part time Data Science Instructor</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -10467,27 +10467,27 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>engineer, ai, india (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Part time Jobs</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785771743?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F6DC64E0C8FB2D27FC25CBE24085394F367A2687</t>
+          <t>https://www.adzuna.in/land/ad/5850983469?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0F708DAB080760E3C6FB3FC40EA3A64A7B0306D9</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>3fd60b2320</t>
+          <t>fa169c0060</t>
         </is>
       </c>
     </row>
@@ -10508,17 +10508,17 @@
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Agentic AI Engineer for AI &amp;DS, BSI</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>engineer, ai, mumbai (place)</t>
+          <t>engineer, ai, india (place)</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773171?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2185A7049B5506DF1182A45172761BBEF73613FA</t>
+          <t>https://www.adzuna.in/land/ad/5785771743?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F6DC64E0C8FB2D27FC25CBE24085394F367A2687</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>43f406da07</t>
+          <t>3fd60b2320</t>
         </is>
       </c>
     </row>
@@ -10569,17 +10569,17 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Data Scientist - People Analytics</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>engineer, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10599,17 +10599,17 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5821999876?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=08993CE6BE520CA2C34926E81E8CBB0072304E1F</t>
+          <t>https://www.adzuna.in/land/ad/5785773171?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2185A7049B5506DF1182A45172761BBEF73613FA</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>187dc9c03e</t>
+          <t>43f406da07</t>
         </is>
       </c>
     </row>
@@ -10630,17 +10630,17 @@
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>Data Scientist - People Analytics</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Itvedant Education Pvt. Ltd.</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10650,27 +10650,27 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Teaching Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5852476426?se=NskdSSae8RGSb8VpDRDiVA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2B7C55A3F795EE4D2F2D732844EDA9B4CAC3F128</t>
+          <t>https://www.adzuna.in/land/ad/5821999876?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=08993CE6BE520CA2C34926E81E8CBB0072304E1F</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>5c41be551e</t>
+          <t>187dc9c03e</t>
         </is>
       </c>
     </row>
@@ -10686,37 +10686,37 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PHP Developer - Work From Home</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CC Staffing International</t>
+          <t>Itvedant Education Pvt. Ltd.</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>developer, software (tag), engineer (tag), backend (tag), php, india (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>PHP-Developer, Backend-Engineer, Web-Development, Software-Developer, Full-Stack-Developer, Remote-PHP-Developer, PHP-Software-Engineer, Backend-PHP-Developer, Remote-Web-Developer, Developer, Mid-level</t>
+          <t>Teaching Jobs</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/cc-staffing-international/jobs/php-developer-work-from-home</t>
+          <t>https://www.adzuna.in/land/ad/5852476426?se=NskdSSae8RGSb8VpDRDiVA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2B7C55A3F795EE4D2F2D732844EDA9B4CAC3F128</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>14b619fb91</t>
+          <t>5c41be551e</t>
         </is>
       </c>
     </row>
@@ -10747,52 +10747,52 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Kannada</t>
+          <t>PHP Developer - Work From Home</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>RWS</t>
+          <t>CC Staffing International</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>ai, delhi (place)</t>
+          <t>developer, software (tag), engineer (tag), backend (tag), php, india (place)</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>PHP-Developer, Backend-Engineer, Web-Development, Software-Developer, Full-Stack-Developer, Remote-PHP-Developer, PHP-Software-Engineer, Backend-PHP-Developer, Remote-Web-Developer, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772642?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=96F9E6C80B83A39F4F2C05268274FD2EBE13B037</t>
+          <t>https://himalayas.app/companies/cc-staffing-international/jobs/php-developer-work-from-home</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>bb43fd7b08</t>
+          <t>14b619fb91</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10813,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Marathi</t>
+          <t>AI Data Specialist - Kannada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772098?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=B26B7FB6A299BC3A2BFD29BF94BF59C981A24A29</t>
+          <t>https://www.adzuna.in/land/ad/5785772642?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=96F9E6C80B83A39F4F2C05268274FD2EBE13B037</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>fe688433d1</t>
+          <t>bb43fd7b08</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Telugu</t>
+          <t>AI Data Specialist - Marathi</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785770664?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=D13E17364CDB48C8A2B963F62AC42C33A76C021B</t>
+          <t>https://www.adzuna.in/land/ad/5785772098?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=B26B7FB6A299BC3A2BFD29BF94BF59C981A24A29</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>91c279dfff</t>
+          <t>fe688433d1</t>
         </is>
       </c>
     </row>
@@ -10935,7 +10935,7 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Hindi</t>
+          <t>AI Data Specialist - Telugu</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10965,17 +10965,17 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5795883387?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=38289BC2F5CA723017CE2916CC4536DEA978B9A6</t>
+          <t>https://www.adzuna.in/land/ad/5785770664?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=D13E17364CDB48C8A2B963F62AC42C33A76C021B</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>170ea3eac1</t>
+          <t>91c279dfff</t>
         </is>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Tamil</t>
+          <t>AI Data Specialist - Hindi</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -11026,17 +11026,17 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772320?se=xp3UHeGd8RGIEJB03vDchg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AB56F1DD143407CEE31E12C4126DC533B06A2AD3</t>
+          <t>https://www.adzuna.in/land/ad/5795883387?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=38289BC2F5CA723017CE2916CC4536DEA978B9A6</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>616fb76ab0</t>
+          <t>170ea3eac1</t>
         </is>
       </c>
     </row>
@@ -11052,52 +11052,52 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Agent Operations Engineer - Fully Remote | Upto $500/task Task based</t>
+          <t>AI Data Specialist - Tamil</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>RWS</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>New Delhi, Delhi</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>engineer, ai (tag), india (place)</t>
+          <t>ai, delhi (place)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Agent-Engineering, LLMOperations, AI-Engineering, AI-Operations, Machine-Learning-Engineering, AgentOps-Engineer, Agent-Orchestration-Engineer, AI-Agents-Engineer, Operations-Engineer, Remote-AI-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/mercor/jobs/agent-operations-engineer-fully-remote-upto-500-task-task-based</t>
+          <t>https://www.adzuna.in/land/ad/5785772320?se=xp3UHeGd8RGIEJB03vDchg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AB56F1DD143407CEE31E12C4126DC533B06A2AD3</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>be05dc52ff</t>
+          <t>616fb76ab0</t>
         </is>
       </c>
     </row>
@@ -11113,17 +11113,17 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS Authorized Instructor</t>
+          <t>Agent Operations Engineer - Fully Remote | Upto $500/task Task based</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>ITC WORLDWIDE</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>cloud (tag), aws, india (place)</t>
+          <t>engineer, ai (tag), india (place)</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>AWS-Training, Cloud-Computing-Instructor, Technical-Trainer, AWS-Authorized-Instructor, Cloud-Education, AWS-Certification-Training, Cloud-Instructor, Cloud-Computing-Trainer, Senior</t>
+          <t>Agent-Engineering, LLMOperations, AI-Engineering, AI-Operations, Machine-Learning-Engineering, AgentOps-Engineer, Agent-Orchestration-Engineer, AI-Agents-Engineer, Operations-Engineer, Remote-AI-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/itc-worldwide/jobs/aws-authorized-instructor</t>
+          <t>https://himalayas.app/companies/mercor/jobs/agent-operations-engineer-fully-remote-upto-500-task-task-based</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>a42ddc7b02</t>
+          <t>be05dc52ff</t>
         </is>
       </c>
     </row>
@@ -11174,37 +11174,37 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Associate Instructor</t>
+          <t>AWS Authorized Instructor</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>ITC WORLDWIDE</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>devops (tag), associate (level), anywhere (place)</t>
+          <t>cloud (tag), aws, india (place)</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>AWS-Training, Cloud-Computing-Instructor, Technical-Trainer, AWS-Authorized-Instructor, Cloud-Education, AWS-Certification-Training, Cloud-Instructor, Cloud-Computing-Trainer, Senior</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/beyondtrust-associate-instructor</t>
+          <t>https://himalayas.app/companies/itc-worldwide/jobs/aws-authorized-instructor</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>4c1963b96c</t>
+          <t>a42ddc7b02</t>
         </is>
       </c>
     </row>
@@ -11235,52 +11235,52 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>E-learning Developer</t>
+          <t>Associate Instructor</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Crowe UAE</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>developer, ahmedabad (place)</t>
+          <t>devops (tag), associate (level), anywhere (place)</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5850983902?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F927DE790D9874EE6BA8C142D15CF3A7A97BFA7E</t>
+          <t>https://weworkremotely.com/remote-jobs/beyondtrust-associate-instructor</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>843701dc9e</t>
+          <t>4c1963b96c</t>
         </is>
       </c>
     </row>
@@ -11296,52 +11296,52 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Developer Educator</t>
+          <t>E-learning Developer</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>PlanetScale</t>
+          <t>Crowe UAE</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Ahmedabad, Gujarat</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>developer, anywhere (place)</t>
+          <t>developer, ahmedabad (place)</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/planetscale-developer-educator</t>
+          <t>https://www.adzuna.in/land/ad/5850983902?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F927DE790D9874EE6BA8C142D15CF3A7A97BFA7E</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>c72ab4031d</t>
+          <t>843701dc9e</t>
         </is>
       </c>
     </row>
@@ -11357,50 +11357,111 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
+          <t>Developer Educator</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>PlanetScale</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Anywhere in the World</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>weworkremotely</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>developer, anywhere (place)</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Sales and Marketing, Full-Time</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/planetscale-developer-educator</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>c72ab4031d</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>11</v>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
           <t>Consultant Implementation Engineer</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>Harbor</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="H180" t="inlineStr">
         <is>
           <t>remoteok</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
+      <c r="I180" t="inlineStr">
         <is>
           <t>engineer, golang (tag), remote (place)</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr">
+      <c r="J180" t="inlineStr">
         <is>
           <t>consulting, technical, accounting, legal, golang, engineer</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-consultant-implementation-engineer-harbor-1136987</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t>f724e65bc8</t>
         </is>
@@ -11408,7 +11469,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of: new, applied, skipped" prompt="Mark this job applied once you have applied." type="list">
+    <dataValidation sqref="A2:A180" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of: new, applied, skipped" prompt="Mark this job applied once you have applied." type="list">
       <formula1>"new,applied,skipped"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M186"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -872,58 +872,56 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Golang Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Arango</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>kubernetes, engineer, golang</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>golang, golang, engineer</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>49</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Laravel Developer</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Quest Global Technologies</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>himalayas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>fullstack (tag), developer, backend (tag), react (tag), php (tag), india (place)</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Laravel-Development, PHP-Development, Backend-Development, Fullstack-Development, Web-Development, Laravel-Developer, Laravel, Mid-Level-Laravel-React-Developer, Laravel-Full-Stack-Development, Laravel-Entwicklung, PHP-Developer, Developer, Mid-level</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/quest-global-technologies/jobs/laravel-developer-6713783437</t>
+          <t>https://remoteOK.com/remote-jobs/remote-golang-kubernetes-engineer-arango-1137400</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>a772f50cb9</t>
+          <t>9b0012b5b3</t>
         </is>
       </c>
     </row>
@@ -939,37 +937,39 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>46</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI agent engineer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sticker Mule</t>
+          <t>Quest Global Technologies</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>fullstack (tag), developer, backend (tag), react (tag), php (tag), india (place)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>Laravel-Development, PHP-Development, Backend-Development, Fullstack-Development, Web-Development, Laravel-Developer, Laravel, Mid-Level-Laravel-React-Developer, Laravel-Full-Stack-Development, Laravel-Entwicklung, PHP-Developer, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/sticker-mule-ai-agent-engineer</t>
+          <t>https://himalayas.app/companies/quest-global-technologies/jobs/laravel-developer-6713783437</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>e0b3cdfcc1</t>
+          <t>a772f50cb9</t>
         </is>
       </c>
     </row>
@@ -1000,17 +1000,17 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Anthropic Fellows Program, AI Safety &amp; Security</t>
+          <t>AI agent engineer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Sticker Mule</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1025,12 +1025,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>All Other Remote, Full-Time</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/anthropic-anthropic-fellows-program-ai-safety-security</t>
+          <t>https://weworkremotely.com/remote-jobs/sticker-mule-ai-agent-engineer</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>bf649aa9a3</t>
+          <t>e0b3cdfcc1</t>
         </is>
       </c>
     </row>
@@ -1057,56 +1057,56 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Anthropic Fellows Program, AI Safety &amp; Security</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlys</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>artificial intelligence, intern (level), india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>All Other Remote, Full-Time</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876870198?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=887C5853FA1B767B096C42327F5C3826C21742CE</t>
+          <t>https://weworkremotely.com/remote-jobs/anthropic-anthropic-fellows-program-ai-safety-security</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>b169bf4100</t>
+          <t>bf649aa9a3</t>
         </is>
       </c>
     </row>
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MTS-1 Machine Learning Engineer</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Atlys</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>artificial intelligence, intern (level), india (place)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877184305?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8749753C0B487764A74F37A03D96F548F15161A9</t>
+          <t>https://www.adzuna.in/land/ad/5876870198?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=887C5853FA1B767B096C42327F5C3826C21742CE</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>fab40e54d1</t>
+          <t>b169bf4100</t>
         </is>
       </c>
     </row>
@@ -1183,52 +1183,52 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MTS-1 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smartcuts</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), frontend (tag), worldwide (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Engineering, Software-Engineer, Frontend-Development, Fullstack-Development, Browser-Extension-Development, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Software-Design-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/smartcuts/jobs/software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5877184305?se=ZLpFT9Ww8RGUZ4dUMDgSxw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8749753C0B487764A74F37A03D96F548F15161A9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1191a23402</t>
+          <t>fab40e54d1</t>
         </is>
       </c>
     </row>
@@ -1244,17 +1244,17 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GitHub Contributor</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Smartcuts</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), frontend (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
+          <t>Engineering, Software-Engineer, Frontend-Development, Fullstack-Development, Browser-Extension-Development, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Software-Design-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-106728860</t>
+          <t>https://himalayas.app/companies/smartcuts/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>f02b389972</t>
+          <t>1191a23402</t>
         </is>
       </c>
     </row>
@@ -1301,58 +1301,56 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Backend Engineer, IAM</t>
+          <t>GitHub Contributor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>engineer, backend, anywhere (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/reddit-backend-engineer-iam</t>
+          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-106728860</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>790d0d9505</t>
+          <t>f02b389972</t>
         </is>
       </c>
     </row>
@@ -1371,16 +1369,16 @@
         <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Developer Advocate - Service Management</t>
+          <t>Backend Engineer, IAM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1395,12 +1393,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>developer, devops (tag), anywhere (place)</t>
+          <t>engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1410,12 +1408,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/datadog-developer-advocate-service-management</t>
+          <t>https://weworkremotely.com/remote-jobs/reddit-backend-engineer-iam</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4df8de53d8</t>
+          <t>790d0d9505</t>
         </is>
       </c>
     </row>
@@ -1431,37 +1429,39 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>QA Testers Wanted (No experience needed)</t>
+          <t>Developer Advocate - Service Management</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tester Work</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Australia &amp; New Zealand (REMOTE)</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>qa, remote (place)</t>
+          <t>developer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1860630/</t>
+          <t>https://weworkremotely.com/remote-jobs/datadog-developer-advocate-service-management</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>bf909f7a1f</t>
+          <t>4df8de53d8</t>
         </is>
       </c>
     </row>
@@ -1488,58 +1488,56 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>74</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist II, ML Infrastructure</t>
+          <t>QA Testers Wanted (No experience needed)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Tester Work</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Australia &amp; New Zealand (REMOTE)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data scientist, ml, anywhere (place)</t>
+          <t>qa, remote (place)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-ml-infrastructure</t>
+          <t>https://www.workingnomads.com/job/go/1860630/</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>a84319c791</t>
+          <t>bf909f7a1f</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1553,14 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist II, Infrastructure</t>
+          <t>Data Scientist II, ML Infrastructure</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>data scientist, anywhere (place)</t>
+          <t>data scientist, ml, anywhere (place)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-infrastructure</t>
+          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-ml-infrastructure</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>def323e358</t>
+          <t>a84319c791</t>
         </is>
       </c>
     </row>
@@ -1616,52 +1616,52 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II, Infrastructure</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mirantis</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>software engineer, golang (tag)</t>
+          <t>data scientist, anywhere (place)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>golang, dev, engineer, digital nomad</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-mirantis-1137387</t>
+          <t>https://weworkremotely.com/remote-jobs/pinterest-data-scientist-ii-infrastructure</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0eb27a0401</t>
+          <t>def323e358</t>
         </is>
       </c>
     </row>
@@ -1673,41 +1673,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Science Engineer - AI</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Mirantis</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>data science, engineer, ai, bangalore (place)</t>
+          <t>software engineer, golang (tag)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>golang, dev, engineer, digital nomad</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880523483?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44AFB881700BC2524FE70C04638A2D65741F5C06</t>
+          <t>https://remoteOK.com/remote-jobs/remote-software-engineer-mirantis-1137387</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>987c89c61a</t>
+          <t>0eb27a0401</t>
         </is>
       </c>
     </row>
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning</t>
+          <t>Data Science Engineer - AI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kotak Neo</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>machine learning, ai, mumbai (place)</t>
+          <t>data science, engineer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880062262?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC74E214D0612FE80831EDD83B8CF67B6032A3E9</t>
+          <t>https://www.adzuna.in/land/ad/5880523483?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44AFB881700BC2524FE70C04638A2D65741F5C06</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>c8b4bb4ba3</t>
+          <t>987c89c61a</t>
         </is>
       </c>
     </row>
@@ -1799,37 +1799,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>AI &amp; Machine Learning</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Kotak Neo</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>software (tag), engineer, ai (tag), ml, worldwide (place)</t>
+          <t>machine learning, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Machine-Learning-Engineer, AI-ML-Engineer, ML-Software-Engineer, ML-Research-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ml-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5880062262?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC74E214D0612FE80831EDD83B8CF67B6032A3E9</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>6b92e0e58d</t>
+          <t>c8b4bb4ba3</t>
         </is>
       </c>
     </row>
@@ -1865,47 +1865,47 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chandigarh, India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>data science, india (place), chandigarh (place)</t>
+          <t>software (tag), engineer, ai (tag), ml, worldwide (place)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Machine-Learning-Engineer, AI-ML-Engineer, ML-Software-Engineer, ML-Research-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5879662958?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7C90B2BB52AA81EB60C613281A1D6AF4E5DC8BD8</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ml-engineer</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>6557a8e75a</t>
+          <t>6b92e0e58d</t>
         </is>
       </c>
     </row>
@@ -1921,54 +1921,52 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PhD &amp; Academic Expert</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Chandigarh, India</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ml (tag), worldwide (place)</t>
+          <t>data science, india (place), chandigarh (place)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Academic-Expert, PhD-Specialist-Consultant, Academic-Consultant, Academic-Subject-Matter-Expert, Academic-Professional, ML-Research-PhD-Expert, PhD-Researcher, Education-Expert, Mid-level, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/phd-academic-expert</t>
+          <t>https://www.adzuna.in/land/ad/5879662958?se=bERrS4Ou8RGuc42MGaSpcg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7C90B2BB52AA81EB60C613281A1D6AF4E5DC8BD8</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>a8281d77e1</t>
+          <t>6557a8e75a</t>
         </is>
       </c>
     </row>
@@ -1980,23 +1978,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>PhD &amp; Academic Expert</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dura Digital</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2011,27 +2009,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>engineer, backend (tag), python (tag), ai, ml (tag), worldwide (place)</t>
+          <t>ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>AI-Engineer, Machine-Learning-Engineer, Backend-Engineer, Data-Engineer, MLOps-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Senior</t>
+          <t>Academic-Expert, PhD-Specialist-Consultant, Academic-Consultant, Academic-Subject-Matter-Expert, Academic-Professional, ML-Research-PhD-Expert, PhD-Researcher, Education-Expert, Mid-level, Senior</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/dura-digital/jobs/ai-engineer</t>
+          <t>https://himalayas.app/companies/micro1/jobs/phd-academic-expert</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>8666ff7b1c</t>
+          <t>a8281d77e1</t>
         </is>
       </c>
     </row>
@@ -2047,17 +2045,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Facial Data Collection Associate</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Dura Digital</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ai, associate (level), worldwide (place)</t>
+          <t>engineer, backend (tag), python (tag), ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>AI-Data-Collection-Specialist, Data-Collection-Associate, Facial-Recognition-Data-Collection, AI-Services-Associate, AI-Operations-Associate, AI-Associate, Entry-level</t>
+          <t>AI-Engineer, Machine-Learning-Engineer, Backend-Engineer, Data-Engineer, MLOps-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Senior</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-facial-data-collection-associate</t>
+          <t>https://himalayas.app/companies/dura-digital/jobs/ai-engineer</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>a024718d12</t>
+          <t>8666ff7b1c</t>
         </is>
       </c>
     </row>
@@ -2108,54 +2108,52 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>49</v>
-      </c>
-      <c r="D28" t="n">
-        <v>3</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Facial Data Collection Associate</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Omnicom Global Solutions</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>ai, associate (level), worldwide (place)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Data-Collection-Specialist, Data-Collection-Associate, Facial-Recognition-Data-Collection, AI-Services-Associate, AI-Operations-Associate, AI-Associate, Entry-level</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5880062427?se=4EjJjS6u8RGGGqTWwpKkng&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E0A2211C95EBCFB9C1236FB6E39F7FBF4A7836A8</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-facial-data-collection-associate</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>c539f926b2</t>
+          <t>a024718d12</t>
         </is>
       </c>
     </row>
@@ -2171,54 +2169,54 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Financial Systems Expert</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Omnicom Global Solutions</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>developer (tag), engineer (tag), worldwide (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Financial-Systems-Specialist, Financial-Systems-Consultant, Financial-Systems-Advisor, Finance-Systems-Specialist, Financial-Systems-Consulting, Finance-Systems-Consultant, Financial-Systems-Developer, Financial-Systems-Integration-Specialist, Financial-Systems-Architect, Financial-Systems-Engineer, Mid-level, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/financial-systems-expert</t>
+          <t>https://www.adzuna.in/land/ad/5880062427?se=4EjJjS6u8RGGGqTWwpKkng&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E0A2211C95EBCFB9C1236FB6E39F7FBF4A7836A8</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>a8090f5869</t>
+          <t>c539f926b2</t>
         </is>
       </c>
     </row>
@@ -2230,56 +2228,58 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>79</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DVP - Data Science AI</t>
+          <t>Financial Systems Expert</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IndiaFirst Life</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>data science, ai, mumbai (place)</t>
+          <t>developer (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Financial-Systems-Specialist, Financial-Systems-Consultant, Financial-Systems-Advisor, Finance-Systems-Specialist, Financial-Systems-Consulting, Finance-Systems-Consultant, Financial-Systems-Developer, Financial-Systems-Integration-Specialist, Financial-Systems-Architect, Financial-Systems-Engineer, Mid-level, Senior</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877452336?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C389ADE3462A8F960BCEB9BFB3D8C01182D8F284</t>
+          <t>https://himalayas.app/companies/micro1/jobs/financial-systems-expert</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>d4091e9b06</t>
+          <t>a8090f5869</t>
         </is>
       </c>
     </row>
@@ -2295,22 +2295,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DVP - Data Science AI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ryewalk</t>
+          <t>IndiaFirst Life</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>data scientist, chennai (place)</t>
+          <t>data science, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877457613?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=858E7DDB9C73029BB012BE9266CDC5516D57BB06</t>
+          <t>https://www.adzuna.in/land/ad/5877452336?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C389ADE3462A8F960BCEB9BFB3D8C01182D8F284</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>5b1e04fbec</t>
+          <t>d4091e9b06</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Ryewalk</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876016078?se=tjzQcmWt8RGk7Nm076a3Fw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=076A6D8BF6D1FAB77910335EA1D3406F73F06FDC</t>
+          <t>https://www.adzuna.in/land/ad/5877457613?se=2qT3mUmt8RGWn_T67fT_Ug&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=858E7DDB9C73029BB012BE9266CDC5516D57BB06</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>03602a7f75</t>
+          <t>5b1e04fbec</t>
         </is>
       </c>
     </row>
@@ -2417,52 +2417,52 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>QA Tester Entry Level</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ace IT Careers</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>testing (tag), qa, entry level (level), remote (place)</t>
+          <t>data scientist, chennai (place)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>testing, dev, analyst, quality assurance, digital nomad</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-qa-tester-entry-level-ace-it-careers-1136701</t>
+          <t>https://www.adzuna.in/land/ad/5876016078?se=tjzQcmWt8RGk7Nm076a3Fw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=076A6D8BF6D1FAB77910335EA1D3406F73F06FDC</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>066819b5ee</t>
+          <t>03602a7f75</t>
         </is>
       </c>
     </row>
@@ -2478,54 +2478,52 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>32</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Application Security Engineer</t>
+          <t>QA Tester Entry Level</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sun King</t>
+          <t>Ace IT Careers</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>software (tag), engineer, cloud (tag), api (tag), india (place)</t>
+          <t>testing (tag), qa, entry level (level), remote (place)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Application-Security-Engineer, Security-Engineer, Penetration-Tester, API-Security, Cloud-Security-Engineer, AppSec-Engineer, Application-Security-Engineering, Application-Security-Specialist, Software-Security-Engineer, Mid-level</t>
+          <t>testing, dev, analyst, quality assurance, digital nomad</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/sun-king/jobs/application-security-engineer</t>
+          <t>https://remoteOK.com/remote-jobs/remote-qa-tester-entry-level-ace-it-careers-1136701</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>41b24c0687</t>
+          <t>066819b5ee</t>
         </is>
       </c>
     </row>
@@ -2543,15 +2541,17 @@
       <c r="C35" t="n">
         <v>32</v>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nuclear Physics Specialist - Fully Remote | Upto $100/hr</t>
+          <t>Application Security Engineer</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>Sun King</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>engineer (tag), ai (tag), india (place)</t>
+          <t>software (tag), engineer, cloud (tag), api (tag), india (place)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Computational-Physics, Nuclear-Physics, Particle-Physics, AI-Evaluation, Scientific-Computing, Nuclear-Physics-AI-Specialist, Freelance-Physics-Specialist, Reactor-Physics-Engineer, Freelance-Physics-Expert, Physics-Research-Specialist, Physics-Freelancer, Mid-level</t>
+          <t>Application-Security-Engineer, Security-Engineer, Penetration-Tester, API-Security, Cloud-Security-Engineer, AppSec-Engineer, Application-Security-Engineering, Application-Security-Specialist, Software-Security-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/mercor/jobs/nuclear-physics-specialist-fully-remote-upto-100-hr-6652317191</t>
+          <t>https://himalayas.app/companies/sun-king/jobs/application-security-engineer</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>e80acb6174</t>
+          <t>41b24c0687</t>
         </is>
       </c>
     </row>
@@ -2598,58 +2598,56 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>65</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Nuclear Physics Specialist - Fully Remote | Upto $100/hr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dynamics Monk Consulting Services</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>artificial intelligence, india (place), delhi (place)</t>
+          <t>engineer (tag), ai (tag), india (place)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Computational-Physics, Nuclear-Physics, Particle-Physics, AI-Evaluation, Scientific-Computing, Nuclear-Physics-AI-Specialist, Freelance-Physics-Specialist, Reactor-Physics-Engineer, Freelance-Physics-Expert, Physics-Research-Specialist, Physics-Freelancer, Mid-level</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028069?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F290F3C8F39D5ABB349E29F918917B30A38BA853</t>
+          <t>https://himalayas.app/companies/mercor/jobs/nuclear-physics-specialist-fully-remote-upto-100-hr-6652317191</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9010d87d61</t>
+          <t>e80acb6174</t>
         </is>
       </c>
     </row>
@@ -2665,22 +2663,24 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>54</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vahan.ai</t>
+          <t>Dynamics Monk Consulting Services</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, india (place), delhi (place)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876029045?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1440DAC38EB3556F9000947FA0A0834CFF14AB75</t>
+          <t>https://www.adzuna.in/land/ad/5876028069?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F290F3C8F39D5ABB349E29F918917B30A38BA853</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>56f72b7a03</t>
+          <t>9010d87d61</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EYEGLOBAL SOLUTIONS PVT. LTD.</t>
+          <t>Vahan.ai</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, chennai (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876028703?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9D6C280D30C30F591E884FDA2F691CC4409C3EC6</t>
+          <t>https://www.adzuna.in/land/ad/5876029045?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1440DAC38EB3556F9000947FA0A0834CFF14AB75</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>bafec6742f</t>
+          <t>56f72b7a03</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Appglide Solutions</t>
+          <t>EYEGLOBAL SOLUTIONS PVT. LTD.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876870603?se=DiEjalis8RGQ-MmLyhoJEg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=987B153BD1BD745987463A7F926C3F0CC163AE60</t>
+          <t>https://www.adzuna.in/land/ad/5876028703?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9D6C280D30C30F591E884FDA2F691CC4409C3EC6</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>d4bbc378a8</t>
+          <t>bafec6742f</t>
         </is>
       </c>
     </row>
@@ -2853,17 +2853,17 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MTS-2 Machine Learning Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Appglide Solutions</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, chennai (place)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5877184044?se=ME0PiYGs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=DBDB737DEAF34AD8D344749E581C417C10EC5A31</t>
+          <t>https://www.adzuna.in/land/ad/5876870603?se=DiEjalis8RGQ-MmLyhoJEg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=987B153BD1BD745987463A7F926C3F0CC163AE60</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>37872b8c00</t>
+          <t>d4bbc378a8</t>
         </is>
       </c>
     </row>
@@ -2909,37 +2909,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Account Executive, AI/HPC, Neo / Sovereign Cloud (EMEA)</t>
+          <t>MTS-2 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Everpure</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>cloud, ai, anywhere (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/everpure-account-executive-ai-hpc-neo-sovereign-cloud-emea</t>
+          <t>https://www.adzuna.in/land/ad/5877184044?se=ME0PiYGs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=DBDB737DEAF34AD8D344749E581C417C10EC5A31</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>44fbf0ebf8</t>
+          <t>37872b8c00</t>
         </is>
       </c>
     </row>
@@ -2970,39 +2970,37 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>49</v>
-      </c>
-      <c r="D42" t="n">
-        <v>3</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Account Executive, AI/HPC, Neo / Sovereign Cloud (EMEA)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Infosys Finacle</t>
+          <t>Everpure</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>cloud, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Sales and Marketing, Full-Time</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3012,12 +3010,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876010793?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8D81876C99F248DACDDC8104E41D7CB59A09112B</t>
+          <t>https://weworkremotely.com/remote-jobs/everpure-account-executive-ai-hpc-neo-sovereign-cloud-emea</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>68b1b69943</t>
+          <t>44fbf0ebf8</t>
         </is>
       </c>
     </row>
@@ -3033,37 +3031,39 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>47</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Frontend Developer - Talent Pool</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Espeo Software</t>
+          <t>Infosys Finacle</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>developer, frontend, software (tag), engineer (tag), react (tag), worldwide (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Frontend-Development, Web-Development, Software-Development, ContractWorks, Freelance-Development, Frontend-Development-Jobs, Tech-Talent-Pool, Front-End-Developer, Technology-Talent-Pool, Engineering-Talent-Pool, Frontend-React-Developer, React-Frontend-Developer, Frontend-Engineer, Developer, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/espeo-software/jobs/frontend-developer-talent-pool</t>
+          <t>https://www.adzuna.in/land/ad/5876010793?se=aCKSUCqs8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8D81876C99F248DACDDC8104E41D7CB59A09112B</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>409bd93507</t>
+          <t>68b1b69943</t>
         </is>
       </c>
     </row>
@@ -3094,17 +3094,17 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe AEP)</t>
+          <t>Frontend Developer - Talent Pool</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TechBiz Global</t>
+          <t>Espeo Software</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3119,12 +3119,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>data engineer, developer (tag), cloud (tag), worldwide (place)</t>
+          <t>developer, frontend, software (tag), engineer (tag), react (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Data-Engineering, ETL-Development, Cloud-Data-Engineering, Adobe-Experience-Platform, Data-Integration, Adobe-CDP-Engineer, Data-Engineer, Adobe-Experience-Platform-Engineer, Data-Engineer-Jobs, Data-Platform-Engineer, Enterprise-Data-Engineer, Developer, Senior</t>
+          <t>Frontend-Development, Web-Development, Software-Development, ContractWorks, Freelance-Development, Frontend-Development-Jobs, Tech-Talent-Pool, Front-End-Developer, Technology-Talent-Pool, Engineering-Talent-Pool, Frontend-React-Developer, React-Frontend-Developer, Frontend-Engineer, Developer, Senior</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/techbiz-global/jobs/data-engineer-adobe-aep-7933835037</t>
+          <t>https://himalayas.app/companies/espeo-software/jobs/frontend-developer-talent-pool</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>3cf5fcdc34</t>
+          <t>409bd93507</t>
         </is>
       </c>
     </row>
@@ -3155,52 +3155,52 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Social Comms</t>
+          <t>Data Engineer (Adobe AEP)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NOPE</t>
+          <t>TechBiz Global</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ai (tag)</t>
+          <t>data engineer, developer (tag), cloud (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>marketing, education, technical, content writing, social media, ai, social</t>
+          <t>Data-Engineering, ETL-Development, Cloud-Data-Engineering, Adobe-Experience-Platform, Data-Integration, Adobe-CDP-Engineer, Data-Engineer, Adobe-Experience-Platform-Engineer, Data-Engineer-Jobs, Data-Platform-Engineer, Enterprise-Data-Engineer, Developer, Senior</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-social-comms-nope-1137314</t>
+          <t>https://himalayas.app/companies/techbiz-global/jobs/data-engineer-adobe-aep-7933835037</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>417f6ff5ea</t>
+          <t>3cf5fcdc34</t>
         </is>
       </c>
     </row>
@@ -3212,56 +3212,56 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Social Comms</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>NOPE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>ai (tag)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>marketing, education, technical, content writing, social media, ai, social</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876024927?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0BB3A9B6F76E859DE51E5C2F0066293EDC5FE6EA</t>
+          <t>https://remoteOK.com/remote-jobs/remote-social-comms-nope-1137314</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0851d46422</t>
+          <t>417f6ff5ea</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3287,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Questhiring</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876027895?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=09A0BE7549E8D3105D5BC0AA92FAA0662C7CD065</t>
+          <t>https://www.adzuna.in/land/ad/5876024927?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0BB3A9B6F76E859DE51E5C2F0066293EDC5FE6EA</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>8a025ec1ce</t>
+          <t>0851d46422</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TBO.COM</t>
+          <t>Questhiring</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026044?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FDDB74C699BD4423DAD1E4FB7120816040F747A</t>
+          <t>https://www.adzuna.in/land/ad/5876027895?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=09A0BE7549E8D3105D5BC0AA92FAA0662C7CD065</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>a427b9cd23</t>
+          <t>8a025ec1ce</t>
         </is>
       </c>
     </row>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ADB SAFEGATE</t>
+          <t>TBO.COM</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, hyderabad (place)</t>
+          <t>artificial intelligence, engineer, india (place)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026294?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9C70BDA29FFF510B21324AF211D635A868DC48AA</t>
+          <t>https://www.adzuna.in/land/ad/5876026044?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FDDB74C699BD4423DAD1E4FB7120816040F747A</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>292ee6d2c1</t>
+          <t>a427b9cd23</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neural Foundry</t>
+          <t>ADB SAFEGATE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026040?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8CA62DE6EFC7E6B952E843BFE686F26AF0E83028</t>
+          <t>https://www.adzuna.in/land/ad/5876026294?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9C70BDA29FFF510B21324AF211D635A868DC48AA</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>c1e16bca2e</t>
+          <t>292ee6d2c1</t>
         </is>
       </c>
     </row>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DotKonnekt</t>
+          <t>Neural Foundry</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, hyderabad (place)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026944?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=51439456D8BA015D122C9B9E72B93BC7715ADC62</t>
+          <t>https://www.adzuna.in/land/ad/5876026040?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8CA62DE6EFC7E6B952E843BFE686F26AF0E83028</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>172ee82bd6</t>
+          <t>c1e16bca2e</t>
         </is>
       </c>
     </row>
@@ -3592,12 +3592,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Recro</t>
+          <t>DotKonnekt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876027463?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=40F66C80D240EB217C5AF3C758F1793D002D574F</t>
+          <t>https://www.adzuna.in/land/ad/5876026944?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=51439456D8BA015D122C9B9E72B93BC7715ADC62</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>91af896417</t>
+          <t>172ee82bd6</t>
         </is>
       </c>
     </row>
@@ -3648,17 +3648,17 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer 2</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Frinks AI</t>
+          <t>Recro</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>artificial intelligence, engineer, bangalore (place)</t>
+          <t>artificial intelligence, engineer, india (place)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876025062?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=75AA49B421B5A4EB6F3C207636FED47095B332D0</t>
+          <t>https://www.adzuna.in/land/ad/5876027463?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=40F66C80D240EB217C5AF3C758F1793D002D574F</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2d2a6d873d</t>
+          <t>91af896417</t>
         </is>
       </c>
     </row>
@@ -3704,22 +3704,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Specialist</t>
+          <t>Artificial Intelligence Engineer 2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ITC Infotech</t>
+          <t>Frinks AI</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>artificial intelligence, india (place)</t>
+          <t>artificial intelligence, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876024946?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=6D480BEF34A3386CBC920920C7CE13B96BCBAD34</t>
+          <t>https://www.adzuna.in/land/ad/5876025062?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=75AA49B421B5A4EB6F3C207636FED47095B332D0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>140496e40b</t>
+          <t>2d2a6d873d</t>
         </is>
       </c>
     </row>
@@ -3770,17 +3770,17 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Artificial Intelligence Specialist</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tech Mahindra</t>
+          <t>ITC Infotech</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>artificial intelligence, bangalore (place)</t>
+          <t>artificial intelligence, india (place)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876026586?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=666546215EA3297D7CF61A793A40232CBB0EC67B</t>
+          <t>https://www.adzuna.in/land/ad/5876024946?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=6D480BEF34A3386CBC920920C7CE13B96BCBAD34</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>25604d55ae</t>
+          <t>140496e40b</t>
         </is>
       </c>
     </row>
@@ -3826,22 +3826,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Data and AI Scientist</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>The Edge Partnership - The Edge in Asia</t>
+          <t>Tech Mahindra</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ai, hyderabad (place)</t>
+          <t>artificial intelligence, bangalore (place)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5876025532?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AD1D30D29AD931A0AA847E54CFF303EEB0007BE9</t>
+          <t>https://www.adzuna.in/land/ad/5876026586?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=666546215EA3297D7CF61A793A40232CBB0EC67B</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>bc9357c4ff</t>
+          <t>25604d55ae</t>
         </is>
       </c>
     </row>
@@ -3887,52 +3887,52 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AI Response Evaluator</t>
+          <t>Data and AI Scientist</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>iMerit</t>
+          <t>The Edge Partnership - The Edge in Asia</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>All Other Remote, Contract</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/imerit-ai-response-evaluator</t>
+          <t>https://www.adzuna.in/land/ad/5876025532?se=ekY8_tOr8RG3WNj7uUI8Mw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AD1D30D29AD931A0AA847E54CFF303EEB0007BE9</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>d4b5bc7818</t>
+          <t>bc9357c4ff</t>
         </is>
       </c>
     </row>
@@ -3948,37 +3948,37 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sustainability Full-Stack Developer (100 % remote) (m/f/d)</t>
+          <t>AI Response Evaluator</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EWOR GmbH</t>
+          <t>iMerit</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>fullstack (tag), developer, software (tag), engineer (tag), worldwide (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Fullstack-Development, Web-Development, Sustainability, Software-Engineer, Sustainability-Technology, Remote-Senior-Full-Stack-Developer, Remote-Full-Stack-Developer, Full-Stack-Developer, Senior</t>
+          <t>All Other Remote, Contract</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ewor-gmbh/jobs/sustainability-full-stack-developer-100-remote-m-f-d</t>
+          <t>https://weworkremotely.com/remote-jobs/imerit-ai-response-evaluator</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>7da6fdc2ab</t>
+          <t>d4b5bc7818</t>
         </is>
       </c>
     </row>
@@ -4009,12 +4009,12 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Industrial Tech AgentOps Engineer (100 % remote) (m/f/d)</t>
+          <t>Sustainability Full-Stack Developer (100 % remote) (m/f/d)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>engineer, devops (tag), worldwide (place)</t>
+          <t>fullstack (tag), developer, software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>AgentOps-Engineer, Industrial-Technology, Operations-Engineering, Technical-Product-Management, Start-Up-Operations, Remote-Operations-Engineer, Industrial-IoT-Engineer, Remote-DevOps-Engineer, TechOps-Engineer, Remote-Infrastructure-Monitoring-Engineer, Remote-Distributed-Systems-Engineer-II, Mid-level</t>
+          <t>Fullstack-Development, Web-Development, Sustainability, Software-Engineer, Sustainability-Technology, Remote-Senior-Full-Stack-Developer, Remote-Full-Stack-Developer, Full-Stack-Developer, Senior</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ewor-gmbh/jobs/industrial-tech-agentops-engineer-100-remote-m-f-d</t>
+          <t>https://himalayas.app/companies/ewor-gmbh/jobs/sustainability-full-stack-developer-100-remote-m-f-d</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>cedc8889fb</t>
+          <t>7da6fdc2ab</t>
         </is>
       </c>
     </row>
@@ -4066,56 +4066,56 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AI Response Analyst</t>
+          <t>Industrial Tech AgentOps Engineer (100 % remote) (m/f/d)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>iMerit Technology</t>
+          <t>EWOR GmbH</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>engineer, devops (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>content writing, quality assurance, ai</t>
+          <t>AgentOps-Engineer, Industrial-Technology, Operations-Engineering, Technical-Product-Management, Start-Up-Operations, Remote-Operations-Engineer, Industrial-IoT-Engineer, Remote-DevOps-Engineer, TechOps-Engineer, Remote-Infrastructure-Monitoring-Engineer, Remote-Distributed-Systems-Engineer-II, Mid-level</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-ai-response-analyst-imerit-technology-1137309</t>
+          <t>https://himalayas.app/companies/ewor-gmbh/jobs/industrial-tech-agentops-engineer-100-remote-m-f-d</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>05cb840193</t>
+          <t>cedc8889fb</t>
         </is>
       </c>
     </row>
@@ -4127,58 +4127,56 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>30</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AI Response Analyst</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>iMerit Technology</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Not listed</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>remoteok</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>content writing, quality assurance, ai</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="C61" t="n">
-        <v>57</v>
-      </c>
-      <c r="D61" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Python Backend Engineer (m/f/x)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Makersite</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Worldwide</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>himalayas</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>developer (tag), software (tag), engineer, backend, python, api (tag), worldwide (place)</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Python-Backend-Engineering, Backend-Development, Software-Engineer, API-Development, Python-Engineering, Python-Backend-Engineer, Python-Backend-Developer, Senior-Backend-Python-Developer, Senior-Python-Backend-Developer, Backend-Engineer, Product-Backend-Engineer, Backend-Services-Engineer, Senior</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/makersite/jobs/python-backend-engineer-m-f-x</t>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-response-analyst-imerit-technology-1137309</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>3eb1e889db</t>
+          <t>05cb840193</t>
         </is>
       </c>
     </row>
@@ -4194,19 +4192,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Python Backend Engineer (m/f/x)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>S-PRO</t>
+          <t>Makersite</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4221,12 +4219,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>software (tag), engineer, backend (tag), python, cloud (tag), aws (tag), worldwide (place)</t>
+          <t>developer (tag), software (tag), engineer, backend, python, api (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Python-Engineering, Backend-Development, AWS-Cloud-Development, Serverless-Development, Software-Engineer, Python-Engineer, Python-Software-Engineer, Mid-level</t>
+          <t>Python-Backend-Engineering, Backend-Development, Software-Engineer, API-Development, Python-Engineering, Python-Backend-Engineer, Python-Backend-Developer, Senior-Backend-Python-Developer, Senior-Python-Backend-Developer, Backend-Engineer, Product-Backend-Engineer, Backend-Services-Engineer, Senior</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4236,12 +4234,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/s-pro/jobs/python-engineer</t>
+          <t>https://himalayas.app/companies/makersite/jobs/python-backend-engineer-m-f-x</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>67bda4c374</t>
+          <t>3eb1e889db</t>
         </is>
       </c>
     </row>
@@ -4257,19 +4255,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Daymark Health</t>
+          <t>S-PRO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4284,12 +4282,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), worldwide (place)</t>
+          <t>software (tag), engineer, backend (tag), python, cloud (tag), aws (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Software-Engineer, Healthcare-Technology, Backend-Engineering, Fullstack-Development, Health-Tech, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Developer, Mid-level</t>
+          <t>Python-Engineering, Backend-Development, AWS-Cloud-Development, Serverless-Development, Software-Engineer, Python-Engineer, Python-Software-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4299,12 +4297,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/daymark-health/jobs/software-engineer</t>
+          <t>https://himalayas.app/companies/s-pro/jobs/python-engineer</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>85c899deaf</t>
+          <t>67bda4c374</t>
         </is>
       </c>
     </row>
@@ -4316,56 +4314,58 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>84</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Specialist, Data Science &amp; Artificial Intelligence</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Daymark Health</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>artificial intelligence, data science, india (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>Software-Engineer, Healthcare-Technology, Backend-Engineering, Fullstack-Development, Health-Tech, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5871846075?se=oI2O_Sup8RGogquEo3zAlQ&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=326B6FA659B880A3C0F3E2CA4AB8E0734BF69D7B</t>
+          <t>https://himalayas.app/companies/daymark-health/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>c1e8559189</t>
+          <t>85c899deaf</t>
         </is>
       </c>
     </row>
@@ -4381,39 +4381,37 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>50</v>
-      </c>
-      <c r="D65" t="n">
-        <v>2</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Specialist, Data Science &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>xneelo</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), devops (tag), worldwide (place)</t>
+          <t>artificial intelligence, data science, india (place)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Software-Engineer, Backend-Development, Fullstack-Development, Infrastructure-Engineering, DevOps, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Senior</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4423,12 +4421,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/xneelo-co/jobs/software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5871846075?se=oI2O_Sup8RGogquEo3zAlQ&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=326B6FA659B880A3C0F3E2CA4AB8E0734BF69D7B</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>679e1ed2b3</t>
+          <t>c1e8559189</t>
         </is>
       </c>
     </row>
@@ -4444,39 +4442,39 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AEM Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vonage</t>
+          <t>xneelo</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>developer, devops (tag), anywhere (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), devops (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Software-Engineer, Backend-Development, Fullstack-Development, Infrastructure-Engineering, DevOps, Software-Engineer-Developer, Software-Developer, IT-Software-Engineer, Software-Engineer-Jobs, Engineering-Software-Developer, Software-Systems-Engineer, Software-Engineering-Jobs, Senior</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4486,12 +4484,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/vonage-aem-developer</t>
+          <t>https://himalayas.app/companies/xneelo-co/jobs/software-engineer</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>9b191a3075</t>
+          <t>679e1ed2b3</t>
         </is>
       </c>
     </row>
@@ -4507,37 +4505,39 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>27</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Video Annotation Expert</t>
+          <t>AEM Developer</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Vonage</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ai (tag), worldwide (place)</t>
+          <t>developer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Video-Annotator, Video-Annotation, Media-Annotation-Specialist, Video-Data-Annotation, Annotation-Specialist, Data-Annotation-Expert, AI-Annotation-Specialist, Content-Annotation-Specialist, Entry-level, Mid-level</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/video-annotation-expert-4408176807</t>
+          <t>https://weworkremotely.com/remote-jobs/vonage-aem-developer</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>1b02a267ff</t>
+          <t>9b191a3075</t>
         </is>
       </c>
     </row>
@@ -4564,56 +4564,56 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Subject Matter Expert - Computer Science and Artificial Intelligence</t>
+          <t>Video Annotation Expert</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sultan Chand &amp; Sons Ltd</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>artificial intelligence, noida (place)</t>
+          <t>ai (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Video-Annotator, Video-Annotation, Media-Annotation-Specialist, Video-Data-Annotation, Annotation-Specialist, Data-Annotation-Expert, AI-Annotation-Specialist, Content-Annotation-Specialist, Entry-level, Mid-level</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5869558953?se=ji27_Tqo8RGDXZRVG-VeHA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=41B18BB78E05B29C6C90DA595F6A5EBB3EFE4072</t>
+          <t>https://himalayas.app/companies/micro1/jobs/video-annotation-expert-4408176807</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>91b1f60d0c</t>
+          <t>1b02a267ff</t>
         </is>
       </c>
     </row>
@@ -4629,37 +4629,37 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Software engineer</t>
+          <t>Subject Matter Expert - Computer Science and Artificial Intelligence</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sticker Mule</t>
+          <t>Sultan Chand &amp; Sons Ltd</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>software engineer, typescript (tag), golang (tag), react (tag), global (place)</t>
+          <t>artificial intelligence, noida (place)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Development, react,typescript,golang,graphql,english</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1833624/</t>
+          <t>https://www.adzuna.in/land/ad/5869558953?se=ji27_Tqo8RGDXZRVG-VeHA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=41B18BB78E05B29C6C90DA595F6A5EBB3EFE4072</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>c557da3996</t>
+          <t>91b1f60d0c</t>
         </is>
       </c>
     </row>
@@ -4686,56 +4686,56 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer 3D Developer (remote part/full time)</t>
+          <t>Software engineer</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Imnoo AG</t>
+          <t>Sticker Mule</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>machine learning, developer, engineer, ai, ml (tag), worldwide (place)</t>
+          <t>software engineer, typescript (tag), golang (tag), react (tag), global (place)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>AI-Machine-Learning-Engineering, 3D-Development, Computer-Vision, AI-Manufacturing, CAD-Development, Remote-Machine-Learning-Engineer, Remote-Senior-AI-Engineer, Remote-AI-Engineer, AI-ML-Engineer, Lead-AI-ML-Engineer, Machine-Learning-Engineer, Senior</t>
+          <t>Development, react,typescript,golang,graphql,english</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/imnoo-ag/jobs/ai-machine-learning-engineer-3d-developer-remote-part-full-time</t>
+          <t>https://www.workingnomads.com/job/go/1833624/</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>a84b2b9b96</t>
+          <t>c557da3996</t>
         </is>
       </c>
     </row>
@@ -4751,37 +4751,37 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>AI Machine Learning Engineer 3D Developer (remote part/full time)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sustainability Economics.ai</t>
+          <t>Imnoo AG</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>machine learning, intern (level), bangalore (place)</t>
+          <t>machine learning, developer, engineer, ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Machine-Learning-Engineering, 3D-Development, Computer-Vision, AI-Manufacturing, CAD-Development, Remote-Machine-Learning-Engineer, Remote-Senior-AI-Engineer, Remote-AI-Engineer, AI-ML-Engineer, Lead-AI-ML-Engineer, Machine-Learning-Engineer, Senior</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5868794497?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C97284B10F6321E0988BF83E6C1B8DFD30952F6C</t>
+          <t>https://himalayas.app/companies/imnoo-ag/jobs/ai-machine-learning-engineer-3d-developer-remote-part-full-time</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>05411f661c</t>
+          <t>a84b2b9b96</t>
         </is>
       </c>
     </row>
@@ -4812,17 +4812,17 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Machine Learning II</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Sustainability Economics.ai</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>machine learning, qa (tag), bangalore (place)</t>
+          <t>machine learning, intern (level), bangalore (place)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Scientific &amp; QA Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5868154123?se=SoAubXKn8RGZGp_UbifwCA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2A76050FF86A705EC1E71FEE64DFE517445586F0</t>
+          <t>https://www.adzuna.in/land/ad/5868794497?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C97284B10F6321E0988BF83E6C1B8DFD30952F6C</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>520f876dc1</t>
+          <t>05411f661c</t>
         </is>
       </c>
     </row>
@@ -4873,22 +4873,22 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>Machine Learning II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4898,27 +4898,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>machine learning, qa (tag), bangalore (place)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5852477157?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C196DCD121C33E5FA7A7F99C735E078C53777A1E</t>
+          <t>https://www.adzuna.in/land/ad/5868154123?se=SoAubXKn8RGZGp_UbifwCA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2A76050FF86A705EC1E71FEE64DFE517445586F0</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>dab94fe012</t>
+          <t>520f876dc1</t>
         </is>
       </c>
     </row>
@@ -4934,54 +4934,52 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>46</v>
-      </c>
-      <c r="D74" t="n">
-        <v>2</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Data Scientist - Inference, Community Support</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>data scientist, anywhere (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/airbnb-data-scientist-inference-community-support</t>
+          <t>https://www.adzuna.in/land/ad/5852477157?se=0g_cQaGn8RGzEp-eIl8cbw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C196DCD121C33E5FA7A7F99C735E078C53777A1E</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>18eaeb9d4e</t>
+          <t>dab94fe012</t>
         </is>
       </c>
     </row>
@@ -4997,54 +4995,54 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Frontend Engineer Specialist</t>
+          <t>Data Scientist - Inference, Community Support</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>developer (tag), frontend, software (tag), engineer, react (tag), worldwide (place)</t>
+          <t>data scientist, anywhere (place)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Frontend-Engineer, Web-Frontend-Engineer, Front-End-Software-Engineer, Frontend-Web-Software-Engineer, Front-End-Developer, React-Frontend-Engineer, UI-Frontend-Developer, Mid-level</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/frontend-engineer-specialist</t>
+          <t>https://weworkremotely.com/remote-jobs/airbnb-data-scientist-inference-community-support</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>ee1605c3a3</t>
+          <t>18eaeb9d4e</t>
         </is>
       </c>
     </row>
@@ -5056,56 +5054,58 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>44</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Frontend Engineer Specialist</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>himalayas</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>developer (tag), frontend, software (tag), engineer, react (tag), worldwide (place)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Frontend-Engineer, Web-Frontend-Engineer, Front-End-Software-Engineer, Frontend-Web-Software-Engineer, Front-End-Developer, React-Frontend-Engineer, UI-Frontend-Developer, Mid-level</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="C76" t="n">
-        <v>86</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; NLP Expert</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Synthenova</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>machine learning, nlp, qa (tag), india (place)</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Scientific &amp; QA Jobs</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864426193?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FA0DA9F5539A8E98A42507C72E66BEA28EFB5F71</t>
+          <t>https://himalayas.app/companies/micro1/jobs/frontend-engineer-specialist</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>06a6232301</t>
+          <t>ee1605c3a3</t>
         </is>
       </c>
     </row>
@@ -5121,22 +5121,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning &amp; NLP Expert</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HT Digital Streams</t>
+          <t>Synthenova</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Delhi, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>data scientist, india (place), delhi (place)</t>
+          <t>machine learning, nlp, qa (tag), india (place)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5161,12 +5161,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427594?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1379BD61E95509405A372328EE4CB12520438AC9</t>
+          <t>https://www.adzuna.in/land/ad/5864426193?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FA0DA9F5539A8E98A42507C72E66BEA28EFB5F71</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>e77b0725ce</t>
+          <t>06a6232301</t>
         </is>
       </c>
     </row>
@@ -5182,52 +5182,52 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>HeadSpin</t>
+          <t>HT Digital Streams</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Delhi, India</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>software engineer, fullstack (tag), developer (tag), backend (tag), associate (level), worldwide (place)</t>
+          <t>data scientist, india (place), delhi (place)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Engineering, Software-Engineer, Associate-Software-Engineer, Backend-Development, Fullstack-Development, Software-Engineering-Associate, Associate-Software-Developer, Software-Developer-Associate, Associate-Engineer, Associate-Platform-Engineer, Associate-Application-Developer, Associate-Systems-Engineer, Developer, Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/headspin/jobs/associate-software-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5864427594?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1379BD61E95509405A372328EE4CB12520438AC9</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>ed41465dce</t>
+          <t>e77b0725ce</t>
         </is>
       </c>
     </row>
@@ -5243,52 +5243,52 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Consultant</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>HeadSpin</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>artificial intelligence, noida (place)</t>
+          <t>software engineer, fullstack (tag), developer (tag), backend (tag), associate (level), worldwide (place)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>HR &amp; Recruitment Jobs</t>
+          <t>Engineering, Software-Engineer, Associate-Software-Engineer, Backend-Development, Fullstack-Development, Software-Engineering-Associate, Associate-Software-Developer, Software-Developer-Associate, Associate-Engineer, Associate-Platform-Engineer, Associate-Application-Developer, Associate-Systems-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864432717?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=616D5B872E024B0E271B6E107D9B24261D8C3B7A</t>
+          <t>https://himalayas.app/companies/headspin/jobs/associate-software-engineer</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>90b00c6445</t>
+          <t>ed41465dce</t>
         </is>
       </c>
     </row>
@@ -5306,22 +5306,20 @@
       <c r="C80" t="n">
         <v>50</v>
       </c>
-      <c r="D80" t="n">
-        <v>3</v>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Machine Learning Specialist</t>
+          <t>Artificial Intelligence Consultant</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bandhan Technologies</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5331,27 +5329,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>machine learning, bangalore (place)</t>
+          <t>artificial intelligence, noida (place)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>HR &amp; Recruitment Jobs</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867037827?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=81D91604A259EFB724EEF9EE68D3642F93D7C52A</t>
+          <t>https://www.adzuna.in/land/ad/5864432717?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=616D5B872E024B0E271B6E107D9B24261D8C3B7A</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>55af0af08c</t>
+          <t>90b00c6445</t>
         </is>
       </c>
     </row>
@@ -5367,19 +5365,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D81" t="n">
         <v>3</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Data Science Specialist</t>
+          <t>Machine Learning Specialist</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Polestar Analytics</t>
+          <t>Bandhan Technologies</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5394,7 +5392,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>data science, bangalore (place)</t>
+          <t>machine learning, bangalore (place)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5404,17 +5402,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864434859?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BE53F35ACA83BD29D328C8745F27CF70F132F879</t>
+          <t>https://www.adzuna.in/land/ad/5867037827?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=81D91604A259EFB724EEF9EE68D3642F93D7C52A</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>620816c318</t>
+          <t>55af0af08c</t>
         </is>
       </c>
     </row>
@@ -5432,20 +5430,22 @@
       <c r="C82" t="n">
         <v>49</v>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="n">
+        <v>3</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Data Science Instructor - Learning Centre</t>
+          <t>Data Science Specialist</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Polestar Analytics</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>data science, bangalore (place)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867037765?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CCE3B589087C9AE3C6FD3C72DD92F3B9146F772F</t>
+          <t>https://www.adzuna.in/land/ad/5864434859?se=YsqS2num8RG8RN41HFlqJw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BE53F35ACA83BD29D328C8745F27CF70F132F879</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>5ae3a66648</t>
+          <t>620816c318</t>
         </is>
       </c>
     </row>
@@ -5496,17 +5496,17 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Science Instructor - Learning Centre</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Infosys Finacle</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867270149?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=284AB41CD26DD62DA43E2E7866A4F2E72052CFA3</t>
+          <t>https://www.adzuna.in/land/ad/5867037765?se=DBSWpdem8RGPo_VrC6plTg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CCE3B589087C9AE3C6FD3C72DD92F3B9146F772F</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>b9e7b78c99</t>
+          <t>5ae3a66648</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Servify</t>
+          <t>Infosys Finacle</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5867265604?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=98C25A013410B0B492855DE45F67FF3409A45C24</t>
+          <t>https://www.adzuna.in/land/ad/5867270149?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=284AB41CD26DD62DA43E2E7866A4F2E72052CFA3</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>339ea3cd4c</t>
+          <t>b9e7b78c99</t>
         </is>
       </c>
     </row>
@@ -5613,37 +5613,37 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CEO, AI Finance</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bjak</t>
+          <t>Servify</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/bjak/jobs/ceo-ai-finance-7034716418</t>
+          <t>https://www.adzuna.in/land/ad/5867265604?se=APJ3igKn8RG27ZP6oeG79w&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=98C25A013410B0B492855DE45F67FF3409A45C24</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>8e23b34067</t>
+          <t>339ea3cd4c</t>
         </is>
       </c>
     </row>
@@ -5674,17 +5674,17 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Accounting Automation Engineer</t>
+          <t>CEO, AI Finance</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spotter Labs</t>
+          <t>Bjak</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>automation, software (tag), engineer, worldwide (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Accounting-Automation-Engineer, Finance-Automation-Engineer, Accounting-Software-Engineer, Accounting-Automation, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3984977259</t>
+          <t>https://himalayas.app/companies/bjak/jobs/ceo-ai-finance-7034716418</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>c570969de5</t>
+          <t>8e23b34067</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Accounting-Automation-Engineer, Accounting, Process-Automation, Financial-Automation, Business-Systems, Finance-Automation-Engineer, Accounting-Software-Engineer, Automation-Engineer, Accounting-Automation, Software-Automation-Engineer, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
+          <t>Accounting-Automation-Engineer, Finance-Automation-Engineer, Accounting-Software-Engineer, Accounting-Automation, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3943339358</t>
+          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3984977259</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>13edcbb44e</t>
+          <t>c570969de5</t>
         </is>
       </c>
     </row>
@@ -5796,37 +5796,37 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Backend Engineer - Platform - Stacks | Ireland | Remote</t>
+          <t>Accounting Automation Engineer</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grafana Labs</t>
+          <t>Spotter Labs</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>engineer, backend, anywhere (place)</t>
+          <t>automation, software (tag), engineer, worldwide (place)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Accounting-Automation-Engineer, Accounting, Process-Automation, Financial-Automation, Business-Systems, Finance-Automation-Engineer, Accounting-Software-Engineer, Automation-Engineer, Accounting-Automation, Software-Automation-Engineer, Finance-Automation-Specialist, Accounting-Software-Engineering, Mid-level</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/grafana-labs-backend-engineer-platform-stacks-ireland-remote</t>
+          <t>https://himalayas.app/companies/spotter-labs/jobs/accounting-automation-engineer-3943339358</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>7aae615c8c</t>
+          <t>13edcbb44e</t>
         </is>
       </c>
     </row>
@@ -5857,37 +5857,37 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>STEM Expert</t>
+          <t>Backend Engineer - Platform - Stacks | Ireland | Remote</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Grafana Labs</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ai (tag), worldwide (place)</t>
+          <t>engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>STEM-Expert, STEM-Specialist, STEM-Consultant, STEM-Domain-Expert, STEM-Researcher, STEM-Educator, STEM-AI-Specialist, Japanese-STEM-Specialist, STEM-Advisor, STEM-Instructor, Mid-level</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/stem-expert-40695367</t>
+          <t>https://weworkremotely.com/remote-jobs/grafana-labs-backend-engineer-platform-stacks-ireland-remote</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>9cb40c45fc</t>
+          <t>7aae615c8c</t>
         </is>
       </c>
     </row>
@@ -5918,14 +5918,12 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>21</v>
-      </c>
-      <c r="D90" t="n">
-        <v>3</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Excel Specialist</t>
+          <t>STEM Expert</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5945,12 +5943,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>automation (tag), developer (tag), worldwide (place)</t>
+          <t>ai (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Excel-Specialist, Excel-Expert, Spreadsheet-Specialist, Excel-Automation-Specialist, Excel-Data-Analyst, Microsoft-Excel-Developer, Microsoft-Office-Specialist, Microsoft-Excel-Development, Entry-level, Mid-level</t>
+          <t>STEM-Expert, STEM-Specialist, STEM-Consultant, STEM-Domain-Expert, STEM-Researcher, STEM-Educator, STEM-AI-Specialist, Japanese-STEM-Specialist, STEM-Advisor, STEM-Instructor, Mid-level</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5960,12 +5958,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/excel-specialist-2996931708</t>
+          <t>https://himalayas.app/companies/micro1/jobs/stem-expert-40695367</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>fddf243627</t>
+          <t>9cb40c45fc</t>
         </is>
       </c>
     </row>
@@ -5977,56 +5975,58 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>69</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="D91" t="n">
+        <v>3</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>Excel Specialist</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ISIR AI</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Noida, Ghaziabad</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>data science, qa (tag), intern (level), noida (place)</t>
+          <t>automation (tag), developer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Scientific &amp; QA Jobs</t>
+          <t>Excel-Specialist, Excel-Expert, Spreadsheet-Specialist, Excel-Automation-Specialist, Excel-Data-Analyst, Microsoft-Excel-Developer, Microsoft-Office-Specialist, Microsoft-Excel-Development, Entry-level, Mid-level</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864427080?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C509B9B88F855FA7348A37AF1CDF8C3ECC7CA889</t>
+          <t>https://himalayas.app/companies/micro1/jobs/excel-specialist-2996931708</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>84896ab3c6</t>
+          <t>fddf243627</t>
         </is>
       </c>
     </row>
@@ -6042,22 +6042,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FRND</t>
+          <t>ISIR AI</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Ghaziabad</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>machine learning, intern (level), bangalore (place)</t>
+          <t>data science, qa (tag), intern (level), noida (place)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Scientific &amp; QA Jobs</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864424613?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9B60872885E8C7073FE0CC2A962D44A1E48845F7</t>
+          <t>https://www.adzuna.in/land/ad/5864427080?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C509B9B88F855FA7348A37AF1CDF8C3ECC7CA889</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>e00b96a707</t>
+          <t>84896ab3c6</t>
         </is>
       </c>
     </row>
@@ -6103,22 +6103,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Intern (Data Science)</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Yubi</t>
+          <t>FRND</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>data science, intern (level), chennai (place)</t>
+          <t>machine learning, intern (level), bangalore (place)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864443163?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4554D5357B8D35F06907356F0816FBF3BD2BBC7E</t>
+          <t>https://www.adzuna.in/land/ad/5864424613?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9B60872885E8C7073FE0CC2A962D44A1E48845F7</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>93516db46a</t>
+          <t>e00b96a707</t>
         </is>
       </c>
     </row>
@@ -6164,37 +6164,37 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AI Inference Engineer QVAC (100% remote Worldwide)</t>
+          <t>Intern (Data Science)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tether Operations Limited</t>
+          <t>Yubi</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>software (tag), engineer, ai, worldwide (place)</t>
+          <t>data science, intern (level), chennai (place)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Software-Engineer, AI-Engineering, Machine-Learning-Engineering, C-Development, Edge-AI, AI-Inference-Engineer, Remote-AI-Engineer, Remote-Machine-Learning-Engineer, Senior-AI-Inference-Engineer, Remote-Senior-AI-Engineer, Senior</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/tether-operations-limited/jobs/ai-inference-engineer-qvac-100-remote-worldwide</t>
+          <t>https://www.adzuna.in/land/ad/5864443163?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4554D5357B8D35F06907356F0816FBF3BD2BBC7E</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>f7f40ca44a</t>
+          <t>93516db46a</t>
         </is>
       </c>
     </row>
@@ -6225,37 +6225,37 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Machine Learning Gen AI_Hyderabad,Pune &amp; Bangalore</t>
+          <t>AI Inference Engineer QVAC (100% remote Worldwide)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services</t>
+          <t>Tether Operations Limited</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>machine learning, hyderabad (place)</t>
+          <t>software (tag), engineer, ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Software-Engineer, AI-Engineering, Machine-Learning-Engineering, C-Development, Edge-AI, AI-Inference-Engineer, Remote-AI-Engineer, Remote-Machine-Learning-Engineer, Senior-AI-Inference-Engineer, Remote-Senior-AI-Engineer, Senior</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6265,12 +6265,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439281?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1F39144C3030195205A212339590BB508623F064</t>
+          <t>https://himalayas.app/companies/tether-operations-limited/jobs/ai-inference-engineer-qvac-100-remote-worldwide</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>55fce19c46</t>
+          <t>f7f40ca44a</t>
         </is>
       </c>
     </row>
@@ -6286,17 +6286,17 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Gen AI_Hyderabad,Pune &amp; Bangalore</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Infosys Consulting</t>
+          <t>Tata Consultancy Services</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>data scientist, hyderabad (place)</t>
+          <t>machine learning, hyderabad (place)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864428905?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4E35D1AC081FE279803556ECA4C1E1871550877F</t>
+          <t>https://www.adzuna.in/land/ad/5864439281?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1F39144C3030195205A212339590BB508623F064</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>af7ebeb057</t>
+          <t>55fce19c46</t>
         </is>
       </c>
     </row>
@@ -6349,9 +6349,7 @@
       <c r="C97" t="n">
         <v>49</v>
       </c>
-      <c r="D97" t="n">
-        <v>2</v>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Data Scientist</t>
@@ -6359,12 +6357,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>super.money</t>
+          <t>Infosys Consulting</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6374,7 +6372,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, hyderabad (place)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6389,12 +6387,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864425941?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BF9A171BDEA00E60475790836A0A3589FB8D9EB6</t>
+          <t>https://www.adzuna.in/land/ad/5864428905?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4E35D1AC081FE279803556ECA4C1E1871550877F</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>4f1a679ea3</t>
+          <t>af7ebeb057</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6410,9 @@
       <c r="C98" t="n">
         <v>49</v>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>Data Scientist</t>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lufthansa Technik Services India Pvt Ltd</t>
+          <t>super.money</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864422634?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
+          <t>https://www.adzuna.in/land/ad/5864425941?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=BF9A171BDEA00E60475790836A0A3589FB8D9EB6</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>c86fa3dfe3</t>
+          <t>4f1a679ea3</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank</t>
+          <t>Lufthansa Technik Services India Pvt Ltd</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Engineering Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439103?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=73CFB6E1B4115AA2A23A99B0EC8886521BA01450</t>
+          <t>https://www.adzuna.in/land/ad/5864422634?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=8B699C55D05CD19C7E5E94BCDEC3F919911CC092</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>08622a68ed</t>
+          <t>c86fa3dfe3</t>
         </is>
       </c>
     </row>
@@ -6537,17 +6537,17 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Navi</t>
+          <t>Kotak Mahindra Bank</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Engineering Jobs</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6572,12 +6572,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864439226?se=jiNNTDmm8RGUNa3mkcr13g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=744BE785510320885EE5287D6F2FE8E098FAED30</t>
+          <t>https://www.adzuna.in/land/ad/5864439103?se=lBayFRKm8RGz9foQI_J8zA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=73CFB6E1B4115AA2A23A99B0EC8886521BA01450</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>4e1bb30522</t>
+          <t>08622a68ed</t>
         </is>
       </c>
     </row>
@@ -6598,17 +6598,17 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tricog Health</t>
+          <t>Navi</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6628,17 +6628,17 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5865291446?se=pmQW9lOm8RGs-Y02KTQxmA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=A9D77535171E8EAD7E7898B67A7ADC8ED3D07410</t>
+          <t>https://www.adzuna.in/land/ad/5864439226?se=jiNNTDmm8RGUNa3mkcr13g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=744BE785510320885EE5287D6F2FE8E098FAED30</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>eaec37f6c0</t>
+          <t>4e1bb30522</t>
         </is>
       </c>
     </row>
@@ -6654,54 +6654,52 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>41</v>
-      </c>
-      <c r="D102" t="n">
-        <v>3</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Remote - Automation QA Engineer (Core Team)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Torrero</t>
+          <t>Tricog Health</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>automation, software (tag), engineer, testing (tag), qa, worldwide (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>QA-Engineer, QA-Automation-Engineer, Software-Testing, Quality-Assurance, Manual-Testing, Remote-Test-Automation-Engineer, Remote-QA-Engineer, Remote-Quality-Assurance-Engineer, Remote-UI-Automation-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/torrero/jobs/remote-automation-qa-engineer-core-team</t>
+          <t>https://www.adzuna.in/land/ad/5865291446?se=pmQW9lOm8RGs-Y02KTQxmA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=A9D77535171E8EAD7E7898B67A7ADC8ED3D07410</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>f03380c71d</t>
+          <t>eaec37f6c0</t>
         </is>
       </c>
     </row>
@@ -6717,17 +6715,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>36</v>
-      </c>
-      <c r="D103" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="D103" t="n">
+        <v>3</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Front-End Developer</t>
+          <t>Remote - Automation QA Engineer (Core Team)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talent Sam</t>
+          <t>Torrero</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>developer, frontend (tag), engineer (tag), react (tag), worldwide (place)</t>
+          <t>automation, software (tag), engineer, testing (tag), qa, worldwide (place)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Frontend-Development, Web-Development, UI-Developer, Frontend-Engineer, Front-End-Developer, Frontend-React-Developer, UI-Frontend-Developer, UX-UI-Front-End-Developer, React-Frontend-Developer, Frontend-Web-Development, Developer, Mid-level</t>
+          <t>QA-Engineer, QA-Automation-Engineer, Software-Testing, Quality-Assurance, Manual-Testing, Remote-Test-Automation-Engineer, Remote-QA-Engineer, Remote-Quality-Assurance-Engineer, Remote-UI-Automation-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/talent-sam/jobs/front-end-developer</t>
+          <t>https://himalayas.app/companies/torrero/jobs/remote-automation-qa-engineer-core-team</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>94d5af612e</t>
+          <t>f03380c71d</t>
         </is>
       </c>
     </row>
@@ -6778,37 +6778,37 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>E-learning Developer</t>
+          <t>Front-End Developer</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VineGarden Films</t>
+          <t>Talent Sam</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>developer, india (place)</t>
+          <t>developer, frontend (tag), engineer (tag), react (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Teaching Jobs</t>
+          <t>Frontend-Development, Web-Development, UI-Developer, Frontend-Engineer, Front-End-Developer, Frontend-React-Developer, UI-Frontend-Developer, UX-UI-Front-End-Developer, React-Frontend-Developer, Frontend-Web-Development, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5864153573?se=SvkgT-Wl8RGUGK7L4gkIgg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FDDF0A4236DF3E6D3081AF93B01799D77599EAD1</t>
+          <t>https://himalayas.app/companies/talent-sam/jobs/front-end-developer</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>248ef46714</t>
+          <t>94d5af612e</t>
         </is>
       </c>
     </row>
@@ -6835,21 +6835,21 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Data Scientist - Python Deterministic Analytics</t>
+          <t>E-learning Developer</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Capco</t>
+          <t>VineGarden Films</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6864,27 +6864,27 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>data scientist, python, india (place)</t>
+          <t>developer, india (place)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Teaching Jobs</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139747?se=olLfvDql8RGL6NrjcRaTpw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9FA82041CC2CC98F084D6827CF82DA2BE289D998</t>
+          <t>https://www.adzuna.in/land/ad/5864153573?se=SvkgT-Wl8RGUGK7L4gkIgg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=FDDF0A4236DF3E6D3081AF93B01799D77599EAD1</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>6f1952e273</t>
+          <t>248ef46714</t>
         </is>
       </c>
     </row>
@@ -6900,22 +6900,22 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - APAC</t>
+          <t>Data Scientist - Python Deterministic Analytics</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional®</t>
+          <t>Capco</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>data scientist, python, india (place)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6935,17 +6935,17 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5862635702?se=9gaugPCk8RGcfKYe_cIpvA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=53D4DF556D646C5F462C8F3FC782D72E8A35D08B</t>
+          <t>https://www.adzuna.in/land/ad/5837139747?se=olLfvDql8RGL6NrjcRaTpw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=9FA82041CC2CC98F084D6827CF82DA2BE289D998</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>d395f3a907</t>
+          <t>6f1952e273</t>
         </is>
       </c>
     </row>
@@ -6961,52 +6961,52 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AI Engineer Data APIs</t>
+          <t>Machine Learning Engineer - APAC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>LexisNexis Legal &amp; Professional®</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>engineer, golang (tag), ai</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>golang, video, engineer</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-ai-engineer-data-apis-benzinga-1137224</t>
+          <t>https://www.adzuna.in/land/ad/5862635702?se=9gaugPCk8RGcfKYe_cIpvA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=53D4DF556D646C5F462C8F3FC782D72E8A35D08B</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>1261a5bcd5</t>
+          <t>d395f3a907</t>
         </is>
       </c>
     </row>
@@ -7022,52 +7022,52 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Agentic Python Engineer</t>
+          <t>AI Engineer Data APIs</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Evaboot</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>WORLDWIDE</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>engineer, python, aws (tag), worldwide (place)</t>
+          <t>engineer, golang (tag), ai</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Development, python,engineer,aws,analytics,seo</t>
+          <t>golang, video, engineer</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1826864/</t>
+          <t>https://remoteOK.com/remote-jobs/remote-ai-engineer-data-apis-benzinga-1137224</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>47ae63b1d0</t>
+          <t>1261a5bcd5</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
@@ -7098,22 +7098,22 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>WORLDWIDE</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>engineer, python, anywhere (place)</t>
+          <t>engineer, python, aws (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Development, python,engineer,aws,analytics,seo</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/evaboot-agentic-python-engineer</t>
+          <t>https://www.workingnomads.com/job/go/1826864/</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>d94554bfc7</t>
+          <t>47ae63b1d0</t>
         </is>
       </c>
     </row>
@@ -7140,56 +7140,56 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Agentic Python Engineer</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Evaboot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>engineer, python, anywhere (place)</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982687?se=BGNyWVik8RGF59teMJsS7Q&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=64C652991D92D5E3DCA4519D688756F962092321</t>
+          <t>https://weworkremotely.com/remote-jobs/evaboot-agentic-python-engineer</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>dd6de0380a</t>
+          <t>d94554bfc7</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Data Scientist, Knowledge Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982533?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=853C1E923E89428D368371363C6206932A9E653B</t>
+          <t>https://www.adzuna.in/land/ad/5857982687?se=BGNyWVik8RGF59teMJsS7Q&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=64C652991D92D5E3DCA4519D688756F962092321</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>e4df1efe77</t>
+          <t>dd6de0380a</t>
         </is>
       </c>
     </row>
@@ -7271,17 +7271,17 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Data Scientist II, Data Analytics, Hyderabad</t>
+          <t>Data Scientist, Knowledge Management</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>data scientist, hyderabad (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7301,17 +7301,17 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5860916020?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2CB3A6FFC4393B68C48E0DBE7C464491C08965D1</t>
+          <t>https://www.adzuna.in/land/ad/5857982533?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=853C1E923E89428D368371363C6206932A9E653B</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>ed5cec24b5</t>
+          <t>e4df1efe77</t>
         </is>
       </c>
     </row>
@@ -7327,52 +7327,52 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform - Hyderabad, India</t>
+          <t>Data Scientist II, Data Analytics, Hyderabad</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Speechify</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>software engineer, backend (tag), cloud (tag), api (tag), india (place)</t>
+          <t>data scientist, hyderabad (place)</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Platform-Engineering, Backend-Engineering, Software-Engineer, API-Development, Cloud-Infrastructure, Software-Platform-Engineer, Platform-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/speechify/jobs/software-engineer-platform-hyderabad-india</t>
+          <t>https://www.adzuna.in/land/ad/5860916020?se=9NmH0sGk8RGxSf1iGXKoQA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2CB3A6FFC4393B68C48E0DBE7C464491C08965D1</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>d972ee3bee</t>
+          <t>ed5cec24b5</t>
         </is>
       </c>
     </row>
@@ -7388,22 +7388,22 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>GitHub Contributor</t>
+          <t>Software Engineer, Platform - Hyderabad, India</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Speechify</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, backend (tag), cloud (tag), api (tag), india (place)</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
+          <t>Platform-Engineering, Backend-Engineering, Software-Engineer, API-Development, Cloud-Infrastructure, Software-Platform-Engineer, Platform-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-2145210908</t>
+          <t>https://himalayas.app/companies/speechify/jobs/software-engineer-platform-hyderabad-india</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>9bd86980fc</t>
+          <t>d972ee3bee</t>
         </is>
       </c>
     </row>
@@ -7445,58 +7445,56 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>38</v>
-      </c>
-      <c r="D115" t="n">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Backend Software Engineer, PDP Experience</t>
+          <t>GitHub Contributor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>software engineer, backend, anywhere (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Back-End Programming, Full-Time</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Community-Contributor, Open-Source-Software-Developer, Open-Source-Engineer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/reddit-backend-software-engineer-pdp-experience</t>
+          <t>https://himalayas.app/companies/micro1/jobs/github-contributor-2145210908</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>a954ce85ab</t>
+          <t>9bd86980fc</t>
         </is>
       </c>
     </row>
@@ -7512,37 +7510,39 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>24</v>
-      </c>
-      <c r="D116" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Open Source Contributor</t>
+          <t>Backend Software Engineer, PDP Experience</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
+          <t>software engineer, backend, anywhere (place)</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Open-Source-Contributor, Open-Source-Developer, Open-Source-Software-Developer, Open-Source-Advocate, Open-Source-Engineer, Open-Source-Software-Engineer, Open-Source-Software-Maintainer, Community-Contributor, Entry-level</t>
+          <t>Back-End Programming, Full-Time</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/open-source-contributor-4150550716</t>
+          <t>https://weworkremotely.com/remote-jobs/reddit-backend-software-engineer-pdp-experience</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>d8033bd793</t>
+          <t>a954ce85ab</t>
         </is>
       </c>
     </row>
@@ -7569,16 +7569,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Open Source Contributor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7598,27 +7598,27 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>engineer, python (tag), ai, ml (tag), worldwide (place)</t>
+          <t>developer (tag), software (tag), engineer (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Mid-level</t>
+          <t>Open-Source-Contributor, Open-Source-Developer, Open-Source-Software-Developer, Open-Source-Advocate, Open-Source-Engineer, Open-Source-Software-Engineer, Open-Source-Software-Maintainer, Community-Contributor, Entry-level</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-engineer-7982880650</t>
+          <t>https://himalayas.app/companies/micro1/jobs/open-source-contributor-4150550716</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>17936ac69e</t>
+          <t>d8033bd793</t>
         </is>
       </c>
     </row>
@@ -7634,37 +7634,37 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>machine learning, engineer, hyderabad (place)</t>
+          <t>engineer, python (tag), ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, AI-Engineering-Specialist, AI-Engineering, Artificial-Intelligence-Engineering, Python-AI-Engineer, AI-Engineering-Jobs, Mid-level</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5859662671?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=77410E24CED3D457054E58156829472F42D5B958</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-engineer-7982880650</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>a8bcca74c0</t>
+          <t>17936ac69e</t>
         </is>
       </c>
     </row>
@@ -7700,17 +7700,17 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (T25)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>machine learning, engineer, hyderabad (place)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7730,17 +7730,17 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858538850?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AA8B404BB5F08B6BBBC1A1DAEA80EDAE2331BB01</t>
+          <t>https://www.adzuna.in/land/ad/5859662671?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=77410E24CED3D457054E58156829472F42D5B958</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>e99054d24c</t>
+          <t>a8bcca74c0</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SWE-3 Machine Learning Engineer</t>
+          <t>Machine Learning Engineer (T25)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858537539?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=49BEDAECA8CA01D8F7BFB9CA5D092D8DD046FCF4</t>
+          <t>https://www.adzuna.in/land/ad/5858538850?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AA8B404BB5F08B6BBBC1A1DAEA80EDAE2331BB01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>83e0ebd10e</t>
+          <t>e99054d24c</t>
         </is>
       </c>
     </row>
@@ -7817,22 +7817,22 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>SWE-3 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>engineer, ai, hyderabad (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857982475?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=61932F7A965BC6190F96EF3EDD6B34FCA7CA0EFF</t>
+          <t>https://www.adzuna.in/land/ad/5858537539?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=49BEDAECA8CA01D8F7BFB9CA5D092D8DD046FCF4</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>ec1b34ae37</t>
+          <t>83e0ebd10e</t>
         </is>
       </c>
     </row>
@@ -7878,52 +7878,52 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AI Data Annotator - Remote</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Argos Multilingual Inc.</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>All Other Remote, Contract</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/argos-multilingual-inc-ai-data-annotator-remote</t>
+          <t>https://www.adzuna.in/land/ad/5857982475?se=nBIHegyj8RGmT-3sKckM2g&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=61932F7A965BC6190F96EF3EDD6B34FCA7CA0EFF</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>5c22526a85</t>
+          <t>ec1b34ae37</t>
         </is>
       </c>
     </row>
@@ -7935,56 +7935,56 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Data Scientist - AI &amp; Automation</t>
+          <t>AI Data Annotator - Remote</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Argos Multilingual Inc.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>data scientist, automation, ai, bangalore (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>All Other Remote, Contract</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251125?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C7BA7BE347A1ADA1FC538497AF302C4F3AD6BEDD</t>
+          <t>https://weworkremotely.com/remote-jobs/argos-multilingual-inc-ai-data-annotator-remote</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2e19a4f3f6</t>
+          <t>5c22526a85</t>
         </is>
       </c>
     </row>
@@ -8000,12 +8000,12 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>MTS-1 Machine Learning Engineer</t>
+          <t>Data Scientist - AI &amp; Automation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>machine learning, engineer, bangalore (place)</t>
+          <t>data scientist, automation, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5858537523?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4219F9238C4FE19DFCEAD65DAA98E56A5B89F388</t>
+          <t>https://www.adzuna.in/land/ad/5857251125?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C7BA7BE347A1ADA1FC538497AF302C4F3AD6BEDD</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>c65fcd065c</t>
+          <t>2e19a4f3f6</t>
         </is>
       </c>
     </row>
@@ -8061,22 +8061,22 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>MTS-1 Machine Learning Engineer</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>data scientist, mumbai (place)</t>
+          <t>machine learning, engineer, bangalore (place)</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8096,17 +8096,17 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5849296977?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FFA2BB725355D26B4B624FA5365F48C2D8B894C</t>
+          <t>https://www.adzuna.in/land/ad/5858537523?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4219F9238C4FE19DFCEAD65DAA98E56A5B89F388</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>200651f002</t>
+          <t>c65fcd065c</t>
         </is>
       </c>
     </row>
@@ -8132,12 +8132,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>data scientist, mumbai (place)</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8157,17 +8157,17 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251146?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=43EC4FC89638B5AB4C3D5267B80E2B1135A6C706</t>
+          <t>https://www.adzuna.in/land/ad/5849296977?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0FFA2BB725355D26B4B624FA5365F48C2D8B894C</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>6a6f7a8419</t>
+          <t>200651f002</t>
         </is>
       </c>
     </row>
@@ -8223,12 +8223,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251173?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7E2FD9B14C3A74461E2352F6CFE714131C13E4BC</t>
+          <t>https://www.adzuna.in/land/ad/5857251146?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=43EC4FC89638B5AB4C3D5267B80E2B1135A6C706</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>aa6eef76e8</t>
+          <t>6a6f7a8419</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Data Scientist, Knowledge Management</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857251185?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=74B3EB71D85FA01AB90B707F8DB6AB9F2A17FAFA</t>
+          <t>https://www.adzuna.in/land/ad/5857251173?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=7E2FD9B14C3A74461E2352F6CFE714131C13E4BC</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>d1497475d4</t>
+          <t>aa6eef76e8</t>
         </is>
       </c>
     </row>
@@ -8310,12 +8310,12 @@
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Data Scientist with R programming</t>
+          <t>Data Scientist, Knowledge Management</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Capco</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8340,17 +8340,17 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139433?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=221D7BCDBBE6E4012ED68B71EDB34DB2E07507EC</t>
+          <t>https://www.adzuna.in/land/ad/5857251185?se=Epj_tuuh8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=74B3EB71D85FA01AB90B707F8DB6AB9F2A17FAFA</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>dbec4a04a4</t>
+          <t>d1497475d4</t>
         </is>
       </c>
     </row>
@@ -8366,52 +8366,52 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Data Scientist with R programming</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capco</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Product, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer-1</t>
+          <t>https://www.adzuna.in/land/ad/5837139433?se=OqwplEii8RGhLffPfv7Txw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=221D7BCDBBE6E4012ED68B71EDB34DB2E07507EC</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>e7de7648c1</t>
+          <t>dbec4a04a4</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer</t>
+          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer-1</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>dada5ade61</t>
+          <t>e7de7648c1</t>
         </is>
       </c>
     </row>
@@ -8488,52 +8488,52 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Education Designer UX UI and AI</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Interaction Design Foundation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>design, content writing, education</t>
+          <t>Product, Full-Time</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-education-designer-ux-ui-and-ai-interaction-design-foundation-1137138</t>
+          <t>https://weworkremotely.com/remote-jobs/databricks-ai-engineer-fde-forward-deployed-engineer</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>ca62234445</t>
+          <t>dada5ade61</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Course Writer and Editor UX UI and AI</t>
+          <t>Education Designer UX UI and AI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>design, content writing</t>
+          <t>design, content writing, education</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-course-writer-and-editor-ux-ui-and-ai-interaction-design-foundation-1137136</t>
+          <t>https://remoteOK.com/remote-jobs/remote-education-designer-ux-ui-and-ai-interaction-design-foundation-1137138</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>01210e4343</t>
+          <t>ca62234445</t>
         </is>
       </c>
     </row>
@@ -8606,56 +8606,56 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>App Developer - AI/ML</t>
+          <t>Course Writer and Editor UX UI and AI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Interaction Design Foundation</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>developer, ai, ml, hyderabad (place)</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>design, content writing</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139469?se=-BSx1eug8RG-Sdz4qyZPjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=16DC1893C3026AA51441662E0B1A61360470917B</t>
+          <t>https://remoteOK.com/remote-jobs/remote-course-writer-and-editor-ux-ui-and-ai-interaction-design-foundation-1137136</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>7a22fe6bd5</t>
+          <t>01210e4343</t>
         </is>
       </c>
     </row>
@@ -8671,17 +8671,17 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>App Developer - AI/ML</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>developer, ai, ml, hyderabad (place)</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5857168441?se=TqYc8W2h8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CEB40CB7335D41898800C58388A2B035DF674757</t>
+          <t>https://www.adzuna.in/land/ad/5837139469?se=-BSx1eug8RG-Sdz4qyZPjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=16DC1893C3026AA51441662E0B1A61360470917B</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>84fdce5107</t>
+          <t>7a22fe6bd5</t>
         </is>
       </c>
     </row>
@@ -8732,37 +8732,37 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AI Speech &amp; Audio Specialist – ASR | TTS | Voice AI | Audio Data</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/ai-speech-audio-specialist-asr-tts-voice-ai-audio-data</t>
+          <t>https://www.adzuna.in/land/ad/5857168441?se=TqYc8W2h8RGhZ7gcUJZivg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=CEB40CB7335D41898800C58388A2B035DF674757</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>bb930fc93f</t>
+          <t>84fdce5107</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Financial Accuracy &amp; Tax Logic Expert (AI Community)</t>
+          <t>AI Speech &amp; Audio Specialist – ASR | TTS | Voice AI | Audio Data</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/financial-accuracy-tax-logic-expert-ai-community-7007868696</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/ai-speech-audio-specialist-asr-tts-voice-ai-audio-data</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>162d6a9ed2</t>
+          <t>bb930fc93f</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Identity Trust &amp; Fraud Intelligence Specialist - Intermediate (AI Community)</t>
+          <t>Financial Accuracy &amp; Tax Logic Expert (AI Community)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/identity-trust-fraud-intelligence-specialist-intermediate-ai-community</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/financial-accuracy-tax-logic-expert-ai-community-7007868696</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>637c85a300</t>
+          <t>162d6a9ed2</t>
         </is>
       </c>
     </row>
@@ -8920,32 +8920,32 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Education Designer: UX, UI, and AI</t>
+          <t>Identity Trust &amp; Fraud Intelligence Specialist - Intermediate (AI Community)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>IxDF - Interaction Design Foundation</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Design, Full-Time</t>
+          <t>Entry-level</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-education-designer-ux-ui-and-ai</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/identity-trust-fraud-intelligence-specialist-intermediate-ai-community</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>9fbe655de3</t>
+          <t>637c85a300</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Course Writer and Editor: UX, UI, and AI</t>
+          <t>Education Designer: UX, UI, and AI</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-course-writer-and-editor-ux-ui-and-ai</t>
+          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-education-designer-ux-ui-and-ai</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>e8e07f5951</t>
+          <t>9fbe655de3</t>
         </is>
       </c>
     </row>
@@ -9042,32 +9042,32 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AI Consulting Domain Expert</t>
+          <t>Course Writer and Editor: UX, UI, and AI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IxDF - Interaction Design Foundation</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>ai, worldwide (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>AI-Domain-Expert, AI-Consultant, AI-Subject-Matter-Expert, Artificial-Intelligence-Consulting, Senior</t>
+          <t>Design, Full-Time</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9077,12 +9077,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/micro1/jobs/ai-consulting-domain-expert-7128968890</t>
+          <t>https://weworkremotely.com/remote-jobs/ixdf-interaction-design-foundation-course-writer-and-editor-ux-ui-and-ai</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>7f1041d829</t>
+          <t>e8e07f5951</t>
         </is>
       </c>
     </row>
@@ -9098,39 +9098,37 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>40</v>
-      </c>
-      <c r="D142" t="n">
-        <v>2</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Software Development Engineer II Full Stack - Business (Remote @ Colombia)</t>
+          <t>AI Consulting Domain Expert</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>full stack, software, engineer, anywhere (place)</t>
+          <t>ai, worldwide (place)</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Full-Stack Programming, Full-Time</t>
+          <t>AI-Domain-Expert, AI-Consultant, AI-Subject-Matter-Expert, Artificial-Intelligence-Consulting, Senior</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9140,12 +9138,12 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/offerup-software-development-engineer-ii-full-stack-business-remote-colombia</t>
+          <t>https://himalayas.app/companies/micro1/jobs/ai-consulting-domain-expert-7128968890</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>6fe968b6b9</t>
+          <t>7f1041d829</t>
         </is>
       </c>
     </row>
@@ -9161,37 +9159,39 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>20</v>
-      </c>
-      <c r="D143" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>QA Speech-to-Text Audio Collection Project</t>
+          <t>Software Development Engineer II Full Stack - Business (Remote @ Colombia)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>qa, worldwide (place)</t>
+          <t>full stack, software, engineer, anywhere (place)</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Entry-level</t>
+          <t>Full-Stack Programming, Full-Time</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/telus-digital/jobs/qa-speech-to-text-audio-collection-project</t>
+          <t>https://weworkremotely.com/remote-jobs/offerup-software-development-engineer-ii-full-stack-business-remote-colombia</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>a44e738ec6</t>
+          <t>6fe968b6b9</t>
         </is>
       </c>
     </row>
@@ -9218,21 +9218,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AI/RAG engineer</t>
+          <t>QA Speech-to-Text Audio Collection Project</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CoinMarketCap</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -9247,27 +9247,27 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>engineer, ai, ml (tag), worldwide (place)</t>
+          <t>qa, worldwide (place)</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>RAG-AI-Engineer, Machine-Learning-Engineering, AI-Engineering, RAG-Development, Vector-Search-Engineer, IA-RAG-Engineer, AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, Mid-level</t>
+          <t>Entry-level</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/coinmarketcap/jobs/ai-rag-engineer</t>
+          <t>https://himalayas.app/companies/telus-digital/jobs/qa-speech-to-text-audio-collection-project</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>d199d5cdfc</t>
+          <t>a44e738ec6</t>
         </is>
       </c>
     </row>
@@ -9283,52 +9283,52 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI/RAG engineer</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>CoinMarketCap</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>engineer, ai, mumbai (place)</t>
+          <t>engineer, ai, ml (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>RAG-AI-Engineer, Machine-Learning-Engineering, AI-Engineering, RAG-Development, Vector-Search-Engineer, IA-RAG-Engineer, AI-Engineer, Artificial-Intelligence-Engineer, AI-ML-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723676?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F83D2913763A01EA6FBE321571CA8B989BE3F382</t>
+          <t>https://himalayas.app/companies/coinmarketcap/jobs/ai-rag-engineer</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>faa646b456</t>
+          <t>d199d5cdfc</t>
         </is>
       </c>
     </row>
@@ -9349,12 +9349,12 @@
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Data Science-Index Quant Specialist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -9369,27 +9369,27 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>data science, mumbai (place)</t>
+          <t>engineer, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Accounting &amp; Finance Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5843137505?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC4079028ED7338B991CD57034DE9EA5AC8D9A0B</t>
+          <t>https://www.adzuna.in/land/ad/5846723676?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F83D2913763A01EA6FBE321571CA8B989BE3F382</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>6ec3848d0b</t>
+          <t>faa646b456</t>
         </is>
       </c>
     </row>
@@ -9410,17 +9410,17 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Science-Index Quant Specialist</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Gurgaon, Haryana</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9430,27 +9430,27 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>data scientist, gurgaon (place)</t>
+          <t>data science, mumbai (place)</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Accounting &amp; Finance Jobs</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5849297019?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E87B9A5E2A9605281144BBEA53533DB7165D1FA0</t>
+          <t>https://www.adzuna.in/land/ad/5843137505?se=zow8fZOg8RGratEa7ObxPA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=EC4079028ED7338B991CD57034DE9EA5AC8D9A0B</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>e2cd9eda9e</t>
+          <t>6ec3848d0b</t>
         </is>
       </c>
     </row>
@@ -9476,12 +9476,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>Gurgaon, Haryana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>data scientist, delhi (place)</t>
+          <t>data scientist, gurgaon (place)</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5848650875?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4DF45BC4D3A230C0689E561399F3F0BA2C0FC825</t>
+          <t>https://www.adzuna.in/land/ad/5849297019?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=E87B9A5E2A9605281144BBEA53533DB7165D1FA0</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>83a3456095</t>
+          <t>e2cd9eda9e</t>
         </is>
       </c>
     </row>
@@ -9527,52 +9527,52 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>GTM AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Customer.io</t>
+          <t>Danaher</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>New Delhi, Delhi</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>engineer, ai, anywhere (place)</t>
+          <t>data scientist, delhi (place)</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/customer-io-gtm-ai-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5848650875?se=9hBOPKOg8RG7j7TsS0oVjg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=4DF45BC4D3A230C0689E561399F3F0BA2C0FC825</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>19a2ae7abb</t>
+          <t>83a3456095</t>
         </is>
       </c>
     </row>
@@ -9588,17 +9588,17 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Performance Creative Strategist and AI Producer</t>
+          <t>GTM AI Engineer</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Icarus Digital Marketing</t>
+          <t>Customer.io</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>engineer, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/icarus-digital-marketing-performance-creative-strategist-and-ai-producer</t>
+          <t>https://weworkremotely.com/remote-jobs/customer-io-gtm-ai-engineer</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>60c87a59fd</t>
+          <t>19a2ae7abb</t>
         </is>
       </c>
     </row>
@@ -9649,37 +9649,37 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>GTM Coordinator, Cloud Native (Talent Pool)</t>
+          <t>Performance Creative Strategist and AI Producer</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Percona</t>
+          <t>Icarus Digital Marketing</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bulgaria, Croatia, Czechia, Greece, Hungary, India, Poland, Portugal, Spain</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>cloud, india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>GTM-Coordinator, Talent-Community-Coordinator, Talent-Operations-Coordinator, Entry-level</t>
+          <t>Sales and Marketing, Full-Time</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/percona/jobs/gtm-coordinator-cloud-native-talent-pool</t>
+          <t>https://weworkremotely.com/remote-jobs/icarus-digital-marketing-performance-creative-strategist-and-ai-producer</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>a97ee1ce9b</t>
+          <t>60c87a59fd</t>
         </is>
       </c>
     </row>
@@ -9710,52 +9710,52 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Offensive Cybersecurity Engineer - Red Team</t>
+          <t>GTM Coordinator, Cloud Native (Talent Pool)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Techno Vista Dynamics</t>
+          <t>Percona</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>APAC,Middle East</t>
+          <t>Bulgaria, Croatia, Czechia, Greece, Hungary, India, Poland, Portugal, Spain</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>workingnomads</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>engineer, testing (tag), apac (place)</t>
+          <t>cloud, india (place)</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Development, engineer,security,penetration testing</t>
+          <t>GTM-Coordinator, Talent-Community-Coordinator, Talent-Operations-Coordinator, Entry-level</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>https://www.workingnomads.com/job/go/1781770/</t>
+          <t>https://himalayas.app/companies/percona/jobs/gtm-coordinator-cloud-native-talent-pool</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>0bde4f9b82</t>
+          <t>a97ee1ce9b</t>
         </is>
       </c>
     </row>
@@ -9767,56 +9767,56 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Human-Centered AI Data Scientist, Strategy and Talent</t>
+          <t>Offensive Cybersecurity Engineer - Red Team</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank</t>
+          <t>Techno Vista Dynamics</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>APAC,Middle East</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>workingnomads</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>data scientist, ai, bangalore (place)</t>
+          <t>engineer, testing (tag), apac (place)</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Development, engineer,security,penetration testing</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139276?se=1M6Kj_qf8RGoxpN31Vp7kA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C0F814CBDD0355075DDB000131DE4C8D130504ED</t>
+          <t>https://www.workingnomads.com/job/go/1781770/</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>3130787ee8</t>
+          <t>0bde4f9b82</t>
         </is>
       </c>
     </row>
@@ -9832,52 +9832,52 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Java Software Develper Engineer</t>
+          <t>Human-Centered AI Data Scientist, Strategy and Talent</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>Standard Chartered Bank</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>programmer (tag), developer (tag), software, engineer, backend (tag), java, india (place)</t>
+          <t>data scientist, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Java-Development, Software-Engineer, Entry-Level-Software-Development, Backend-Development, Technical-Support, Java-Software-Engineer, Java-Developer, Java-Developer-Jobs, Java-Application-Developer, Java-Programmer, Developer, Entry-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/csg/jobs/java-software-develper-engineer</t>
+          <t>https://www.adzuna.in/land/ad/5837139276?se=1M6Kj_qf8RGoxpN31Vp7kA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=C0F814CBDD0355075DDB000131DE4C8D130504ED</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>7626a2cdd6</t>
+          <t>3130787ee8</t>
         </is>
       </c>
     </row>
@@ -9893,22 +9893,22 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Android Software Engineer</t>
+          <t>Java Software Develper Engineer</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9918,27 +9918,27 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>software engineer, android, kotlin (tag), worldwide (place)</t>
+          <t>programmer (tag), developer (tag), software, engineer, backend (tag), java, india (place)</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Android-Software-Engineer, Mobile-Development, Android-Development, Software-Engineer, Kotlin, Android-Engineer, Android-Software-Engineering, Mobile-Android-Engineer, Android-Systems-Engineer, Android-Engineering, Mobile-Software-Engineer, Senior</t>
+          <t>Java-Development, Software-Engineer, Entry-Level-Software-Development, Backend-Development, Technical-Support, Java-Software-Engineer, Java-Developer, Java-Developer-Jobs, Java-Application-Developer, Java-Programmer, Developer, Entry-level</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/hudson-manpower/jobs/android-software-engineer</t>
+          <t>https://himalayas.app/companies/csg/jobs/java-software-develper-engineer</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>afb7954487</t>
+          <t>7626a2cdd6</t>
         </is>
       </c>
     </row>
@@ -9954,37 +9954,37 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Application Security Engineer II</t>
+          <t>Android Software Engineer</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Abnormal</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>engineer, devops (tag), anywhere (place)</t>
+          <t>software engineer, android, kotlin (tag), worldwide (place)</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>Android-Software-Engineer, Mobile-Development, Android-Development, Software-Engineer, Kotlin, Android-Engineer, Android-Software-Engineering, Mobile-Android-Engineer, Android-Systems-Engineer, Android-Engineering, Mobile-Software-Engineer, Senior</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/abnormal-application-security-engineer-ii</t>
+          <t>https://himalayas.app/companies/hudson-manpower/jobs/android-software-engineer</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>dc9a51cdbc</t>
+          <t>afb7954487</t>
         </is>
       </c>
     </row>
@@ -10011,56 +10011,56 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>DESARROLLADOR FULL STACK</t>
+          <t>Application Security Engineer II</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kruger NearShore LLC - Rekluti</t>
+          <t>Abnormal</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Not listed</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>remoteok</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>full stack, front end (tag), backend (tag), angular (tag), testing (tag), python (tag), golang (tag), devops (tag), cloud (tag), git (tag)</t>
+          <t>engineer, devops (tag), anywhere (place)</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>full stack, front end, python, dev, testing, web dev, quality assurance, devops, c, cloud, nosql, git, flutter, angular, mobile, golang, backend, digital nomad</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-desarrollador-full-stack-kruger-nearshore-llc-rekluti-1137062</t>
+          <t>https://weworkremotely.com/remote-jobs/abnormal-application-security-engineer-ii</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>911da99485</t>
+          <t>dc9a51cdbc</t>
         </is>
       </c>
     </row>
@@ -10076,52 +10076,52 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AI Transformation Owner, Product &amp; Design</t>
+          <t>DESARROLLADOR FULL STACK</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Kruger NearShore LLC - Rekluti</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Not listed</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>remoteok</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>ai, anywhere (place)</t>
+          <t>full stack, front end (tag), backend (tag), angular (tag), testing (tag), python (tag), golang (tag), devops (tag), cloud (tag), git (tag)</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Product, Full-Time</t>
+          <t>full stack, front end, python, dev, testing, web dev, quality assurance, devops, c, cloud, nosql, git, flutter, angular, mobile, golang, backend, digital nomad</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/gitlab-ai-transformation-owner-product-design</t>
+          <t>https://remoteOK.com/remote-jobs/remote-desarrollador-full-stack-kruger-nearshore-llc-rekluti-1137062</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>a0e38d6b98</t>
+          <t>911da99485</t>
         </is>
       </c>
     </row>
@@ -10137,52 +10137,52 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>AI Transformation Owner, Product &amp; Design</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Forrester Research, Inc. (US)</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>developer, software (tag), cloud (tag), india (place)</t>
+          <t>ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Salesforce-Developer, CRM-Developer, Salesforce-Administrator, Integration-Developer, Software-Developer, Salesforce-CRM-Developer, Salesforce-Application-Developer, Salesforce-Sales-Cloud-Developer, Salesforce-Development, Salesforce-Solutions-Developer, Salesforce-Platform-Developer, Salesforce-Apex-Developer, Force.Com-Developer, Mid-level</t>
+          <t>Product, Full-Time</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/forrester-research-inc-us/jobs/salesforce-developer-8148624472</t>
+          <t>https://weworkremotely.com/remote-jobs/gitlab-ai-transformation-owner-product-design</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>bbbc562c11</t>
+          <t>a0e38d6b98</t>
         </is>
       </c>
     </row>
@@ -10198,17 +10198,17 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>IT Systems Administrator</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ralliant</t>
+          <t>Forrester Research, Inc. (US)</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -10223,27 +10223,27 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>developer (tag), engineer (tag), india (place)</t>
+          <t>developer, software (tag), cloud (tag), india (place)</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Power-Platform-Engineer, Business-intelligence-Engineer, Analytics-Engineer, Microsoft-Fabric-Engineer, Power-BI-Developer, IT-Systems-Administrator, IT-System-Administrator, Systems-Administrator, IT-Systems-Administration, IT-Administrator, Systems-Support-Administrator, Mid-level</t>
+          <t>Salesforce-Developer, CRM-Developer, Salesforce-Administrator, Integration-Developer, Software-Developer, Salesforce-CRM-Developer, Salesforce-Application-Developer, Salesforce-Sales-Cloud-Developer, Salesforce-Development, Salesforce-Solutions-Developer, Salesforce-Platform-Developer, Salesforce-Apex-Developer, Force.Com-Developer, Mid-level</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/ralliant/jobs/it-systems-administrator</t>
+          <t>https://himalayas.app/companies/forrester-research-inc-us/jobs/salesforce-developer-8148624472</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>a720a38bd1</t>
+          <t>bbbc562c11</t>
         </is>
       </c>
     </row>
@@ -10255,56 +10255,56 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Talent Pool -FP&amp;A- Data Scientist / Analytics Specialist / Data &amp; AI Specialist</t>
+          <t>IT Systems Administrator</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Ralliant</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>data scientist, ai, bangalore (place)</t>
+          <t>developer (tag), engineer (tag), india (place)</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Energy, Oil &amp; Gas Jobs</t>
+          <t>Power-Platform-Engineer, Business-intelligence-Engineer, Analytics-Engineer, Microsoft-Fabric-Engineer, Power-BI-Developer, IT-Systems-Administrator, IT-System-Administrator, Systems-Administrator, IT-Systems-Administration, IT-Administrator, Systems-Support-Administrator, Mid-level</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773115?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=888721B9EAAF876B1F079BC209DECF1099E63440</t>
+          <t>https://himalayas.app/companies/ralliant/jobs/it-systems-administrator</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>5ee47ace79</t>
+          <t>a720a38bd1</t>
         </is>
       </c>
     </row>
@@ -10320,17 +10320,17 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AI and Automation Developer</t>
+          <t>Talent Pool -FP&amp;A- Data Scientist / Analytics Specialist / Data &amp; AI Specialist</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -10345,27 +10345,27 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>automation, developer, ai, bangalore (place)</t>
+          <t>data scientist, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Energy, Oil &amp; Gas Jobs</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5847959817?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44960F01CCAE33F814C0EF4448956DF38E8344F5</t>
+          <t>https://www.adzuna.in/land/ad/5785773115?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=888721B9EAAF876B1F079BC209DECF1099E63440</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>98337240aa</t>
+          <t>5ee47ace79</t>
         </is>
       </c>
     </row>
@@ -10381,52 +10381,52 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>DevOps &amp; Security Engineer - AI-Native Healthcare SaaS</t>
+          <t>AI and Automation Developer</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Zenara Health</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>engineer, devops, ai, anywhere (place)</t>
+          <t>automation, developer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/zenara-health-devops-security-engineer-ai-native-healthcare-saas</t>
+          <t>https://www.adzuna.in/land/ad/5847959817?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=44960F01CCAE33F814C0EF4448956DF38E8344F5</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>d592e60ddc</t>
+          <t>98337240aa</t>
         </is>
       </c>
     </row>
@@ -10442,37 +10442,37 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps &amp; Security Engineer - AI-Native Healthcare SaaS</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Zenara Health</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>data scientist, mumbai (place)</t>
+          <t>engineer, devops, ai, anywhere (place)</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723381?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F9660467E3895814968DA45F3A82EF6912496F70</t>
+          <t>https://weworkremotely.com/remote-jobs/zenara-health-devops-security-engineer-ai-native-healthcare-saas</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>c46d670134</t>
+          <t>d592e60ddc</t>
         </is>
       </c>
     </row>
@@ -10513,12 +10513,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>data scientist, mumbai (place)</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10538,17 +10538,17 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837138848?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=86962F79F06A105F30676367582529277DE10978</t>
+          <t>https://www.adzuna.in/land/ad/5846723381?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F9660467E3895814968DA45F3A82EF6912496F70</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>39dacd7158</t>
+          <t>c46d670134</t>
         </is>
       </c>
     </row>
@@ -10569,12 +10569,12 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Itvedant Education Pvt. Ltd.</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10599,17 +10599,17 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5833434843?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=95E30E442ED8EDC695067D6ACDD8806A1A4DBE0E</t>
+          <t>https://www.adzuna.in/land/ad/5837138848?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=86962F79F06A105F30676367582529277DE10978</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>660701d5cb</t>
+          <t>39dacd7158</t>
         </is>
       </c>
     </row>
@@ -10630,17 +10630,17 @@
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Itvedant Education Pvt. Ltd.</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>engineer, ai, hyderabad (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10660,17 +10660,17 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5837139103?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=23D035D0F5CFDFF88D2FBA2CB9721442B70F9874</t>
+          <t>https://www.adzuna.in/land/ad/5833434843?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=95E30E442ED8EDC695067D6ACDD8806A1A4DBE0E</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>c2ca14412d</t>
+          <t>660701d5cb</t>
         </is>
       </c>
     </row>
@@ -10691,17 +10691,17 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>data scientist, india (place)</t>
+          <t>engineer, ai, hyderabad (place)</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10721,17 +10721,17 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773097?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1AD120B3FB3DFBC7F01669BC535E68EC0F2123A3</t>
+          <t>https://www.adzuna.in/land/ad/5837139103?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=23D035D0F5CFDFF88D2FBA2CB9721442B70F9874</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>1a0dea6270</t>
+          <t>c2ca14412d</t>
         </is>
       </c>
     </row>
@@ -10752,17 +10752,17 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>engineer, ai, bangalore (place)</t>
+          <t>data scientist, india (place)</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10782,17 +10782,17 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5846723241?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0084818D71681FAC4F572D55AE1C6BC637792931</t>
+          <t>https://www.adzuna.in/land/ad/5785773097?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=1AD120B3FB3DFBC7F01669BC535E68EC0F2123A3</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>a2c0a3fc16</t>
+          <t>1a0dea6270</t>
         </is>
       </c>
     </row>
@@ -10813,17 +10813,17 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Part time Data Science Instructor</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10833,27 +10833,27 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>data science, india (place)</t>
+          <t>engineer, ai, bangalore (place)</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Part time Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5850983469?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0F708DAB080760E3C6FB3FC40EA3A64A7B0306D9</t>
+          <t>https://www.adzuna.in/land/ad/5846723241?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0084818D71681FAC4F572D55AE1C6BC637792931</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>fa169c0060</t>
+          <t>a2c0a3fc16</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10874,12 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer for AI &amp;DS, BSI</t>
+          <t>Part time Data Science Instructor</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -10894,27 +10894,27 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>engineer, ai, india (place)</t>
+          <t>data science, india (place)</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>Part time Jobs</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785771743?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F6DC64E0C8FB2D27FC25CBE24085394F367A2687</t>
+          <t>https://www.adzuna.in/land/ad/5850983469?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=0F708DAB080760E3C6FB3FC40EA3A64A7B0306D9</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>3fd60b2320</t>
+          <t>fa169c0060</t>
         </is>
       </c>
     </row>
@@ -10935,17 +10935,17 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Agentic AI Engineer for AI &amp;DS, BSI</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>engineer, ai, mumbai (place)</t>
+          <t>engineer, ai, india (place)</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785773171?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2185A7049B5506DF1182A45172761BBEF73613FA</t>
+          <t>https://www.adzuna.in/land/ad/5785771743?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F6DC64E0C8FB2D27FC25CBE24085394F367A2687</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>43f406da07</t>
+          <t>3fd60b2320</t>
         </is>
       </c>
     </row>
@@ -10996,17 +10996,17 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Data Scientist - People Analytics</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Mumbai, Maharashtra</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>data scientist, bangalore (place)</t>
+          <t>engineer, ai, mumbai (place)</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11026,17 +11026,17 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5821999876?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=08993CE6BE520CA2C34926E81E8CBB0072304E1F</t>
+          <t>https://www.adzuna.in/land/ad/5785773171?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2185A7049B5506DF1182A45172761BBEF73613FA</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>187dc9c03e</t>
+          <t>43f406da07</t>
         </is>
       </c>
     </row>
@@ -11057,17 +11057,17 @@
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Data Science Instructor</t>
+          <t>Data Scientist - People Analytics</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Itvedant Education Pvt. Ltd.</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11077,27 +11077,27 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>data science, hyderabad (place)</t>
+          <t>data scientist, bangalore (place)</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Teaching Jobs</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5852476426?se=NskdSSae8RGSb8VpDRDiVA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2B7C55A3F795EE4D2F2D732844EDA9B4CAC3F128</t>
+          <t>https://www.adzuna.in/land/ad/5821999876?se=uNVelwOe8RGfQpohglHoaw&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=08993CE6BE520CA2C34926E81E8CBB0072304E1F</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>5c41be551e</t>
+          <t>187dc9c03e</t>
         </is>
       </c>
     </row>
@@ -11113,37 +11113,37 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PHP Developer - Work From Home</t>
+          <t>Data Science Instructor</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CC Staffing International</t>
+          <t>Itvedant Education Pvt. Ltd.</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hyderabad, Telangana</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>developer, software (tag), engineer (tag), backend (tag), php, india (place)</t>
+          <t>data science, hyderabad (place)</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>PHP-Developer, Backend-Engineer, Web-Development, Software-Developer, Full-Stack-Developer, Remote-PHP-Developer, PHP-Software-Engineer, Backend-PHP-Developer, Remote-Web-Developer, Developer, Mid-level</t>
+          <t>Teaching Jobs</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/cc-staffing-international/jobs/php-developer-work-from-home</t>
+          <t>https://www.adzuna.in/land/ad/5852476426?se=NskdSSae8RGSb8VpDRDiVA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=2B7C55A3F795EE4D2F2D732844EDA9B4CAC3F128</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>14b619fb91</t>
+          <t>5c41be551e</t>
         </is>
       </c>
     </row>
@@ -11174,52 +11174,52 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Kannada</t>
+          <t>PHP Developer - Work From Home</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>RWS</t>
+          <t>CC Staffing International</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>ai, delhi (place)</t>
+          <t>developer, software (tag), engineer (tag), backend (tag), php, india (place)</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>PHP-Developer, Backend-Engineer, Web-Development, Software-Developer, Full-Stack-Developer, Remote-PHP-Developer, PHP-Software-Engineer, Backend-PHP-Developer, Remote-Web-Developer, Developer, Mid-level</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772642?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=96F9E6C80B83A39F4F2C05268274FD2EBE13B037</t>
+          <t>https://himalayas.app/companies/cc-staffing-international/jobs/php-developer-work-from-home</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>bb43fd7b08</t>
+          <t>14b619fb91</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Marathi</t>
+          <t>AI Data Specialist - Kannada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772098?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=B26B7FB6A299BC3A2BFD29BF94BF59C981A24A29</t>
+          <t>https://www.adzuna.in/land/ad/5785772642?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=96F9E6C80B83A39F4F2C05268274FD2EBE13B037</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>fe688433d1</t>
+          <t>bb43fd7b08</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Telugu</t>
+          <t>AI Data Specialist - Marathi</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785770664?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=D13E17364CDB48C8A2B963F62AC42C33A76C021B</t>
+          <t>https://www.adzuna.in/land/ad/5785772098?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=B26B7FB6A299BC3A2BFD29BF94BF59C981A24A29</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>91c279dfff</t>
+          <t>fe688433d1</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Hindi</t>
+          <t>AI Data Specialist - Telugu</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -11392,17 +11392,17 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5795883387?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=38289BC2F5CA723017CE2916CC4536DEA978B9A6</t>
+          <t>https://www.adzuna.in/land/ad/5785770664?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=D13E17364CDB48C8A2B963F62AC42C33A76C021B</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>170ea3eac1</t>
+          <t>91c279dfff</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AI Data Specialist - Tamil</t>
+          <t>AI Data Specialist - Hindi</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -11453,17 +11453,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5785772320?se=xp3UHeGd8RGIEJB03vDchg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AB56F1DD143407CEE31E12C4126DC533B06A2AD3</t>
+          <t>https://www.adzuna.in/land/ad/5795883387?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=38289BC2F5CA723017CE2916CC4536DEA978B9A6</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>616fb76ab0</t>
+          <t>170ea3eac1</t>
         </is>
       </c>
     </row>
@@ -11479,52 +11479,52 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Agent Operations Engineer - Fully Remote | Upto $500/task Task based</t>
+          <t>AI Data Specialist - Tamil</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>mercor</t>
+          <t>RWS</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>New Delhi, Delhi</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>himalayas</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>engineer, ai (tag), india (place)</t>
+          <t>ai, delhi (place)</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Agent-Engineering, LLMOperations, AI-Engineering, AI-Operations, Machine-Learning-Engineering, AgentOps-Engineer, Agent-Orchestration-Engineer, AI-Agents-Engineer, Operations-Engineer, Remote-AI-Engineer, Mid-level</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/mercor/jobs/agent-operations-engineer-fully-remote-upto-500-task-task-based</t>
+          <t>https://www.adzuna.in/land/ad/5785772320?se=xp3UHeGd8RGIEJB03vDchg&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=AB56F1DD143407CEE31E12C4126DC533B06A2AD3</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>be05dc52ff</t>
+          <t>616fb76ab0</t>
         </is>
       </c>
     </row>
@@ -11540,17 +11540,17 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS Authorized Instructor</t>
+          <t>Agent Operations Engineer - Fully Remote | Upto $500/task Task based</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ITC WORLDWIDE</t>
+          <t>mercor</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>cloud (tag), aws, india (place)</t>
+          <t>engineer, ai (tag), india (place)</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>AWS-Training, Cloud-Computing-Instructor, Technical-Trainer, AWS-Authorized-Instructor, Cloud-Education, AWS-Certification-Training, Cloud-Instructor, Cloud-Computing-Trainer, Senior</t>
+          <t>Agent-Engineering, LLMOperations, AI-Engineering, AI-Operations, Machine-Learning-Engineering, AgentOps-Engineer, Agent-Orchestration-Engineer, AI-Agents-Engineer, Operations-Engineer, Remote-AI-Engineer, Mid-level</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/itc-worldwide/jobs/aws-authorized-instructor</t>
+          <t>https://himalayas.app/companies/mercor/jobs/agent-operations-engineer-fully-remote-upto-500-task-task-based</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>a42ddc7b02</t>
+          <t>be05dc52ff</t>
         </is>
       </c>
     </row>
@@ -11601,37 +11601,37 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Associate Instructor</t>
+          <t>AWS Authorized Instructor</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>ITC WORLDWIDE</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>devops (tag), associate (level), anywhere (place)</t>
+          <t>cloud (tag), aws, india (place)</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>DevOps and Sysadmin, Full-Time</t>
+          <t>AWS-Training, Cloud-Computing-Instructor, Technical-Trainer, AWS-Authorized-Instructor, Cloud-Education, AWS-Certification-Training, Cloud-Instructor, Cloud-Computing-Trainer, Senior</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/beyondtrust-associate-instructor</t>
+          <t>https://himalayas.app/companies/itc-worldwide/jobs/aws-authorized-instructor</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>4c1963b96c</t>
+          <t>a42ddc7b02</t>
         </is>
       </c>
     </row>
@@ -11662,52 +11662,52 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>E-learning Developer</t>
+          <t>Associate Instructor</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Crowe UAE</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat</t>
+          <t>Anywhere in the World</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>adzuna</t>
+          <t>weworkremotely</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>developer, ahmedabad (place)</t>
+          <t>devops (tag), associate (level), anywhere (place)</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>IT Jobs</t>
+          <t>DevOps and Sysadmin, Full-Time</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5850983902?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F927DE790D9874EE6BA8C142D15CF3A7A97BFA7E</t>
+          <t>https://weworkremotely.com/remote-jobs/beyondtrust-associate-instructor</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>843701dc9e</t>
+          <t>4c1963b96c</t>
         </is>
       </c>
     </row>
@@ -11723,52 +11723,52 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Developer Educator</t>
+          <t>E-learning Developer</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>PlanetScale</t>
+          <t>Crowe UAE</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Anywhere in the World</t>
+          <t>Ahmedabad, Gujarat</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>weworkremotely</t>
+          <t>adzuna</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>developer, anywhere (place)</t>
+          <t>developer, ahmedabad (place)</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Sales and Marketing, Full-Time</t>
+          <t>IT Jobs</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/planetscale-developer-educator</t>
+          <t>https://www.adzuna.in/land/ad/5850983902?se=aqlCTd-d8RGU6LIjyaRnwA&amp;utm_medium=api&amp;utm_source=28154f3f&amp;v=F927DE790D9874EE6BA8C142D15CF3A7A97BFA7E</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>c72ab4031d</t>
+          <t>843701dc9e</t>
         </is>
       </c>
     </row>
@@ -11784,50 +11784,111 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
+          <t>Developer Educator</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>PlanetScale</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Anywhere in the World</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>weworkremotely</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>developer, anywhere (place)</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Sales and Marketing, Full-Time</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/planetscale-developer-educator</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>c72ab4031d</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>11</v>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
           <t>Consultant Implementation Engineer</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>Harbor</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
+      <c r="H187" t="inlineStr">
         <is>
           <t>remoteok</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
+      <c r="I187" t="inlineStr">
         <is>
           <t>engineer, golang (tag), remote (place)</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr">
+      <c r="J187" t="inlineStr">
         <is>
           <t>consulting, technical, accounting, legal, golang, engineer</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="K187" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t>https://remoteOK.com/remote-jobs/remote-consultant-implementation-engineer-harbor-1136987</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t>f724e65bc8</t>
         </is>
@@ -11835,7 +11896,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of: new, applied, skipped" prompt="Mark this job applied once you have applied." type="list">
+    <dataValidation sqref="A2:A187" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick one of: new, applied, skipped" prompt="Mark this job applied once you have applied." type="list">
       <formula1>"new,applied,skipped"</formula1>
     </dataValidation>
   </dataValidations>
